--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="2169" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4234DC4-0560-426D-8E83-6F5F9C0544EC}"/>
+  <xr:revisionPtr revIDLastSave="2175" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7302FB0B-EFE3-4B09-BD3B-805310FDE20E}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1636,10 +1636,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5639,7 +5635,7 @@
         <v>58</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F121" s="17" t="s">
         <v>312</v>
@@ -5943,7 +5939,7 @@
         <v>316</v>
       </c>
       <c r="E131" s="17" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F131" s="17" t="s">
         <v>313</v>
@@ -6779,7 +6775,7 @@
         <v>58</v>
       </c>
       <c r="E155" s="17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F155" s="17" t="s">
         <v>312</v>
@@ -7097,7 +7093,7 @@
         <v>58</v>
       </c>
       <c r="E165" s="17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F165" s="17" t="s">
         <v>314</v>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="2175" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7302FB0B-EFE3-4B09-BD3B-805310FDE20E}"/>
+  <xr:revisionPtr revIDLastSave="2607" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EC30897-F0CD-4D6B-ADBA-7D9CF6C926C3}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Instructions" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="456">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -981,6 +981,414 @@
   </si>
   <si>
     <t>ashiqul-abi, dilinaabi</t>
+  </si>
+  <si>
+    <t>Start and Stop buttons not working</t>
+  </si>
+  <si>
+    <t>Start and Stop buttons do not respond when pressed on the home page</t>
+  </si>
+  <si>
+    <t>ui,bug</t>
+  </si>
+  <si>
+    <t>Run button does not start the system</t>
+  </si>
+  <si>
+    <t>When the run button is pressed, the system does not start</t>
+  </si>
+  <si>
+    <t>Alarm should display when safety is active and run is pressed</t>
+  </si>
+  <si>
+    <t>System should display an alarm when safety interlock is active and user attempts to run</t>
+  </si>
+  <si>
+    <t>ui,safety</t>
+  </si>
+  <si>
+    <t>Safety active but system appears running when run is pressed</t>
+  </si>
+  <si>
+    <t>When safety is active, pressing run should not allow the system to appear to be running</t>
+  </si>
+  <si>
+    <t>ui,safety,bug</t>
+  </si>
+  <si>
+    <t>Home page settings panel issues</t>
+  </si>
+  <si>
+    <t>Settings panel on home page needs review and fixes</t>
+  </si>
+  <si>
+    <t>ui</t>
+  </si>
+  <si>
+    <t>Tools tab showing in Conveyor tab - move to Advanced Settings</t>
+  </si>
+  <si>
+    <t>Tools UI component is incorrectly placed in the Conveyor tab; should be moved to Advanced Settings</t>
+  </si>
+  <si>
+    <t>ui,ux</t>
+  </si>
+  <si>
+    <t>Conveyor tab missing conveyor speed - DB record missing</t>
+  </si>
+  <si>
+    <t>Conveyor tab does not show conveyor speed; DB record for this setting appears to be missing</t>
+  </si>
+  <si>
+    <t>ui,bug,db</t>
+  </si>
+  <si>
+    <t>Emergency stop from Robot not displayed in KII UI status bar</t>
+  </si>
+  <si>
+    <t>No indication of emergency stops originating from the Robot is shown in the KII top status bar</t>
+  </si>
+  <si>
+    <t>Home screen UI should display robot status</t>
+  </si>
+  <si>
+    <t>Add robot status indicators to the home screen</t>
+  </si>
+  <si>
+    <t>Logs not updating on main page</t>
+  </si>
+  <si>
+    <t>The log view on the main/home page is not refreshing or updating in real time</t>
+  </si>
+  <si>
+    <t>Remove or hide language selector (internationalization)</t>
+  </si>
+  <si>
+    <t>Language selector should be hidden; internationalization not needed for current scope</t>
+  </si>
+  <si>
+    <t>Add production rates and scoring rates from KI</t>
+  </si>
+  <si>
+    <t>Bring production rates and scoring rates display from KI into the home page</t>
+  </si>
+  <si>
+    <t>ui,feature</t>
+  </si>
+  <si>
+    <t>Changeable conveyor speed from UI</t>
+  </si>
+  <si>
+    <t>Allow operator to change conveyor speed directly from the UI</t>
+  </si>
+  <si>
+    <t>Live badge should show offline when system not running</t>
+  </si>
+  <si>
+    <t>Replace or remove the live badge; show offline state when system is not running</t>
+  </si>
+  <si>
+    <t>Home screen preview rotation - portrait image</t>
+  </si>
+  <si>
+    <t>Home screen scan preview image should display in portrait orientation</t>
+  </si>
+  <si>
+    <t>Universal error popup for any errors - TBD</t>
+  </si>
+  <si>
+    <t>Implement a universal popup component to display any system errors consistently; design TBD</t>
+  </si>
+  <si>
+    <t>Recipe preview not showing cuts [bug]</t>
+  </si>
+  <si>
+    <t>Recipe preview is not working and does not display cut lines</t>
+  </si>
+  <si>
+    <t>ui,bug,recipes</t>
+  </si>
+  <si>
+    <t>Recipe edit - validate conveyor speed and fix page navigation</t>
+  </si>
+  <si>
+    <t>Validate conveyor speed field on recipe edit page; fix normal navigation flow to the page</t>
+  </si>
+  <si>
+    <t>Add text labels to recipe icons</t>
+  </si>
+  <si>
+    <t>Recipe icon buttons need visible text labels for clarity</t>
+  </si>
+  <si>
+    <t>ui,ux,recipes</t>
+  </si>
+  <si>
+    <t>Recipe wizard - bind client name and creation date on UI</t>
+  </si>
+  <si>
+    <t>Left side of recipe wizard should display bound client name and creation date</t>
+  </si>
+  <si>
+    <t>ui,recipes</t>
+  </si>
+  <si>
+    <t>Log search not working</t>
+  </si>
+  <si>
+    <t>Log search functionality is broken; logs should be searchable</t>
+  </si>
+  <si>
+    <t>ui,bug,logs</t>
+  </si>
+  <si>
+    <t>Maintenance - hide 2D camera sensor</t>
+  </si>
+  <si>
+    <t>Hide the 2D camera entry from the sensors section on the maintenance page</t>
+  </si>
+  <si>
+    <t>ashiqul-abi, dilinaabi, MauricioDuqueABI</t>
+  </si>
+  <si>
+    <t>ui,maintenance</t>
+  </si>
+  <si>
+    <t>Maintenance - bind 3D camera image and IP address</t>
+  </si>
+  <si>
+    <t>3D camera image and IP address should be data-bound and displayed correctly on maintenance page</t>
+  </si>
+  <si>
+    <t>Maintenance - show health status for Robot, 3D cameras, Ultrasonic, Pump, Conveyor</t>
+  </si>
+  <si>
+    <t>Display health indicators for all major components on the maintenance page including sequential conveyor running status</t>
+  </si>
+  <si>
+    <t>ui,maintenance,feature</t>
+  </si>
+  <si>
+    <t>Maintenance Robot - add installation date and last maintenance date inputs</t>
+  </si>
+  <si>
+    <t>Add input fields for installation date and last maintenance date; store robot offsets in DB</t>
+  </si>
+  <si>
+    <t>ui,maintenance,db</t>
+  </si>
+  <si>
+    <t>Maintenance Robot - hide working hours</t>
+  </si>
+  <si>
+    <t>Working hours field should be hidden on the robot maintenance page for now</t>
+  </si>
+  <si>
+    <t>Maintenance Robot - hide right side panel</t>
+  </si>
+  <si>
+    <t>Right side panel on the robot maintenance page should be hidden</t>
+  </si>
+  <si>
+    <t>Maintenance 3D cameras - hide page, implement camera blink ID, add calibration tool</t>
+  </si>
+  <si>
+    <t>3D cameras maintenance page: hide until XML config submitted; implement camera identification blink; add calibration tool</t>
+  </si>
+  <si>
+    <t>ui,maintenance,3d-camera</t>
+  </si>
+  <si>
+    <t>Maintenance 3D cameras - update camera image</t>
+  </si>
+  <si>
+    <t>Update/replace the camera image displayed on the 3D cameras maintenance page</t>
+  </si>
+  <si>
+    <t>Maintenance Pump - hide right side panel</t>
+  </si>
+  <si>
+    <t>Right side panel on the pump maintenance page should be hidden</t>
+  </si>
+  <si>
+    <t>Production Statistics - redesign pages</t>
+  </si>
+  <si>
+    <t>Production Statistics pages need a full redesign; design TBD</t>
+  </si>
+  <si>
+    <t>Last Images - pending test</t>
+  </si>
+  <si>
+    <t>Last Images feature is pending testing; check and verify later</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>User management - fix threading issue causing page load error</t>
+  </si>
+  <si>
+    <t>User management page fails to load due to a threading issue; only loads successfully once</t>
+  </si>
+  <si>
+    <t>User Actions - hide superadmin and fix duplicate admin accounts</t>
+  </si>
+  <si>
+    <t>Hide the superadmin user from user selection; resolve duplicate admin and Admin entries</t>
+  </si>
+  <si>
+    <t>ui,bug,security</t>
+  </si>
+  <si>
+    <t>Engineering Settings - fix advanced settings tab height and button styles</t>
+  </si>
+  <si>
+    <t>Advanced settings tab should match page height; fix button design and styles</t>
+  </si>
+  <si>
+    <t>Engineering Settings - bind tools in tool settings page</t>
+  </si>
+  <si>
+    <t>Tool settings page should have all tools properly data-bound</t>
+  </si>
+  <si>
+    <t>Engineering Settings - fix layout and fonts</t>
+  </si>
+  <si>
+    <t>Fix page layout issues and font consistency in Engineering Settings</t>
+  </si>
+  <si>
+    <t>Engineering Settings - replace scrolling with page-by-page navigation</t>
+  </si>
+  <si>
+    <t>Remove vertical scrolling from settings; implement paginated navigation instead</t>
+  </si>
+  <si>
+    <t>Move Incident Reports to main navigation bar bottom</t>
+  </si>
+  <si>
+    <t>Incident reports section should be accessible from the bottom of the main navigation bar</t>
+  </si>
+  <si>
+    <t>Move Documentation to main navigation bar bottom</t>
+  </si>
+  <si>
+    <t>Documentation section should be accessible from the bottom of the main navigation bar</t>
+  </si>
+  <si>
+    <t>Find and update Incident and Documentation pages from GitHub</t>
+  </si>
+  <si>
+    <t>Locate Incident and Documentation page code in GitHub and bring to latest codebase</t>
+  </si>
+  <si>
+    <t>dev</t>
+  </si>
+  <si>
+    <t>Tools - add ability to create new tools and manage Tool IDs</t>
+  </si>
+  <si>
+    <t>No UI exists to create new tools or Tool IDs; implement tool creation with proper ID separation and management</t>
+  </si>
+  <si>
+    <t>feature,tools</t>
+  </si>
+  <si>
+    <t>Backend - update OPC server to EyeQ version for Katana</t>
+  </si>
+  <si>
+    <t>Bring OPC server for Katana up to the same version used in EyeQ</t>
+  </si>
+  <si>
+    <t>backend,opc</t>
+  </si>
+  <si>
+    <t>Backend - add toggle between robot controller and PLC for specific tags</t>
+  </si>
+  <si>
+    <t>Katana should support switching between robot controller and PLC for selected OPC tags</t>
+  </si>
+  <si>
+    <t>Backend - recipe save/load centralized to SSOT</t>
+  </si>
+  <si>
+    <t>Recipe save and load logic was inconsistent between WPF and Blazor; now centralized to single source of truth</t>
+  </si>
+  <si>
+    <t>backend,recipes</t>
+  </si>
+  <si>
+    <t>Completed 2026-06-04</t>
+  </si>
+  <si>
+    <t>Backend - permission hidden features set to readonly</t>
+  </si>
+  <si>
+    <t>Hidden features behind permissions are now set to readonly mode</t>
+  </si>
+  <si>
+    <t>backend,security</t>
+  </si>
+  <si>
+    <t>Robot - keep RAPID code at latest version</t>
+  </si>
+  <si>
+    <t>Ensure RAPID code is always maintained at the latest stable version</t>
+  </si>
+  <si>
+    <t>robot,rapid</t>
+  </si>
+  <si>
+    <t>Robot - error and stop when current tool is blank</t>
+  </si>
+  <si>
+    <t>If the current tool field is blank when Katana starts, it should raise an error and stop</t>
+  </si>
+  <si>
+    <t>robot,safety,bug</t>
+  </si>
+  <si>
+    <t>Robot - Katana start: robot stuck in semistatic RAPID</t>
+  </si>
+  <si>
+    <t>When Katana starts, the robot never starts and gets stuck in semistatic RAPID state</t>
+  </si>
+  <si>
+    <t>robot,bug</t>
+  </si>
+  <si>
+    <t>Discovered 2026-05-19</t>
+  </si>
+  <si>
+    <t>Robot - Cut Z-Depth=0 cuts product, height calculation error</t>
+  </si>
+  <si>
+    <t>Setting cut Z-Depth to 0 still cuts the product; likely a height calculation bug</t>
+  </si>
+  <si>
+    <t>Discovered 2026-06-02</t>
+  </si>
+  <si>
+    <t>PLC - OPC communication map and UDTs</t>
+  </si>
+  <si>
+    <t>Define and implement OPC communication map and UDT structures for Katana-PLC interface [in progress]</t>
+  </si>
+  <si>
+    <t>plc,opc</t>
+  </si>
+  <si>
+    <t>PLC - OPC multiple interfaces in Katana and PLC</t>
+  </si>
+  <si>
+    <t>Support multiple OPC interfaces between Katana application and PLC</t>
+  </si>
+  <si>
+    <t>Task unification</t>
+  </si>
+  <si>
+    <t>Unify all the tasks in one single file consolidation</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1740,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1424,6 +1832,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1634,6 +2043,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1990,22 +2403,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="32"/>
+      <c r="C2" s="33"/>
     </row>
     <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="33"/>
+      <c r="C4" s="34"/>
     </row>
     <row r="6" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="31"/>
+      <c r="C6" s="32"/>
     </row>
     <row r="7" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -2032,10 +2445,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="31"/>
+      <c r="C11" s="32"/>
     </row>
     <row r="12" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
@@ -2134,10 +2547,10 @@
       </c>
     </row>
     <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="31"/>
+      <c r="C25" s="32"/>
     </row>
     <row r="26" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
@@ -2188,10 +2601,10 @@
       </c>
     </row>
     <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="31"/>
+      <c r="C33" s="32"/>
     </row>
     <row r="34" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
@@ -2252,7 +2665,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:M234"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" customWidth="1"/>
@@ -7638,6 +8051,1405 @@
       <c r="L181" s="22"/>
       <c r="M181" s="26" t="s">
         <v>309</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D182" t="s">
+        <v>319</v>
+      </c>
+      <c r="E182" t="s">
+        <v>59</v>
+      </c>
+      <c r="F182" t="s">
+        <v>312</v>
+      </c>
+      <c r="K182" t="s">
+        <v>322</v>
+      </c>
+      <c r="M182" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D183" t="s">
+        <v>319</v>
+      </c>
+      <c r="E183" t="s">
+        <v>59</v>
+      </c>
+      <c r="F183" t="s">
+        <v>312</v>
+      </c>
+      <c r="K183" t="s">
+        <v>322</v>
+      </c>
+      <c r="M183" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D184" t="s">
+        <v>319</v>
+      </c>
+      <c r="E184" t="s">
+        <v>59</v>
+      </c>
+      <c r="F184" t="s">
+        <v>312</v>
+      </c>
+      <c r="K184" t="s">
+        <v>327</v>
+      </c>
+      <c r="M184" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D185" t="s">
+        <v>319</v>
+      </c>
+      <c r="E185" t="s">
+        <v>59</v>
+      </c>
+      <c r="F185" t="s">
+        <v>312</v>
+      </c>
+      <c r="K185" t="s">
+        <v>330</v>
+      </c>
+      <c r="M185" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D186" t="s">
+        <v>319</v>
+      </c>
+      <c r="E186" t="s">
+        <v>59</v>
+      </c>
+      <c r="F186" t="s">
+        <v>312</v>
+      </c>
+      <c r="K186" t="s">
+        <v>333</v>
+      </c>
+      <c r="M186" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D187" t="s">
+        <v>319</v>
+      </c>
+      <c r="E187" t="s">
+        <v>59</v>
+      </c>
+      <c r="F187" t="s">
+        <v>312</v>
+      </c>
+      <c r="K187" t="s">
+        <v>336</v>
+      </c>
+      <c r="M187" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D188" t="s">
+        <v>319</v>
+      </c>
+      <c r="E188" t="s">
+        <v>59</v>
+      </c>
+      <c r="F188" t="s">
+        <v>312</v>
+      </c>
+      <c r="K188" t="s">
+        <v>339</v>
+      </c>
+      <c r="M188" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D189" t="s">
+        <v>319</v>
+      </c>
+      <c r="E189" t="s">
+        <v>59</v>
+      </c>
+      <c r="F189" t="s">
+        <v>312</v>
+      </c>
+      <c r="K189" t="s">
+        <v>327</v>
+      </c>
+      <c r="M189" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D190" t="s">
+        <v>319</v>
+      </c>
+      <c r="E190" t="s">
+        <v>59</v>
+      </c>
+      <c r="F190" t="s">
+        <v>312</v>
+      </c>
+      <c r="K190" t="s">
+        <v>336</v>
+      </c>
+      <c r="M190" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D191" t="s">
+        <v>319</v>
+      </c>
+      <c r="E191" t="s">
+        <v>59</v>
+      </c>
+      <c r="F191" t="s">
+        <v>312</v>
+      </c>
+      <c r="K191" t="s">
+        <v>322</v>
+      </c>
+      <c r="M191" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D192" t="s">
+        <v>319</v>
+      </c>
+      <c r="E192" t="s">
+        <v>59</v>
+      </c>
+      <c r="F192" t="s">
+        <v>312</v>
+      </c>
+      <c r="K192" t="s">
+        <v>333</v>
+      </c>
+      <c r="M192" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D193" t="s">
+        <v>319</v>
+      </c>
+      <c r="E193" t="s">
+        <v>59</v>
+      </c>
+      <c r="F193" t="s">
+        <v>312</v>
+      </c>
+      <c r="K193" t="s">
+        <v>350</v>
+      </c>
+      <c r="M193" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D194" t="s">
+        <v>319</v>
+      </c>
+      <c r="E194" t="s">
+        <v>59</v>
+      </c>
+      <c r="F194" t="s">
+        <v>312</v>
+      </c>
+      <c r="K194" t="s">
+        <v>350</v>
+      </c>
+      <c r="M194" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D195" t="s">
+        <v>319</v>
+      </c>
+      <c r="E195" t="s">
+        <v>59</v>
+      </c>
+      <c r="F195" t="s">
+        <v>312</v>
+      </c>
+      <c r="K195" t="s">
+        <v>336</v>
+      </c>
+      <c r="M195" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D196" t="s">
+        <v>319</v>
+      </c>
+      <c r="E196" t="s">
+        <v>59</v>
+      </c>
+      <c r="F196" t="s">
+        <v>312</v>
+      </c>
+      <c r="K196" t="s">
+        <v>322</v>
+      </c>
+      <c r="M196" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D197" t="s">
+        <v>319</v>
+      </c>
+      <c r="E197" t="s">
+        <v>59</v>
+      </c>
+      <c r="F197" t="s">
+        <v>312</v>
+      </c>
+      <c r="K197" t="s">
+        <v>350</v>
+      </c>
+      <c r="M197" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D198" t="s">
+        <v>60</v>
+      </c>
+      <c r="E198" t="s">
+        <v>59</v>
+      </c>
+      <c r="F198" t="s">
+        <v>313</v>
+      </c>
+      <c r="K198" t="s">
+        <v>361</v>
+      </c>
+      <c r="M198" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D199" t="s">
+        <v>60</v>
+      </c>
+      <c r="E199" t="s">
+        <v>59</v>
+      </c>
+      <c r="F199" t="s">
+        <v>313</v>
+      </c>
+      <c r="K199" t="s">
+        <v>361</v>
+      </c>
+      <c r="M199" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D200" t="s">
+        <v>60</v>
+      </c>
+      <c r="E200" t="s">
+        <v>59</v>
+      </c>
+      <c r="F200" t="s">
+        <v>313</v>
+      </c>
+      <c r="K200" t="s">
+        <v>366</v>
+      </c>
+      <c r="M200" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D201" t="s">
+        <v>60</v>
+      </c>
+      <c r="E201" t="s">
+        <v>59</v>
+      </c>
+      <c r="F201" t="s">
+        <v>313</v>
+      </c>
+      <c r="K201" t="s">
+        <v>369</v>
+      </c>
+      <c r="M201" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D202" t="s">
+        <v>60</v>
+      </c>
+      <c r="E202" t="s">
+        <v>59</v>
+      </c>
+      <c r="F202" t="s">
+        <v>314</v>
+      </c>
+      <c r="K202" t="s">
+        <v>372</v>
+      </c>
+      <c r="M202" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D203" t="s">
+        <v>375</v>
+      </c>
+      <c r="E203" t="s">
+        <v>59</v>
+      </c>
+      <c r="F203" t="s">
+        <v>313</v>
+      </c>
+      <c r="K203" t="s">
+        <v>376</v>
+      </c>
+      <c r="M203" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D204" t="s">
+        <v>375</v>
+      </c>
+      <c r="E204" t="s">
+        <v>59</v>
+      </c>
+      <c r="F204" t="s">
+        <v>313</v>
+      </c>
+      <c r="K204" t="s">
+        <v>376</v>
+      </c>
+      <c r="M204" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D205" t="s">
+        <v>375</v>
+      </c>
+      <c r="E205" t="s">
+        <v>59</v>
+      </c>
+      <c r="F205" t="s">
+        <v>313</v>
+      </c>
+      <c r="K205" t="s">
+        <v>381</v>
+      </c>
+      <c r="M205" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D206" t="s">
+        <v>60</v>
+      </c>
+      <c r="E206" t="s">
+        <v>59</v>
+      </c>
+      <c r="F206" t="s">
+        <v>314</v>
+      </c>
+      <c r="K206" t="s">
+        <v>384</v>
+      </c>
+      <c r="M206" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D207" t="s">
+        <v>60</v>
+      </c>
+      <c r="E207" t="s">
+        <v>59</v>
+      </c>
+      <c r="F207" t="s">
+        <v>314</v>
+      </c>
+      <c r="K207" t="s">
+        <v>376</v>
+      </c>
+      <c r="M207" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D208" t="s">
+        <v>60</v>
+      </c>
+      <c r="E208" t="s">
+        <v>59</v>
+      </c>
+      <c r="F208" t="s">
+        <v>314</v>
+      </c>
+      <c r="K208" t="s">
+        <v>376</v>
+      </c>
+      <c r="M208" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D209" t="s">
+        <v>61</v>
+      </c>
+      <c r="E209" t="s">
+        <v>59</v>
+      </c>
+      <c r="F209" t="s">
+        <v>313</v>
+      </c>
+      <c r="K209" t="s">
+        <v>391</v>
+      </c>
+      <c r="M209" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D210" t="s">
+        <v>61</v>
+      </c>
+      <c r="E210" t="s">
+        <v>59</v>
+      </c>
+      <c r="F210" t="s">
+        <v>313</v>
+      </c>
+      <c r="K210" t="s">
+        <v>391</v>
+      </c>
+      <c r="M210" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D211" t="s">
+        <v>58</v>
+      </c>
+      <c r="E211" t="s">
+        <v>59</v>
+      </c>
+      <c r="F211" t="s">
+        <v>314</v>
+      </c>
+      <c r="K211" t="s">
+        <v>376</v>
+      </c>
+      <c r="M211" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D212" t="s">
+        <v>58</v>
+      </c>
+      <c r="E212" t="s">
+        <v>59</v>
+      </c>
+      <c r="F212" t="s">
+        <v>314</v>
+      </c>
+      <c r="K212" t="s">
+        <v>350</v>
+      </c>
+      <c r="M212" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E213" t="s">
+        <v>59</v>
+      </c>
+      <c r="F213" t="s">
+        <v>314</v>
+      </c>
+      <c r="K213" t="s">
+        <v>400</v>
+      </c>
+      <c r="M213" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D214" t="s">
+        <v>61</v>
+      </c>
+      <c r="E214" t="s">
+        <v>59</v>
+      </c>
+      <c r="F214" t="s">
+        <v>314</v>
+      </c>
+      <c r="K214" t="s">
+        <v>322</v>
+      </c>
+      <c r="M214" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D215" t="s">
+        <v>60</v>
+      </c>
+      <c r="E215" t="s">
+        <v>59</v>
+      </c>
+      <c r="F215" t="s">
+        <v>314</v>
+      </c>
+      <c r="K215" t="s">
+        <v>405</v>
+      </c>
+      <c r="M215" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D216" t="s">
+        <v>60</v>
+      </c>
+      <c r="E216" t="s">
+        <v>59</v>
+      </c>
+      <c r="F216" t="s">
+        <v>312</v>
+      </c>
+      <c r="K216" t="s">
+        <v>336</v>
+      </c>
+      <c r="M216" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D217" t="s">
+        <v>60</v>
+      </c>
+      <c r="E217" t="s">
+        <v>59</v>
+      </c>
+      <c r="F217" t="s">
+        <v>312</v>
+      </c>
+      <c r="K217" t="s">
+        <v>350</v>
+      </c>
+      <c r="M217" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D218" t="s">
+        <v>60</v>
+      </c>
+      <c r="E218" t="s">
+        <v>59</v>
+      </c>
+      <c r="F218" t="s">
+        <v>312</v>
+      </c>
+      <c r="K218" t="s">
+        <v>336</v>
+      </c>
+      <c r="M218" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D219" t="s">
+        <v>60</v>
+      </c>
+      <c r="E219" t="s">
+        <v>59</v>
+      </c>
+      <c r="F219" t="s">
+        <v>312</v>
+      </c>
+      <c r="K219" t="s">
+        <v>336</v>
+      </c>
+      <c r="M219" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D220" t="s">
+        <v>60</v>
+      </c>
+      <c r="E220" t="s">
+        <v>59</v>
+      </c>
+      <c r="F220" t="s">
+        <v>314</v>
+      </c>
+      <c r="K220" t="s">
+        <v>336</v>
+      </c>
+      <c r="M220" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D221" t="s">
+        <v>60</v>
+      </c>
+      <c r="E221" t="s">
+        <v>59</v>
+      </c>
+      <c r="F221" t="s">
+        <v>314</v>
+      </c>
+      <c r="K221" t="s">
+        <v>336</v>
+      </c>
+      <c r="M221" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D222" t="s">
+        <v>60</v>
+      </c>
+      <c r="E222" t="s">
+        <v>59</v>
+      </c>
+      <c r="F222" t="s">
+        <v>314</v>
+      </c>
+      <c r="K222" t="s">
+        <v>420</v>
+      </c>
+      <c r="M222" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E223" t="s">
+        <v>59</v>
+      </c>
+      <c r="F223" t="s">
+        <v>312</v>
+      </c>
+      <c r="K223" t="s">
+        <v>423</v>
+      </c>
+      <c r="M223" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D224" t="s">
+        <v>61</v>
+      </c>
+      <c r="E224" t="s">
+        <v>59</v>
+      </c>
+      <c r="F224" t="s">
+        <v>312</v>
+      </c>
+      <c r="K224" t="s">
+        <v>426</v>
+      </c>
+      <c r="M224" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D225" t="s">
+        <v>61</v>
+      </c>
+      <c r="E225" t="s">
+        <v>59</v>
+      </c>
+      <c r="F225" t="s">
+        <v>312</v>
+      </c>
+      <c r="K225" t="s">
+        <v>426</v>
+      </c>
+      <c r="M225" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D226" t="s">
+        <v>61</v>
+      </c>
+      <c r="E226" t="s">
+        <v>73</v>
+      </c>
+      <c r="F226" t="s">
+        <v>313</v>
+      </c>
+      <c r="H226" s="31">
+        <v>46177</v>
+      </c>
+      <c r="K226" t="s">
+        <v>431</v>
+      </c>
+      <c r="L226" t="s">
+        <v>432</v>
+      </c>
+      <c r="M226" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D227" t="s">
+        <v>61</v>
+      </c>
+      <c r="E227" t="s">
+        <v>73</v>
+      </c>
+      <c r="F227" t="s">
+        <v>313</v>
+      </c>
+      <c r="H227" s="31">
+        <v>46177</v>
+      </c>
+      <c r="K227" t="s">
+        <v>435</v>
+      </c>
+      <c r="L227" t="s">
+        <v>432</v>
+      </c>
+      <c r="M227" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D228" t="s">
+        <v>58</v>
+      </c>
+      <c r="E228" t="s">
+        <v>59</v>
+      </c>
+      <c r="F228" t="s">
+        <v>312</v>
+      </c>
+      <c r="K228" t="s">
+        <v>438</v>
+      </c>
+      <c r="M228" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D229" t="s">
+        <v>58</v>
+      </c>
+      <c r="E229" t="s">
+        <v>59</v>
+      </c>
+      <c r="F229" t="s">
+        <v>312</v>
+      </c>
+      <c r="K229" t="s">
+        <v>441</v>
+      </c>
+      <c r="M229" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D230" t="s">
+        <v>58</v>
+      </c>
+      <c r="E230" t="s">
+        <v>59</v>
+      </c>
+      <c r="F230" t="s">
+        <v>312</v>
+      </c>
+      <c r="H230" s="31">
+        <v>46161</v>
+      </c>
+      <c r="K230" t="s">
+        <v>444</v>
+      </c>
+      <c r="L230" t="s">
+        <v>445</v>
+      </c>
+      <c r="M230" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D231" t="s">
+        <v>58</v>
+      </c>
+      <c r="E231" t="s">
+        <v>59</v>
+      </c>
+      <c r="F231" t="s">
+        <v>312</v>
+      </c>
+      <c r="H231" s="31">
+        <v>46175</v>
+      </c>
+      <c r="K231" t="s">
+        <v>444</v>
+      </c>
+      <c r="L231" t="s">
+        <v>448</v>
+      </c>
+      <c r="M231" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D232" t="s">
+        <v>58</v>
+      </c>
+      <c r="E232" t="s">
+        <v>62</v>
+      </c>
+      <c r="F232" t="s">
+        <v>312</v>
+      </c>
+      <c r="K232" t="s">
+        <v>451</v>
+      </c>
+      <c r="L232" t="s">
+        <v>62</v>
+      </c>
+      <c r="M232" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D233" t="s">
+        <v>58</v>
+      </c>
+      <c r="E233" t="s">
+        <v>59</v>
+      </c>
+      <c r="F233" t="s">
+        <v>312</v>
+      </c>
+      <c r="K233" t="s">
+        <v>451</v>
+      </c>
+      <c r="M233" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D234" t="s">
+        <v>58</v>
+      </c>
+      <c r="E234" t="s">
+        <v>62</v>
+      </c>
+      <c r="F234" t="s">
+        <v>312</v>
+      </c>
+      <c r="H234" s="31">
+        <v>46205</v>
+      </c>
+      <c r="M234" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="2607" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EC30897-F0CD-4D6B-ADBA-7D9CF6C926C3}"/>
+  <xr:revisionPtr revIDLastSave="2923" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{286F0175-1D6F-433A-8684-006ADA3805B2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1395,7 +1395,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+  </numFmts>
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1462,8 +1465,43 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF385723"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7F6000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1496,8 +1534,62 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F7FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1736,11 +1828,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1802,24 +1972,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1832,7 +1984,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1841,6 +1992,132 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="15" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2403,22 +2680,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="33"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="34"/>
+      <c r="C4" s="27"/>
     </row>
     <row r="6" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="32"/>
+      <c r="C6" s="25"/>
     </row>
     <row r="7" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -2445,10 +2722,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="32"/>
+      <c r="C11" s="25"/>
     </row>
     <row r="12" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
@@ -2547,10 +2824,10 @@
       </c>
     </row>
     <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="32"/>
+      <c r="C25" s="25"/>
     </row>
     <row r="26" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
@@ -2601,10 +2878,10 @@
       </c>
     </row>
     <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="32"/>
+      <c r="C33" s="25"/>
     </row>
     <row r="34" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
@@ -7984,1471 +8261,1729 @@
       </c>
     </row>
     <row r="180" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="14">
+      <c r="A180" s="28">
         <v>179</v>
       </c>
-      <c r="B180" s="15" t="s">
+      <c r="B180" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="C180" s="15" t="s">
+      <c r="C180" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="D180" s="16" t="s">
+      <c r="D180" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="E180" s="17" t="s">
+      <c r="E180" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="F180" s="17" t="s">
+      <c r="F180" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="G180" s="17"/>
-      <c r="H180" s="17">
+      <c r="G180" s="31"/>
+      <c r="H180" s="31">
         <v>10</v>
       </c>
-      <c r="I180" s="19">
+      <c r="I180" s="32">
         <v>46120</v>
       </c>
-      <c r="J180" s="19">
+      <c r="J180" s="32">
         <v>46136</v>
       </c>
-      <c r="K180" s="16"/>
-      <c r="L180" s="15"/>
-      <c r="M180" s="20" t="s">
+      <c r="K180" s="30"/>
+      <c r="L180" s="29"/>
+      <c r="M180" s="33" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="21">
+      <c r="A181" s="14">
         <v>180</v>
       </c>
-      <c r="B181" s="22" t="s">
+      <c r="B181" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C181" s="22" t="s">
+      <c r="C181" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="D181" s="23" t="s">
+      <c r="D181" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="E181" s="24" t="s">
+      <c r="E181" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="F181" s="24" t="s">
+      <c r="F181" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="G181" s="24"/>
-      <c r="H181" s="24">
+      <c r="G181" s="17"/>
+      <c r="H181" s="17">
         <v>10</v>
       </c>
-      <c r="I181" s="25">
+      <c r="I181" s="19">
         <v>46113</v>
       </c>
-      <c r="J181" s="25">
+      <c r="J181" s="19">
         <v>46122</v>
       </c>
-      <c r="K181" s="23"/>
-      <c r="L181" s="22"/>
-      <c r="M181" s="26" t="s">
+      <c r="K181" s="16"/>
+      <c r="L181" s="15"/>
+      <c r="M181" s="20" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A182">
+    <row r="182" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="62">
         <v>181</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="63" t="s">
         <v>320</v>
       </c>
-      <c r="C182" s="3" t="s">
+      <c r="C182" s="63" t="s">
         <v>321</v>
       </c>
-      <c r="D182" t="s">
+      <c r="D182" s="64" t="s">
         <v>319</v>
       </c>
-      <c r="E182" t="s">
-        <v>59</v>
-      </c>
-      <c r="F182" t="s">
+      <c r="E182" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="F182" s="66" t="s">
         <v>312</v>
       </c>
-      <c r="K182" t="s">
+      <c r="G182" s="67"/>
+      <c r="H182" s="67"/>
+      <c r="I182" s="68"/>
+      <c r="J182" s="68"/>
+      <c r="K182" s="64" t="s">
         <v>322</v>
       </c>
-      <c r="M182" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A183">
+      <c r="L182" s="64"/>
+      <c r="M182" s="69" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="50">
         <v>182</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="C183" s="3" t="s">
+      <c r="C183" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D183" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="E183" t="s">
-        <v>59</v>
-      </c>
-      <c r="F183" t="s">
+      <c r="E183" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F183" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K183" t="s">
+      <c r="G183" s="38"/>
+      <c r="H183" s="38"/>
+      <c r="I183" s="39"/>
+      <c r="J183" s="39"/>
+      <c r="K183" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="M183" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A184">
+      <c r="L183" s="35"/>
+      <c r="M183" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="51">
         <v>183</v>
       </c>
-      <c r="B184" s="3" t="s">
+      <c r="B184" s="40" t="s">
         <v>325</v>
       </c>
-      <c r="C184" s="3" t="s">
+      <c r="C184" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="D184" t="s">
+      <c r="D184" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="E184" t="s">
-        <v>59</v>
-      </c>
-      <c r="F184" t="s">
+      <c r="E184" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F184" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K184" t="s">
+      <c r="G184" s="42"/>
+      <c r="H184" s="42"/>
+      <c r="I184" s="43"/>
+      <c r="J184" s="43"/>
+      <c r="K184" s="41" t="s">
         <v>327</v>
       </c>
-      <c r="M184" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A185">
+      <c r="L184" s="41"/>
+      <c r="M184" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="50">
         <v>184</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="C185" s="3" t="s">
+      <c r="C185" s="34" t="s">
         <v>329</v>
       </c>
-      <c r="D185" t="s">
+      <c r="D185" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="E185" t="s">
-        <v>59</v>
-      </c>
-      <c r="F185" t="s">
+      <c r="E185" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F185" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K185" t="s">
+      <c r="G185" s="38"/>
+      <c r="H185" s="38"/>
+      <c r="I185" s="39"/>
+      <c r="J185" s="39"/>
+      <c r="K185" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="M185" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A186">
+      <c r="L185" s="35"/>
+      <c r="M185" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="51">
         <v>185</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="40" t="s">
         <v>331</v>
       </c>
-      <c r="C186" s="3" t="s">
+      <c r="C186" s="40" t="s">
         <v>332</v>
       </c>
-      <c r="D186" t="s">
+      <c r="D186" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="E186" t="s">
-        <v>59</v>
-      </c>
-      <c r="F186" t="s">
+      <c r="E186" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F186" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K186" t="s">
+      <c r="G186" s="42"/>
+      <c r="H186" s="42"/>
+      <c r="I186" s="43"/>
+      <c r="J186" s="43"/>
+      <c r="K186" s="41" t="s">
         <v>333</v>
       </c>
-      <c r="M186" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="187" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A187">
+      <c r="L186" s="41"/>
+      <c r="M186" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="50">
         <v>186</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="C187" s="3" t="s">
+      <c r="C187" s="34" t="s">
         <v>335</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D187" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="E187" t="s">
-        <v>59</v>
-      </c>
-      <c r="F187" t="s">
+      <c r="E187" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F187" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K187" t="s">
+      <c r="G187" s="38"/>
+      <c r="H187" s="38"/>
+      <c r="I187" s="39"/>
+      <c r="J187" s="39"/>
+      <c r="K187" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="M187" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="188" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A188">
+      <c r="L187" s="35"/>
+      <c r="M187" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="51">
         <v>187</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="40" t="s">
         <v>337</v>
       </c>
-      <c r="C188" s="3" t="s">
+      <c r="C188" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D188" t="s">
+      <c r="D188" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="E188" t="s">
-        <v>59</v>
-      </c>
-      <c r="F188" t="s">
+      <c r="E188" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F188" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K188" t="s">
+      <c r="G188" s="42"/>
+      <c r="H188" s="42"/>
+      <c r="I188" s="43"/>
+      <c r="J188" s="43"/>
+      <c r="K188" s="41" t="s">
         <v>339</v>
       </c>
-      <c r="M188" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="189" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A189">
+      <c r="L188" s="41"/>
+      <c r="M188" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="50">
         <v>188</v>
       </c>
-      <c r="B189" s="3" t="s">
+      <c r="B189" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="C189" s="3" t="s">
+      <c r="C189" s="34" t="s">
         <v>341</v>
       </c>
-      <c r="D189" t="s">
+      <c r="D189" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="E189" t="s">
-        <v>59</v>
-      </c>
-      <c r="F189" t="s">
+      <c r="E189" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F189" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K189" t="s">
+      <c r="G189" s="38"/>
+      <c r="H189" s="38"/>
+      <c r="I189" s="39"/>
+      <c r="J189" s="39"/>
+      <c r="K189" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="M189" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A190">
+      <c r="L189" s="35"/>
+      <c r="M189" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="51">
         <v>189</v>
       </c>
-      <c r="B190" s="3" t="s">
+      <c r="B190" s="40" t="s">
         <v>342</v>
       </c>
-      <c r="C190" s="3" t="s">
+      <c r="C190" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D190" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="E190" t="s">
-        <v>59</v>
-      </c>
-      <c r="F190" t="s">
+      <c r="E190" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F190" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K190" t="s">
+      <c r="G190" s="42"/>
+      <c r="H190" s="42"/>
+      <c r="I190" s="43"/>
+      <c r="J190" s="43"/>
+      <c r="K190" s="41" t="s">
         <v>336</v>
       </c>
-      <c r="M190" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A191">
+      <c r="L190" s="41"/>
+      <c r="M190" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="50">
         <v>190</v>
       </c>
-      <c r="B191" s="3" t="s">
+      <c r="B191" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="C191" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="D191" t="s">
+      <c r="D191" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="E191" t="s">
-        <v>59</v>
-      </c>
-      <c r="F191" t="s">
+      <c r="E191" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F191" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K191" t="s">
+      <c r="G191" s="38"/>
+      <c r="H191" s="38"/>
+      <c r="I191" s="39"/>
+      <c r="J191" s="39"/>
+      <c r="K191" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="M191" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A192">
+      <c r="L191" s="35"/>
+      <c r="M191" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="51">
         <v>191</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B192" s="40" t="s">
         <v>346</v>
       </c>
-      <c r="C192" s="3" t="s">
+      <c r="C192" s="40" t="s">
         <v>347</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D192" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="E192" t="s">
-        <v>59</v>
-      </c>
-      <c r="F192" t="s">
+      <c r="E192" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F192" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K192" t="s">
+      <c r="G192" s="42"/>
+      <c r="H192" s="42"/>
+      <c r="I192" s="43"/>
+      <c r="J192" s="43"/>
+      <c r="K192" s="41" t="s">
         <v>333</v>
       </c>
-      <c r="M192" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A193">
+      <c r="L192" s="41"/>
+      <c r="M192" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="50">
         <v>192</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="B193" s="34" t="s">
         <v>348</v>
       </c>
-      <c r="C193" s="3" t="s">
+      <c r="C193" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="D193" t="s">
+      <c r="D193" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="E193" t="s">
-        <v>59</v>
-      </c>
-      <c r="F193" t="s">
+      <c r="E193" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F193" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K193" t="s">
+      <c r="G193" s="38"/>
+      <c r="H193" s="38"/>
+      <c r="I193" s="39"/>
+      <c r="J193" s="39"/>
+      <c r="K193" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="M193" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A194">
+      <c r="L193" s="35"/>
+      <c r="M193" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="51">
         <v>193</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="B194" s="40" t="s">
         <v>351</v>
       </c>
-      <c r="C194" s="3" t="s">
+      <c r="C194" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="D194" t="s">
+      <c r="D194" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="E194" t="s">
-        <v>59</v>
-      </c>
-      <c r="F194" t="s">
+      <c r="E194" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F194" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K194" t="s">
+      <c r="G194" s="42"/>
+      <c r="H194" s="42"/>
+      <c r="I194" s="43"/>
+      <c r="J194" s="43"/>
+      <c r="K194" s="41" t="s">
         <v>350</v>
       </c>
-      <c r="M194" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A195">
+      <c r="L194" s="41"/>
+      <c r="M194" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="50">
         <v>194</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B195" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="C195" s="3" t="s">
+      <c r="C195" s="34" t="s">
         <v>354</v>
       </c>
-      <c r="D195" t="s">
+      <c r="D195" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="E195" t="s">
-        <v>59</v>
-      </c>
-      <c r="F195" t="s">
+      <c r="E195" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F195" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K195" t="s">
+      <c r="G195" s="38"/>
+      <c r="H195" s="38"/>
+      <c r="I195" s="39"/>
+      <c r="J195" s="39"/>
+      <c r="K195" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="M195" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A196">
+      <c r="L195" s="35"/>
+      <c r="M195" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="51">
         <v>195</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B196" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="C196" s="3" t="s">
+      <c r="C196" s="40" t="s">
         <v>356</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D196" s="41" t="s">
         <v>319</v>
       </c>
-      <c r="E196" t="s">
-        <v>59</v>
-      </c>
-      <c r="F196" t="s">
+      <c r="E196" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F196" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K196" t="s">
+      <c r="G196" s="42"/>
+      <c r="H196" s="42"/>
+      <c r="I196" s="43"/>
+      <c r="J196" s="43"/>
+      <c r="K196" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="M196" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A197">
+      <c r="L196" s="41"/>
+      <c r="M196" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="50">
         <v>196</v>
       </c>
-      <c r="B197" s="3" t="s">
+      <c r="B197" s="34" t="s">
         <v>357</v>
       </c>
-      <c r="C197" s="3" t="s">
+      <c r="C197" s="34" t="s">
         <v>358</v>
       </c>
-      <c r="D197" t="s">
+      <c r="D197" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="E197" t="s">
-        <v>59</v>
-      </c>
-      <c r="F197" t="s">
+      <c r="E197" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F197" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K197" t="s">
+      <c r="G197" s="38"/>
+      <c r="H197" s="38"/>
+      <c r="I197" s="39"/>
+      <c r="J197" s="39"/>
+      <c r="K197" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="M197" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A198">
+      <c r="L197" s="35"/>
+      <c r="M197" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="51">
         <v>197</v>
       </c>
-      <c r="B198" s="3" t="s">
+      <c r="B198" s="40" t="s">
         <v>359</v>
       </c>
-      <c r="C198" s="3" t="s">
+      <c r="C198" s="40" t="s">
         <v>360</v>
       </c>
-      <c r="D198" t="s">
+      <c r="D198" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E198" t="s">
-        <v>59</v>
-      </c>
-      <c r="F198" t="s">
+      <c r="E198" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F198" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K198" t="s">
+      <c r="G198" s="42"/>
+      <c r="H198" s="42"/>
+      <c r="I198" s="43"/>
+      <c r="J198" s="43"/>
+      <c r="K198" s="41" t="s">
         <v>361</v>
       </c>
-      <c r="M198" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="199" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A199">
+      <c r="L198" s="41"/>
+      <c r="M198" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="50">
         <v>198</v>
       </c>
-      <c r="B199" s="3" t="s">
+      <c r="B199" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="C199" s="3" t="s">
+      <c r="C199" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="D199" t="s">
+      <c r="D199" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="E199" t="s">
-        <v>59</v>
-      </c>
-      <c r="F199" t="s">
+      <c r="E199" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F199" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K199" t="s">
+      <c r="G199" s="38"/>
+      <c r="H199" s="38"/>
+      <c r="I199" s="39"/>
+      <c r="J199" s="39"/>
+      <c r="K199" s="35" t="s">
         <v>361</v>
       </c>
-      <c r="M199" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A200">
+      <c r="L199" s="35"/>
+      <c r="M199" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="51">
         <v>199</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B200" s="40" t="s">
         <v>364</v>
       </c>
-      <c r="C200" s="3" t="s">
+      <c r="C200" s="40" t="s">
         <v>365</v>
       </c>
-      <c r="D200" t="s">
+      <c r="D200" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E200" t="s">
-        <v>59</v>
-      </c>
-      <c r="F200" t="s">
+      <c r="E200" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F200" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K200" t="s">
+      <c r="G200" s="42"/>
+      <c r="H200" s="42"/>
+      <c r="I200" s="43"/>
+      <c r="J200" s="43"/>
+      <c r="K200" s="41" t="s">
         <v>366</v>
       </c>
-      <c r="M200" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A201">
+      <c r="L200" s="41"/>
+      <c r="M200" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="50">
         <v>200</v>
       </c>
-      <c r="B201" s="3" t="s">
+      <c r="B201" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="C201" s="3" t="s">
+      <c r="C201" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D201" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="E201" t="s">
-        <v>59</v>
-      </c>
-      <c r="F201" t="s">
+      <c r="E201" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F201" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K201" t="s">
+      <c r="G201" s="38"/>
+      <c r="H201" s="38"/>
+      <c r="I201" s="39"/>
+      <c r="J201" s="39"/>
+      <c r="K201" s="35" t="s">
         <v>369</v>
       </c>
-      <c r="M201" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A202">
+      <c r="L201" s="35"/>
+      <c r="M201" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="51">
         <v>201</v>
       </c>
-      <c r="B202" s="3" t="s">
+      <c r="B202" s="40" t="s">
         <v>370</v>
       </c>
-      <c r="C202" s="3" t="s">
+      <c r="C202" s="40" t="s">
         <v>371</v>
       </c>
-      <c r="D202" t="s">
+      <c r="D202" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E202" t="s">
-        <v>59</v>
-      </c>
-      <c r="F202" t="s">
+      <c r="E202" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F202" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K202" t="s">
+      <c r="G202" s="42"/>
+      <c r="H202" s="42"/>
+      <c r="I202" s="43"/>
+      <c r="J202" s="43"/>
+      <c r="K202" s="41" t="s">
         <v>372</v>
       </c>
-      <c r="M202" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A203">
+      <c r="L202" s="41"/>
+      <c r="M202" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="50">
         <v>202</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B203" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="C203" s="3" t="s">
+      <c r="C203" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="D203" t="s">
+      <c r="D203" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="E203" t="s">
-        <v>59</v>
-      </c>
-      <c r="F203" t="s">
+      <c r="E203" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F203" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K203" t="s">
+      <c r="G203" s="38"/>
+      <c r="H203" s="38"/>
+      <c r="I203" s="39"/>
+      <c r="J203" s="39"/>
+      <c r="K203" s="35" t="s">
         <v>376</v>
       </c>
-      <c r="M203" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="204" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A204">
+      <c r="L203" s="35"/>
+      <c r="M203" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="51">
         <v>203</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="40" t="s">
         <v>377</v>
       </c>
-      <c r="C204" s="3" t="s">
+      <c r="C204" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="D204" t="s">
+      <c r="D204" s="41" t="s">
         <v>375</v>
       </c>
-      <c r="E204" t="s">
-        <v>59</v>
-      </c>
-      <c r="F204" t="s">
+      <c r="E204" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F204" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K204" t="s">
+      <c r="G204" s="42"/>
+      <c r="H204" s="42"/>
+      <c r="I204" s="43"/>
+      <c r="J204" s="43"/>
+      <c r="K204" s="41" t="s">
         <v>376</v>
       </c>
-      <c r="M204" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="205" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A205">
+      <c r="L204" s="41"/>
+      <c r="M204" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="50">
         <v>204</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B205" s="34" t="s">
         <v>379</v>
       </c>
-      <c r="C205" s="3" t="s">
+      <c r="C205" s="34" t="s">
         <v>380</v>
       </c>
-      <c r="D205" t="s">
+      <c r="D205" s="35" t="s">
         <v>375</v>
       </c>
-      <c r="E205" t="s">
-        <v>59</v>
-      </c>
-      <c r="F205" t="s">
+      <c r="E205" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F205" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K205" t="s">
+      <c r="G205" s="38"/>
+      <c r="H205" s="38"/>
+      <c r="I205" s="39"/>
+      <c r="J205" s="39"/>
+      <c r="K205" s="35" t="s">
         <v>381</v>
       </c>
-      <c r="M205" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="206" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A206">
+      <c r="L205" s="35"/>
+      <c r="M205" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="51">
         <v>205</v>
       </c>
-      <c r="B206" s="3" t="s">
+      <c r="B206" s="40" t="s">
         <v>382</v>
       </c>
-      <c r="C206" s="3" t="s">
+      <c r="C206" s="40" t="s">
         <v>383</v>
       </c>
-      <c r="D206" t="s">
+      <c r="D206" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E206" t="s">
-        <v>59</v>
-      </c>
-      <c r="F206" t="s">
+      <c r="E206" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F206" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K206" t="s">
+      <c r="G206" s="42"/>
+      <c r="H206" s="42"/>
+      <c r="I206" s="43"/>
+      <c r="J206" s="43"/>
+      <c r="K206" s="41" t="s">
         <v>384</v>
       </c>
-      <c r="M206" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A207">
+      <c r="L206" s="41"/>
+      <c r="M206" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="50">
         <v>206</v>
       </c>
-      <c r="B207" s="3" t="s">
+      <c r="B207" s="34" t="s">
         <v>385</v>
       </c>
-      <c r="C207" s="3" t="s">
+      <c r="C207" s="34" t="s">
         <v>386</v>
       </c>
-      <c r="D207" t="s">
+      <c r="D207" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="E207" t="s">
-        <v>59</v>
-      </c>
-      <c r="F207" t="s">
+      <c r="E207" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F207" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K207" t="s">
+      <c r="G207" s="38"/>
+      <c r="H207" s="38"/>
+      <c r="I207" s="39"/>
+      <c r="J207" s="39"/>
+      <c r="K207" s="35" t="s">
         <v>376</v>
       </c>
-      <c r="M207" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A208">
+      <c r="L207" s="35"/>
+      <c r="M207" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="51">
         <v>207</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B208" s="40" t="s">
         <v>387</v>
       </c>
-      <c r="C208" s="3" t="s">
+      <c r="C208" s="40" t="s">
         <v>388</v>
       </c>
-      <c r="D208" t="s">
+      <c r="D208" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E208" t="s">
-        <v>59</v>
-      </c>
-      <c r="F208" t="s">
+      <c r="E208" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F208" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K208" t="s">
+      <c r="G208" s="42"/>
+      <c r="H208" s="42"/>
+      <c r="I208" s="43"/>
+      <c r="J208" s="43"/>
+      <c r="K208" s="41" t="s">
         <v>376</v>
       </c>
-      <c r="M208" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="209" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A209">
+      <c r="L208" s="41"/>
+      <c r="M208" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="50">
         <v>208</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="34" t="s">
         <v>389</v>
       </c>
-      <c r="C209" s="3" t="s">
+      <c r="C209" s="34" t="s">
         <v>390</v>
       </c>
-      <c r="D209" t="s">
+      <c r="D209" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="E209" t="s">
-        <v>59</v>
-      </c>
-      <c r="F209" t="s">
+      <c r="E209" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F209" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K209" t="s">
+      <c r="G209" s="38"/>
+      <c r="H209" s="38"/>
+      <c r="I209" s="39"/>
+      <c r="J209" s="39"/>
+      <c r="K209" s="35" t="s">
         <v>391</v>
       </c>
-      <c r="M209" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A210">
+      <c r="L209" s="35"/>
+      <c r="M209" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="51">
         <v>209</v>
       </c>
-      <c r="B210" s="3" t="s">
+      <c r="B210" s="40" t="s">
         <v>392</v>
       </c>
-      <c r="C210" s="3" t="s">
+      <c r="C210" s="40" t="s">
         <v>393</v>
       </c>
-      <c r="D210" t="s">
+      <c r="D210" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="E210" t="s">
-        <v>59</v>
-      </c>
-      <c r="F210" t="s">
+      <c r="E210" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F210" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="K210" t="s">
+      <c r="G210" s="42"/>
+      <c r="H210" s="42"/>
+      <c r="I210" s="43"/>
+      <c r="J210" s="43"/>
+      <c r="K210" s="41" t="s">
         <v>391</v>
       </c>
-      <c r="M210" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A211">
+      <c r="L210" s="41"/>
+      <c r="M210" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="50">
         <v>210</v>
       </c>
-      <c r="B211" s="3" t="s">
+      <c r="B211" s="34" t="s">
         <v>394</v>
       </c>
-      <c r="C211" s="3" t="s">
+      <c r="C211" s="34" t="s">
         <v>395</v>
       </c>
-      <c r="D211" t="s">
+      <c r="D211" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="E211" t="s">
-        <v>59</v>
-      </c>
-      <c r="F211" t="s">
+      <c r="E211" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F211" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K211" t="s">
+      <c r="G211" s="38"/>
+      <c r="H211" s="38"/>
+      <c r="I211" s="39"/>
+      <c r="J211" s="39"/>
+      <c r="K211" s="35" t="s">
         <v>376</v>
       </c>
-      <c r="M211" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A212">
+      <c r="L211" s="35"/>
+      <c r="M211" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="51">
         <v>211</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B212" s="40" t="s">
         <v>396</v>
       </c>
-      <c r="C212" s="3" t="s">
+      <c r="C212" s="40" t="s">
         <v>397</v>
       </c>
-      <c r="D212" t="s">
+      <c r="D212" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="E212" t="s">
-        <v>59</v>
-      </c>
-      <c r="F212" t="s">
+      <c r="E212" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F212" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K212" t="s">
+      <c r="G212" s="42"/>
+      <c r="H212" s="42"/>
+      <c r="I212" s="43"/>
+      <c r="J212" s="43"/>
+      <c r="K212" s="41" t="s">
         <v>350</v>
       </c>
-      <c r="M212" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A213">
+      <c r="L212" s="41"/>
+      <c r="M212" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="50">
         <v>212</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B213" s="34" t="s">
         <v>398</v>
       </c>
-      <c r="C213" s="3" t="s">
+      <c r="C213" s="34" t="s">
         <v>399</v>
       </c>
-      <c r="E213" t="s">
-        <v>59</v>
-      </c>
-      <c r="F213" t="s">
+      <c r="D213" s="35"/>
+      <c r="E213" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F213" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K213" t="s">
+      <c r="G213" s="38"/>
+      <c r="H213" s="38"/>
+      <c r="I213" s="39"/>
+      <c r="J213" s="39"/>
+      <c r="K213" s="35" t="s">
         <v>400</v>
       </c>
-      <c r="M213" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="214" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A214">
+      <c r="L213" s="35"/>
+      <c r="M213" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="51">
         <v>213</v>
       </c>
-      <c r="B214" s="3" t="s">
+      <c r="B214" s="40" t="s">
         <v>401</v>
       </c>
-      <c r="C214" s="3" t="s">
+      <c r="C214" s="40" t="s">
         <v>402</v>
       </c>
-      <c r="D214" t="s">
+      <c r="D214" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="E214" t="s">
-        <v>59</v>
-      </c>
-      <c r="F214" t="s">
+      <c r="E214" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F214" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K214" t="s">
+      <c r="G214" s="42"/>
+      <c r="H214" s="42"/>
+      <c r="I214" s="43"/>
+      <c r="J214" s="43"/>
+      <c r="K214" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="M214" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="215" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A215">
+      <c r="L214" s="41"/>
+      <c r="M214" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="50">
         <v>214</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B215" s="34" t="s">
         <v>403</v>
       </c>
-      <c r="C215" s="3" t="s">
+      <c r="C215" s="34" t="s">
         <v>404</v>
       </c>
-      <c r="D215" t="s">
+      <c r="D215" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="E215" t="s">
-        <v>59</v>
-      </c>
-      <c r="F215" t="s">
+      <c r="E215" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F215" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K215" t="s">
+      <c r="G215" s="38"/>
+      <c r="H215" s="38"/>
+      <c r="I215" s="39"/>
+      <c r="J215" s="39"/>
+      <c r="K215" s="35" t="s">
         <v>405</v>
       </c>
-      <c r="M215" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="216" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A216">
+      <c r="L215" s="35"/>
+      <c r="M215" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="51">
         <v>215</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B216" s="40" t="s">
         <v>406</v>
       </c>
-      <c r="C216" s="3" t="s">
+      <c r="C216" s="40" t="s">
         <v>407</v>
       </c>
-      <c r="D216" t="s">
+      <c r="D216" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E216" t="s">
-        <v>59</v>
-      </c>
-      <c r="F216" t="s">
+      <c r="E216" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F216" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K216" t="s">
+      <c r="G216" s="42"/>
+      <c r="H216" s="42"/>
+      <c r="I216" s="43"/>
+      <c r="J216" s="43"/>
+      <c r="K216" s="41" t="s">
         <v>336</v>
       </c>
-      <c r="M216" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A217">
+      <c r="L216" s="41"/>
+      <c r="M216" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="50">
         <v>216</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="34" t="s">
         <v>408</v>
       </c>
-      <c r="C217" s="3" t="s">
+      <c r="C217" s="34" t="s">
         <v>409</v>
       </c>
-      <c r="D217" t="s">
+      <c r="D217" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="E217" t="s">
-        <v>59</v>
-      </c>
-      <c r="F217" t="s">
+      <c r="E217" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F217" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K217" t="s">
+      <c r="G217" s="38"/>
+      <c r="H217" s="38"/>
+      <c r="I217" s="39"/>
+      <c r="J217" s="39"/>
+      <c r="K217" s="35" t="s">
         <v>350</v>
       </c>
-      <c r="M217" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A218">
+      <c r="L217" s="35"/>
+      <c r="M217" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="51">
         <v>217</v>
       </c>
-      <c r="B218" s="3" t="s">
+      <c r="B218" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="C218" s="3" t="s">
+      <c r="C218" s="40" t="s">
         <v>411</v>
       </c>
-      <c r="D218" t="s">
+      <c r="D218" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E218" t="s">
-        <v>59</v>
-      </c>
-      <c r="F218" t="s">
+      <c r="E218" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F218" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K218" t="s">
+      <c r="G218" s="42"/>
+      <c r="H218" s="42"/>
+      <c r="I218" s="43"/>
+      <c r="J218" s="43"/>
+      <c r="K218" s="41" t="s">
         <v>336</v>
       </c>
-      <c r="M218" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="219" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A219">
+      <c r="L218" s="41"/>
+      <c r="M218" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="50">
         <v>218</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="B219" s="34" t="s">
         <v>412</v>
       </c>
-      <c r="C219" s="3" t="s">
+      <c r="C219" s="34" t="s">
         <v>413</v>
       </c>
-      <c r="D219" t="s">
+      <c r="D219" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="E219" t="s">
-        <v>59</v>
-      </c>
-      <c r="F219" t="s">
+      <c r="E219" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F219" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K219" t="s">
+      <c r="G219" s="38"/>
+      <c r="H219" s="38"/>
+      <c r="I219" s="39"/>
+      <c r="J219" s="39"/>
+      <c r="K219" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="M219" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A220">
+      <c r="L219" s="35"/>
+      <c r="M219" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="51">
         <v>219</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B220" s="40" t="s">
         <v>414</v>
       </c>
-      <c r="C220" s="3" t="s">
+      <c r="C220" s="40" t="s">
         <v>415</v>
       </c>
-      <c r="D220" t="s">
+      <c r="D220" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E220" t="s">
-        <v>59</v>
-      </c>
-      <c r="F220" t="s">
+      <c r="E220" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F220" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K220" t="s">
+      <c r="G220" s="42"/>
+      <c r="H220" s="42"/>
+      <c r="I220" s="43"/>
+      <c r="J220" s="43"/>
+      <c r="K220" s="41" t="s">
         <v>336</v>
       </c>
-      <c r="M220" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A221">
+      <c r="L220" s="41"/>
+      <c r="M220" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="50">
         <v>220</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B221" s="34" t="s">
         <v>416</v>
       </c>
-      <c r="C221" s="3" t="s">
+      <c r="C221" s="34" t="s">
         <v>417</v>
       </c>
-      <c r="D221" t="s">
+      <c r="D221" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="E221" t="s">
-        <v>59</v>
-      </c>
-      <c r="F221" t="s">
+      <c r="E221" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F221" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K221" t="s">
+      <c r="G221" s="38"/>
+      <c r="H221" s="38"/>
+      <c r="I221" s="39"/>
+      <c r="J221" s="39"/>
+      <c r="K221" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="M221" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="222" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A222">
+      <c r="L221" s="35"/>
+      <c r="M221" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="51">
         <v>221</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="B222" s="40" t="s">
         <v>418</v>
       </c>
-      <c r="C222" s="3" t="s">
+      <c r="C222" s="40" t="s">
         <v>419</v>
       </c>
-      <c r="D222" t="s">
+      <c r="D222" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E222" t="s">
-        <v>59</v>
-      </c>
-      <c r="F222" t="s">
+      <c r="E222" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F222" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="K222" t="s">
+      <c r="G222" s="42"/>
+      <c r="H222" s="42"/>
+      <c r="I222" s="43"/>
+      <c r="J222" s="43"/>
+      <c r="K222" s="41" t="s">
         <v>420</v>
       </c>
-      <c r="M222" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="223" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A223">
+      <c r="L222" s="41"/>
+      <c r="M222" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="50">
         <v>222</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B223" s="34" t="s">
         <v>421</v>
       </c>
-      <c r="C223" s="3" t="s">
+      <c r="C223" s="34" t="s">
         <v>422</v>
       </c>
-      <c r="E223" t="s">
-        <v>59</v>
-      </c>
-      <c r="F223" t="s">
+      <c r="D223" s="35"/>
+      <c r="E223" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F223" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K223" t="s">
+      <c r="G223" s="38"/>
+      <c r="H223" s="38"/>
+      <c r="I223" s="39"/>
+      <c r="J223" s="39"/>
+      <c r="K223" s="35" t="s">
         <v>423</v>
       </c>
-      <c r="M223" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A224">
+      <c r="L223" s="35"/>
+      <c r="M223" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="51">
         <v>223</v>
       </c>
-      <c r="B224" s="3" t="s">
+      <c r="B224" s="40" t="s">
         <v>424</v>
       </c>
-      <c r="C224" s="3" t="s">
+      <c r="C224" s="40" t="s">
         <v>425</v>
       </c>
-      <c r="D224" t="s">
+      <c r="D224" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="E224" t="s">
-        <v>59</v>
-      </c>
-      <c r="F224" t="s">
+      <c r="E224" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F224" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K224" t="s">
+      <c r="G224" s="42"/>
+      <c r="H224" s="42"/>
+      <c r="I224" s="43"/>
+      <c r="J224" s="43"/>
+      <c r="K224" s="41" t="s">
         <v>426</v>
       </c>
-      <c r="M224" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A225">
+      <c r="L224" s="41"/>
+      <c r="M224" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="50">
         <v>224</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B225" s="34" t="s">
         <v>427</v>
       </c>
-      <c r="C225" s="3" t="s">
+      <c r="C225" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="D225" t="s">
+      <c r="D225" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="E225" t="s">
-        <v>59</v>
-      </c>
-      <c r="F225" t="s">
+      <c r="E225" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F225" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K225" t="s">
+      <c r="G225" s="38"/>
+      <c r="H225" s="38"/>
+      <c r="I225" s="39"/>
+      <c r="J225" s="39"/>
+      <c r="K225" s="35" t="s">
         <v>426</v>
       </c>
-      <c r="M225" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A226">
+      <c r="L225" s="35"/>
+      <c r="M225" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="51">
         <v>225</v>
       </c>
-      <c r="B226" s="3" t="s">
+      <c r="B226" s="40" t="s">
         <v>429</v>
       </c>
-      <c r="C226" s="3" t="s">
+      <c r="C226" s="40" t="s">
         <v>430</v>
       </c>
-      <c r="D226" t="s">
+      <c r="D226" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="E226" t="s">
+      <c r="E226" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="F226" t="s">
+      <c r="F226" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="H226" s="31">
+      <c r="G226" s="42"/>
+      <c r="H226" s="47">
         <v>46177</v>
       </c>
-      <c r="K226" t="s">
+      <c r="I226" s="43"/>
+      <c r="J226" s="43"/>
+      <c r="K226" s="41" t="s">
         <v>431</v>
       </c>
-      <c r="L226" t="s">
+      <c r="L226" s="41" t="s">
         <v>432</v>
       </c>
-      <c r="M226" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A227">
+      <c r="M226" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="50">
         <v>226</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="B227" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="C227" s="3" t="s">
+      <c r="C227" s="34" t="s">
         <v>434</v>
       </c>
-      <c r="D227" t="s">
+      <c r="D227" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E227" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="F227" t="s">
+      <c r="F227" s="44" t="s">
         <v>313</v>
       </c>
-      <c r="H227" s="31">
+      <c r="G227" s="38"/>
+      <c r="H227" s="48">
         <v>46177</v>
       </c>
-      <c r="K227" t="s">
+      <c r="I227" s="39"/>
+      <c r="J227" s="39"/>
+      <c r="K227" s="35" t="s">
         <v>435</v>
       </c>
-      <c r="L227" t="s">
+      <c r="L227" s="35" t="s">
         <v>432</v>
       </c>
-      <c r="M227" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A228">
+      <c r="M227" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="51">
         <v>227</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B228" s="40" t="s">
         <v>436</v>
       </c>
-      <c r="C228" s="3" t="s">
+      <c r="C228" s="40" t="s">
         <v>437</v>
       </c>
-      <c r="D228" t="s">
+      <c r="D228" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="E228" t="s">
-        <v>59</v>
-      </c>
-      <c r="F228" t="s">
+      <c r="E228" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F228" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K228" t="s">
+      <c r="G228" s="42"/>
+      <c r="H228" s="42"/>
+      <c r="I228" s="43"/>
+      <c r="J228" s="43"/>
+      <c r="K228" s="41" t="s">
         <v>438</v>
       </c>
-      <c r="M228" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A229">
+      <c r="L228" s="41"/>
+      <c r="M228" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="50">
         <v>228</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="B229" s="34" t="s">
         <v>439</v>
       </c>
-      <c r="C229" s="3" t="s">
+      <c r="C229" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="D229" t="s">
+      <c r="D229" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="E229" t="s">
-        <v>59</v>
-      </c>
-      <c r="F229" t="s">
+      <c r="E229" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F229" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K229" t="s">
+      <c r="G229" s="38"/>
+      <c r="H229" s="38"/>
+      <c r="I229" s="39"/>
+      <c r="J229" s="39"/>
+      <c r="K229" s="35" t="s">
         <v>441</v>
       </c>
-      <c r="M229" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A230">
+      <c r="L229" s="35"/>
+      <c r="M229" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="51">
         <v>229</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B230" s="40" t="s">
         <v>442</v>
       </c>
-      <c r="C230" s="3" t="s">
+      <c r="C230" s="40" t="s">
         <v>443</v>
       </c>
-      <c r="D230" t="s">
+      <c r="D230" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="E230" t="s">
-        <v>59</v>
-      </c>
-      <c r="F230" t="s">
+      <c r="E230" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F230" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="H230" s="31">
+      <c r="G230" s="42"/>
+      <c r="H230" s="47">
         <v>46161</v>
       </c>
-      <c r="K230" t="s">
+      <c r="I230" s="43"/>
+      <c r="J230" s="43"/>
+      <c r="K230" s="41" t="s">
         <v>444</v>
       </c>
-      <c r="L230" t="s">
+      <c r="L230" s="41" t="s">
         <v>445</v>
       </c>
-      <c r="M230" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A231">
+      <c r="M230" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="50">
         <v>230</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="34" t="s">
         <v>446</v>
       </c>
-      <c r="C231" s="3" t="s">
+      <c r="C231" s="34" t="s">
         <v>447</v>
       </c>
-      <c r="D231" t="s">
+      <c r="D231" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="E231" t="s">
-        <v>59</v>
-      </c>
-      <c r="F231" t="s">
+      <c r="E231" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F231" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="H231" s="31">
+      <c r="G231" s="38"/>
+      <c r="H231" s="48">
         <v>46175</v>
       </c>
-      <c r="K231" t="s">
+      <c r="I231" s="39"/>
+      <c r="J231" s="39"/>
+      <c r="K231" s="35" t="s">
         <v>444</v>
       </c>
-      <c r="L231" t="s">
+      <c r="L231" s="35" t="s">
         <v>448</v>
       </c>
-      <c r="M231" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="232" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A232">
+      <c r="M231" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="51">
         <v>231</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="40" t="s">
         <v>449</v>
       </c>
-      <c r="C232" s="3" t="s">
+      <c r="C232" s="40" t="s">
         <v>450</v>
       </c>
-      <c r="D232" t="s">
+      <c r="D232" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="E232" t="s">
+      <c r="E232" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="F232" t="s">
+      <c r="F232" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K232" t="s">
+      <c r="G232" s="42"/>
+      <c r="H232" s="42"/>
+      <c r="I232" s="43"/>
+      <c r="J232" s="43"/>
+      <c r="K232" s="41" t="s">
         <v>451</v>
       </c>
-      <c r="L232" t="s">
+      <c r="L232" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="M232" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A233">
+      <c r="M232" s="52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="50">
         <v>232</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="B233" s="34" t="s">
         <v>452</v>
       </c>
-      <c r="C233" s="3" t="s">
+      <c r="C233" s="34" t="s">
         <v>453</v>
       </c>
-      <c r="D233" t="s">
+      <c r="D233" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="E233" t="s">
-        <v>59</v>
-      </c>
-      <c r="F233" t="s">
+      <c r="E233" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F233" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="K233" t="s">
+      <c r="G233" s="38"/>
+      <c r="H233" s="38"/>
+      <c r="I233" s="39"/>
+      <c r="J233" s="39"/>
+      <c r="K233" s="35" t="s">
         <v>451</v>
       </c>
-      <c r="M233" t="s">
+      <c r="L233" s="35"/>
+      <c r="M233" s="52" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A234">
+      <c r="A234" s="53">
         <v>233</v>
       </c>
-      <c r="B234" s="3" t="s">
+      <c r="B234" s="54" t="s">
         <v>454</v>
       </c>
-      <c r="C234" s="3" t="s">
+      <c r="C234" s="54" t="s">
         <v>455</v>
       </c>
-      <c r="D234" t="s">
+      <c r="D234" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="E234" t="s">
+      <c r="E234" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="F234" t="s">
+      <c r="F234" s="57" t="s">
         <v>312</v>
       </c>
-      <c r="H234" s="31">
+      <c r="G234" s="58"/>
+      <c r="H234" s="59">
         <v>46205</v>
       </c>
-      <c r="M234" t="s">
+      <c r="I234" s="60"/>
+      <c r="J234" s="60"/>
+      <c r="K234" s="55"/>
+      <c r="L234" s="55"/>
+      <c r="M234" s="61" t="s">
         <v>308</v>
       </c>
     </row>
@@ -9541,37 +10076,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="21" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="22" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="23" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="23" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="23" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="23" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="24" t="s">
         <v>65</v>
       </c>
     </row>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="3527" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B48112E-A30E-4091-B8E9-DDFCDE58AF1E}"/>
+  <xr:revisionPtr revIDLastSave="3607" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08C817B7-E7A0-4E37-A754-5B328C5601CF}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="502">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -1476,9 +1476,6 @@
     <t>LLR Turkey Stitching problems</t>
   </si>
   <si>
-    <t xml:space="preserve">Check Logs for stitching problems </t>
-  </si>
-  <si>
     <t>OPC integration MTC - Redstone</t>
   </si>
   <si>
@@ -1516,6 +1513,36 @@
   </si>
   <si>
     <t>Create a executable program for Purchasing</t>
+  </si>
+  <si>
+    <t>In progress | Estimation finishing time?</t>
+  </si>
+  <si>
+    <t>MD - Dates?</t>
+  </si>
+  <si>
+    <t>Cibersecurity - Standard</t>
+  </si>
+  <si>
+    <t>Document Cibersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the logs </t>
+  </si>
+  <si>
+    <t>Check Logs for stitching problems use the log and find the root cause</t>
+  </si>
+  <si>
+    <t>LLR Turkey, provide a fixing plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redstone Scoring Camera Flickering </t>
+  </si>
+  <si>
+    <t>Provide an action plan to LLR TK</t>
+  </si>
+  <si>
+    <t>Dignose laser flickering, switch from encoder base to time base and detect if the laser became solid, if so, swap the encoder.</t>
   </si>
 </sst>
 </file>
@@ -2038,7 +2065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -2269,15 +2296,6 @@
     <xf numFmtId="0" fontId="13" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2356,11 +2374,62 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4F7FB"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2460,22 +2529,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF4F7FB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF4F7FB"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2487,6 +2540,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2848,22 +2905,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="79"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="80"/>
+      <c r="C4" s="106"/>
     </row>
     <row r="6" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="78"/>
+      <c r="C6" s="104"/>
     </row>
     <row r="7" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -2890,10 +2947,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="78"/>
+      <c r="C11" s="104"/>
     </row>
     <row r="12" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
@@ -2992,10 +3049,10 @@
       </c>
     </row>
     <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="78" t="s">
+      <c r="B25" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="78"/>
+      <c r="C25" s="104"/>
     </row>
     <row r="26" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
@@ -3046,10 +3103,10 @@
       </c>
     </row>
     <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="78" t="s">
+      <c r="B33" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="78"/>
+      <c r="C33" s="104"/>
     </row>
     <row r="34" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
@@ -3120,7 +3177,7 @@
     <col min="5" max="5" width="20.33203125" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" customWidth="1"/>
     <col min="7" max="7" width="11.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" style="118" customWidth="1"/>
     <col min="9" max="10" width="17.5546875" customWidth="1"/>
     <col min="11" max="11" width="22.33203125" customWidth="1"/>
     <col min="12" max="12" width="44.44140625" customWidth="1"/>
@@ -3150,7 +3207,7 @@
       <c r="G1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="107" t="s">
         <v>24</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -3165,11 +3222,11 @@
       <c r="L1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="106" t="s">
+      <c r="M1" s="103" t="s">
         <v>58</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3193,15 +3250,15 @@
         <v>63</v>
       </c>
       <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
       <c r="K2" s="9"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="105" t="s">
-        <v>64</v>
-      </c>
-      <c r="N2" s="90"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="102" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" s="87"/>
     </row>
     <row r="3" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="68">
@@ -3222,15 +3279,15 @@
         <v>63</v>
       </c>
       <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+      <c r="H3" s="109"/>
       <c r="I3" s="17"/>
       <c r="J3" s="17"/>
       <c r="K3" s="14"/>
-      <c r="L3" s="83"/>
+      <c r="L3" s="80"/>
       <c r="M3" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N3" s="91"/>
+      <c r="N3" s="88"/>
     </row>
     <row r="4" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="68">
@@ -3251,15 +3308,15 @@
         <v>63</v>
       </c>
       <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="H4" s="109"/>
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
       <c r="K4" s="14"/>
-      <c r="L4" s="83"/>
+      <c r="L4" s="80"/>
       <c r="M4" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N4" s="91"/>
+      <c r="N4" s="88"/>
     </row>
     <row r="5" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="68">
@@ -3280,15 +3337,15 @@
         <v>68</v>
       </c>
       <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="H5" s="109"/>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
       <c r="K5" s="14"/>
-      <c r="L5" s="83"/>
+      <c r="L5" s="80"/>
       <c r="M5" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N5" s="91"/>
+      <c r="N5" s="88"/>
     </row>
     <row r="6" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="68">
@@ -3309,15 +3366,15 @@
         <v>68</v>
       </c>
       <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="H6" s="109"/>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
       <c r="K6" s="14"/>
-      <c r="L6" s="83"/>
+      <c r="L6" s="80"/>
       <c r="M6" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="91"/>
+      <c r="N6" s="88"/>
     </row>
     <row r="7" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="68">
@@ -3338,15 +3395,15 @@
         <v>68</v>
       </c>
       <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
+      <c r="H7" s="109"/>
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
       <c r="K7" s="14"/>
-      <c r="L7" s="83"/>
+      <c r="L7" s="80"/>
       <c r="M7" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N7" s="91"/>
+      <c r="N7" s="88"/>
     </row>
     <row r="8" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="68">
@@ -3367,15 +3424,15 @@
         <v>63</v>
       </c>
       <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="H8" s="109"/>
       <c r="I8" s="17"/>
       <c r="J8" s="17"/>
       <c r="K8" s="14"/>
-      <c r="L8" s="83"/>
+      <c r="L8" s="80"/>
       <c r="M8" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N8" s="91"/>
+      <c r="N8" s="88"/>
     </row>
     <row r="9" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="68">
@@ -3390,21 +3447,21 @@
         <v>61</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>75</v>
       </c>
       <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
+      <c r="H9" s="109"/>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="14"/>
-      <c r="L9" s="83"/>
+      <c r="L9" s="80"/>
       <c r="M9" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N9" s="91"/>
+      <c r="N9" s="88"/>
     </row>
     <row r="10" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="68">
@@ -3425,15 +3482,15 @@
         <v>75</v>
       </c>
       <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
+      <c r="H10" s="109"/>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
       <c r="K10" s="14"/>
-      <c r="L10" s="83"/>
+      <c r="L10" s="80"/>
       <c r="M10" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N10" s="91"/>
+      <c r="N10" s="88"/>
     </row>
     <row r="11" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="68">
@@ -3454,15 +3511,15 @@
         <v>68</v>
       </c>
       <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+      <c r="H11" s="109"/>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="14"/>
-      <c r="L11" s="83"/>
+      <c r="L11" s="80"/>
       <c r="M11" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N11" s="91"/>
+      <c r="N11" s="88"/>
     </row>
     <row r="12" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="68">
@@ -3477,21 +3534,21 @@
         <v>79</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>63</v>
       </c>
       <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
+      <c r="H12" s="109"/>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="14"/>
-      <c r="L12" s="83"/>
+      <c r="L12" s="80"/>
       <c r="M12" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N12" s="91"/>
+      <c r="N12" s="88"/>
     </row>
     <row r="13" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="68">
@@ -3512,15 +3569,15 @@
         <v>75</v>
       </c>
       <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
+      <c r="H13" s="109"/>
       <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="14"/>
-      <c r="L13" s="83"/>
+      <c r="L13" s="80"/>
       <c r="M13" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N13" s="91"/>
+      <c r="N13" s="88"/>
     </row>
     <row r="14" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="68">
@@ -3541,15 +3598,15 @@
         <v>68</v>
       </c>
       <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
+      <c r="H14" s="109"/>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="14"/>
-      <c r="L14" s="83"/>
+      <c r="L14" s="80"/>
       <c r="M14" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N14" s="91"/>
+      <c r="N14" s="88"/>
     </row>
     <row r="15" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="68">
@@ -3570,15 +3627,15 @@
         <v>75</v>
       </c>
       <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="H15" s="109"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="14"/>
-      <c r="L15" s="83"/>
+      <c r="L15" s="80"/>
       <c r="M15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N15" s="91"/>
+      <c r="N15" s="88"/>
     </row>
     <row r="16" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="68">
@@ -3599,15 +3656,15 @@
         <v>68</v>
       </c>
       <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
+      <c r="H16" s="109"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="14"/>
-      <c r="L16" s="83"/>
+      <c r="L16" s="80"/>
       <c r="M16" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N16" s="91"/>
+      <c r="N16" s="88"/>
     </row>
     <row r="17" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="68">
@@ -3628,15 +3685,15 @@
         <v>63</v>
       </c>
       <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
+      <c r="H17" s="109"/>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="14"/>
-      <c r="L17" s="83"/>
+      <c r="L17" s="80"/>
       <c r="M17" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N17" s="91"/>
+      <c r="N17" s="88"/>
     </row>
     <row r="18" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="68">
@@ -3657,15 +3714,15 @@
         <v>68</v>
       </c>
       <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
+      <c r="H18" s="109"/>
       <c r="I18" s="17"/>
       <c r="J18" s="17"/>
       <c r="K18" s="14"/>
-      <c r="L18" s="83"/>
+      <c r="L18" s="80"/>
       <c r="M18" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N18" s="91"/>
+      <c r="N18" s="88"/>
     </row>
     <row r="19" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="68">
@@ -3686,15 +3743,15 @@
         <v>68</v>
       </c>
       <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
+      <c r="H19" s="109"/>
       <c r="I19" s="17"/>
       <c r="J19" s="17"/>
       <c r="K19" s="14"/>
-      <c r="L19" s="83"/>
+      <c r="L19" s="80"/>
       <c r="M19" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N19" s="91"/>
+      <c r="N19" s="88"/>
     </row>
     <row r="20" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="68">
@@ -3717,17 +3774,17 @@
         <v>68</v>
       </c>
       <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
+      <c r="H20" s="109"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="14"/>
-      <c r="L20" s="83" t="s">
+      <c r="L20" s="80" t="s">
         <v>90</v>
       </c>
       <c r="M20" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N20" s="91"/>
+      <c r="N20" s="88"/>
     </row>
     <row r="21" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="68">
@@ -3750,15 +3807,15 @@
         <v>68</v>
       </c>
       <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
+      <c r="H21" s="109"/>
       <c r="I21" s="17"/>
       <c r="J21" s="17"/>
       <c r="K21" s="14"/>
-      <c r="L21" s="83"/>
+      <c r="L21" s="80"/>
       <c r="M21" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N21" s="91"/>
+      <c r="N21" s="88"/>
     </row>
     <row r="22" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="68">
@@ -3781,15 +3838,15 @@
         <v>75</v>
       </c>
       <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
+      <c r="H22" s="109"/>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
       <c r="K22" s="14"/>
-      <c r="L22" s="83"/>
+      <c r="L22" s="80"/>
       <c r="M22" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N22" s="91"/>
+      <c r="N22" s="88"/>
     </row>
     <row r="23" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="68">
@@ -3812,15 +3869,15 @@
         <v>75</v>
       </c>
       <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
+      <c r="H23" s="109"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="14"/>
-      <c r="L23" s="83"/>
+      <c r="L23" s="80"/>
       <c r="M23" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N23" s="91"/>
+      <c r="N23" s="88"/>
     </row>
     <row r="24" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="68">
@@ -3843,15 +3900,15 @@
         <v>63</v>
       </c>
       <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
+      <c r="H24" s="109"/>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="83"/>
+      <c r="L24" s="80"/>
       <c r="M24" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N24" s="91"/>
+      <c r="N24" s="88"/>
     </row>
     <row r="25" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="68">
@@ -3874,15 +3931,15 @@
         <v>75</v>
       </c>
       <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
+      <c r="H25" s="109"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="14"/>
-      <c r="L25" s="83"/>
+      <c r="L25" s="80"/>
       <c r="M25" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N25" s="91"/>
+      <c r="N25" s="88"/>
     </row>
     <row r="26" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="68">
@@ -3905,15 +3962,15 @@
         <v>63</v>
       </c>
       <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
+      <c r="H26" s="109"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
       <c r="K26" s="14"/>
-      <c r="L26" s="83"/>
+      <c r="L26" s="80"/>
       <c r="M26" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N26" s="91"/>
+      <c r="N26" s="88"/>
     </row>
     <row r="27" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="68">
@@ -3936,15 +3993,15 @@
         <v>63</v>
       </c>
       <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
+      <c r="H27" s="109"/>
       <c r="I27" s="17"/>
       <c r="J27" s="17"/>
       <c r="K27" s="14"/>
-      <c r="L27" s="83"/>
+      <c r="L27" s="80"/>
       <c r="M27" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N27" s="91"/>
+      <c r="N27" s="88"/>
     </row>
     <row r="28" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="68">
@@ -3967,15 +4024,15 @@
         <v>63</v>
       </c>
       <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
+      <c r="H28" s="109"/>
       <c r="I28" s="17"/>
       <c r="J28" s="17"/>
       <c r="K28" s="14"/>
-      <c r="L28" s="83"/>
+      <c r="L28" s="80"/>
       <c r="M28" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N28" s="91"/>
+      <c r="N28" s="88"/>
     </row>
     <row r="29" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="68">
@@ -3998,15 +4055,15 @@
         <v>68</v>
       </c>
       <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
+      <c r="H29" s="109"/>
       <c r="I29" s="17"/>
       <c r="J29" s="17"/>
       <c r="K29" s="14"/>
-      <c r="L29" s="83"/>
+      <c r="L29" s="80"/>
       <c r="M29" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N29" s="91"/>
+      <c r="N29" s="88"/>
     </row>
     <row r="30" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="68">
@@ -4029,15 +4086,15 @@
         <v>68</v>
       </c>
       <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
+      <c r="H30" s="109"/>
       <c r="I30" s="17"/>
       <c r="J30" s="17"/>
       <c r="K30" s="14"/>
-      <c r="L30" s="83"/>
+      <c r="L30" s="80"/>
       <c r="M30" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N30" s="91"/>
+      <c r="N30" s="88"/>
     </row>
     <row r="31" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="68">
@@ -4056,15 +4113,15 @@
         <v>68</v>
       </c>
       <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
+      <c r="H31" s="109"/>
       <c r="I31" s="17"/>
       <c r="J31" s="17"/>
       <c r="K31" s="14"/>
-      <c r="L31" s="83"/>
+      <c r="L31" s="80"/>
       <c r="M31" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N31" s="91"/>
+      <c r="N31" s="88"/>
     </row>
     <row r="32" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="68">
@@ -4087,17 +4144,17 @@
         <v>68</v>
       </c>
       <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
+      <c r="H32" s="109"/>
       <c r="I32" s="17"/>
       <c r="J32" s="17"/>
       <c r="K32" s="14"/>
-      <c r="L32" s="83" t="s">
+      <c r="L32" s="80" t="s">
         <v>477</v>
       </c>
       <c r="M32" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N32" s="91"/>
+      <c r="N32" s="88"/>
     </row>
     <row r="33" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="68">
@@ -4120,17 +4177,17 @@
         <v>63</v>
       </c>
       <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
+      <c r="H33" s="109"/>
       <c r="I33" s="17"/>
       <c r="J33" s="17"/>
       <c r="K33" s="14"/>
-      <c r="L33" s="83" t="s">
+      <c r="L33" s="80" t="s">
         <v>110</v>
       </c>
       <c r="M33" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N33" s="91"/>
+      <c r="N33" s="88"/>
     </row>
     <row r="34" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="68">
@@ -4153,17 +4210,17 @@
         <v>63</v>
       </c>
       <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
+      <c r="H34" s="109"/>
       <c r="I34" s="17"/>
       <c r="J34" s="17"/>
       <c r="K34" s="14"/>
-      <c r="L34" s="83" t="s">
+      <c r="L34" s="80" t="s">
         <v>112</v>
       </c>
       <c r="M34" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N34" s="91"/>
+      <c r="N34" s="88"/>
     </row>
     <row r="35" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="68">
@@ -4184,15 +4241,15 @@
         <v>75</v>
       </c>
       <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
+      <c r="H35" s="109"/>
       <c r="I35" s="17"/>
       <c r="J35" s="17"/>
       <c r="K35" s="14"/>
-      <c r="L35" s="83"/>
+      <c r="L35" s="80"/>
       <c r="M35" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N35" s="91"/>
+      <c r="N35" s="88"/>
     </row>
     <row r="36" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="68">
@@ -4215,7 +4272,7 @@
         <v>63</v>
       </c>
       <c r="G36" s="15"/>
-      <c r="H36" s="15">
+      <c r="H36" s="109">
         <v>40</v>
       </c>
       <c r="I36" s="17">
@@ -4225,11 +4282,11 @@
         <v>46142</v>
       </c>
       <c r="K36" s="14"/>
-      <c r="L36" s="83"/>
+      <c r="L36" s="80"/>
       <c r="M36" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N36" s="91"/>
+      <c r="N36" s="88"/>
     </row>
     <row r="37" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="68">
@@ -4248,15 +4305,15 @@
         <v>68</v>
       </c>
       <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
+      <c r="H37" s="109"/>
       <c r="I37" s="17"/>
       <c r="J37" s="17"/>
       <c r="K37" s="14"/>
-      <c r="L37" s="83"/>
+      <c r="L37" s="80"/>
       <c r="M37" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N37" s="91"/>
+      <c r="N37" s="88"/>
     </row>
     <row r="38" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="68">
@@ -4279,15 +4336,15 @@
         <v>68</v>
       </c>
       <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
+      <c r="H38" s="109"/>
       <c r="I38" s="17"/>
       <c r="J38" s="17"/>
       <c r="K38" s="14"/>
-      <c r="L38" s="83"/>
+      <c r="L38" s="80"/>
       <c r="M38" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N38" s="91"/>
+      <c r="N38" s="88"/>
     </row>
     <row r="39" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="68">
@@ -4308,15 +4365,15 @@
         <v>68</v>
       </c>
       <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
+      <c r="H39" s="109"/>
       <c r="I39" s="17"/>
       <c r="J39" s="17"/>
       <c r="K39" s="14"/>
-      <c r="L39" s="83"/>
+      <c r="L39" s="80"/>
       <c r="M39" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N39" s="91"/>
+      <c r="N39" s="88"/>
     </row>
     <row r="40" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="68">
@@ -4337,15 +4394,15 @@
         <v>68</v>
       </c>
       <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
+      <c r="H40" s="109"/>
       <c r="I40" s="17"/>
       <c r="J40" s="17"/>
       <c r="K40" s="14"/>
-      <c r="L40" s="83"/>
+      <c r="L40" s="80"/>
       <c r="M40" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N40" s="91"/>
+      <c r="N40" s="88"/>
     </row>
     <row r="41" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="68">
@@ -4366,15 +4423,15 @@
         <v>75</v>
       </c>
       <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
+      <c r="H41" s="109"/>
       <c r="I41" s="17"/>
       <c r="J41" s="17"/>
       <c r="K41" s="14"/>
-      <c r="L41" s="83"/>
+      <c r="L41" s="80"/>
       <c r="M41" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N41" s="91"/>
+      <c r="N41" s="88"/>
     </row>
     <row r="42" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="68">
@@ -4395,15 +4452,15 @@
         <v>75</v>
       </c>
       <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
+      <c r="H42" s="109"/>
       <c r="I42" s="17"/>
       <c r="J42" s="17"/>
       <c r="K42" s="14"/>
-      <c r="L42" s="83"/>
+      <c r="L42" s="80"/>
       <c r="M42" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N42" s="91"/>
+      <c r="N42" s="88"/>
     </row>
     <row r="43" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="68">
@@ -4424,15 +4481,15 @@
         <v>68</v>
       </c>
       <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
+      <c r="H43" s="109"/>
       <c r="I43" s="17"/>
       <c r="J43" s="17"/>
       <c r="K43" s="14"/>
-      <c r="L43" s="83"/>
+      <c r="L43" s="80"/>
       <c r="M43" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N43" s="91"/>
+      <c r="N43" s="88"/>
     </row>
     <row r="44" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="68">
@@ -4453,15 +4510,15 @@
         <v>68</v>
       </c>
       <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
+      <c r="H44" s="109"/>
       <c r="I44" s="17"/>
       <c r="J44" s="17"/>
       <c r="K44" s="14"/>
-      <c r="L44" s="83"/>
+      <c r="L44" s="80"/>
       <c r="M44" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N44" s="91"/>
+      <c r="N44" s="88"/>
     </row>
     <row r="45" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="68">
@@ -4482,15 +4539,15 @@
         <v>75</v>
       </c>
       <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
+      <c r="H45" s="109"/>
       <c r="I45" s="17"/>
       <c r="J45" s="17"/>
       <c r="K45" s="14"/>
-      <c r="L45" s="83"/>
+      <c r="L45" s="80"/>
       <c r="M45" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N45" s="91"/>
+      <c r="N45" s="88"/>
     </row>
     <row r="46" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="68">
@@ -4511,15 +4568,15 @@
         <v>68</v>
       </c>
       <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
+      <c r="H46" s="109"/>
       <c r="I46" s="17"/>
       <c r="J46" s="17"/>
       <c r="K46" s="14"/>
-      <c r="L46" s="83"/>
+      <c r="L46" s="80"/>
       <c r="M46" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N46" s="91"/>
+      <c r="N46" s="88"/>
     </row>
     <row r="47" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="68">
@@ -4540,15 +4597,15 @@
         <v>68</v>
       </c>
       <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
+      <c r="H47" s="109"/>
       <c r="I47" s="17"/>
       <c r="J47" s="17"/>
       <c r="K47" s="14"/>
-      <c r="L47" s="83"/>
+      <c r="L47" s="80"/>
       <c r="M47" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N47" s="91"/>
+      <c r="N47" s="88"/>
     </row>
     <row r="48" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="68">
@@ -4569,15 +4626,15 @@
         <v>68</v>
       </c>
       <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
+      <c r="H48" s="109"/>
       <c r="I48" s="17"/>
       <c r="J48" s="17"/>
       <c r="K48" s="14"/>
-      <c r="L48" s="83"/>
+      <c r="L48" s="80"/>
       <c r="M48" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N48" s="91"/>
+      <c r="N48" s="88"/>
     </row>
     <row r="49" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="68">
@@ -4598,15 +4655,15 @@
         <v>68</v>
       </c>
       <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
+      <c r="H49" s="109"/>
       <c r="I49" s="17"/>
       <c r="J49" s="17"/>
       <c r="K49" s="14"/>
-      <c r="L49" s="83"/>
+      <c r="L49" s="80"/>
       <c r="M49" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N49" s="91"/>
+      <c r="N49" s="88"/>
     </row>
     <row r="50" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="68">
@@ -4627,15 +4684,15 @@
         <v>68</v>
       </c>
       <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
+      <c r="H50" s="109"/>
       <c r="I50" s="17"/>
       <c r="J50" s="17"/>
       <c r="K50" s="14"/>
-      <c r="L50" s="83"/>
+      <c r="L50" s="80"/>
       <c r="M50" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N50" s="91"/>
+      <c r="N50" s="88"/>
     </row>
     <row r="51" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="68">
@@ -4656,15 +4713,15 @@
         <v>75</v>
       </c>
       <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
+      <c r="H51" s="109"/>
       <c r="I51" s="17"/>
       <c r="J51" s="17"/>
       <c r="K51" s="14"/>
-      <c r="L51" s="83"/>
+      <c r="L51" s="80"/>
       <c r="M51" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N51" s="91"/>
+      <c r="N51" s="88"/>
     </row>
     <row r="52" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="68">
@@ -4685,15 +4742,15 @@
         <v>75</v>
       </c>
       <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
+      <c r="H52" s="109"/>
       <c r="I52" s="17"/>
       <c r="J52" s="17"/>
       <c r="K52" s="14"/>
-      <c r="L52" s="83"/>
+      <c r="L52" s="80"/>
       <c r="M52" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N52" s="91"/>
+      <c r="N52" s="88"/>
     </row>
     <row r="53" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="68">
@@ -4716,15 +4773,15 @@
         <v>75</v>
       </c>
       <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
+      <c r="H53" s="109"/>
       <c r="I53" s="17"/>
       <c r="J53" s="17"/>
       <c r="K53" s="14"/>
-      <c r="L53" s="83"/>
+      <c r="L53" s="80"/>
       <c r="M53" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N53" s="91"/>
+      <c r="N53" s="88"/>
     </row>
     <row r="54" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="68">
@@ -4745,15 +4802,15 @@
         <v>75</v>
       </c>
       <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
+      <c r="H54" s="109"/>
       <c r="I54" s="17"/>
       <c r="J54" s="17"/>
       <c r="K54" s="14"/>
-      <c r="L54" s="83"/>
+      <c r="L54" s="80"/>
       <c r="M54" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N54" s="91"/>
+      <c r="N54" s="88"/>
     </row>
     <row r="55" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="68">
@@ -4774,15 +4831,15 @@
         <v>75</v>
       </c>
       <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
+      <c r="H55" s="109"/>
       <c r="I55" s="17"/>
       <c r="J55" s="17"/>
       <c r="K55" s="14"/>
-      <c r="L55" s="83"/>
+      <c r="L55" s="80"/>
       <c r="M55" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N55" s="91"/>
+      <c r="N55" s="88"/>
     </row>
     <row r="56" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="68">
@@ -4803,15 +4860,15 @@
         <v>68</v>
       </c>
       <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
+      <c r="H56" s="109"/>
       <c r="I56" s="17"/>
       <c r="J56" s="17"/>
       <c r="K56" s="14"/>
-      <c r="L56" s="83"/>
+      <c r="L56" s="80"/>
       <c r="M56" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N56" s="91"/>
+      <c r="N56" s="88"/>
     </row>
     <row r="57" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="68">
@@ -4832,15 +4889,15 @@
         <v>75</v>
       </c>
       <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
+      <c r="H57" s="109"/>
       <c r="I57" s="17"/>
       <c r="J57" s="17"/>
       <c r="K57" s="14"/>
-      <c r="L57" s="83"/>
+      <c r="L57" s="80"/>
       <c r="M57" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N57" s="91"/>
+      <c r="N57" s="88"/>
     </row>
     <row r="58" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="68">
@@ -4861,15 +4918,15 @@
         <v>68</v>
       </c>
       <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
+      <c r="H58" s="109"/>
       <c r="I58" s="17"/>
       <c r="J58" s="17"/>
       <c r="K58" s="14"/>
-      <c r="L58" s="83"/>
+      <c r="L58" s="80"/>
       <c r="M58" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N58" s="91"/>
+      <c r="N58" s="88"/>
     </row>
     <row r="59" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="68">
@@ -4890,15 +4947,15 @@
         <v>63</v>
       </c>
       <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
+      <c r="H59" s="109"/>
       <c r="I59" s="17"/>
       <c r="J59" s="17"/>
       <c r="K59" s="14"/>
-      <c r="L59" s="83"/>
+      <c r="L59" s="80"/>
       <c r="M59" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N59" s="91"/>
+      <c r="N59" s="88"/>
     </row>
     <row r="60" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="68">
@@ -4919,15 +4976,15 @@
         <v>63</v>
       </c>
       <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
+      <c r="H60" s="109"/>
       <c r="I60" s="17"/>
       <c r="J60" s="17"/>
       <c r="K60" s="14"/>
-      <c r="L60" s="83"/>
+      <c r="L60" s="80"/>
       <c r="M60" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N60" s="91"/>
+      <c r="N60" s="88"/>
     </row>
     <row r="61" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="68">
@@ -4948,15 +5005,15 @@
         <v>75</v>
       </c>
       <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
+      <c r="H61" s="109"/>
       <c r="I61" s="17"/>
       <c r="J61" s="17"/>
       <c r="K61" s="14"/>
-      <c r="L61" s="83"/>
+      <c r="L61" s="80"/>
       <c r="M61" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N61" s="91"/>
+      <c r="N61" s="88"/>
     </row>
     <row r="62" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="68">
@@ -4977,15 +5034,15 @@
         <v>68</v>
       </c>
       <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
+      <c r="H62" s="109"/>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
       <c r="K62" s="14"/>
-      <c r="L62" s="83"/>
+      <c r="L62" s="80"/>
       <c r="M62" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N62" s="91"/>
+      <c r="N62" s="88"/>
     </row>
     <row r="63" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="68">
@@ -5006,15 +5063,15 @@
         <v>63</v>
       </c>
       <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
+      <c r="H63" s="109"/>
       <c r="I63" s="17"/>
       <c r="J63" s="17"/>
       <c r="K63" s="14"/>
-      <c r="L63" s="83"/>
+      <c r="L63" s="80"/>
       <c r="M63" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N63" s="91"/>
+      <c r="N63" s="88"/>
     </row>
     <row r="64" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="68">
@@ -5035,15 +5092,15 @@
         <v>63</v>
       </c>
       <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
+      <c r="H64" s="109"/>
       <c r="I64" s="17"/>
       <c r="J64" s="17"/>
       <c r="K64" s="14"/>
-      <c r="L64" s="83"/>
+      <c r="L64" s="80"/>
       <c r="M64" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N64" s="91"/>
+      <c r="N64" s="88"/>
     </row>
     <row r="65" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="68">
@@ -5064,15 +5121,15 @@
         <v>63</v>
       </c>
       <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
+      <c r="H65" s="109"/>
       <c r="I65" s="17"/>
       <c r="J65" s="17"/>
       <c r="K65" s="14"/>
-      <c r="L65" s="83"/>
+      <c r="L65" s="80"/>
       <c r="M65" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N65" s="91"/>
+      <c r="N65" s="88"/>
     </row>
     <row r="66" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="68">
@@ -5093,15 +5150,15 @@
         <v>68</v>
       </c>
       <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
+      <c r="H66" s="109"/>
       <c r="I66" s="17"/>
       <c r="J66" s="17"/>
       <c r="K66" s="14"/>
-      <c r="L66" s="83"/>
+      <c r="L66" s="80"/>
       <c r="M66" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N66" s="91"/>
+      <c r="N66" s="88"/>
     </row>
     <row r="67" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="68">
@@ -5120,15 +5177,15 @@
         <v>75</v>
       </c>
       <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
+      <c r="H67" s="109"/>
       <c r="I67" s="17"/>
       <c r="J67" s="17"/>
       <c r="K67" s="14"/>
-      <c r="L67" s="83"/>
+      <c r="L67" s="80"/>
       <c r="M67" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N67" s="91"/>
+      <c r="N67" s="88"/>
     </row>
     <row r="68" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="68">
@@ -5149,15 +5206,15 @@
         <v>63</v>
       </c>
       <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
+      <c r="H68" s="109"/>
       <c r="I68" s="17"/>
       <c r="J68" s="17"/>
       <c r="K68" s="14"/>
-      <c r="L68" s="83"/>
+      <c r="L68" s="80"/>
       <c r="M68" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N68" s="91"/>
+      <c r="N68" s="88"/>
     </row>
     <row r="69" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="68">
@@ -5178,15 +5235,15 @@
         <v>68</v>
       </c>
       <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
+      <c r="H69" s="109"/>
       <c r="I69" s="17"/>
       <c r="J69" s="17"/>
       <c r="K69" s="14"/>
-      <c r="L69" s="83"/>
+      <c r="L69" s="80"/>
       <c r="M69" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N69" s="91"/>
+      <c r="N69" s="88"/>
     </row>
     <row r="70" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="68">
@@ -5205,15 +5262,15 @@
         <v>75</v>
       </c>
       <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
+      <c r="H70" s="109"/>
       <c r="I70" s="17"/>
       <c r="J70" s="17"/>
       <c r="K70" s="14"/>
-      <c r="L70" s="83"/>
+      <c r="L70" s="80"/>
       <c r="M70" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N70" s="91"/>
+      <c r="N70" s="88"/>
     </row>
     <row r="71" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="68">
@@ -5234,15 +5291,15 @@
         <v>75</v>
       </c>
       <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
+      <c r="H71" s="109"/>
       <c r="I71" s="17"/>
       <c r="J71" s="17"/>
       <c r="K71" s="14"/>
-      <c r="L71" s="83"/>
+      <c r="L71" s="80"/>
       <c r="M71" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N71" s="91"/>
+      <c r="N71" s="88"/>
     </row>
     <row r="72" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="68">
@@ -5263,15 +5320,15 @@
         <v>63</v>
       </c>
       <c r="G72" s="15"/>
-      <c r="H72" s="15"/>
+      <c r="H72" s="109"/>
       <c r="I72" s="17"/>
       <c r="J72" s="17"/>
       <c r="K72" s="14"/>
-      <c r="L72" s="83"/>
+      <c r="L72" s="80"/>
       <c r="M72" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N72" s="91"/>
+      <c r="N72" s="88"/>
     </row>
     <row r="73" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="68">
@@ -5292,15 +5349,15 @@
         <v>63</v>
       </c>
       <c r="G73" s="15"/>
-      <c r="H73" s="15"/>
+      <c r="H73" s="109"/>
       <c r="I73" s="17"/>
       <c r="J73" s="17"/>
       <c r="K73" s="14"/>
-      <c r="L73" s="83"/>
+      <c r="L73" s="80"/>
       <c r="M73" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N73" s="91"/>
+      <c r="N73" s="88"/>
     </row>
     <row r="74" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="68">
@@ -5321,15 +5378,15 @@
         <v>75</v>
       </c>
       <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
+      <c r="H74" s="109"/>
       <c r="I74" s="17"/>
       <c r="J74" s="17"/>
       <c r="K74" s="14"/>
-      <c r="L74" s="83"/>
+      <c r="L74" s="80"/>
       <c r="M74" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N74" s="91"/>
+      <c r="N74" s="88"/>
     </row>
     <row r="75" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="68">
@@ -5348,15 +5405,15 @@
         <v>75</v>
       </c>
       <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
+      <c r="H75" s="109"/>
       <c r="I75" s="17"/>
       <c r="J75" s="17"/>
       <c r="K75" s="14"/>
-      <c r="L75" s="83"/>
+      <c r="L75" s="80"/>
       <c r="M75" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N75" s="91"/>
+      <c r="N75" s="88"/>
     </row>
     <row r="76" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="68">
@@ -5377,15 +5434,15 @@
         <v>68</v>
       </c>
       <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
+      <c r="H76" s="109"/>
       <c r="I76" s="17"/>
       <c r="J76" s="17"/>
       <c r="K76" s="14"/>
-      <c r="L76" s="83"/>
+      <c r="L76" s="80"/>
       <c r="M76" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N76" s="91"/>
+      <c r="N76" s="88"/>
     </row>
     <row r="77" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="68">
@@ -5406,15 +5463,15 @@
         <v>68</v>
       </c>
       <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
+      <c r="H77" s="109"/>
       <c r="I77" s="17"/>
       <c r="J77" s="17"/>
       <c r="K77" s="14"/>
-      <c r="L77" s="83"/>
+      <c r="L77" s="80"/>
       <c r="M77" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N77" s="91"/>
+      <c r="N77" s="88"/>
     </row>
     <row r="78" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="68">
@@ -5435,15 +5492,15 @@
         <v>75</v>
       </c>
       <c r="G78" s="15"/>
-      <c r="H78" s="15"/>
+      <c r="H78" s="109"/>
       <c r="I78" s="17"/>
       <c r="J78" s="17"/>
       <c r="K78" s="14"/>
-      <c r="L78" s="83"/>
+      <c r="L78" s="80"/>
       <c r="M78" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N78" s="91"/>
+      <c r="N78" s="88"/>
     </row>
     <row r="79" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="68">
@@ -5464,15 +5521,15 @@
         <v>75</v>
       </c>
       <c r="G79" s="15"/>
-      <c r="H79" s="15"/>
+      <c r="H79" s="109"/>
       <c r="I79" s="17"/>
       <c r="J79" s="17"/>
       <c r="K79" s="14"/>
-      <c r="L79" s="83"/>
+      <c r="L79" s="80"/>
       <c r="M79" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N79" s="91"/>
+      <c r="N79" s="88"/>
     </row>
     <row r="80" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="68">
@@ -5493,15 +5550,15 @@
         <v>68</v>
       </c>
       <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
+      <c r="H80" s="109"/>
       <c r="I80" s="17"/>
       <c r="J80" s="17"/>
       <c r="K80" s="14"/>
-      <c r="L80" s="83"/>
+      <c r="L80" s="80"/>
       <c r="M80" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N80" s="91"/>
+      <c r="N80" s="88"/>
     </row>
     <row r="81" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="68">
@@ -5522,15 +5579,15 @@
         <v>63</v>
       </c>
       <c r="G81" s="15"/>
-      <c r="H81" s="15"/>
+      <c r="H81" s="109"/>
       <c r="I81" s="17"/>
       <c r="J81" s="17"/>
       <c r="K81" s="14"/>
-      <c r="L81" s="83"/>
+      <c r="L81" s="80"/>
       <c r="M81" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N81" s="91"/>
+      <c r="N81" s="88"/>
     </row>
     <row r="82" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="68">
@@ -5551,15 +5608,15 @@
         <v>63</v>
       </c>
       <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
+      <c r="H82" s="109"/>
       <c r="I82" s="17"/>
       <c r="J82" s="17"/>
       <c r="K82" s="14"/>
-      <c r="L82" s="83"/>
+      <c r="L82" s="80"/>
       <c r="M82" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N82" s="91"/>
+      <c r="N82" s="88"/>
     </row>
     <row r="83" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="68">
@@ -5580,15 +5637,15 @@
         <v>75</v>
       </c>
       <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
+      <c r="H83" s="109"/>
       <c r="I83" s="17"/>
       <c r="J83" s="17"/>
       <c r="K83" s="14"/>
-      <c r="L83" s="83"/>
+      <c r="L83" s="80"/>
       <c r="M83" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N83" s="91"/>
+      <c r="N83" s="88"/>
     </row>
     <row r="84" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="68">
@@ -5609,15 +5666,15 @@
         <v>75</v>
       </c>
       <c r="G84" s="15"/>
-      <c r="H84" s="15"/>
+      <c r="H84" s="109"/>
       <c r="I84" s="17"/>
       <c r="J84" s="17"/>
       <c r="K84" s="14"/>
-      <c r="L84" s="83"/>
+      <c r="L84" s="80"/>
       <c r="M84" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N84" s="91"/>
+      <c r="N84" s="88"/>
     </row>
     <row r="85" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="68">
@@ -5638,15 +5695,15 @@
         <v>75</v>
       </c>
       <c r="G85" s="15"/>
-      <c r="H85" s="15"/>
+      <c r="H85" s="109"/>
       <c r="I85" s="17"/>
       <c r="J85" s="17"/>
       <c r="K85" s="14"/>
-      <c r="L85" s="83"/>
+      <c r="L85" s="80"/>
       <c r="M85" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N85" s="91"/>
+      <c r="N85" s="88"/>
     </row>
     <row r="86" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="68">
@@ -5667,15 +5724,15 @@
         <v>75</v>
       </c>
       <c r="G86" s="15"/>
-      <c r="H86" s="15"/>
+      <c r="H86" s="109"/>
       <c r="I86" s="17"/>
       <c r="J86" s="17"/>
       <c r="K86" s="14"/>
-      <c r="L86" s="83"/>
+      <c r="L86" s="80"/>
       <c r="M86" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N86" s="91"/>
+      <c r="N86" s="88"/>
     </row>
     <row r="87" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="68">
@@ -5694,15 +5751,15 @@
         <v>63</v>
       </c>
       <c r="G87" s="15"/>
-      <c r="H87" s="15"/>
+      <c r="H87" s="109"/>
       <c r="I87" s="17"/>
       <c r="J87" s="17"/>
       <c r="K87" s="14"/>
-      <c r="L87" s="83"/>
+      <c r="L87" s="80"/>
       <c r="M87" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N87" s="91"/>
+      <c r="N87" s="88"/>
     </row>
     <row r="88" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="68">
@@ -5723,15 +5780,15 @@
         <v>75</v>
       </c>
       <c r="G88" s="15"/>
-      <c r="H88" s="15"/>
+      <c r="H88" s="109"/>
       <c r="I88" s="17"/>
       <c r="J88" s="17"/>
       <c r="K88" s="14"/>
-      <c r="L88" s="83"/>
+      <c r="L88" s="80"/>
       <c r="M88" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N88" s="91"/>
+      <c r="N88" s="88"/>
     </row>
     <row r="89" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="68">
@@ -5754,15 +5811,15 @@
         <v>68</v>
       </c>
       <c r="G89" s="15"/>
-      <c r="H89" s="15"/>
+      <c r="H89" s="109"/>
       <c r="I89" s="17"/>
       <c r="J89" s="17"/>
       <c r="K89" s="14"/>
-      <c r="L89" s="83"/>
+      <c r="L89" s="80"/>
       <c r="M89" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N89" s="91"/>
+      <c r="N89" s="88"/>
     </row>
     <row r="90" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="68">
@@ -5785,15 +5842,15 @@
         <v>75</v>
       </c>
       <c r="G90" s="15"/>
-      <c r="H90" s="15"/>
+      <c r="H90" s="109"/>
       <c r="I90" s="17"/>
       <c r="J90" s="17"/>
       <c r="K90" s="14"/>
-      <c r="L90" s="83"/>
+      <c r="L90" s="80"/>
       <c r="M90" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N90" s="91"/>
+      <c r="N90" s="88"/>
     </row>
     <row r="91" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="68">
@@ -5816,15 +5873,15 @@
         <v>68</v>
       </c>
       <c r="G91" s="15"/>
-      <c r="H91" s="15"/>
+      <c r="H91" s="109"/>
       <c r="I91" s="17"/>
       <c r="J91" s="17"/>
       <c r="K91" s="14"/>
-      <c r="L91" s="83"/>
+      <c r="L91" s="80"/>
       <c r="M91" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N91" s="91"/>
+      <c r="N91" s="88"/>
     </row>
     <row r="92" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="68">
@@ -5847,15 +5904,15 @@
         <v>75</v>
       </c>
       <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
+      <c r="H92" s="109"/>
       <c r="I92" s="17"/>
       <c r="J92" s="17"/>
       <c r="K92" s="14"/>
-      <c r="L92" s="83"/>
+      <c r="L92" s="80"/>
       <c r="M92" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N92" s="91"/>
+      <c r="N92" s="88"/>
     </row>
     <row r="93" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="68">
@@ -5876,15 +5933,15 @@
         <v>63</v>
       </c>
       <c r="G93" s="15"/>
-      <c r="H93" s="15"/>
+      <c r="H93" s="109"/>
       <c r="I93" s="17"/>
       <c r="J93" s="17"/>
       <c r="K93" s="14"/>
-      <c r="L93" s="83"/>
+      <c r="L93" s="80"/>
       <c r="M93" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N93" s="91"/>
+      <c r="N93" s="88"/>
     </row>
     <row r="94" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="68">
@@ -5907,15 +5964,15 @@
         <v>75</v>
       </c>
       <c r="G94" s="15"/>
-      <c r="H94" s="15"/>
+      <c r="H94" s="109"/>
       <c r="I94" s="17"/>
       <c r="J94" s="17"/>
       <c r="K94" s="14"/>
-      <c r="L94" s="83"/>
+      <c r="L94" s="80"/>
       <c r="M94" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N94" s="91"/>
+      <c r="N94" s="88"/>
     </row>
     <row r="95" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="68">
@@ -5936,15 +5993,15 @@
         <v>68</v>
       </c>
       <c r="G95" s="15"/>
-      <c r="H95" s="15"/>
+      <c r="H95" s="109"/>
       <c r="I95" s="17"/>
       <c r="J95" s="17"/>
       <c r="K95" s="14"/>
-      <c r="L95" s="83"/>
+      <c r="L95" s="80"/>
       <c r="M95" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N95" s="91"/>
+      <c r="N95" s="88"/>
     </row>
     <row r="96" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="68">
@@ -5965,15 +6022,15 @@
         <v>68</v>
       </c>
       <c r="G96" s="15"/>
-      <c r="H96" s="15"/>
+      <c r="H96" s="109"/>
       <c r="I96" s="17"/>
       <c r="J96" s="17"/>
       <c r="K96" s="14"/>
-      <c r="L96" s="83"/>
+      <c r="L96" s="80"/>
       <c r="M96" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N96" s="91"/>
+      <c r="N96" s="88"/>
     </row>
     <row r="97" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="68">
@@ -5994,15 +6051,15 @@
         <v>68</v>
       </c>
       <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
+      <c r="H97" s="109"/>
       <c r="I97" s="17"/>
       <c r="J97" s="17"/>
       <c r="K97" s="14"/>
-      <c r="L97" s="83"/>
+      <c r="L97" s="80"/>
       <c r="M97" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N97" s="91"/>
+      <c r="N97" s="88"/>
     </row>
     <row r="98" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="68">
@@ -6023,15 +6080,15 @@
         <v>68</v>
       </c>
       <c r="G98" s="15"/>
-      <c r="H98" s="15"/>
+      <c r="H98" s="109"/>
       <c r="I98" s="17"/>
       <c r="J98" s="17"/>
       <c r="K98" s="14"/>
-      <c r="L98" s="83"/>
+      <c r="L98" s="80"/>
       <c r="M98" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N98" s="91"/>
+      <c r="N98" s="88"/>
     </row>
     <row r="99" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="68">
@@ -6050,15 +6107,15 @@
         <v>68</v>
       </c>
       <c r="G99" s="15"/>
-      <c r="H99" s="15"/>
+      <c r="H99" s="109"/>
       <c r="I99" s="17"/>
       <c r="J99" s="17"/>
       <c r="K99" s="14"/>
-      <c r="L99" s="83"/>
+      <c r="L99" s="80"/>
       <c r="M99" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N99" s="91"/>
+      <c r="N99" s="88"/>
     </row>
     <row r="100" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="68">
@@ -6079,15 +6136,15 @@
         <v>68</v>
       </c>
       <c r="G100" s="15"/>
-      <c r="H100" s="15"/>
+      <c r="H100" s="109"/>
       <c r="I100" s="17"/>
       <c r="J100" s="17"/>
       <c r="K100" s="14"/>
-      <c r="L100" s="83"/>
+      <c r="L100" s="80"/>
       <c r="M100" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N100" s="91"/>
+      <c r="N100" s="88"/>
     </row>
     <row r="101" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="68">
@@ -6108,15 +6165,15 @@
         <v>68</v>
       </c>
       <c r="G101" s="15"/>
-      <c r="H101" s="15"/>
+      <c r="H101" s="109"/>
       <c r="I101" s="17"/>
       <c r="J101" s="17"/>
       <c r="K101" s="14"/>
-      <c r="L101" s="83"/>
+      <c r="L101" s="80"/>
       <c r="M101" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N101" s="91"/>
+      <c r="N101" s="88"/>
     </row>
     <row r="102" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="68">
@@ -6137,15 +6194,15 @@
         <v>75</v>
       </c>
       <c r="G102" s="15"/>
-      <c r="H102" s="15"/>
+      <c r="H102" s="109"/>
       <c r="I102" s="17"/>
       <c r="J102" s="17"/>
       <c r="K102" s="14"/>
-      <c r="L102" s="83"/>
+      <c r="L102" s="80"/>
       <c r="M102" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N102" s="91"/>
+      <c r="N102" s="88"/>
     </row>
     <row r="103" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="68">
@@ -6166,15 +6223,15 @@
         <v>63</v>
       </c>
       <c r="G103" s="15"/>
-      <c r="H103" s="15"/>
+      <c r="H103" s="109"/>
       <c r="I103" s="17"/>
       <c r="J103" s="17"/>
       <c r="K103" s="14"/>
-      <c r="L103" s="83"/>
+      <c r="L103" s="80"/>
       <c r="M103" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N103" s="91"/>
+      <c r="N103" s="88"/>
     </row>
     <row r="104" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="68">
@@ -6195,15 +6252,15 @@
         <v>75</v>
       </c>
       <c r="G104" s="15"/>
-      <c r="H104" s="15"/>
+      <c r="H104" s="109"/>
       <c r="I104" s="17"/>
       <c r="J104" s="17"/>
       <c r="K104" s="14"/>
-      <c r="L104" s="83"/>
+      <c r="L104" s="80"/>
       <c r="M104" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N104" s="91"/>
+      <c r="N104" s="88"/>
     </row>
     <row r="105" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="68">
@@ -6222,15 +6279,15 @@
         <v>75</v>
       </c>
       <c r="G105" s="15"/>
-      <c r="H105" s="15"/>
+      <c r="H105" s="109"/>
       <c r="I105" s="17"/>
       <c r="J105" s="17"/>
       <c r="K105" s="14"/>
-      <c r="L105" s="83"/>
+      <c r="L105" s="80"/>
       <c r="M105" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N105" s="91"/>
+      <c r="N105" s="88"/>
     </row>
     <row r="106" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="68">
@@ -6251,15 +6308,15 @@
         <v>68</v>
       </c>
       <c r="G106" s="15"/>
-      <c r="H106" s="15"/>
+      <c r="H106" s="109"/>
       <c r="I106" s="17"/>
       <c r="J106" s="17"/>
       <c r="K106" s="14"/>
-      <c r="L106" s="83"/>
+      <c r="L106" s="80"/>
       <c r="M106" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N106" s="91"/>
+      <c r="N106" s="88"/>
     </row>
     <row r="107" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="68">
@@ -6280,15 +6337,15 @@
         <v>68</v>
       </c>
       <c r="G107" s="15"/>
-      <c r="H107" s="15"/>
+      <c r="H107" s="109"/>
       <c r="I107" s="17"/>
       <c r="J107" s="17"/>
       <c r="K107" s="14"/>
-      <c r="L107" s="83"/>
+      <c r="L107" s="80"/>
       <c r="M107" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N107" s="91"/>
+      <c r="N107" s="88"/>
     </row>
     <row r="108" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="68">
@@ -6301,7 +6358,9 @@
       <c r="C108" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="D108" s="14"/>
+      <c r="D108" s="14" t="s">
+        <v>61</v>
+      </c>
       <c r="E108" s="15" t="s">
         <v>71</v>
       </c>
@@ -6309,15 +6368,17 @@
         <v>68</v>
       </c>
       <c r="G108" s="15"/>
-      <c r="H108" s="15"/>
+      <c r="H108" s="109"/>
       <c r="I108" s="17"/>
       <c r="J108" s="17"/>
       <c r="K108" s="14"/>
-      <c r="L108" s="83"/>
+      <c r="L108" s="80" t="s">
+        <v>493</v>
+      </c>
       <c r="M108" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N108" s="91"/>
+      <c r="N108" s="88"/>
     </row>
     <row r="109" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="68">
@@ -6338,15 +6399,15 @@
         <v>68</v>
       </c>
       <c r="G109" s="15"/>
-      <c r="H109" s="15"/>
+      <c r="H109" s="109"/>
       <c r="I109" s="17"/>
       <c r="J109" s="17"/>
       <c r="K109" s="14"/>
-      <c r="L109" s="83"/>
+      <c r="L109" s="80"/>
       <c r="M109" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N109" s="91"/>
+      <c r="N109" s="88"/>
     </row>
     <row r="110" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="68">
@@ -6369,17 +6430,17 @@
         <v>68</v>
       </c>
       <c r="G110" s="15"/>
-      <c r="H110" s="15">
+      <c r="H110" s="109">
         <v>10</v>
       </c>
       <c r="I110" s="17"/>
       <c r="J110" s="17"/>
       <c r="K110" s="14"/>
-      <c r="L110" s="83"/>
+      <c r="L110" s="80"/>
       <c r="M110" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N110" s="91"/>
+      <c r="N110" s="88"/>
     </row>
     <row r="111" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="68">
@@ -6402,15 +6463,15 @@
         <v>63</v>
       </c>
       <c r="G111" s="15"/>
-      <c r="H111" s="15">
+      <c r="H111" s="109">
         <v>20</v>
       </c>
       <c r="I111" s="17"/>
       <c r="J111" s="17"/>
       <c r="K111" s="14"/>
-      <c r="L111" s="83"/>
+      <c r="L111" s="80"/>
       <c r="M111" s="15"/>
-      <c r="N111" s="91"/>
+      <c r="N111" s="88"/>
     </row>
     <row r="112" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="68">
@@ -6433,7 +6494,7 @@
         <v>68</v>
       </c>
       <c r="G112" s="15"/>
-      <c r="H112" s="15">
+      <c r="H112" s="109">
         <v>20</v>
       </c>
       <c r="I112" s="17">
@@ -6443,11 +6504,11 @@
         <v>46176</v>
       </c>
       <c r="K112" s="14"/>
-      <c r="L112" s="83"/>
+      <c r="L112" s="80"/>
       <c r="M112" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N112" s="91"/>
+      <c r="N112" s="88"/>
     </row>
     <row r="113" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="68">
@@ -6468,15 +6529,15 @@
         <v>63</v>
       </c>
       <c r="G113" s="15"/>
-      <c r="H113" s="15"/>
+      <c r="H113" s="109"/>
       <c r="I113" s="17"/>
       <c r="J113" s="17"/>
       <c r="K113" s="14"/>
-      <c r="L113" s="83"/>
+      <c r="L113" s="80"/>
       <c r="M113" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N113" s="91"/>
+      <c r="N113" s="88"/>
     </row>
     <row r="114" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="68">
@@ -6499,7 +6560,7 @@
         <v>63</v>
       </c>
       <c r="G114" s="15"/>
-      <c r="H114" s="15">
+      <c r="H114" s="109">
         <v>10</v>
       </c>
       <c r="I114" s="17">
@@ -6509,11 +6570,11 @@
         <v>46022</v>
       </c>
       <c r="K114" s="14"/>
-      <c r="L114" s="83"/>
+      <c r="L114" s="80"/>
       <c r="M114" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N114" s="91"/>
+      <c r="N114" s="88"/>
     </row>
     <row r="115" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="68">
@@ -6536,7 +6597,7 @@
         <v>68</v>
       </c>
       <c r="G115" s="15"/>
-      <c r="H115" s="15">
+      <c r="H115" s="109">
         <v>30</v>
       </c>
       <c r="I115" s="17">
@@ -6546,11 +6607,11 @@
         <v>46142</v>
       </c>
       <c r="K115" s="14"/>
-      <c r="L115" s="83"/>
+      <c r="L115" s="80"/>
       <c r="M115" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N115" s="91"/>
+      <c r="N115" s="88"/>
     </row>
     <row r="116" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="68">
@@ -6573,7 +6634,7 @@
         <v>68</v>
       </c>
       <c r="G116" s="15"/>
-      <c r="H116" s="15">
+      <c r="H116" s="109">
         <v>10</v>
       </c>
       <c r="I116" s="17">
@@ -6583,11 +6644,11 @@
         <v>46052</v>
       </c>
       <c r="K116" s="14"/>
-      <c r="L116" s="83"/>
+      <c r="L116" s="80"/>
       <c r="M116" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N116" s="91"/>
+      <c r="N116" s="88"/>
     </row>
     <row r="117" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="68">
@@ -6610,7 +6671,7 @@
         <v>63</v>
       </c>
       <c r="G117" s="15"/>
-      <c r="H117" s="15">
+      <c r="H117" s="109">
         <v>10</v>
       </c>
       <c r="I117" s="17">
@@ -6620,11 +6681,11 @@
         <v>46164</v>
       </c>
       <c r="K117" s="14"/>
-      <c r="L117" s="83"/>
+      <c r="L117" s="80"/>
       <c r="M117" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N117" s="91"/>
+      <c r="N117" s="88"/>
     </row>
     <row r="118" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="68">
@@ -6647,7 +6708,7 @@
         <v>68</v>
       </c>
       <c r="G118" s="15"/>
-      <c r="H118" s="15">
+      <c r="H118" s="109">
         <v>10</v>
       </c>
       <c r="I118" s="17">
@@ -6657,11 +6718,11 @@
         <v>46052</v>
       </c>
       <c r="K118" s="14"/>
-      <c r="L118" s="83"/>
+      <c r="L118" s="80"/>
       <c r="M118" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N118" s="91"/>
+      <c r="N118" s="88"/>
     </row>
     <row r="119" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="68">
@@ -6684,7 +6745,7 @@
         <v>68</v>
       </c>
       <c r="G119" s="15"/>
-      <c r="H119" s="15">
+      <c r="H119" s="109">
         <v>20</v>
       </c>
       <c r="I119" s="17">
@@ -6694,11 +6755,11 @@
         <v>46142</v>
       </c>
       <c r="K119" s="14"/>
-      <c r="L119" s="83"/>
+      <c r="L119" s="80"/>
       <c r="M119" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N119" s="91"/>
+      <c r="N119" s="88"/>
     </row>
     <row r="120" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="68">
@@ -6721,15 +6782,15 @@
         <v>68</v>
       </c>
       <c r="G120" s="15"/>
-      <c r="H120" s="15"/>
+      <c r="H120" s="109"/>
       <c r="I120" s="17"/>
       <c r="J120" s="17"/>
       <c r="K120" s="14"/>
-      <c r="L120" s="83"/>
+      <c r="L120" s="80"/>
       <c r="M120" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N120" s="91"/>
+      <c r="N120" s="88"/>
     </row>
     <row r="121" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="68">
@@ -6752,7 +6813,7 @@
         <v>63</v>
       </c>
       <c r="G121" s="15"/>
-      <c r="H121" s="15">
+      <c r="H121" s="109">
         <v>40</v>
       </c>
       <c r="I121" s="17">
@@ -6762,11 +6823,11 @@
         <v>46171</v>
       </c>
       <c r="K121" s="14"/>
-      <c r="L121" s="83"/>
+      <c r="L121" s="80"/>
       <c r="M121" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N121" s="91"/>
+      <c r="N121" s="88"/>
     </row>
     <row r="122" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="68">
@@ -6787,15 +6848,15 @@
         <v>75</v>
       </c>
       <c r="G122" s="15"/>
-      <c r="H122" s="15"/>
+      <c r="H122" s="109"/>
       <c r="I122" s="17"/>
       <c r="J122" s="17"/>
       <c r="K122" s="14"/>
-      <c r="L122" s="83"/>
+      <c r="L122" s="80"/>
       <c r="M122" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N122" s="91"/>
+      <c r="N122" s="88"/>
     </row>
     <row r="123" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="68">
@@ -6816,15 +6877,15 @@
         <v>68</v>
       </c>
       <c r="G123" s="15"/>
-      <c r="H123" s="15"/>
+      <c r="H123" s="109"/>
       <c r="I123" s="17"/>
       <c r="J123" s="17"/>
       <c r="K123" s="14"/>
-      <c r="L123" s="83"/>
+      <c r="L123" s="80"/>
       <c r="M123" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N123" s="91"/>
+      <c r="N123" s="88"/>
     </row>
     <row r="124" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="68">
@@ -6847,7 +6908,7 @@
         <v>68</v>
       </c>
       <c r="G124" s="15"/>
-      <c r="H124" s="15">
+      <c r="H124" s="109">
         <v>20</v>
       </c>
       <c r="I124" s="17">
@@ -6857,11 +6918,11 @@
         <v>46073</v>
       </c>
       <c r="K124" s="14"/>
-      <c r="L124" s="83"/>
+      <c r="L124" s="80"/>
       <c r="M124" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N124" s="91"/>
+      <c r="N124" s="88"/>
     </row>
     <row r="125" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="68">
@@ -6884,7 +6945,7 @@
         <v>75</v>
       </c>
       <c r="G125" s="15"/>
-      <c r="H125" s="15">
+      <c r="H125" s="109">
         <v>10</v>
       </c>
       <c r="I125" s="17">
@@ -6894,11 +6955,11 @@
         <v>46066</v>
       </c>
       <c r="K125" s="14"/>
-      <c r="L125" s="83"/>
+      <c r="L125" s="80"/>
       <c r="M125" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N125" s="91"/>
+      <c r="N125" s="88"/>
     </row>
     <row r="126" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="68">
@@ -6919,15 +6980,15 @@
         <v>68</v>
       </c>
       <c r="G126" s="15"/>
-      <c r="H126" s="15"/>
+      <c r="H126" s="109"/>
       <c r="I126" s="17"/>
       <c r="J126" s="17"/>
       <c r="K126" s="14"/>
-      <c r="L126" s="83"/>
+      <c r="L126" s="80"/>
       <c r="M126" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N126" s="91"/>
+      <c r="N126" s="88"/>
     </row>
     <row r="127" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="68">
@@ -6950,15 +7011,15 @@
         <v>68</v>
       </c>
       <c r="G127" s="15"/>
-      <c r="H127" s="15"/>
+      <c r="H127" s="109"/>
       <c r="I127" s="17"/>
       <c r="J127" s="17"/>
       <c r="K127" s="14"/>
-      <c r="L127" s="83"/>
+      <c r="L127" s="80"/>
       <c r="M127" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N127" s="91"/>
+      <c r="N127" s="88"/>
     </row>
     <row r="128" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="68">
@@ -6979,15 +7040,15 @@
         <v>68</v>
       </c>
       <c r="G128" s="15"/>
-      <c r="H128" s="15"/>
+      <c r="H128" s="109"/>
       <c r="I128" s="17"/>
       <c r="J128" s="17"/>
       <c r="K128" s="14"/>
-      <c r="L128" s="83"/>
+      <c r="L128" s="80"/>
       <c r="M128" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N128" s="91"/>
+      <c r="N128" s="88"/>
     </row>
     <row r="129" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="68">
@@ -7008,15 +7069,15 @@
         <v>68</v>
       </c>
       <c r="G129" s="15"/>
-      <c r="H129" s="15"/>
+      <c r="H129" s="109"/>
       <c r="I129" s="17"/>
       <c r="J129" s="17"/>
       <c r="K129" s="14"/>
-      <c r="L129" s="83"/>
+      <c r="L129" s="80"/>
       <c r="M129" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N129" s="91"/>
+      <c r="N129" s="88"/>
     </row>
     <row r="130" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="68">
@@ -7039,7 +7100,7 @@
         <v>68</v>
       </c>
       <c r="G130" s="15"/>
-      <c r="H130" s="15">
+      <c r="H130" s="109">
         <v>4</v>
       </c>
       <c r="I130" s="17">
@@ -7049,11 +7110,11 @@
         <v>46142</v>
       </c>
       <c r="K130" s="14"/>
-      <c r="L130" s="83"/>
+      <c r="L130" s="80"/>
       <c r="M130" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N130" s="91"/>
+      <c r="N130" s="88"/>
     </row>
     <row r="131" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="68">
@@ -7076,7 +7137,7 @@
         <v>68</v>
       </c>
       <c r="G131" s="15"/>
-      <c r="H131" s="15">
+      <c r="H131" s="109">
         <v>60</v>
       </c>
       <c r="I131" s="17">
@@ -7086,11 +7147,11 @@
         <v>46192</v>
       </c>
       <c r="K131" s="14"/>
-      <c r="L131" s="83"/>
+      <c r="L131" s="80"/>
       <c r="M131" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N131" s="91"/>
+      <c r="N131" s="88"/>
     </row>
     <row r="132" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="68">
@@ -7113,7 +7174,7 @@
         <v>63</v>
       </c>
       <c r="G132" s="15"/>
-      <c r="H132" s="15">
+      <c r="H132" s="109">
         <v>30</v>
       </c>
       <c r="I132" s="17">
@@ -7123,11 +7184,11 @@
         <v>46170</v>
       </c>
       <c r="K132" s="14"/>
-      <c r="L132" s="83"/>
+      <c r="L132" s="80"/>
       <c r="M132" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N132" s="91"/>
+      <c r="N132" s="88"/>
     </row>
     <row r="133" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="68">
@@ -7150,7 +7211,7 @@
         <v>75</v>
       </c>
       <c r="G133" s="15"/>
-      <c r="H133" s="15">
+      <c r="H133" s="109">
         <v>20</v>
       </c>
       <c r="I133" s="17">
@@ -7160,11 +7221,11 @@
         <v>46171</v>
       </c>
       <c r="K133" s="14"/>
-      <c r="L133" s="83"/>
+      <c r="L133" s="80"/>
       <c r="M133" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N133" s="91"/>
+      <c r="N133" s="88"/>
     </row>
     <row r="134" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="68">
@@ -7187,7 +7248,7 @@
         <v>68</v>
       </c>
       <c r="G134" s="15"/>
-      <c r="H134" s="15">
+      <c r="H134" s="109">
         <v>20</v>
       </c>
       <c r="I134" s="17">
@@ -7197,11 +7258,11 @@
         <v>46129</v>
       </c>
       <c r="K134" s="14"/>
-      <c r="L134" s="83"/>
+      <c r="L134" s="80"/>
       <c r="M134" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N134" s="91"/>
+      <c r="N134" s="88"/>
     </row>
     <row r="135" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="68">
@@ -7224,7 +7285,7 @@
         <v>68</v>
       </c>
       <c r="G135" s="15"/>
-      <c r="H135" s="15">
+      <c r="H135" s="109">
         <v>30</v>
       </c>
       <c r="I135" s="17">
@@ -7234,11 +7295,11 @@
         <v>46129</v>
       </c>
       <c r="K135" s="14"/>
-      <c r="L135" s="83"/>
+      <c r="L135" s="80"/>
       <c r="M135" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N135" s="91"/>
+      <c r="N135" s="88"/>
     </row>
     <row r="136" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="68">
@@ -7261,7 +7322,7 @@
         <v>68</v>
       </c>
       <c r="G136" s="15"/>
-      <c r="H136" s="15">
+      <c r="H136" s="109">
         <v>30</v>
       </c>
       <c r="I136" s="17">
@@ -7271,11 +7332,11 @@
         <v>46142</v>
       </c>
       <c r="K136" s="14"/>
-      <c r="L136" s="83"/>
+      <c r="L136" s="80"/>
       <c r="M136" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N136" s="91"/>
+      <c r="N136" s="88"/>
     </row>
     <row r="137" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="68">
@@ -7298,7 +7359,7 @@
         <v>68</v>
       </c>
       <c r="G137" s="15"/>
-      <c r="H137" s="15">
+      <c r="H137" s="109">
         <v>45</v>
       </c>
       <c r="I137" s="17">
@@ -7308,11 +7369,11 @@
         <v>46022</v>
       </c>
       <c r="K137" s="14"/>
-      <c r="L137" s="83"/>
+      <c r="L137" s="80"/>
       <c r="M137" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N137" s="91"/>
+      <c r="N137" s="88"/>
     </row>
     <row r="138" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="68">
@@ -7335,7 +7396,7 @@
         <v>68</v>
       </c>
       <c r="G138" s="15"/>
-      <c r="H138" s="15">
+      <c r="H138" s="109">
         <v>30</v>
       </c>
       <c r="I138" s="17">
@@ -7345,11 +7406,11 @@
         <v>46017</v>
       </c>
       <c r="K138" s="14"/>
-      <c r="L138" s="83"/>
+      <c r="L138" s="80"/>
       <c r="M138" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N138" s="91"/>
+      <c r="N138" s="88"/>
     </row>
     <row r="139" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="68">
@@ -7372,7 +7433,7 @@
         <v>68</v>
       </c>
       <c r="G139" s="15"/>
-      <c r="H139" s="15">
+      <c r="H139" s="109">
         <v>20</v>
       </c>
       <c r="I139" s="17">
@@ -7382,11 +7443,11 @@
         <v>46045</v>
       </c>
       <c r="K139" s="14"/>
-      <c r="L139" s="83"/>
+      <c r="L139" s="80"/>
       <c r="M139" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N139" s="91"/>
+      <c r="N139" s="88"/>
     </row>
     <row r="140" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="68">
@@ -7407,7 +7468,7 @@
         <v>68</v>
       </c>
       <c r="G140" s="15"/>
-      <c r="H140" s="15">
+      <c r="H140" s="109">
         <v>20</v>
       </c>
       <c r="I140" s="17">
@@ -7417,11 +7478,11 @@
         <v>46199</v>
       </c>
       <c r="K140" s="14"/>
-      <c r="L140" s="83"/>
+      <c r="L140" s="80"/>
       <c r="M140" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N140" s="91"/>
+      <c r="N140" s="88"/>
     </row>
     <row r="141" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="68">
@@ -7444,7 +7505,7 @@
         <v>68</v>
       </c>
       <c r="G141" s="15"/>
-      <c r="H141" s="15">
+      <c r="H141" s="109">
         <v>30</v>
       </c>
       <c r="I141" s="17">
@@ -7454,11 +7515,11 @@
         <v>46142</v>
       </c>
       <c r="K141" s="14"/>
-      <c r="L141" s="83"/>
+      <c r="L141" s="80"/>
       <c r="M141" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N141" s="91"/>
+      <c r="N141" s="88"/>
     </row>
     <row r="142" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="68">
@@ -7481,7 +7542,7 @@
         <v>68</v>
       </c>
       <c r="G142" s="15"/>
-      <c r="H142" s="15">
+      <c r="H142" s="109">
         <v>40</v>
       </c>
       <c r="I142" s="17">
@@ -7491,11 +7552,11 @@
         <v>46142</v>
       </c>
       <c r="K142" s="14"/>
-      <c r="L142" s="83"/>
+      <c r="L142" s="80"/>
       <c r="M142" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N142" s="91"/>
+      <c r="N142" s="88"/>
     </row>
     <row r="143" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="68">
@@ -7518,7 +7579,7 @@
         <v>63</v>
       </c>
       <c r="G143" s="15"/>
-      <c r="H143" s="15">
+      <c r="H143" s="109">
         <v>25</v>
       </c>
       <c r="I143" s="17">
@@ -7528,11 +7589,11 @@
         <v>46142</v>
       </c>
       <c r="K143" s="14"/>
-      <c r="L143" s="83"/>
+      <c r="L143" s="80"/>
       <c r="M143" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N143" s="91"/>
+      <c r="N143" s="88"/>
     </row>
     <row r="144" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="68">
@@ -7555,7 +7616,7 @@
         <v>75</v>
       </c>
       <c r="G144" s="15"/>
-      <c r="H144" s="15">
+      <c r="H144" s="109">
         <v>20</v>
       </c>
       <c r="I144" s="17">
@@ -7565,11 +7626,11 @@
         <v>46129</v>
       </c>
       <c r="K144" s="14"/>
-      <c r="L144" s="83"/>
+      <c r="L144" s="80"/>
       <c r="M144" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="N144" s="91"/>
+      <c r="N144" s="88"/>
     </row>
     <row r="145" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="68">
@@ -7592,7 +7653,7 @@
         <v>68</v>
       </c>
       <c r="G145" s="15"/>
-      <c r="H145" s="15">
+      <c r="H145" s="109">
         <v>88</v>
       </c>
       <c r="I145" s="17">
@@ -7602,11 +7663,11 @@
         <v>46122</v>
       </c>
       <c r="K145" s="14"/>
-      <c r="L145" s="83"/>
+      <c r="L145" s="80"/>
       <c r="M145" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N145" s="91"/>
+      <c r="N145" s="88"/>
     </row>
     <row r="146" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="68">
@@ -7629,7 +7690,7 @@
         <v>75</v>
       </c>
       <c r="G146" s="15"/>
-      <c r="H146" s="15">
+      <c r="H146" s="109">
         <v>2</v>
       </c>
       <c r="I146" s="17">
@@ -7639,11 +7700,11 @@
         <v>46038</v>
       </c>
       <c r="K146" s="14"/>
-      <c r="L146" s="83"/>
+      <c r="L146" s="80"/>
       <c r="M146" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N146" s="91"/>
+      <c r="N146" s="88"/>
     </row>
     <row r="147" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="68">
@@ -7666,7 +7727,7 @@
         <v>68</v>
       </c>
       <c r="G147" s="15"/>
-      <c r="H147" s="15">
+      <c r="H147" s="109">
         <v>40</v>
       </c>
       <c r="I147" s="17">
@@ -7676,11 +7737,11 @@
         <v>46043</v>
       </c>
       <c r="K147" s="14"/>
-      <c r="L147" s="83"/>
+      <c r="L147" s="80"/>
       <c r="M147" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N147" s="91"/>
+      <c r="N147" s="88"/>
     </row>
     <row r="148" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="68">
@@ -7703,7 +7764,7 @@
         <v>63</v>
       </c>
       <c r="G148" s="15"/>
-      <c r="H148" s="15">
+      <c r="H148" s="109">
         <v>100</v>
       </c>
       <c r="I148" s="17">
@@ -7713,11 +7774,11 @@
         <v>46061</v>
       </c>
       <c r="K148" s="14"/>
-      <c r="L148" s="83"/>
+      <c r="L148" s="80"/>
       <c r="M148" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N148" s="91"/>
+      <c r="N148" s="88"/>
     </row>
     <row r="149" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="68">
@@ -7740,7 +7801,7 @@
         <v>63</v>
       </c>
       <c r="G149" s="15"/>
-      <c r="H149" s="15">
+      <c r="H149" s="109">
         <v>110</v>
       </c>
       <c r="I149" s="17">
@@ -7750,11 +7811,11 @@
         <v>46115</v>
       </c>
       <c r="K149" s="14"/>
-      <c r="L149" s="83"/>
+      <c r="L149" s="80"/>
       <c r="M149" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N149" s="91"/>
+      <c r="N149" s="88"/>
     </row>
     <row r="150" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="68">
@@ -7777,7 +7838,7 @@
         <v>68</v>
       </c>
       <c r="G150" s="15"/>
-      <c r="H150" s="15">
+      <c r="H150" s="109">
         <v>80</v>
       </c>
       <c r="I150" s="17">
@@ -7787,11 +7848,11 @@
         <v>46100</v>
       </c>
       <c r="K150" s="14"/>
-      <c r="L150" s="83"/>
+      <c r="L150" s="80"/>
       <c r="M150" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N150" s="91"/>
+      <c r="N150" s="88"/>
     </row>
     <row r="151" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="68">
@@ -7814,7 +7875,7 @@
         <v>68</v>
       </c>
       <c r="G151" s="15"/>
-      <c r="H151" s="15">
+      <c r="H151" s="109">
         <v>40</v>
       </c>
       <c r="I151" s="17">
@@ -7824,11 +7885,11 @@
         <v>46112</v>
       </c>
       <c r="K151" s="14"/>
-      <c r="L151" s="83"/>
+      <c r="L151" s="80"/>
       <c r="M151" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N151" s="91"/>
+      <c r="N151" s="88"/>
     </row>
     <row r="152" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="68">
@@ -7849,7 +7910,7 @@
         <v>63</v>
       </c>
       <c r="G152" s="15"/>
-      <c r="H152" s="15">
+      <c r="H152" s="109">
         <v>80</v>
       </c>
       <c r="I152" s="17">
@@ -7859,11 +7920,11 @@
         <v>46112</v>
       </c>
       <c r="K152" s="14"/>
-      <c r="L152" s="83"/>
+      <c r="L152" s="80"/>
       <c r="M152" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N152" s="91"/>
+      <c r="N152" s="88"/>
     </row>
     <row r="153" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="68">
@@ -7886,7 +7947,7 @@
         <v>63</v>
       </c>
       <c r="G153" s="15"/>
-      <c r="H153" s="15">
+      <c r="H153" s="109">
         <v>30</v>
       </c>
       <c r="I153" s="17">
@@ -7896,11 +7957,11 @@
         <v>46155</v>
       </c>
       <c r="K153" s="14"/>
-      <c r="L153" s="83"/>
+      <c r="L153" s="80"/>
       <c r="M153" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N153" s="91"/>
+      <c r="N153" s="88"/>
     </row>
     <row r="154" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="68">
@@ -7923,7 +7984,7 @@
         <v>63</v>
       </c>
       <c r="G154" s="15"/>
-      <c r="H154" s="15">
+      <c r="H154" s="109">
         <v>30</v>
       </c>
       <c r="I154" s="17">
@@ -7933,11 +7994,11 @@
         <v>46155</v>
       </c>
       <c r="K154" s="14"/>
-      <c r="L154" s="83"/>
+      <c r="L154" s="80"/>
       <c r="M154" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N154" s="91"/>
+      <c r="N154" s="88"/>
     </row>
     <row r="155" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="68">
@@ -7960,7 +8021,7 @@
         <v>63</v>
       </c>
       <c r="G155" s="15"/>
-      <c r="H155" s="15">
+      <c r="H155" s="109">
         <v>30</v>
       </c>
       <c r="I155" s="17">
@@ -7970,11 +8031,11 @@
         <v>46155</v>
       </c>
       <c r="K155" s="14"/>
-      <c r="L155" s="83"/>
+      <c r="L155" s="80"/>
       <c r="M155" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N155" s="91"/>
+      <c r="N155" s="88"/>
     </row>
     <row r="156" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="68">
@@ -7997,7 +8058,7 @@
         <v>68</v>
       </c>
       <c r="G156" s="15"/>
-      <c r="H156" s="15">
+      <c r="H156" s="109">
         <v>80</v>
       </c>
       <c r="I156" s="17">
@@ -8007,11 +8068,11 @@
         <v>46113</v>
       </c>
       <c r="K156" s="14"/>
-      <c r="L156" s="83"/>
+      <c r="L156" s="80"/>
       <c r="M156" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N156" s="91"/>
+      <c r="N156" s="88"/>
     </row>
     <row r="157" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="68">
@@ -8032,15 +8093,15 @@
         <v>68</v>
       </c>
       <c r="G157" s="15"/>
-      <c r="H157" s="15"/>
+      <c r="H157" s="109"/>
       <c r="I157" s="17"/>
       <c r="J157" s="17"/>
       <c r="K157" s="14"/>
-      <c r="L157" s="83"/>
+      <c r="L157" s="80"/>
       <c r="M157" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N157" s="91"/>
+      <c r="N157" s="88"/>
     </row>
     <row r="158" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="68">
@@ -8061,15 +8122,15 @@
         <v>75</v>
       </c>
       <c r="G158" s="15"/>
-      <c r="H158" s="15"/>
+      <c r="H158" s="109"/>
       <c r="I158" s="17"/>
       <c r="J158" s="17"/>
       <c r="K158" s="14"/>
-      <c r="L158" s="83"/>
+      <c r="L158" s="80"/>
       <c r="M158" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N158" s="91"/>
+      <c r="N158" s="88"/>
     </row>
     <row r="159" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="68">
@@ -8092,7 +8153,7 @@
         <v>68</v>
       </c>
       <c r="G159" s="15"/>
-      <c r="H159" s="15">
+      <c r="H159" s="109">
         <v>160</v>
       </c>
       <c r="I159" s="17">
@@ -8102,11 +8163,11 @@
         <v>46118</v>
       </c>
       <c r="K159" s="14"/>
-      <c r="L159" s="83"/>
+      <c r="L159" s="80"/>
       <c r="M159" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N159" s="91"/>
+      <c r="N159" s="88"/>
     </row>
     <row r="160" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="68">
@@ -8129,7 +8190,7 @@
         <v>68</v>
       </c>
       <c r="G160" s="15"/>
-      <c r="H160" s="15">
+      <c r="H160" s="109">
         <v>40</v>
       </c>
       <c r="I160" s="17">
@@ -8139,11 +8200,11 @@
         <v>46108</v>
       </c>
       <c r="K160" s="14"/>
-      <c r="L160" s="83"/>
+      <c r="L160" s="80"/>
       <c r="M160" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N160" s="91"/>
+      <c r="N160" s="88"/>
     </row>
     <row r="161" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="68">
@@ -8164,15 +8225,15 @@
         <v>68</v>
       </c>
       <c r="G161" s="15"/>
-      <c r="H161" s="15"/>
+      <c r="H161" s="109"/>
       <c r="I161" s="17"/>
       <c r="J161" s="17"/>
       <c r="K161" s="14"/>
-      <c r="L161" s="83"/>
+      <c r="L161" s="80"/>
       <c r="M161" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N161" s="91"/>
+      <c r="N161" s="88"/>
     </row>
     <row r="162" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="68">
@@ -8193,15 +8254,15 @@
         <v>68</v>
       </c>
       <c r="G162" s="15"/>
-      <c r="H162" s="15"/>
+      <c r="H162" s="109"/>
       <c r="I162" s="17"/>
       <c r="J162" s="17"/>
       <c r="K162" s="14"/>
-      <c r="L162" s="83"/>
+      <c r="L162" s="80"/>
       <c r="M162" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N162" s="91"/>
+      <c r="N162" s="88"/>
     </row>
     <row r="163" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="68">
@@ -8224,7 +8285,7 @@
         <v>68</v>
       </c>
       <c r="G163" s="15"/>
-      <c r="H163" s="15">
+      <c r="H163" s="109">
         <v>20</v>
       </c>
       <c r="I163" s="17">
@@ -8234,11 +8295,11 @@
         <v>46120</v>
       </c>
       <c r="K163" s="14"/>
-      <c r="L163" s="83"/>
+      <c r="L163" s="80"/>
       <c r="M163" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N163" s="91"/>
+      <c r="N163" s="88"/>
     </row>
     <row r="164" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="68">
@@ -8261,7 +8322,7 @@
         <v>68</v>
       </c>
       <c r="G164" s="15"/>
-      <c r="H164" s="15">
+      <c r="H164" s="109">
         <v>40</v>
       </c>
       <c r="I164" s="17">
@@ -8271,11 +8332,11 @@
         <v>46123</v>
       </c>
       <c r="K164" s="14"/>
-      <c r="L164" s="83"/>
+      <c r="L164" s="80"/>
       <c r="M164" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N164" s="91"/>
+      <c r="N164" s="88"/>
     </row>
     <row r="165" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="68">
@@ -8298,7 +8359,7 @@
         <v>75</v>
       </c>
       <c r="G165" s="15"/>
-      <c r="H165" s="15">
+      <c r="H165" s="109">
         <v>100</v>
       </c>
       <c r="I165" s="17">
@@ -8308,11 +8369,11 @@
         <v>46128</v>
       </c>
       <c r="K165" s="14"/>
-      <c r="L165" s="83"/>
+      <c r="L165" s="80"/>
       <c r="M165" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N165" s="91"/>
+      <c r="N165" s="88"/>
     </row>
     <row r="166" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="68">
@@ -8333,7 +8394,7 @@
         <v>68</v>
       </c>
       <c r="G166" s="15"/>
-      <c r="H166" s="15">
+      <c r="H166" s="109">
         <v>10</v>
       </c>
       <c r="I166" s="17">
@@ -8343,11 +8404,11 @@
         <v>46127</v>
       </c>
       <c r="K166" s="14"/>
-      <c r="L166" s="83"/>
+      <c r="L166" s="80"/>
       <c r="M166" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N166" s="91"/>
+      <c r="N166" s="88"/>
     </row>
     <row r="167" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="68">
@@ -8370,7 +8431,7 @@
         <v>63</v>
       </c>
       <c r="G167" s="15"/>
-      <c r="H167" s="15">
+      <c r="H167" s="109">
         <v>78</v>
       </c>
       <c r="I167" s="17">
@@ -8380,11 +8441,11 @@
         <v>46101</v>
       </c>
       <c r="K167" s="14"/>
-      <c r="L167" s="83"/>
+      <c r="L167" s="80"/>
       <c r="M167" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N167" s="91"/>
+      <c r="N167" s="88"/>
     </row>
     <row r="168" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="68">
@@ -8405,7 +8466,7 @@
         <v>63</v>
       </c>
       <c r="G168" s="15"/>
-      <c r="H168" s="15">
+      <c r="H168" s="109">
         <v>1</v>
       </c>
       <c r="I168" s="17">
@@ -8415,11 +8476,11 @@
         <v>46112</v>
       </c>
       <c r="K168" s="14"/>
-      <c r="L168" s="83"/>
+      <c r="L168" s="80"/>
       <c r="M168" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N168" s="91"/>
+      <c r="N168" s="88"/>
     </row>
     <row r="169" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="68">
@@ -8440,17 +8501,17 @@
         <v>68</v>
       </c>
       <c r="G169" s="15"/>
-      <c r="H169" s="15">
+      <c r="H169" s="109">
         <v>50</v>
       </c>
       <c r="I169" s="17"/>
       <c r="J169" s="17"/>
       <c r="K169" s="14"/>
-      <c r="L169" s="83"/>
+      <c r="L169" s="80"/>
       <c r="M169" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="N169" s="91"/>
+      <c r="N169" s="88"/>
     </row>
     <row r="170" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="68">
@@ -8473,7 +8534,7 @@
         <v>68</v>
       </c>
       <c r="G170" s="15"/>
-      <c r="H170" s="15">
+      <c r="H170" s="109">
         <v>10</v>
       </c>
       <c r="I170" s="17">
@@ -8483,11 +8544,11 @@
         <v>46387</v>
       </c>
       <c r="K170" s="14"/>
-      <c r="L170" s="83"/>
+      <c r="L170" s="80"/>
       <c r="M170" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N170" s="91"/>
+      <c r="N170" s="88"/>
     </row>
     <row r="171" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="68">
@@ -8510,17 +8571,17 @@
         <v>75</v>
       </c>
       <c r="G171" s="15"/>
-      <c r="H171" s="15">
+      <c r="H171" s="109">
         <v>10</v>
       </c>
       <c r="I171" s="17"/>
       <c r="J171" s="17"/>
       <c r="K171" s="14"/>
-      <c r="L171" s="83"/>
+      <c r="L171" s="80"/>
       <c r="M171" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N171" s="91"/>
+      <c r="N171" s="88"/>
     </row>
     <row r="172" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="68">
@@ -8541,15 +8602,15 @@
         <v>68</v>
       </c>
       <c r="G172" s="15"/>
-      <c r="H172" s="15"/>
+      <c r="H172" s="109"/>
       <c r="I172" s="17"/>
       <c r="J172" s="17"/>
       <c r="K172" s="14"/>
-      <c r="L172" s="83"/>
+      <c r="L172" s="80"/>
       <c r="M172" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N172" s="91"/>
+      <c r="N172" s="88"/>
     </row>
     <row r="173" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="68">
@@ -8572,7 +8633,7 @@
         <v>68</v>
       </c>
       <c r="G173" s="15"/>
-      <c r="H173" s="15">
+      <c r="H173" s="109">
         <v>30</v>
       </c>
       <c r="I173" s="17">
@@ -8582,11 +8643,11 @@
         <v>46108</v>
       </c>
       <c r="K173" s="14"/>
-      <c r="L173" s="83"/>
+      <c r="L173" s="80"/>
       <c r="M173" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N173" s="91"/>
+      <c r="N173" s="88"/>
     </row>
     <row r="174" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="68">
@@ -8607,15 +8668,15 @@
         <v>68</v>
       </c>
       <c r="G174" s="15"/>
-      <c r="H174" s="15"/>
+      <c r="H174" s="109"/>
       <c r="I174" s="17"/>
       <c r="J174" s="17"/>
       <c r="K174" s="14"/>
-      <c r="L174" s="83"/>
+      <c r="L174" s="80"/>
       <c r="M174" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N174" s="91"/>
+      <c r="N174" s="88"/>
     </row>
     <row r="175" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="68">
@@ -8638,7 +8699,7 @@
         <v>75</v>
       </c>
       <c r="G175" s="15"/>
-      <c r="H175" s="15">
+      <c r="H175" s="109">
         <v>5</v>
       </c>
       <c r="I175" s="17">
@@ -8648,11 +8709,11 @@
         <v>46038</v>
       </c>
       <c r="K175" s="14"/>
-      <c r="L175" s="83"/>
+      <c r="L175" s="80"/>
       <c r="M175" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N175" s="91"/>
+      <c r="N175" s="88"/>
     </row>
     <row r="176" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="68">
@@ -8675,7 +8736,7 @@
         <v>68</v>
       </c>
       <c r="G176" s="15"/>
-      <c r="H176" s="15">
+      <c r="H176" s="109">
         <v>5</v>
       </c>
       <c r="I176" s="17">
@@ -8685,11 +8746,11 @@
         <v>46045</v>
       </c>
       <c r="K176" s="14"/>
-      <c r="L176" s="83"/>
+      <c r="L176" s="80"/>
       <c r="M176" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N176" s="91"/>
+      <c r="N176" s="88"/>
     </row>
     <row r="177" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="68">
@@ -8712,17 +8773,17 @@
         <v>68</v>
       </c>
       <c r="G177" s="15"/>
-      <c r="H177" s="15">
+      <c r="H177" s="109">
         <v>40</v>
       </c>
       <c r="I177" s="17"/>
       <c r="J177" s="17"/>
       <c r="K177" s="14"/>
-      <c r="L177" s="83"/>
+      <c r="L177" s="80"/>
       <c r="M177" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N177" s="91"/>
+      <c r="N177" s="88"/>
     </row>
     <row r="178" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="68">
@@ -8745,7 +8806,7 @@
         <v>75</v>
       </c>
       <c r="G178" s="15"/>
-      <c r="H178" s="15">
+      <c r="H178" s="109">
         <v>20</v>
       </c>
       <c r="I178" s="17">
@@ -8755,11 +8816,11 @@
         <v>46142</v>
       </c>
       <c r="K178" s="14"/>
-      <c r="L178" s="83"/>
+      <c r="L178" s="80"/>
       <c r="M178" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N178" s="91"/>
+      <c r="N178" s="88"/>
     </row>
     <row r="179" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="68">
@@ -8782,7 +8843,7 @@
         <v>75</v>
       </c>
       <c r="G179" s="15"/>
-      <c r="H179" s="15">
+      <c r="H179" s="109">
         <v>20</v>
       </c>
       <c r="I179" s="17">
@@ -8792,11 +8853,11 @@
         <v>46101</v>
       </c>
       <c r="K179" s="14"/>
-      <c r="L179" s="83"/>
+      <c r="L179" s="80"/>
       <c r="M179" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N179" s="91"/>
+      <c r="N179" s="88"/>
     </row>
     <row r="180" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="68">
@@ -8819,7 +8880,7 @@
         <v>75</v>
       </c>
       <c r="G180" s="24"/>
-      <c r="H180" s="24">
+      <c r="H180" s="110">
         <v>10</v>
       </c>
       <c r="I180" s="25">
@@ -8829,11 +8890,11 @@
         <v>46136</v>
       </c>
       <c r="K180" s="23"/>
-      <c r="L180" s="84"/>
+      <c r="L180" s="81"/>
       <c r="M180" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="N180" s="92"/>
+      <c r="N180" s="89"/>
     </row>
     <row r="181" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="68">
@@ -8856,7 +8917,7 @@
         <v>68</v>
       </c>
       <c r="G181" s="15"/>
-      <c r="H181" s="15">
+      <c r="H181" s="109">
         <v>10</v>
       </c>
       <c r="I181" s="17">
@@ -8866,11 +8927,11 @@
         <v>46122</v>
       </c>
       <c r="K181" s="14"/>
-      <c r="L181" s="83"/>
+      <c r="L181" s="80"/>
       <c r="M181" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="N181" s="91"/>
+      <c r="N181" s="88"/>
     </row>
     <row r="182" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="68">
@@ -8893,17 +8954,17 @@
         <v>63</v>
       </c>
       <c r="G182" s="44"/>
-      <c r="H182" s="44"/>
+      <c r="H182" s="111"/>
       <c r="I182" s="45"/>
       <c r="J182" s="45"/>
       <c r="K182" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="L182" s="85"/>
-      <c r="M182" s="100" t="s">
-        <v>64</v>
-      </c>
-      <c r="N182" s="93"/>
+      <c r="L182" s="82"/>
+      <c r="M182" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="N182" s="90"/>
     </row>
     <row r="183" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="68">
@@ -8926,17 +8987,17 @@
         <v>63</v>
       </c>
       <c r="G183" s="30"/>
-      <c r="H183" s="30"/>
+      <c r="H183" s="112"/>
       <c r="I183" s="31"/>
       <c r="J183" s="31"/>
       <c r="K183" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="L183" s="86"/>
-      <c r="M183" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N183" s="94"/>
+      <c r="L183" s="83"/>
+      <c r="M183" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N183" s="91"/>
     </row>
     <row r="184" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="68">
@@ -8959,19 +9020,19 @@
         <v>63</v>
       </c>
       <c r="G184" s="34"/>
-      <c r="H184" s="34"/>
+      <c r="H184" s="113"/>
       <c r="I184" s="35"/>
       <c r="J184" s="35"/>
       <c r="K184" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="L184" s="87" t="s">
-        <v>485</v>
-      </c>
-      <c r="M184" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N184" s="95"/>
+      <c r="L184" s="84" t="s">
+        <v>484</v>
+      </c>
+      <c r="M184" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N184" s="92"/>
     </row>
     <row r="185" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="68">
@@ -8994,19 +9055,19 @@
         <v>63</v>
       </c>
       <c r="G185" s="30"/>
-      <c r="H185" s="30"/>
+      <c r="H185" s="112"/>
       <c r="I185" s="31"/>
       <c r="J185" s="31"/>
       <c r="K185" s="27" t="s">
         <v>330</v>
       </c>
-      <c r="L185" s="86" t="s">
-        <v>485</v>
-      </c>
-      <c r="M185" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N185" s="94"/>
+      <c r="L185" s="83" t="s">
+        <v>484</v>
+      </c>
+      <c r="M185" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N185" s="91"/>
     </row>
     <row r="186" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="68">
@@ -9029,19 +9090,19 @@
         <v>63</v>
       </c>
       <c r="G186" s="34"/>
-      <c r="H186" s="34"/>
+      <c r="H186" s="113"/>
       <c r="I186" s="35"/>
       <c r="J186" s="35"/>
       <c r="K186" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="L186" s="87" t="s">
-        <v>485</v>
-      </c>
-      <c r="M186" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N186" s="95"/>
+      <c r="L186" s="84" t="s">
+        <v>484</v>
+      </c>
+      <c r="M186" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N186" s="92"/>
     </row>
     <row r="187" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="68">
@@ -9058,23 +9119,23 @@
         <v>118</v>
       </c>
       <c r="E187" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F187" s="29" t="s">
         <v>63</v>
       </c>
       <c r="G187" s="30"/>
-      <c r="H187" s="30"/>
+      <c r="H187" s="112"/>
       <c r="I187" s="31"/>
       <c r="J187" s="31"/>
       <c r="K187" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="L187" s="86"/>
-      <c r="M187" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N187" s="94"/>
+      <c r="L187" s="83"/>
+      <c r="M187" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N187" s="91"/>
     </row>
     <row r="188" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="68">
@@ -9097,19 +9158,19 @@
         <v>63</v>
       </c>
       <c r="G188" s="34"/>
-      <c r="H188" s="34"/>
+      <c r="H188" s="113"/>
       <c r="I188" s="35"/>
       <c r="J188" s="35"/>
       <c r="K188" s="33" t="s">
         <v>339</v>
       </c>
-      <c r="L188" s="87" t="s">
-        <v>485</v>
-      </c>
-      <c r="M188" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N188" s="95"/>
+      <c r="L188" s="84" t="s">
+        <v>484</v>
+      </c>
+      <c r="M188" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N188" s="92"/>
     </row>
     <row r="189" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="68">
@@ -9132,19 +9193,19 @@
         <v>63</v>
       </c>
       <c r="G189" s="30"/>
-      <c r="H189" s="30"/>
+      <c r="H189" s="112"/>
       <c r="I189" s="31"/>
       <c r="J189" s="31"/>
       <c r="K189" s="27" t="s">
         <v>327</v>
       </c>
-      <c r="L189" s="86" t="s">
-        <v>485</v>
-      </c>
-      <c r="M189" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N189" s="94"/>
+      <c r="L189" s="83" t="s">
+        <v>484</v>
+      </c>
+      <c r="M189" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N189" s="91"/>
     </row>
     <row r="190" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="68">
@@ -9161,23 +9222,23 @@
         <v>118</v>
       </c>
       <c r="E190" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F190" s="29" t="s">
         <v>63</v>
       </c>
       <c r="G190" s="34"/>
-      <c r="H190" s="34"/>
+      <c r="H190" s="113"/>
       <c r="I190" s="35"/>
       <c r="J190" s="35"/>
       <c r="K190" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="L190" s="87"/>
-      <c r="M190" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N190" s="95"/>
+      <c r="L190" s="84"/>
+      <c r="M190" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N190" s="92"/>
     </row>
     <row r="191" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="68">
@@ -9194,25 +9255,25 @@
         <v>118</v>
       </c>
       <c r="E191" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F191" s="29" t="s">
         <v>63</v>
       </c>
       <c r="G191" s="30"/>
-      <c r="H191" s="30"/>
+      <c r="H191" s="112"/>
       <c r="I191" s="31"/>
       <c r="J191" s="31"/>
       <c r="K191" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="L191" s="86" t="s">
-        <v>486</v>
-      </c>
-      <c r="M191" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N191" s="94"/>
+      <c r="L191" s="83" t="s">
+        <v>485</v>
+      </c>
+      <c r="M191" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N191" s="91"/>
     </row>
     <row r="192" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="68">
@@ -9235,19 +9296,19 @@
         <v>63</v>
       </c>
       <c r="G192" s="34"/>
-      <c r="H192" s="34"/>
+      <c r="H192" s="113"/>
       <c r="I192" s="35"/>
       <c r="J192" s="35"/>
       <c r="K192" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="L192" s="87" t="s">
-        <v>485</v>
-      </c>
-      <c r="M192" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N192" s="95"/>
+      <c r="L192" s="84" t="s">
+        <v>484</v>
+      </c>
+      <c r="M192" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N192" s="92"/>
     </row>
     <row r="193" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="68">
@@ -9270,17 +9331,17 @@
         <v>63</v>
       </c>
       <c r="G193" s="30"/>
-      <c r="H193" s="30"/>
+      <c r="H193" s="112"/>
       <c r="I193" s="31"/>
       <c r="J193" s="31"/>
       <c r="K193" s="27" t="s">
         <v>350</v>
       </c>
-      <c r="L193" s="86"/>
-      <c r="M193" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N193" s="94"/>
+      <c r="L193" s="83"/>
+      <c r="M193" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N193" s="91"/>
     </row>
     <row r="194" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="68">
@@ -9303,17 +9364,17 @@
         <v>63</v>
       </c>
       <c r="G194" s="34"/>
-      <c r="H194" s="34"/>
+      <c r="H194" s="113"/>
       <c r="I194" s="35"/>
       <c r="J194" s="35"/>
       <c r="K194" s="33" t="s">
         <v>350</v>
       </c>
-      <c r="L194" s="87"/>
-      <c r="M194" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N194" s="95"/>
+      <c r="L194" s="84"/>
+      <c r="M194" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N194" s="92"/>
     </row>
     <row r="195" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="68">
@@ -9330,23 +9391,23 @@
         <v>118</v>
       </c>
       <c r="E195" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F195" s="29" t="s">
         <v>63</v>
       </c>
       <c r="G195" s="30"/>
-      <c r="H195" s="30"/>
+      <c r="H195" s="112"/>
       <c r="I195" s="31"/>
       <c r="J195" s="31"/>
       <c r="K195" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="L195" s="86"/>
-      <c r="M195" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N195" s="94"/>
+      <c r="L195" s="83"/>
+      <c r="M195" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N195" s="91"/>
     </row>
     <row r="196" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="68">
@@ -9363,23 +9424,23 @@
         <v>118</v>
       </c>
       <c r="E196" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F196" s="29" t="s">
         <v>63</v>
       </c>
       <c r="G196" s="34"/>
-      <c r="H196" s="34"/>
+      <c r="H196" s="113"/>
       <c r="I196" s="35"/>
       <c r="J196" s="35"/>
       <c r="K196" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="L196" s="87"/>
-      <c r="M196" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N196" s="95"/>
+      <c r="L196" s="84"/>
+      <c r="M196" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N196" s="92"/>
     </row>
     <row r="197" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="68">
@@ -9402,17 +9463,17 @@
         <v>63</v>
       </c>
       <c r="G197" s="30"/>
-      <c r="H197" s="30"/>
+      <c r="H197" s="112"/>
       <c r="I197" s="31"/>
       <c r="J197" s="31"/>
       <c r="K197" s="27" t="s">
         <v>350</v>
       </c>
-      <c r="L197" s="86"/>
-      <c r="M197" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N197" s="94"/>
+      <c r="L197" s="83"/>
+      <c r="M197" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N197" s="91"/>
     </row>
     <row r="198" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="68">
@@ -9435,17 +9496,17 @@
         <v>68</v>
       </c>
       <c r="G198" s="34"/>
-      <c r="H198" s="34"/>
+      <c r="H198" s="113"/>
       <c r="I198" s="35"/>
       <c r="J198" s="35"/>
       <c r="K198" s="33" t="s">
         <v>361</v>
       </c>
-      <c r="L198" s="87"/>
-      <c r="M198" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N198" s="95"/>
+      <c r="L198" s="84"/>
+      <c r="M198" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N198" s="92"/>
     </row>
     <row r="199" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="68">
@@ -9468,17 +9529,17 @@
         <v>68</v>
       </c>
       <c r="G199" s="30"/>
-      <c r="H199" s="30"/>
+      <c r="H199" s="112"/>
       <c r="I199" s="31"/>
       <c r="J199" s="31"/>
       <c r="K199" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="L199" s="86"/>
-      <c r="M199" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N199" s="94"/>
+      <c r="L199" s="83"/>
+      <c r="M199" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N199" s="91"/>
     </row>
     <row r="200" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="68">
@@ -9495,23 +9556,23 @@
         <v>79</v>
       </c>
       <c r="E200" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F200" s="36" t="s">
         <v>68</v>
       </c>
       <c r="G200" s="34"/>
-      <c r="H200" s="34"/>
+      <c r="H200" s="113"/>
       <c r="I200" s="35"/>
       <c r="J200" s="35"/>
       <c r="K200" s="33" t="s">
         <v>366</v>
       </c>
-      <c r="L200" s="87"/>
-      <c r="M200" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N200" s="95"/>
+      <c r="L200" s="84"/>
+      <c r="M200" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N200" s="92"/>
     </row>
     <row r="201" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="68">
@@ -9528,23 +9589,23 @@
         <v>79</v>
       </c>
       <c r="E201" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F201" s="36" t="s">
         <v>68</v>
       </c>
       <c r="G201" s="30"/>
-      <c r="H201" s="30"/>
+      <c r="H201" s="112"/>
       <c r="I201" s="31"/>
       <c r="J201" s="31"/>
       <c r="K201" s="27" t="s">
         <v>369</v>
       </c>
-      <c r="L201" s="86"/>
-      <c r="M201" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N201" s="94"/>
+      <c r="L201" s="83"/>
+      <c r="M201" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N201" s="91"/>
     </row>
     <row r="202" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="68">
@@ -9561,25 +9622,25 @@
         <v>79</v>
       </c>
       <c r="E202" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F202" s="37" t="s">
         <v>75</v>
       </c>
       <c r="G202" s="34"/>
-      <c r="H202" s="34"/>
+      <c r="H202" s="113"/>
       <c r="I202" s="35"/>
       <c r="J202" s="35"/>
       <c r="K202" s="33" t="s">
         <v>372</v>
       </c>
-      <c r="L202" s="87" t="s">
-        <v>484</v>
-      </c>
-      <c r="M202" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N202" s="95"/>
+      <c r="L202" s="84" t="s">
+        <v>483</v>
+      </c>
+      <c r="M202" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N202" s="92"/>
     </row>
     <row r="203" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="68">
@@ -9602,17 +9663,17 @@
         <v>68</v>
       </c>
       <c r="G203" s="30"/>
-      <c r="H203" s="30"/>
+      <c r="H203" s="112"/>
       <c r="I203" s="31"/>
       <c r="J203" s="31"/>
       <c r="K203" s="27" t="s">
         <v>376</v>
       </c>
-      <c r="L203" s="86"/>
-      <c r="M203" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N203" s="94"/>
+      <c r="L203" s="83"/>
+      <c r="M203" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N203" s="91"/>
     </row>
     <row r="204" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="68">
@@ -9635,17 +9696,17 @@
         <v>68</v>
       </c>
       <c r="G204" s="34"/>
-      <c r="H204" s="34"/>
+      <c r="H204" s="113"/>
       <c r="I204" s="35"/>
       <c r="J204" s="35"/>
       <c r="K204" s="33" t="s">
         <v>376</v>
       </c>
-      <c r="L204" s="87"/>
-      <c r="M204" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N204" s="95"/>
+      <c r="L204" s="84"/>
+      <c r="M204" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N204" s="92"/>
     </row>
     <row r="205" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="68">
@@ -9668,17 +9729,17 @@
         <v>68</v>
       </c>
       <c r="G205" s="30"/>
-      <c r="H205" s="30"/>
+      <c r="H205" s="112"/>
       <c r="I205" s="31"/>
       <c r="J205" s="31"/>
       <c r="K205" s="27" t="s">
         <v>381</v>
       </c>
-      <c r="L205" s="86"/>
-      <c r="M205" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N205" s="94"/>
+      <c r="L205" s="83"/>
+      <c r="M205" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N205" s="91"/>
     </row>
     <row r="206" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="68">
@@ -9701,17 +9762,17 @@
         <v>75</v>
       </c>
       <c r="G206" s="34"/>
-      <c r="H206" s="34"/>
+      <c r="H206" s="113"/>
       <c r="I206" s="35"/>
       <c r="J206" s="35"/>
       <c r="K206" s="33" t="s">
         <v>384</v>
       </c>
-      <c r="L206" s="87"/>
-      <c r="M206" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N206" s="95"/>
+      <c r="L206" s="84"/>
+      <c r="M206" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N206" s="92"/>
     </row>
     <row r="207" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="68">
@@ -9734,17 +9795,17 @@
         <v>75</v>
       </c>
       <c r="G207" s="30"/>
-      <c r="H207" s="30"/>
+      <c r="H207" s="112"/>
       <c r="I207" s="31"/>
       <c r="J207" s="31"/>
       <c r="K207" s="27" t="s">
         <v>376</v>
       </c>
-      <c r="L207" s="86"/>
-      <c r="M207" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N207" s="94"/>
+      <c r="L207" s="83"/>
+      <c r="M207" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N207" s="91"/>
     </row>
     <row r="208" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="68">
@@ -9767,17 +9828,17 @@
         <v>75</v>
       </c>
       <c r="G208" s="34"/>
-      <c r="H208" s="34"/>
+      <c r="H208" s="113"/>
       <c r="I208" s="35"/>
       <c r="J208" s="35"/>
       <c r="K208" s="33" t="s">
         <v>376</v>
       </c>
-      <c r="L208" s="87"/>
-      <c r="M208" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N208" s="95"/>
+      <c r="L208" s="84"/>
+      <c r="M208" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N208" s="92"/>
     </row>
     <row r="209" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="68">
@@ -9800,17 +9861,17 @@
         <v>68</v>
       </c>
       <c r="G209" s="30"/>
-      <c r="H209" s="30"/>
+      <c r="H209" s="112"/>
       <c r="I209" s="31"/>
       <c r="J209" s="31"/>
       <c r="K209" s="27" t="s">
         <v>391</v>
       </c>
-      <c r="L209" s="86"/>
-      <c r="M209" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N209" s="94"/>
+      <c r="L209" s="83"/>
+      <c r="M209" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N209" s="91"/>
     </row>
     <row r="210" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="68">
@@ -9833,17 +9894,17 @@
         <v>68</v>
       </c>
       <c r="G210" s="34"/>
-      <c r="H210" s="34"/>
+      <c r="H210" s="113"/>
       <c r="I210" s="35"/>
       <c r="J210" s="35"/>
       <c r="K210" s="33" t="s">
         <v>391</v>
       </c>
-      <c r="L210" s="87"/>
-      <c r="M210" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N210" s="95"/>
+      <c r="L210" s="84"/>
+      <c r="M210" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N210" s="92"/>
     </row>
     <row r="211" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="68">
@@ -9866,17 +9927,17 @@
         <v>75</v>
       </c>
       <c r="G211" s="30"/>
-      <c r="H211" s="30"/>
+      <c r="H211" s="112"/>
       <c r="I211" s="31"/>
       <c r="J211" s="31"/>
       <c r="K211" s="27" t="s">
         <v>376</v>
       </c>
-      <c r="L211" s="86"/>
-      <c r="M211" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N211" s="94"/>
+      <c r="L211" s="83"/>
+      <c r="M211" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N211" s="91"/>
     </row>
     <row r="212" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="68">
@@ -9899,17 +9960,17 @@
         <v>75</v>
       </c>
       <c r="G212" s="34"/>
-      <c r="H212" s="34"/>
+      <c r="H212" s="113"/>
       <c r="I212" s="35"/>
       <c r="J212" s="35"/>
       <c r="K212" s="33" t="s">
         <v>350</v>
       </c>
-      <c r="L212" s="87"/>
-      <c r="M212" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N212" s="95"/>
+      <c r="L212" s="84"/>
+      <c r="M212" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N212" s="92"/>
     </row>
     <row r="213" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="68">
@@ -9932,19 +9993,19 @@
         <v>75</v>
       </c>
       <c r="G213" s="30"/>
-      <c r="H213" s="30"/>
+      <c r="H213" s="112"/>
       <c r="I213" s="31"/>
       <c r="J213" s="31"/>
       <c r="K213" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="L213" s="86" t="s">
-        <v>483</v>
-      </c>
-      <c r="M213" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N213" s="94"/>
+      <c r="L213" s="83" t="s">
+        <v>482</v>
+      </c>
+      <c r="M213" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N213" s="91"/>
     </row>
     <row r="214" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="68">
@@ -9961,23 +10022,23 @@
         <v>61</v>
       </c>
       <c r="E214" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F214" s="37" t="s">
         <v>75</v>
       </c>
       <c r="G214" s="34"/>
-      <c r="H214" s="34"/>
+      <c r="H214" s="113"/>
       <c r="I214" s="35"/>
       <c r="J214" s="35"/>
       <c r="K214" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="L214" s="87"/>
-      <c r="M214" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N214" s="95"/>
+      <c r="L214" s="84"/>
+      <c r="M214" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N214" s="92"/>
     </row>
     <row r="215" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="68">
@@ -10000,17 +10061,17 @@
         <v>75</v>
       </c>
       <c r="G215" s="30"/>
-      <c r="H215" s="30"/>
+      <c r="H215" s="112"/>
       <c r="I215" s="31"/>
       <c r="J215" s="31"/>
       <c r="K215" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="L215" s="86"/>
-      <c r="M215" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N215" s="94"/>
+      <c r="L215" s="83"/>
+      <c r="M215" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N215" s="91"/>
     </row>
     <row r="216" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="68">
@@ -10033,17 +10094,17 @@
         <v>63</v>
       </c>
       <c r="G216" s="34"/>
-      <c r="H216" s="34"/>
+      <c r="H216" s="113"/>
       <c r="I216" s="35"/>
       <c r="J216" s="35"/>
       <c r="K216" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="L216" s="87"/>
-      <c r="M216" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N216" s="95"/>
+      <c r="L216" s="84"/>
+      <c r="M216" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N216" s="92"/>
     </row>
     <row r="217" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="68">
@@ -10060,23 +10121,23 @@
         <v>79</v>
       </c>
       <c r="E217" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F217" s="29" t="s">
         <v>63</v>
       </c>
       <c r="G217" s="30"/>
-      <c r="H217" s="30"/>
+      <c r="H217" s="112"/>
       <c r="I217" s="31"/>
       <c r="J217" s="31"/>
       <c r="K217" s="27" t="s">
         <v>350</v>
       </c>
-      <c r="L217" s="86"/>
-      <c r="M217" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N217" s="94"/>
+      <c r="L217" s="83"/>
+      <c r="M217" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N217" s="91"/>
     </row>
     <row r="218" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="68">
@@ -10099,17 +10160,17 @@
         <v>63</v>
       </c>
       <c r="G218" s="34"/>
-      <c r="H218" s="34"/>
+      <c r="H218" s="113"/>
       <c r="I218" s="35"/>
       <c r="J218" s="35"/>
       <c r="K218" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="L218" s="87"/>
-      <c r="M218" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N218" s="95"/>
+      <c r="L218" s="84"/>
+      <c r="M218" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N218" s="92"/>
     </row>
     <row r="219" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="68">
@@ -10126,23 +10187,23 @@
         <v>79</v>
       </c>
       <c r="E219" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F219" s="29" t="s">
         <v>63</v>
       </c>
       <c r="G219" s="30"/>
-      <c r="H219" s="30"/>
+      <c r="H219" s="112"/>
       <c r="I219" s="31"/>
       <c r="J219" s="31"/>
       <c r="K219" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="L219" s="86"/>
-      <c r="M219" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N219" s="94"/>
+      <c r="L219" s="83"/>
+      <c r="M219" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N219" s="91"/>
     </row>
     <row r="220" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="68">
@@ -10159,23 +10220,23 @@
         <v>79</v>
       </c>
       <c r="E220" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F220" s="37" t="s">
         <v>75</v>
       </c>
       <c r="G220" s="34"/>
-      <c r="H220" s="34"/>
+      <c r="H220" s="113"/>
       <c r="I220" s="35"/>
       <c r="J220" s="35"/>
       <c r="K220" s="33" t="s">
         <v>336</v>
       </c>
-      <c r="L220" s="87"/>
-      <c r="M220" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N220" s="95"/>
+      <c r="L220" s="84"/>
+      <c r="M220" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N220" s="92"/>
     </row>
     <row r="221" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="68">
@@ -10192,23 +10253,23 @@
         <v>79</v>
       </c>
       <c r="E221" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F221" s="37" t="s">
         <v>75</v>
       </c>
       <c r="G221" s="30"/>
-      <c r="H221" s="30"/>
+      <c r="H221" s="112"/>
       <c r="I221" s="31"/>
       <c r="J221" s="31"/>
       <c r="K221" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="L221" s="86"/>
-      <c r="M221" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N221" s="94"/>
+      <c r="L221" s="83"/>
+      <c r="M221" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N221" s="91"/>
     </row>
     <row r="222" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="68">
@@ -10225,23 +10286,23 @@
         <v>79</v>
       </c>
       <c r="E222" s="28" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F222" s="37" t="s">
         <v>75</v>
       </c>
       <c r="G222" s="34"/>
-      <c r="H222" s="34"/>
+      <c r="H222" s="113"/>
       <c r="I222" s="35"/>
       <c r="J222" s="35"/>
       <c r="K222" s="33" t="s">
         <v>420</v>
       </c>
-      <c r="L222" s="87"/>
-      <c r="M222" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N222" s="95"/>
+      <c r="L222" s="84"/>
+      <c r="M222" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N222" s="92"/>
     </row>
     <row r="223" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="68">
@@ -10262,17 +10323,17 @@
         <v>63</v>
       </c>
       <c r="G223" s="30"/>
-      <c r="H223" s="30"/>
+      <c r="H223" s="112"/>
       <c r="I223" s="31"/>
       <c r="J223" s="31"/>
       <c r="K223" s="27" t="s">
         <v>423</v>
       </c>
-      <c r="L223" s="86"/>
-      <c r="M223" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N223" s="94"/>
+      <c r="L223" s="83"/>
+      <c r="M223" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N223" s="91"/>
     </row>
     <row r="224" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="68">
@@ -10295,17 +10356,17 @@
         <v>63</v>
       </c>
       <c r="G224" s="34"/>
-      <c r="H224" s="34"/>
+      <c r="H224" s="113"/>
       <c r="I224" s="35"/>
       <c r="J224" s="35"/>
       <c r="K224" s="33" t="s">
         <v>426</v>
       </c>
-      <c r="L224" s="87"/>
-      <c r="M224" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N224" s="95"/>
+      <c r="L224" s="84"/>
+      <c r="M224" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N224" s="92"/>
     </row>
     <row r="225" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="68">
@@ -10328,17 +10389,17 @@
         <v>63</v>
       </c>
       <c r="G225" s="30"/>
-      <c r="H225" s="30"/>
+      <c r="H225" s="112"/>
       <c r="I225" s="31"/>
       <c r="J225" s="31"/>
       <c r="K225" s="27" t="s">
         <v>426</v>
       </c>
-      <c r="L225" s="86"/>
-      <c r="M225" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N225" s="94"/>
+      <c r="L225" s="83"/>
+      <c r="M225" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N225" s="91"/>
     </row>
     <row r="226" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="68">
@@ -10361,19 +10422,19 @@
         <v>68</v>
       </c>
       <c r="G226" s="34"/>
-      <c r="H226" s="35"/>
+      <c r="H226" s="113"/>
       <c r="I226" s="35"/>
       <c r="J226" s="35"/>
       <c r="K226" s="33" t="s">
         <v>431</v>
       </c>
-      <c r="L226" s="87" t="s">
+      <c r="L226" s="84" t="s">
         <v>432</v>
       </c>
-      <c r="M226" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N226" s="95"/>
+      <c r="M226" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N226" s="92"/>
     </row>
     <row r="227" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="68">
@@ -10396,19 +10457,19 @@
         <v>68</v>
       </c>
       <c r="G227" s="30"/>
-      <c r="H227" s="31"/>
+      <c r="H227" s="112"/>
       <c r="I227" s="31"/>
       <c r="J227" s="31"/>
       <c r="K227" s="27" t="s">
         <v>435</v>
       </c>
-      <c r="L227" s="86" t="s">
+      <c r="L227" s="83" t="s">
         <v>432</v>
       </c>
-      <c r="M227" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N227" s="94"/>
+      <c r="M227" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N227" s="91"/>
     </row>
     <row r="228" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="68">
@@ -10431,19 +10492,19 @@
         <v>63</v>
       </c>
       <c r="G228" s="34"/>
-      <c r="H228" s="34"/>
+      <c r="H228" s="113"/>
       <c r="I228" s="35"/>
       <c r="J228" s="35"/>
       <c r="K228" s="33" t="s">
         <v>438</v>
       </c>
-      <c r="L228" s="87" t="s">
-        <v>482</v>
-      </c>
-      <c r="M228" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N228" s="95"/>
+      <c r="L228" s="84" t="s">
+        <v>481</v>
+      </c>
+      <c r="M228" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N228" s="92"/>
     </row>
     <row r="229" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="68">
@@ -10466,19 +10527,19 @@
         <v>63</v>
       </c>
       <c r="G229" s="30"/>
-      <c r="H229" s="30"/>
+      <c r="H229" s="112"/>
       <c r="I229" s="31"/>
       <c r="J229" s="31"/>
       <c r="K229" s="27" t="s">
         <v>441</v>
       </c>
-      <c r="L229" s="86" t="s">
-        <v>481</v>
-      </c>
-      <c r="M229" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N229" s="94"/>
+      <c r="L229" s="83" t="s">
+        <v>480</v>
+      </c>
+      <c r="M229" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N229" s="91"/>
     </row>
     <row r="230" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="68">
@@ -10501,19 +10562,19 @@
         <v>63</v>
       </c>
       <c r="G230" s="34"/>
-      <c r="H230" s="35"/>
+      <c r="H230" s="113"/>
       <c r="I230" s="35"/>
       <c r="J230" s="35"/>
       <c r="K230" s="33" t="s">
         <v>444</v>
       </c>
-      <c r="L230" s="87" t="s">
+      <c r="L230" s="84" t="s">
         <v>445</v>
       </c>
-      <c r="M230" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N230" s="95"/>
+      <c r="M230" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N230" s="92"/>
     </row>
     <row r="231" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="68">
@@ -10536,19 +10597,19 @@
         <v>63</v>
       </c>
       <c r="G231" s="30"/>
-      <c r="H231" s="31"/>
+      <c r="H231" s="112"/>
       <c r="I231" s="31"/>
       <c r="J231" s="31"/>
       <c r="K231" s="27" t="s">
         <v>444</v>
       </c>
-      <c r="L231" s="86" t="s">
+      <c r="L231" s="83" t="s">
         <v>448</v>
       </c>
-      <c r="M231" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N231" s="94"/>
+      <c r="M231" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N231" s="91"/>
     </row>
     <row r="232" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="68">
@@ -10571,19 +10632,19 @@
         <v>63</v>
       </c>
       <c r="G232" s="34"/>
-      <c r="H232" s="34"/>
+      <c r="H232" s="113"/>
       <c r="I232" s="35"/>
       <c r="J232" s="35"/>
       <c r="K232" s="33" t="s">
         <v>451</v>
       </c>
-      <c r="L232" s="87" t="s">
+      <c r="L232" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="M232" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="N232" s="95"/>
+      <c r="M232" s="98" t="s">
+        <v>64</v>
+      </c>
+      <c r="N232" s="92"/>
     </row>
     <row r="233" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="68">
@@ -10606,17 +10667,17 @@
         <v>63</v>
       </c>
       <c r="G233" s="50"/>
-      <c r="H233" s="50"/>
+      <c r="H233" s="114"/>
       <c r="I233" s="51"/>
       <c r="J233" s="51"/>
       <c r="K233" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="L233" s="88"/>
-      <c r="M233" s="102" t="s">
-        <v>64</v>
-      </c>
-      <c r="N233" s="96"/>
+      <c r="L233" s="85"/>
+      <c r="M233" s="99" t="s">
+        <v>64</v>
+      </c>
+      <c r="N233" s="93"/>
     </row>
     <row r="234" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="68">
@@ -10633,21 +10694,27 @@
         <v>89</v>
       </c>
       <c r="E234" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F234" s="55" t="s">
         <v>63</v>
       </c>
       <c r="G234" s="56"/>
-      <c r="H234" s="57"/>
-      <c r="I234" s="57"/>
-      <c r="J234" s="57"/>
+      <c r="H234" s="115">
+        <v>10</v>
+      </c>
+      <c r="I234" s="57">
+        <v>46202</v>
+      </c>
+      <c r="J234" s="57">
+        <v>46203</v>
+      </c>
       <c r="K234" s="53"/>
-      <c r="L234" s="89"/>
-      <c r="M234" s="103" t="s">
-        <v>64</v>
-      </c>
-      <c r="N234" s="97"/>
+      <c r="L234" s="86"/>
+      <c r="M234" s="100" t="s">
+        <v>64</v>
+      </c>
+      <c r="N234" s="94"/>
     </row>
     <row r="235" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="68">
@@ -10670,7 +10737,7 @@
         <v>75</v>
       </c>
       <c r="G235" s="62"/>
-      <c r="H235" s="63"/>
+      <c r="H235" s="116"/>
       <c r="I235" s="63"/>
       <c r="J235" s="63"/>
       <c r="K235" s="59" t="s">
@@ -10679,10 +10746,10 @@
       <c r="L235" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="M235" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="N235" s="98"/>
+      <c r="M235" s="101" t="s">
+        <v>64</v>
+      </c>
+      <c r="N235" s="95"/>
     </row>
     <row r="236" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="68">
@@ -10705,17 +10772,17 @@
         <v>75</v>
       </c>
       <c r="G236" s="66"/>
-      <c r="H236" s="67"/>
+      <c r="H236" s="117"/>
       <c r="I236" s="67"/>
       <c r="J236" s="67"/>
       <c r="K236" s="65" t="s">
         <v>462</v>
       </c>
       <c r="L236" s="74" t="s">
-        <v>73</v>
-      </c>
-      <c r="M236" s="104"/>
-      <c r="N236" s="99"/>
+        <v>492</v>
+      </c>
+      <c r="M236" s="101"/>
+      <c r="N236" s="96"/>
     </row>
     <row r="237" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="68">
@@ -10738,17 +10805,17 @@
         <v>75</v>
       </c>
       <c r="G237" s="72"/>
-      <c r="H237" s="63"/>
+      <c r="H237" s="116"/>
       <c r="I237" s="63"/>
       <c r="J237" s="63"/>
       <c r="K237" s="59" t="s">
         <v>462</v>
       </c>
       <c r="L237" s="70" t="s">
-        <v>73</v>
-      </c>
-      <c r="M237" s="104"/>
-      <c r="N237" s="98"/>
+        <v>492</v>
+      </c>
+      <c r="M237" s="101"/>
+      <c r="N237" s="95"/>
     </row>
     <row r="238" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="68">
@@ -10770,17 +10837,21 @@
         <v>68</v>
       </c>
       <c r="G238" s="76"/>
-      <c r="H238" s="67"/>
-      <c r="I238" s="67"/>
+      <c r="H238" s="117">
+        <v>10</v>
+      </c>
+      <c r="I238" s="67">
+        <v>46206</v>
+      </c>
       <c r="J238" s="67">
         <v>46209</v>
       </c>
       <c r="K238" s="65"/>
       <c r="L238" s="74"/>
-      <c r="M238" s="104" t="s">
+      <c r="M238" s="101" t="s">
         <v>240</v>
       </c>
-      <c r="N238" s="99"/>
+      <c r="N238" s="96"/>
     </row>
     <row r="239" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="68">
@@ -10802,17 +10873,17 @@
         <v>63</v>
       </c>
       <c r="G239" s="72"/>
-      <c r="H239" s="63"/>
+      <c r="H239" s="116"/>
       <c r="I239" s="63"/>
       <c r="J239" s="63">
         <v>46210</v>
       </c>
       <c r="K239" s="59"/>
       <c r="L239" s="70"/>
-      <c r="M239" s="104" t="s">
+      <c r="M239" s="101" t="s">
         <v>240</v>
       </c>
-      <c r="N239" s="98"/>
+      <c r="N239" s="95"/>
     </row>
     <row r="240" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="68">
@@ -10834,7 +10905,9 @@
         <v>68</v>
       </c>
       <c r="G240" s="76"/>
-      <c r="H240" s="67"/>
+      <c r="H240" s="109">
+        <v>2</v>
+      </c>
       <c r="I240" s="67"/>
       <c r="J240" s="67">
         <v>46205</v>
@@ -10843,10 +10916,10 @@
       <c r="L240" s="74" t="s">
         <v>476</v>
       </c>
-      <c r="M240" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="N240" s="99"/>
+      <c r="M240" s="101" t="s">
+        <v>64</v>
+      </c>
+      <c r="N240" s="96"/>
     </row>
     <row r="241" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="68">
@@ -10868,17 +10941,19 @@
         <v>68</v>
       </c>
       <c r="G241" s="72"/>
-      <c r="H241" s="63"/>
+      <c r="H241" s="116">
+        <v>10</v>
+      </c>
       <c r="I241" s="63"/>
       <c r="J241" s="63">
         <v>46210</v>
       </c>
       <c r="K241" s="59"/>
       <c r="L241" s="70"/>
-      <c r="M241" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="N241" s="98"/>
+      <c r="M241" s="101" t="s">
+        <v>64</v>
+      </c>
+      <c r="N241" s="95"/>
     </row>
     <row r="242" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="68">
@@ -10888,32 +10963,40 @@
         <v>478</v>
       </c>
       <c r="C242" s="64" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="D242" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="E242" s="81"/>
+        <v>79</v>
+      </c>
+      <c r="E242" s="78"/>
       <c r="F242" s="73" t="s">
         <v>63</v>
       </c>
       <c r="G242" s="76"/>
-      <c r="H242" s="67"/>
-      <c r="I242" s="67"/>
-      <c r="J242" s="67"/>
+      <c r="H242" s="117">
+        <v>6</v>
+      </c>
+      <c r="I242" s="67">
+        <v>46205</v>
+      </c>
+      <c r="J242" s="67">
+        <v>46206</v>
+      </c>
       <c r="K242" s="65"/>
-      <c r="L242" s="74"/>
-      <c r="M242" s="104" t="s">
-        <v>64</v>
-      </c>
-      <c r="N242" s="99"/>
+      <c r="L242" s="74" t="s">
+        <v>496</v>
+      </c>
+      <c r="M242" s="101" t="s">
+        <v>64</v>
+      </c>
+      <c r="N242" s="96"/>
     </row>
     <row r="243" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="68">
         <v>242</v>
       </c>
       <c r="B243" s="58" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C243" s="58"/>
       <c r="D243" s="70" t="s">
@@ -10926,59 +11009,63 @@
         <v>63</v>
       </c>
       <c r="G243" s="72"/>
-      <c r="H243" s="63"/>
+      <c r="H243" s="116"/>
       <c r="I243" s="63"/>
       <c r="J243" s="63">
         <v>46210</v>
       </c>
       <c r="K243" s="59"/>
       <c r="L243" s="70"/>
-      <c r="M243" s="104" t="s">
+      <c r="M243" s="101" t="s">
         <v>240</v>
       </c>
-      <c r="N243" s="98"/>
+      <c r="N243" s="95"/>
     </row>
     <row r="244" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="68">
         <v>243</v>
       </c>
       <c r="B244" s="64" t="s">
+        <v>486</v>
+      </c>
+      <c r="C244" s="64" t="s">
         <v>487</v>
-      </c>
-      <c r="C244" s="64" t="s">
-        <v>488</v>
       </c>
       <c r="D244" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="E244" s="81" t="s">
+      <c r="E244" s="78" t="s">
         <v>73</v>
       </c>
       <c r="F244" s="73" t="s">
         <v>63</v>
       </c>
       <c r="G244" s="76"/>
-      <c r="H244" s="67"/>
+      <c r="H244" s="117">
+        <v>1</v>
+      </c>
       <c r="I244" s="67"/>
-      <c r="J244" s="67"/>
+      <c r="J244" s="67">
+        <v>46210</v>
+      </c>
       <c r="K244" s="65"/>
       <c r="L244" s="74" t="s">
-        <v>489</v>
-      </c>
-      <c r="M244" s="104" t="s">
+        <v>488</v>
+      </c>
+      <c r="M244" s="101" t="s">
         <v>240</v>
       </c>
-      <c r="N244" s="99"/>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N244" s="96"/>
+    </row>
+    <row r="245" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="68">
         <v>244</v>
       </c>
       <c r="B245" s="58" t="s">
+        <v>490</v>
+      </c>
+      <c r="C245" s="58" t="s">
         <v>491</v>
-      </c>
-      <c r="C245" s="58" t="s">
-        <v>492</v>
       </c>
       <c r="D245" s="70" t="s">
         <v>79</v>
@@ -10990,27 +11077,127 @@
         <v>68</v>
       </c>
       <c r="G245" s="72"/>
-      <c r="H245" s="63"/>
-      <c r="I245" s="63"/>
+      <c r="H245" s="116">
+        <v>6</v>
+      </c>
+      <c r="I245" s="63">
+        <v>46205</v>
+      </c>
       <c r="J245" s="63">
         <v>46210</v>
       </c>
       <c r="K245" s="59"/>
       <c r="L245" s="70"/>
-      <c r="M245" s="104"/>
-      <c r="N245" s="98"/>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I246" s="69"/>
-      <c r="J246" s="69"/>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I247" s="69"/>
-      <c r="J247" s="69"/>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I248" s="69"/>
-      <c r="J248" s="69"/>
+      <c r="M245" s="101"/>
+      <c r="N245" s="95"/>
+    </row>
+    <row r="246" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="68">
+        <v>245</v>
+      </c>
+      <c r="B246" s="64" t="s">
+        <v>494</v>
+      </c>
+      <c r="C246" s="64" t="s">
+        <v>495</v>
+      </c>
+      <c r="D246" s="74" t="s">
+        <v>89</v>
+      </c>
+      <c r="E246" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="F246" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="G246" s="76"/>
+      <c r="H246" s="117">
+        <v>6</v>
+      </c>
+      <c r="I246" s="67">
+        <v>46205</v>
+      </c>
+      <c r="J246" s="67">
+        <v>46234</v>
+      </c>
+      <c r="K246" s="65"/>
+      <c r="L246" s="74"/>
+      <c r="M246" s="101" t="s">
+        <v>119</v>
+      </c>
+      <c r="N246" s="96"/>
+    </row>
+    <row r="247" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="68">
+        <v>246</v>
+      </c>
+      <c r="B247" s="58" t="s">
+        <v>498</v>
+      </c>
+      <c r="C247" s="58" t="s">
+        <v>500</v>
+      </c>
+      <c r="D247" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="E247" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="F247" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="G247" s="72"/>
+      <c r="H247" s="116">
+        <v>4</v>
+      </c>
+      <c r="I247" s="63">
+        <v>46206</v>
+      </c>
+      <c r="J247" s="63">
+        <v>46206</v>
+      </c>
+      <c r="K247" s="59"/>
+      <c r="L247" s="70"/>
+      <c r="M247" s="101" t="s">
+        <v>64</v>
+      </c>
+      <c r="N247" s="95"/>
+    </row>
+    <row r="248" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A248" s="68">
+        <v>247</v>
+      </c>
+      <c r="B248" s="64" t="s">
+        <v>499</v>
+      </c>
+      <c r="C248" s="64" t="s">
+        <v>501</v>
+      </c>
+      <c r="D248" s="74" t="s">
+        <v>89</v>
+      </c>
+      <c r="E248" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="F248" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="G248" s="76"/>
+      <c r="H248" s="117">
+        <v>4</v>
+      </c>
+      <c r="I248" s="67">
+        <v>46210</v>
+      </c>
+      <c r="J248" s="67">
+        <v>46210</v>
+      </c>
+      <c r="K248" s="65"/>
+      <c r="L248" s="74"/>
+      <c r="M248" s="101" t="s">
+        <v>64</v>
+      </c>
+      <c r="N248" s="96"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I249" s="69"/>
@@ -14022,44 +14209,34 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M181" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
-  <conditionalFormatting sqref="G246:M1048576 G2:N245 A2:D1048576">
-    <cfRule type="expression" dxfId="9" priority="1">
-      <formula>AND($B2&lt;&gt;"",ISEVEN(ROW()))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E300">
-    <cfRule type="expression" dxfId="7" priority="15">
+  <conditionalFormatting sqref="E250:E300 E2:E248">
+    <cfRule type="expression" dxfId="8" priority="15">
       <formula>$E2="Done"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E300">
-    <cfRule type="expression" dxfId="6" priority="16">
+    <cfRule type="expression" dxfId="7" priority="16">
       <formula>$E2="In progress"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E300">
-    <cfRule type="expression" dxfId="5" priority="17">
+    <cfRule type="expression" dxfId="6" priority="17">
       <formula>$E2="In review"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E300">
-    <cfRule type="expression" dxfId="4" priority="18">
+    <cfRule type="expression" dxfId="5" priority="18">
       <formula>$E2="Backlog"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F300">
-    <cfRule type="expression" dxfId="3" priority="19">
+    <cfRule type="expression" dxfId="4" priority="19">
       <formula>$F2="High"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F300">
-    <cfRule type="expression" dxfId="2" priority="20">
+    <cfRule type="expression" dxfId="3" priority="20">
       <formula>$F2="Medium"</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="2" priority="21">
+      <formula>$F2="Low"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F300">
-    <cfRule type="expression" dxfId="1" priority="21">
-      <formula>$F2="Low"</formula>
+  <conditionalFormatting sqref="G249:M1048576 G2:N248 A2:D1048576">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AND($B2&lt;&gt;"",ISEVEN(ROW()))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
@@ -14073,7 +14250,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F300" xr:uid="{C1780BFE-B567-4F5D-87FE-F9B5A57B4712}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E245:E300 E2:E243" xr:uid="{6858018E-BA70-46A0-BA18-28D3782838CF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E243 E245:E248 E250:E300" xr:uid="{6858018E-BA70-46A0-BA18-28D3782838CF}">
       <formula1>"Backlog,In progress,In review,Done"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M300" xr:uid="{8D5FF901-AF31-4455-A46F-0DE26D440B1D}">
@@ -14152,26 +14329,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -14426,10 +14583,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
+    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14446,20 +14634,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
-    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="3923" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7824CDDF-1735-47AF-98F8-BA7EBD15F3B2}"/>
+  <xr:revisionPtr revIDLastSave="3998" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3A51BA9-20D2-4560-BDD8-F2D0DC300AD2}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,7 @@
     <sheet name="Team" sheetId="2" state="veryHidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'KII Tasks'!$A$1:$M$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'KII Tasks'!$A$1:$M$273</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="551">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -285,6 +285,9 @@
     <t>Ensure RAPID code is always maintained at the latest stable version</t>
   </si>
   <si>
+    <t>Done</t>
+  </si>
+  <si>
     <t>robot,rapid</t>
   </si>
   <si>
@@ -357,6 +360,9 @@
     <t>Dignose laser flickering, switch from encoder base to time base and detect if the laser became solid, if so, swap the encoder.</t>
   </si>
   <si>
+    <t>Encoder and cameras are ok, problem could be the calibration, tool definition</t>
+  </si>
+  <si>
     <t>Add current recipe settings page</t>
   </si>
   <si>
@@ -534,9 +540,6 @@
     <t>dilinaabi, ashiqul-abi</t>
   </si>
   <si>
-    <t>Done</t>
-  </si>
-  <si>
     <t>Critical UI Bugs Fix</t>
   </si>
   <si>
@@ -1587,13 +1590,13 @@
     <t>Change the visibilyt on some menu items in the settings based on logged in user</t>
   </si>
   <si>
+    <t>Disable Text Selection</t>
+  </si>
+  <si>
+    <t>Disable text selection behavior across the web view. when empty spaces are accidentally clicked and held it would select the text.</t>
+  </si>
+  <si>
     <t>BDF Feedback</t>
-  </si>
-  <si>
-    <t>Disable Text Selection</t>
-  </si>
-  <si>
-    <t>Disable text selection behavior across the web view. when empty spaces are accidentally clicked and held it would select the text.</t>
   </si>
   <si>
     <t>Fix Robot Label Alignment</t>
@@ -1622,6 +1625,9 @@
   </si>
   <si>
     <t>Katana PLC Settings Control</t>
+  </si>
+  <si>
+    <t>Update the system to manage all Line PLC settings via Katana on a per-recipe basis.  The customer wants every line setting available on Katana so they can modify everything from the Katana interface and save it directly to the recipe. Check with JM and Raphael</t>
   </si>
   <si>
     <t>Phantom Folder Image Saving</t>
@@ -1659,6 +1665,9 @@
     <t>BDF SCADA Integration / Export Feature</t>
   </si>
   <si>
+    <t> Explore the possibility of connecting with the BDF SCADA system to push production page data for internal continuous improvement. At least, look into adding a dedicated export button to allow manual extraction of production data. Check with JM and Raphael</t>
+  </si>
+  <si>
     <t>Automated Incident Reports</t>
   </si>
   <si>
@@ -1680,13 +1689,10 @@
     <t>ThongHHuynhh</t>
   </si>
   <si>
-    <t>Update the system to manage all Line PLC settings via Katana on a per-recipe basis.  The customer wants every line setting available on Katana so they can modify everything from the Katana interface and save it directly to the recipe. Check with JM and Raphael</t>
-  </si>
-  <si>
-    <t> Explore the possibility of connecting with the BDF SCADA system to push production page data for internal continuous improvement. At least, look into adding a dedicated export button to allow manual extraction of production data. Check with JM and Raphael</t>
-  </si>
-  <si>
-    <t>Encoder and cameras are ok, problem could be the calibration, tool definition</t>
+    <t>Gonnella EyeQ commisioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation and gonnella EyeQ commisioning </t>
   </si>
 </sst>
 </file>
@@ -1696,7 +1702,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1834,6 +1840,17 @@
       <sz val="11"/>
       <color rgb="FF375623"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7F6000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1943,7 +1960,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -2242,11 +2259,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF2F75B6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -2480,9 +2510,6 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2541,9 +2568,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2577,9 +2601,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2590,9 +2611,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2606,6 +2624,48 @@
     <xf numFmtId="0" fontId="10" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2615,56 +2675,93 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2789,6 +2886,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3150,22 +3251,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="124"/>
+      <c r="C2" s="134"/>
     </row>
     <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="135" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="125"/>
+      <c r="C4" s="135"/>
     </row>
     <row r="6" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="123" t="s">
+      <c r="B6" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="123"/>
+      <c r="C6" s="133"/>
     </row>
     <row r="7" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -3192,10 +3293,10 @@
       </c>
     </row>
     <row r="11" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="123" t="s">
+      <c r="B11" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="123"/>
+      <c r="C11" s="133"/>
     </row>
     <row r="12" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
@@ -3294,10 +3395,10 @@
       </c>
     </row>
     <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="123" t="s">
+      <c r="B25" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="123"/>
+      <c r="C25" s="133"/>
     </row>
     <row r="26" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
@@ -3348,10 +3449,10 @@
       </c>
     </row>
     <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="123" t="s">
+      <c r="B33" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="123"/>
+      <c r="C33" s="133"/>
     </row>
     <row r="34" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
@@ -3430,47 +3531,47 @@
     <col min="14" max="14" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="118" customFormat="1" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="119" t="s">
+    <row r="1" spans="1:14" s="114" customFormat="1" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="120" t="s">
+      <c r="B1" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="120" t="s">
+      <c r="C1" s="116" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="120" t="s">
+      <c r="D1" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="120" t="s">
+      <c r="E1" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="120" t="s">
+      <c r="F1" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="120" t="s">
+      <c r="G1" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="120" t="s">
+      <c r="H1" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="120" t="s">
+      <c r="J1" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="120" t="s">
+      <c r="K1" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="120" t="s">
+      <c r="L1" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="121" t="s">
+      <c r="M1" s="117" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="122" t="s">
+      <c r="N1" s="118" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3504,16 +3605,16 @@
       <c r="N2" s="52"/>
     </row>
     <row r="3" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="99">
+      <c r="A3" s="98">
         <v>248</v>
       </c>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="107" t="s">
+      <c r="C3" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="109" t="s">
+      <c r="D3" s="107" t="s">
         <v>67</v>
       </c>
       <c r="E3" s="76" t="s">
@@ -3522,21 +3623,21 @@
       <c r="F3" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="109"/>
-      <c r="H3" s="111">
+      <c r="G3" s="107"/>
+      <c r="H3" s="109">
         <v>10</v>
       </c>
-      <c r="I3" s="113">
+      <c r="I3" s="110">
         <v>46209</v>
       </c>
-      <c r="J3" s="113">
+      <c r="J3" s="110">
         <v>46210</v>
       </c>
-      <c r="K3" s="109" t="s">
+      <c r="K3" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="114"/>
-      <c r="M3" s="109"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="107"/>
       <c r="N3" s="53"/>
     </row>
     <row r="4" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3688,7 +3789,7 @@
         <v>79</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>73</v>
@@ -3698,10 +3799,10 @@
       <c r="I8" s="31"/>
       <c r="J8" s="31"/>
       <c r="K8" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L8" s="50" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M8" s="62" t="s">
         <v>64</v>
@@ -3714,10 +3815,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>79</v>
@@ -3733,10 +3834,10 @@
       <c r="I9" s="27"/>
       <c r="J9" s="27"/>
       <c r="K9" s="23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L9" s="49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M9" s="62" t="s">
         <v>64</v>
@@ -3749,10 +3850,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="29" t="s">
         <v>79</v>
@@ -3768,7 +3869,7 @@
       <c r="I10" s="31"/>
       <c r="J10" s="31"/>
       <c r="K10" s="29" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L10" s="50" t="s">
         <v>72</v>
@@ -3784,10 +3885,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>79</v>
@@ -3803,7 +3904,7 @@
       <c r="I11" s="27"/>
       <c r="J11" s="27"/>
       <c r="K11" s="23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L11" s="49"/>
       <c r="M11" s="62" t="s">
@@ -3816,32 +3917,32 @@
         <v>238</v>
       </c>
       <c r="B12" s="65" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" s="65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" s="70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12" s="76" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F12" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="88"/>
-      <c r="J12" s="88">
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87">
         <v>46210</v>
       </c>
-      <c r="K12" s="88">
+      <c r="K12" s="87">
         <v>46211</v>
       </c>
-      <c r="L12" s="93"/>
-      <c r="M12" s="97" t="s">
-        <v>96</v>
+      <c r="L12" s="92"/>
+      <c r="M12" s="96" t="s">
+        <v>97</v>
       </c>
       <c r="N12" s="53"/>
     </row>
@@ -3850,10 +3951,10 @@
         <v>241</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" s="66" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" s="71" t="s">
         <v>67</v>
@@ -3864,21 +3965,21 @@
       <c r="F13" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84">
+      <c r="G13" s="83"/>
+      <c r="H13" s="83">
         <v>6</v>
       </c>
-      <c r="I13" s="89">
+      <c r="I13" s="88">
         <v>46205</v>
       </c>
-      <c r="J13" s="89">
+      <c r="J13" s="88">
         <v>46206</v>
       </c>
       <c r="K13" s="71"/>
-      <c r="L13" s="94" t="s">
-        <v>99</v>
-      </c>
-      <c r="M13" s="97" t="s">
+      <c r="L13" s="93" t="s">
+        <v>100</v>
+      </c>
+      <c r="M13" s="96" t="s">
         <v>64</v>
       </c>
       <c r="N13" s="53"/>
@@ -3888,7 +3989,7 @@
         <v>242</v>
       </c>
       <c r="B14" s="65" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="65"/>
       <c r="D14" s="70" t="s">
@@ -3900,16 +4001,16 @@
       <c r="F14" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="88"/>
-      <c r="J14" s="88">
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87">
         <v>46210</v>
       </c>
       <c r="K14" s="70"/>
-      <c r="L14" s="93"/>
-      <c r="M14" s="97" t="s">
-        <v>96</v>
+      <c r="L14" s="92"/>
+      <c r="M14" s="96" t="s">
+        <v>97</v>
       </c>
       <c r="N14" s="53"/>
     </row>
@@ -3918,10 +4019,10 @@
         <v>243</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" s="71" t="s">
         <v>67</v>
@@ -3932,20 +4033,20 @@
       <c r="F15" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84">
+      <c r="G15" s="83"/>
+      <c r="H15" s="83">
         <v>1</v>
       </c>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89">
+      <c r="I15" s="88"/>
+      <c r="J15" s="88">
         <v>46210</v>
       </c>
       <c r="K15" s="71"/>
-      <c r="L15" s="94" t="s">
-        <v>103</v>
-      </c>
-      <c r="M15" s="97" t="s">
-        <v>96</v>
+      <c r="L15" s="93" t="s">
+        <v>104</v>
+      </c>
+      <c r="M15" s="96" t="s">
+        <v>97</v>
       </c>
       <c r="N15" s="53"/>
     </row>
@@ -3954,35 +4055,35 @@
         <v>247</v>
       </c>
       <c r="B16" s="66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D16" s="71" t="s">
         <v>79</v>
       </c>
       <c r="E16" s="78" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F16" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="84"/>
-      <c r="H16" s="84">
+      <c r="G16" s="83"/>
+      <c r="H16" s="83">
         <v>4</v>
       </c>
-      <c r="I16" s="89">
+      <c r="I16" s="88">
         <v>46210</v>
       </c>
-      <c r="J16" s="89">
+      <c r="J16" s="88">
         <v>46211</v>
       </c>
       <c r="K16" s="71"/>
-      <c r="L16" s="94" t="s">
-        <v>548</v>
-      </c>
-      <c r="M16" s="97" t="s">
+      <c r="L16" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="M16" s="96" t="s">
         <v>64</v>
       </c>
       <c r="N16" s="53"/>
@@ -3993,10 +4094,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>67</v>
@@ -4024,10 +4125,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>67</v>
@@ -4055,10 +4156,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="11" t="s">
@@ -4084,10 +4185,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11" t="s">
@@ -4113,10 +4214,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>67</v>
@@ -4140,7 +4241,7 @@
       <c r="K21" s="10"/>
       <c r="L21" s="47"/>
       <c r="M21" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N21" s="53"/>
     </row>
@@ -4150,10 +4251,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>79</v>
@@ -4187,13 +4288,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>72</v>
@@ -4210,7 +4311,7 @@
       <c r="K23" s="10"/>
       <c r="L23" s="47"/>
       <c r="M23" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N23" s="53"/>
     </row>
@@ -4220,13 +4321,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="65" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D24" s="70" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E24" s="76" t="s">
         <v>72</v>
@@ -4234,17 +4335,17 @@
       <c r="F24" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="G24" s="82"/>
-      <c r="H24" s="82"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="87"/>
       <c r="K24" s="70" t="s">
-        <v>124</v>
-      </c>
-      <c r="L24" s="93" t="s">
+        <v>126</v>
+      </c>
+      <c r="L24" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="M24" s="97" t="s">
+      <c r="M24" s="96" t="s">
         <v>64</v>
       </c>
       <c r="N24" s="53"/>
@@ -4255,13 +4356,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="66" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="71" t="s">
         <v>125</v>
-      </c>
-      <c r="C25" s="66" t="s">
-        <v>126</v>
-      </c>
-      <c r="D25" s="71" t="s">
-        <v>123</v>
       </c>
       <c r="E25" s="76" t="s">
         <v>72</v>
@@ -4269,17 +4370,17 @@
       <c r="F25" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="84"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="89"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="88"/>
+      <c r="J25" s="88"/>
       <c r="K25" s="71" t="s">
-        <v>127</v>
-      </c>
-      <c r="L25" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="M25" s="97"/>
+        <v>129</v>
+      </c>
+      <c r="L25" s="93" t="s">
+        <v>130</v>
+      </c>
+      <c r="M25" s="96"/>
       <c r="N25" s="53"/>
     </row>
     <row r="26" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4288,13 +4389,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="65" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C26" s="65" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D26" s="70" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E26" s="76" t="s">
         <v>72</v>
@@ -4302,17 +4403,17 @@
       <c r="F26" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="G26" s="82"/>
-      <c r="H26" s="82"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="88"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="87"/>
       <c r="K26" s="70" t="s">
-        <v>127</v>
-      </c>
-      <c r="L26" s="93" t="s">
-        <v>128</v>
-      </c>
-      <c r="M26" s="97"/>
+        <v>129</v>
+      </c>
+      <c r="L26" s="92" t="s">
+        <v>130</v>
+      </c>
+      <c r="M26" s="96"/>
       <c r="N26" s="53"/>
     </row>
     <row r="27" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4320,10 +4421,10 @@
         <v>245</v>
       </c>
       <c r="B27" s="66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D27" s="71" t="s">
         <v>79</v>
@@ -4334,20 +4435,20 @@
       <c r="F27" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="84"/>
-      <c r="H27" s="84">
+      <c r="G27" s="83"/>
+      <c r="H27" s="83">
         <v>6</v>
       </c>
-      <c r="I27" s="89">
+      <c r="I27" s="88">
         <v>46205</v>
       </c>
-      <c r="J27" s="89">
+      <c r="J27" s="88">
         <v>46234</v>
       </c>
       <c r="K27" s="71"/>
-      <c r="L27" s="94"/>
-      <c r="M27" s="97" t="s">
-        <v>120</v>
+      <c r="L27" s="93"/>
+      <c r="M27" s="96" t="s">
+        <v>122</v>
       </c>
       <c r="N27" s="53"/>
     </row>
@@ -4357,10 +4458,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>67</v>
@@ -4388,10 +4489,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>71</v>
@@ -4419,10 +4520,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>79</v>
@@ -4450,10 +4551,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="11" t="s">
@@ -4479,10 +4580,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="11" t="s">
@@ -4508,10 +4609,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>79</v>
@@ -4535,7 +4636,7 @@
       <c r="K33" s="10"/>
       <c r="L33" s="47"/>
       <c r="M33" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N33" s="53"/>
     </row>
@@ -4545,10 +4646,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="11" t="s">
@@ -4570,7 +4671,7 @@
       <c r="K34" s="10"/>
       <c r="L34" s="47"/>
       <c r="M34" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N34" s="53"/>
     </row>
@@ -4580,13 +4681,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>72</v>
@@ -4617,13 +4718,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>72</v>
@@ -4654,13 +4755,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>72</v>
@@ -4691,10 +4792,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>67</v>
@@ -4718,7 +4819,7 @@
       <c r="K38" s="10"/>
       <c r="L38" s="47"/>
       <c r="M38" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N38" s="53"/>
     </row>
@@ -4728,13 +4829,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E39" s="24" t="s">
         <v>72</v>
@@ -4747,7 +4848,7 @@
       <c r="I39" s="27"/>
       <c r="J39" s="27"/>
       <c r="K39" s="23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L39" s="49"/>
       <c r="M39" s="62" t="s">
@@ -4761,13 +4862,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="29" t="s">
         <v>153</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="D40" s="29" t="s">
-        <v>151</v>
       </c>
       <c r="E40" s="24" t="s">
         <v>72</v>
@@ -4780,7 +4881,7 @@
       <c r="I40" s="31"/>
       <c r="J40" s="31"/>
       <c r="K40" s="29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L40" s="50"/>
       <c r="M40" s="62" t="s">
@@ -4794,13 +4895,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E41" s="24" t="s">
         <v>72</v>
@@ -4813,7 +4914,7 @@
       <c r="I41" s="27"/>
       <c r="J41" s="27"/>
       <c r="K41" s="23" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L41" s="49"/>
       <c r="M41" s="62" t="s">
@@ -4826,33 +4927,33 @@
         <v>239</v>
       </c>
       <c r="B42" s="66" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C42" s="66" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D42" s="71" t="s">
         <v>79</v>
       </c>
       <c r="E42" s="76" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F42" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G42" s="84"/>
+      <c r="G42" s="83"/>
       <c r="H42" s="11">
         <v>2</v>
       </c>
-      <c r="I42" s="89"/>
-      <c r="J42" s="89">
+      <c r="I42" s="88"/>
+      <c r="J42" s="88">
         <v>46205</v>
       </c>
       <c r="K42" s="71"/>
-      <c r="L42" s="94" t="s">
-        <v>160</v>
-      </c>
-      <c r="M42" s="97" t="s">
+      <c r="L42" s="93" t="s">
+        <v>162</v>
+      </c>
+      <c r="M42" s="96" t="s">
         <v>64</v>
       </c>
       <c r="N42" s="53"/>
@@ -4862,10 +4963,10 @@
         <v>240</v>
       </c>
       <c r="B43" s="65" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C43" s="65" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D43" s="70" t="s">
         <v>79</v>
@@ -4876,17 +4977,17 @@
       <c r="F43" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G43" s="82"/>
-      <c r="H43" s="82">
+      <c r="G43" s="81"/>
+      <c r="H43" s="81">
         <v>10</v>
       </c>
-      <c r="I43" s="88"/>
-      <c r="J43" s="88">
+      <c r="I43" s="87"/>
+      <c r="J43" s="87">
         <v>46210</v>
       </c>
       <c r="K43" s="70"/>
-      <c r="L43" s="93"/>
-      <c r="M43" s="97" t="s">
+      <c r="L43" s="92"/>
+      <c r="M43" s="96" t="s">
         <v>64</v>
       </c>
       <c r="N43" s="53"/>
@@ -4897,16 +4998,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>73</v>
@@ -4924,7 +5025,7 @@
       <c r="K44" s="10"/>
       <c r="L44" s="47"/>
       <c r="M44" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N44" s="53"/>
     </row>
@@ -4934,7 +5035,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>77</v>
@@ -4943,7 +5044,7 @@
         <v>67</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>73</v>
@@ -4970,34 +5071,34 @@
         <v>237</v>
       </c>
       <c r="B46" s="66" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C46" s="66" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D46" s="71" t="s">
         <v>67</v>
       </c>
       <c r="E46" s="76" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F46" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="G46" s="84"/>
-      <c r="H46" s="84">
+      <c r="G46" s="83"/>
+      <c r="H46" s="83">
         <v>10</v>
       </c>
-      <c r="I46" s="89">
+      <c r="I46" s="88">
         <v>46206</v>
       </c>
-      <c r="J46" s="89">
+      <c r="J46" s="88">
         <v>46209</v>
       </c>
       <c r="K46" s="71"/>
-      <c r="L46" s="94"/>
-      <c r="M46" s="97" t="s">
-        <v>96</v>
+      <c r="L46" s="93"/>
+      <c r="M46" s="96" t="s">
+        <v>97</v>
       </c>
       <c r="N46" s="53"/>
     </row>
@@ -5007,14 +5108,14 @@
         <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>73</v>
@@ -5036,7 +5137,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>75</v>
@@ -5045,7 +5146,7 @@
         <v>71</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>73</v>
@@ -5067,7 +5168,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>75</v>
@@ -5076,7 +5177,7 @@
         <v>71</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>73</v>
@@ -5098,7 +5199,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>75</v>
@@ -5107,7 +5208,7 @@
         <v>71</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>73</v>
@@ -5129,7 +5230,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>75</v>
@@ -5138,7 +5239,7 @@
         <v>79</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>73</v>
@@ -5149,7 +5250,7 @@
       <c r="J51" s="13"/>
       <c r="K51" s="10"/>
       <c r="L51" s="47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M51" s="11" t="s">
         <v>64</v>
@@ -5162,7 +5263,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>75</v>
@@ -5171,7 +5272,7 @@
         <v>79</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>73</v>
@@ -5182,7 +5283,7 @@
       <c r="J52" s="13"/>
       <c r="K52" s="10"/>
       <c r="L52" s="47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M52" s="11" t="s">
         <v>64</v>
@@ -5195,16 +5296,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>73</v>
@@ -5222,7 +5323,7 @@
       <c r="K53" s="10"/>
       <c r="L53" s="47"/>
       <c r="M53" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N53" s="53"/>
     </row>
@@ -5232,14 +5333,14 @@
         <v>53</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D54" s="10"/>
       <c r="E54" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>73</v>
@@ -5261,14 +5362,14 @@
         <v>54</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>73</v>
@@ -5290,16 +5391,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F56" s="11" t="s">
         <v>73</v>
@@ -5321,16 +5422,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F57" s="11" t="s">
         <v>73</v>
@@ -5348,7 +5449,7 @@
       <c r="K57" s="10"/>
       <c r="L57" s="47"/>
       <c r="M57" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N57" s="53"/>
     </row>
@@ -5358,16 +5459,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F58" s="11" t="s">
         <v>73</v>
@@ -5385,7 +5486,7 @@
       <c r="K58" s="10"/>
       <c r="L58" s="47"/>
       <c r="M58" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N58" s="53"/>
     </row>
@@ -5395,16 +5496,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>73</v>
@@ -5422,7 +5523,7 @@
       <c r="K59" s="10"/>
       <c r="L59" s="47"/>
       <c r="M59" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N59" s="53"/>
     </row>
@@ -5432,16 +5533,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F60" s="11" t="s">
         <v>73</v>
@@ -5459,7 +5560,7 @@
       <c r="K60" s="10"/>
       <c r="L60" s="47"/>
       <c r="M60" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N60" s="53"/>
     </row>
@@ -5469,7 +5570,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>77</v>
@@ -5478,7 +5579,7 @@
         <v>71</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F61" s="11" t="s">
         <v>73</v>
@@ -5506,7 +5607,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>77</v>
@@ -5515,7 +5616,7 @@
         <v>67</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F62" s="11" t="s">
         <v>73</v>
@@ -5543,14 +5644,14 @@
         <v>62</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D63" s="10"/>
       <c r="E63" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>73</v>
@@ -5578,16 +5679,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F64" s="11" t="s">
         <v>73</v>
@@ -5615,14 +5716,14 @@
         <v>64</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D65" s="10"/>
       <c r="E65" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>73</v>
@@ -5650,16 +5751,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F66" s="25" t="s">
         <v>73</v>
@@ -5669,7 +5770,7 @@
       <c r="I66" s="31"/>
       <c r="J66" s="31"/>
       <c r="K66" s="29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L66" s="50"/>
       <c r="M66" s="62" t="s">
@@ -5683,16 +5784,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F67" s="25" t="s">
         <v>73</v>
@@ -5702,7 +5803,7 @@
       <c r="I67" s="27"/>
       <c r="J67" s="27"/>
       <c r="K67" s="23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L67" s="49"/>
       <c r="M67" s="62" t="s">
@@ -5716,16 +5817,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F68" s="25" t="s">
         <v>73</v>
@@ -5735,10 +5836,10 @@
       <c r="I68" s="31"/>
       <c r="J68" s="31"/>
       <c r="K68" s="29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L68" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M68" s="62" t="s">
         <v>64</v>
@@ -5751,16 +5852,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E69" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F69" s="25" t="s">
         <v>73</v>
@@ -5770,10 +5871,10 @@
       <c r="I69" s="27"/>
       <c r="J69" s="27"/>
       <c r="K69" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L69" s="49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M69" s="62" t="s">
         <v>64</v>
@@ -5786,16 +5887,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F70" s="25" t="s">
         <v>73</v>
@@ -5805,10 +5906,10 @@
       <c r="I70" s="31"/>
       <c r="J70" s="31"/>
       <c r="K70" s="29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L70" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M70" s="62" t="s">
         <v>64</v>
@@ -5821,16 +5922,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E71" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F71" s="25" t="s">
         <v>73</v>
@@ -5840,7 +5941,7 @@
       <c r="I71" s="27"/>
       <c r="J71" s="27"/>
       <c r="K71" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L71" s="49"/>
       <c r="M71" s="62" t="s">
@@ -5854,16 +5955,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E72" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F72" s="25" t="s">
         <v>73</v>
@@ -5873,10 +5974,10 @@
       <c r="I72" s="31"/>
       <c r="J72" s="31"/>
       <c r="K72" s="29" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L72" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M72" s="62" t="s">
         <v>64</v>
@@ -5889,16 +5990,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E73" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F73" s="25" t="s">
         <v>73</v>
@@ -5908,10 +6009,10 @@
       <c r="I73" s="27"/>
       <c r="J73" s="27"/>
       <c r="K73" s="23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L73" s="49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M73" s="62" t="s">
         <v>64</v>
@@ -5924,16 +6025,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="28" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F74" s="25" t="s">
         <v>73</v>
@@ -5943,7 +6044,7 @@
       <c r="I74" s="31"/>
       <c r="J74" s="31"/>
       <c r="K74" s="29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L74" s="50"/>
       <c r="M74" s="62" t="s">
@@ -5957,16 +6058,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E75" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F75" s="25" t="s">
         <v>73</v>
@@ -5976,10 +6077,10 @@
       <c r="I75" s="27"/>
       <c r="J75" s="27"/>
       <c r="K75" s="23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L75" s="49" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M75" s="62" t="s">
         <v>64</v>
@@ -5992,16 +6093,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F76" s="25" t="s">
         <v>73</v>
@@ -6011,10 +6112,10 @@
       <c r="I76" s="31"/>
       <c r="J76" s="31"/>
       <c r="K76" s="29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L76" s="50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M76" s="62" t="s">
         <v>64</v>
@@ -6027,16 +6128,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E77" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F77" s="25" t="s">
         <v>73</v>
@@ -6046,7 +6147,7 @@
       <c r="I77" s="27"/>
       <c r="J77" s="27"/>
       <c r="K77" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L77" s="49"/>
       <c r="M77" s="62" t="s">
@@ -6060,16 +6161,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="28" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F78" s="25" t="s">
         <v>73</v>
@@ -6079,7 +6180,7 @@
       <c r="I78" s="31"/>
       <c r="J78" s="31"/>
       <c r="K78" s="29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L78" s="50"/>
       <c r="M78" s="62" t="s">
@@ -6093,16 +6194,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D79" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E79" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F79" s="25" t="s">
         <v>73</v>
@@ -6112,7 +6213,7 @@
       <c r="I79" s="27"/>
       <c r="J79" s="27"/>
       <c r="K79" s="23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L79" s="49"/>
       <c r="M79" s="62" t="s">
@@ -6126,16 +6227,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D80" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F80" s="25" t="s">
         <v>73</v>
@@ -6145,7 +6246,7 @@
       <c r="I80" s="27"/>
       <c r="J80" s="27"/>
       <c r="K80" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L80" s="49"/>
       <c r="M80" s="62" t="s">
@@ -6159,16 +6260,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D81" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E81" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F81" s="25" t="s">
         <v>73</v>
@@ -6178,7 +6279,7 @@
       <c r="I81" s="27"/>
       <c r="J81" s="27"/>
       <c r="K81" s="23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L81" s="49"/>
       <c r="M81" s="62" t="s">
@@ -6192,16 +6293,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="28" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D82" s="29" t="s">
         <v>79</v>
       </c>
       <c r="E82" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F82" s="25" t="s">
         <v>73</v>
@@ -6211,10 +6312,10 @@
       <c r="I82" s="31"/>
       <c r="J82" s="31"/>
       <c r="K82" s="29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L82" s="50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M82" s="62" t="s">
         <v>64</v>
@@ -6227,33 +6328,33 @@
         <v>82</v>
       </c>
       <c r="B83" s="68" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C83" s="68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D83" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="E83" s="80" t="s">
-        <v>165</v>
-      </c>
-      <c r="F83" s="81" t="s">
+      <c r="E83" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="F83" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="G83" s="87"/>
-      <c r="H83" s="87">
+      <c r="G83" s="86"/>
+      <c r="H83" s="86">
         <v>10</v>
       </c>
-      <c r="I83" s="91">
+      <c r="I83" s="90">
         <v>46202</v>
       </c>
-      <c r="J83" s="91">
+      <c r="J83" s="90">
         <v>46203</v>
       </c>
       <c r="K83" s="74"/>
-      <c r="L83" s="95"/>
-      <c r="M83" s="98" t="s">
+      <c r="L83" s="94"/>
+      <c r="M83" s="97" t="s">
         <v>64</v>
       </c>
       <c r="N83" s="53"/>
@@ -6263,33 +6364,33 @@
         <v>246</v>
       </c>
       <c r="B84" s="65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C84" s="65" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D84" s="70" t="s">
         <v>79</v>
       </c>
       <c r="E84" s="76" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F84" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82">
+      <c r="G84" s="81"/>
+      <c r="H84" s="81">
         <v>4</v>
       </c>
-      <c r="I84" s="88">
+      <c r="I84" s="87">
         <v>46206</v>
       </c>
-      <c r="J84" s="88">
+      <c r="J84" s="87">
         <v>46206</v>
       </c>
       <c r="K84" s="70"/>
-      <c r="L84" s="93"/>
-      <c r="M84" s="97" t="s">
+      <c r="L84" s="92"/>
+      <c r="M84" s="96" t="s">
         <v>64</v>
       </c>
       <c r="N84" s="53"/>
@@ -6300,14 +6401,14 @@
         <v>84</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>63</v>
@@ -6329,16 +6430,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>63</v>
@@ -6360,16 +6461,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F87" s="11" t="s">
         <v>63</v>
@@ -6391,16 +6492,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F88" s="11" t="s">
         <v>63</v>
@@ -6422,16 +6523,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F89" s="11" t="s">
         <v>63</v>
@@ -6449,7 +6550,7 @@
       <c r="K89" s="10"/>
       <c r="L89" s="47"/>
       <c r="M89" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N89" s="53"/>
     </row>
@@ -6459,16 +6560,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>63</v>
@@ -6486,7 +6587,7 @@
       <c r="K90" s="10"/>
       <c r="L90" s="47"/>
       <c r="M90" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N90" s="53"/>
     </row>
@@ -6496,16 +6597,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F91" s="11" t="s">
         <v>63</v>
@@ -6533,16 +6634,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F92" s="11" t="s">
         <v>63</v>
@@ -6560,7 +6661,7 @@
       <c r="K92" s="10"/>
       <c r="L92" s="47"/>
       <c r="M92" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N92" s="53"/>
     </row>
@@ -6570,16 +6671,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F93" s="11" t="s">
         <v>63</v>
@@ -6597,7 +6698,7 @@
       <c r="K93" s="10"/>
       <c r="L93" s="47"/>
       <c r="M93" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N93" s="53"/>
     </row>
@@ -6607,16 +6708,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F94" s="11" t="s">
         <v>63</v>
@@ -6634,7 +6735,7 @@
       <c r="K94" s="10"/>
       <c r="L94" s="47"/>
       <c r="M94" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N94" s="53"/>
     </row>
@@ -6644,16 +6745,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>63</v>
@@ -6671,7 +6772,7 @@
       <c r="K95" s="10"/>
       <c r="L95" s="47"/>
       <c r="M95" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N95" s="53"/>
     </row>
@@ -6681,16 +6782,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D96" s="29" t="s">
         <v>67</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F96" s="33" t="s">
         <v>63</v>
@@ -6700,10 +6801,10 @@
       <c r="I96" s="31"/>
       <c r="J96" s="31"/>
       <c r="K96" s="29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L96" s="50" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M96" s="62" t="s">
         <v>64</v>
@@ -6716,16 +6817,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="28" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D97" s="29" t="s">
         <v>71</v>
       </c>
       <c r="E97" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F97" s="33" t="s">
         <v>63</v>
@@ -6735,7 +6836,7 @@
       <c r="I97" s="31"/>
       <c r="J97" s="31"/>
       <c r="K97" s="29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L97" s="50"/>
       <c r="M97" s="62" t="s">
@@ -6749,16 +6850,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="28" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D98" s="29" t="s">
         <v>67</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F98" s="33" t="s">
         <v>63</v>
@@ -6768,7 +6869,7 @@
       <c r="I98" s="31"/>
       <c r="J98" s="31"/>
       <c r="K98" s="29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L98" s="50"/>
       <c r="M98" s="62" t="s">
@@ -6782,16 +6883,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D99" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E99" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F99" s="33" t="s">
         <v>63</v>
@@ -6801,7 +6902,7 @@
       <c r="I99" s="27"/>
       <c r="J99" s="27"/>
       <c r="K99" s="23" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L99" s="49"/>
       <c r="M99" s="62" t="s">
@@ -6815,16 +6916,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D100" s="29" t="s">
         <v>67</v>
       </c>
       <c r="E100" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F100" s="33" t="s">
         <v>63</v>
@@ -6834,7 +6935,7 @@
       <c r="I100" s="31"/>
       <c r="J100" s="31"/>
       <c r="K100" s="29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L100" s="50"/>
       <c r="M100" s="62" t="s">
@@ -6848,14 +6949,14 @@
         <v>100</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F101" s="11" t="s">
         <v>68</v>
@@ -6877,16 +6978,16 @@
         <v>101</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>68</v>
@@ -6897,7 +6998,7 @@
       <c r="J102" s="13"/>
       <c r="K102" s="10"/>
       <c r="L102" s="47" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M102" s="11" t="s">
         <v>64</v>
@@ -6910,16 +7011,16 @@
         <v>102</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F103" s="11" t="s">
         <v>68</v>
@@ -6930,7 +7031,7 @@
       <c r="J103" s="13"/>
       <c r="K103" s="10"/>
       <c r="L103" s="47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M103" s="11" t="s">
         <v>64</v>
@@ -6943,16 +7044,16 @@
         <v>103</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>68</v>
@@ -6974,16 +7075,16 @@
         <v>104</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F105" s="11" t="s">
         <v>68</v>
@@ -7005,14 +7106,14 @@
         <v>105</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D106" s="10"/>
       <c r="E106" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>68</v>
@@ -7034,14 +7135,14 @@
         <v>106</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D107" s="10"/>
       <c r="E107" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>68</v>
@@ -7063,14 +7164,14 @@
         <v>107</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D108" s="10"/>
       <c r="E108" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F108" s="11" t="s">
         <v>68</v>
@@ -7092,14 +7193,14 @@
         <v>108</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D109" s="10"/>
       <c r="E109" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F109" s="11" t="s">
         <v>68</v>
@@ -7121,16 +7222,16 @@
         <v>109</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F110" s="11" t="s">
         <v>68</v>
@@ -7141,7 +7242,7 @@
       <c r="J110" s="13"/>
       <c r="K110" s="10"/>
       <c r="L110" s="47" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M110" s="11" t="s">
         <v>64</v>
@@ -7154,16 +7255,16 @@
         <v>110</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F111" s="11" t="s">
         <v>68</v>
@@ -7177,7 +7278,7 @@
       <c r="K111" s="10"/>
       <c r="L111" s="47"/>
       <c r="M111" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N111" s="53"/>
     </row>
@@ -7187,16 +7288,16 @@
         <v>111</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D112" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F112" s="11" t="s">
         <v>68</v>
@@ -7214,7 +7315,7 @@
       <c r="K112" s="10"/>
       <c r="L112" s="47"/>
       <c r="M112" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N112" s="53"/>
     </row>
@@ -7224,16 +7325,16 @@
         <v>112</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D113" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F113" s="11" t="s">
         <v>68</v>
@@ -7251,7 +7352,7 @@
       <c r="K113" s="10"/>
       <c r="L113" s="47"/>
       <c r="M113" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N113" s="53"/>
     </row>
@@ -7261,16 +7362,16 @@
         <v>113</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F114" s="11" t="s">
         <v>68</v>
@@ -7288,7 +7389,7 @@
       <c r="K114" s="10"/>
       <c r="L114" s="47"/>
       <c r="M114" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N114" s="53"/>
     </row>
@@ -7298,16 +7399,16 @@
         <v>114</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D115" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F115" s="11" t="s">
         <v>68</v>
@@ -7325,7 +7426,7 @@
       <c r="K115" s="10"/>
       <c r="L115" s="47"/>
       <c r="M115" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N115" s="53"/>
     </row>
@@ -7335,16 +7436,16 @@
         <v>115</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D116" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F116" s="11" t="s">
         <v>68</v>
@@ -7362,7 +7463,7 @@
       <c r="K116" s="10"/>
       <c r="L116" s="47"/>
       <c r="M116" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N116" s="53"/>
     </row>
@@ -7372,16 +7473,16 @@
         <v>116</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D117" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F117" s="11" t="s">
         <v>68</v>
@@ -7399,7 +7500,7 @@
       <c r="K117" s="10"/>
       <c r="L117" s="47"/>
       <c r="M117" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N117" s="53"/>
     </row>
@@ -7409,16 +7510,16 @@
         <v>117</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>68</v>
@@ -7436,7 +7537,7 @@
       <c r="K118" s="10"/>
       <c r="L118" s="47"/>
       <c r="M118" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N118" s="53"/>
     </row>
@@ -7446,16 +7547,16 @@
         <v>118</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D119" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F119" s="11" t="s">
         <v>68</v>
@@ -7473,7 +7574,7 @@
       <c r="K119" s="10"/>
       <c r="L119" s="47"/>
       <c r="M119" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N119" s="53"/>
     </row>
@@ -7483,16 +7584,16 @@
         <v>119</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>68</v>
@@ -7510,7 +7611,7 @@
       <c r="K120" s="10"/>
       <c r="L120" s="47"/>
       <c r="M120" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N120" s="53"/>
     </row>
@@ -7520,16 +7621,16 @@
         <v>120</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D121" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>68</v>
@@ -7547,7 +7648,7 @@
       <c r="K121" s="10"/>
       <c r="L121" s="47"/>
       <c r="M121" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N121" s="53"/>
     </row>
@@ -7557,16 +7658,16 @@
         <v>121</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D122" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>68</v>
@@ -7584,7 +7685,7 @@
       <c r="K122" s="10"/>
       <c r="L122" s="47"/>
       <c r="M122" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N122" s="53"/>
     </row>
@@ -7594,16 +7695,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D123" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F123" s="11" t="s">
         <v>68</v>
@@ -7621,7 +7722,7 @@
       <c r="K123" s="10"/>
       <c r="L123" s="47"/>
       <c r="M123" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N123" s="53"/>
     </row>
@@ -7631,16 +7732,16 @@
         <v>123</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D124" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F124" s="11" t="s">
         <v>68</v>
@@ -7658,7 +7759,7 @@
       <c r="K124" s="10"/>
       <c r="L124" s="47"/>
       <c r="M124" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N124" s="53"/>
     </row>
@@ -7668,16 +7769,16 @@
         <v>124</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D125" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F125" s="11" t="s">
         <v>68</v>
@@ -7695,7 +7796,7 @@
       <c r="K125" s="10"/>
       <c r="L125" s="47"/>
       <c r="M125" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N125" s="53"/>
     </row>
@@ -7705,16 +7806,16 @@
         <v>125</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F126" s="11" t="s">
         <v>68</v>
@@ -7732,7 +7833,7 @@
       <c r="K126" s="10"/>
       <c r="L126" s="47"/>
       <c r="M126" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N126" s="53"/>
     </row>
@@ -7742,7 +7843,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C127" s="9" t="s">
         <v>77</v>
@@ -7751,7 +7852,7 @@
         <v>79</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F127" s="11" t="s">
         <v>68</v>
@@ -7779,7 +7880,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C128" s="9" t="s">
         <v>77</v>
@@ -7788,7 +7889,7 @@
         <v>67</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F128" s="11" t="s">
         <v>68</v>
@@ -7816,7 +7917,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C129" s="9" t="s">
         <v>77</v>
@@ -7825,7 +7926,7 @@
         <v>67</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>68</v>
@@ -7853,16 +7954,16 @@
         <v>129</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>79</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F130" s="11" t="s">
         <v>68</v>
@@ -7890,14 +7991,14 @@
         <v>130</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D131" s="10"/>
       <c r="E131" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>68</v>
@@ -7919,14 +8020,14 @@
         <v>131</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D132" s="10"/>
       <c r="E132" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>68</v>
@@ -7948,16 +8049,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D133" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F133" s="11" t="s">
         <v>68</v>
@@ -7985,16 +8086,16 @@
         <v>133</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D134" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F134" s="11" t="s">
         <v>68</v>
@@ -8022,14 +8123,14 @@
         <v>134</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D135" s="10"/>
       <c r="E135" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F135" s="11" t="s">
         <v>68</v>
@@ -8057,16 +8158,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D136" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F136" s="11" t="s">
         <v>68</v>
@@ -8084,7 +8185,7 @@
       <c r="K136" s="10"/>
       <c r="L136" s="47"/>
       <c r="M136" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N136" s="53"/>
     </row>
@@ -8094,16 +8195,16 @@
         <v>136</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D137" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F137" s="11" t="s">
         <v>68</v>
@@ -8121,7 +8222,7 @@
       <c r="K137" s="10"/>
       <c r="L137" s="47"/>
       <c r="M137" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N137" s="53"/>
     </row>
@@ -8131,16 +8232,16 @@
         <v>137</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D138" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F138" s="11" t="s">
         <v>68</v>
@@ -8158,7 +8259,7 @@
       <c r="K138" s="10"/>
       <c r="L138" s="47"/>
       <c r="M138" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N138" s="53"/>
     </row>
@@ -8168,16 +8269,16 @@
         <v>138</v>
       </c>
       <c r="B139" s="28" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C139" s="28" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D139" s="29" t="s">
         <v>67</v>
       </c>
       <c r="E139" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F139" s="32" t="s">
         <v>68</v>
@@ -8187,7 +8288,7 @@
       <c r="I139" s="31"/>
       <c r="J139" s="31"/>
       <c r="K139" s="29" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L139" s="50"/>
       <c r="M139" s="62" t="s">
@@ -8201,16 +8302,16 @@
         <v>139</v>
       </c>
       <c r="B140" s="22" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D140" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E140" s="24" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F140" s="32" t="s">
         <v>68</v>
@@ -8220,7 +8321,7 @@
       <c r="I140" s="27"/>
       <c r="J140" s="27"/>
       <c r="K140" s="23" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L140" s="49"/>
       <c r="M140" s="62" t="s">
@@ -8234,16 +8335,16 @@
         <v>140</v>
       </c>
       <c r="B141" s="28" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C141" s="28" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D141" s="29" t="s">
         <v>71</v>
       </c>
       <c r="E141" s="34" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F141" s="32" t="s">
         <v>68</v>
@@ -8253,10 +8354,10 @@
       <c r="I141" s="31"/>
       <c r="J141" s="31"/>
       <c r="K141" s="29" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L141" s="50" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M141" s="62" t="s">
         <v>64</v>
@@ -8269,16 +8370,16 @@
         <v>141</v>
       </c>
       <c r="B142" s="22" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D142" s="23" t="s">
         <v>71</v>
       </c>
       <c r="E142" s="34" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="F142" s="32" t="s">
         <v>68</v>
@@ -8288,10 +8389,10 @@
       <c r="I142" s="27"/>
       <c r="J142" s="27"/>
       <c r="K142" s="23" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L142" s="49" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M142" s="62" t="s">
         <v>64</v>
@@ -8304,16 +8405,16 @@
         <v>142</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F143" s="12" t="s">
         <v>73</v>
@@ -8335,14 +8436,14 @@
         <v>143</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C144" s="9"/>
       <c r="D144" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F144" s="12" t="s">
         <v>73</v>
@@ -8364,14 +8465,14 @@
         <v>144</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E145" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F145" s="12" t="s">
         <v>73</v>
@@ -8393,14 +8494,14 @@
         <v>145</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C146" s="9"/>
       <c r="D146" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E146" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F146" s="11" t="s">
         <v>73</v>
@@ -8422,14 +8523,14 @@
         <v>146</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C147" s="9" t="s">
         <v>75</v>
       </c>
       <c r="D147" s="10"/>
       <c r="E147" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F147" s="11" t="s">
         <v>73</v>
@@ -8451,14 +8552,14 @@
         <v>147</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C148" s="9" t="s">
         <v>75</v>
       </c>
       <c r="D148" s="10"/>
       <c r="E148" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F148" s="11" t="s">
         <v>73</v>
@@ -8480,14 +8581,14 @@
         <v>148</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C149" s="9" t="s">
         <v>75</v>
       </c>
       <c r="D149" s="10"/>
       <c r="E149" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F149" s="11" t="s">
         <v>73</v>
@@ -8509,14 +8610,14 @@
         <v>149</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C150" s="9" t="s">
         <v>75</v>
       </c>
       <c r="D150" s="10"/>
       <c r="E150" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F150" s="11" t="s">
         <v>73</v>
@@ -8538,14 +8639,14 @@
         <v>150</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C151" s="9" t="s">
         <v>75</v>
       </c>
       <c r="D151" s="10"/>
       <c r="E151" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F151" s="11" t="s">
         <v>73</v>
@@ -8567,14 +8668,14 @@
         <v>151</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D152" s="10"/>
       <c r="E152" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F152" s="11" t="s">
         <v>73</v>
@@ -8596,14 +8697,14 @@
         <v>152</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C153" s="9" t="s">
         <v>75</v>
       </c>
       <c r="D153" s="10"/>
       <c r="E153" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F153" s="11" t="s">
         <v>73</v>
@@ -8625,14 +8726,14 @@
         <v>153</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C154" s="9" t="s">
         <v>75</v>
       </c>
       <c r="D154" s="10"/>
       <c r="E154" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F154" s="11" t="s">
         <v>73</v>
@@ -8654,14 +8755,14 @@
         <v>154</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D155" s="10"/>
       <c r="E155" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F155" s="11" t="s">
         <v>73</v>
@@ -8683,14 +8784,14 @@
         <v>155</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C156" s="9" t="s">
         <v>75</v>
       </c>
       <c r="D156" s="10"/>
       <c r="E156" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F156" s="11" t="s">
         <v>73</v>
@@ -8712,12 +8813,12 @@
         <v>156</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="10"/>
       <c r="E157" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F157" s="11" t="s">
         <v>73</v>
@@ -8739,14 +8840,14 @@
         <v>157</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F158" s="11" t="s">
         <v>73</v>
@@ -8758,7 +8859,7 @@
       <c r="K158" s="10"/>
       <c r="L158" s="47"/>
       <c r="M158" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N158" s="53"/>
     </row>
@@ -8768,16 +8869,16 @@
         <v>158</v>
       </c>
       <c r="B159" s="22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C159" s="22" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D159" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E159" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F159" s="25" t="s">
         <v>73</v>
@@ -8787,7 +8888,7 @@
       <c r="I159" s="27"/>
       <c r="J159" s="27"/>
       <c r="K159" s="23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L159" s="49"/>
       <c r="M159" s="62" t="s">
@@ -8801,16 +8902,16 @@
         <v>159</v>
       </c>
       <c r="B160" s="28" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C160" s="28" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D160" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E160" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F160" s="25" t="s">
         <v>73</v>
@@ -8820,7 +8921,7 @@
       <c r="I160" s="31"/>
       <c r="J160" s="31"/>
       <c r="K160" s="29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L160" s="50"/>
       <c r="M160" s="62" t="s">
@@ -8834,16 +8935,16 @@
         <v>160</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C161" s="22" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D161" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E161" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F161" s="25" t="s">
         <v>73</v>
@@ -8853,7 +8954,7 @@
       <c r="I161" s="27"/>
       <c r="J161" s="27"/>
       <c r="K161" s="23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L161" s="49"/>
       <c r="M161" s="62" t="s">
@@ -8867,16 +8968,16 @@
         <v>161</v>
       </c>
       <c r="B162" s="28" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C162" s="28" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D162" s="29" t="s">
         <v>67</v>
       </c>
       <c r="E162" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F162" s="25" t="s">
         <v>73</v>
@@ -8886,7 +8987,7 @@
       <c r="I162" s="31"/>
       <c r="J162" s="31"/>
       <c r="K162" s="29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L162" s="50"/>
       <c r="M162" s="62" t="s">
@@ -8900,16 +9001,16 @@
         <v>162</v>
       </c>
       <c r="B163" s="28" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C163" s="28" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D163" s="29" t="s">
         <v>67</v>
       </c>
       <c r="E163" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F163" s="25" t="s">
         <v>73</v>
@@ -8919,7 +9020,7 @@
       <c r="I163" s="31"/>
       <c r="J163" s="31"/>
       <c r="K163" s="29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L163" s="50"/>
       <c r="M163" s="62" t="s">
@@ -8933,16 +9034,16 @@
         <v>163</v>
       </c>
       <c r="B164" s="28" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C164" s="28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D164" s="29" t="s">
         <v>71</v>
       </c>
       <c r="E164" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F164" s="25" t="s">
         <v>73</v>
@@ -8952,7 +9053,7 @@
       <c r="I164" s="31"/>
       <c r="J164" s="31"/>
       <c r="K164" s="29" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L164" s="50"/>
       <c r="M164" s="62" t="s">
@@ -8966,16 +9067,16 @@
         <v>164</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D165" s="23" t="s">
         <v>71</v>
       </c>
       <c r="E165" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F165" s="25" t="s">
         <v>73</v>
@@ -8985,7 +9086,7 @@
       <c r="I165" s="27"/>
       <c r="J165" s="27"/>
       <c r="K165" s="23" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L165" s="49"/>
       <c r="M165" s="62" t="s">
@@ -8999,16 +9100,16 @@
         <v>165</v>
       </c>
       <c r="B166" s="22" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C166" s="22" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D166" s="23" t="s">
         <v>79</v>
       </c>
       <c r="E166" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F166" s="25" t="s">
         <v>73</v>
@@ -9018,10 +9119,10 @@
       <c r="I166" s="27"/>
       <c r="J166" s="27"/>
       <c r="K166" s="23" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L166" s="49" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M166" s="62" t="s">
         <v>64</v>
@@ -9034,14 +9135,14 @@
         <v>166</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E167" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F167" s="11" t="s">
         <v>63</v>
@@ -9063,14 +9164,14 @@
         <v>167</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C168" s="9"/>
       <c r="D168" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E168" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F168" s="11" t="s">
         <v>63</v>
@@ -9092,14 +9193,14 @@
         <v>168</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E169" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F169" s="11" t="s">
         <v>63</v>
@@ -9121,16 +9222,16 @@
         <v>169</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D170" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E170" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F170" s="11" t="s">
         <v>63</v>
@@ -9152,14 +9253,14 @@
         <v>170</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D171" s="10"/>
       <c r="E171" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F171" s="11" t="s">
         <v>63</v>
@@ -9181,14 +9282,14 @@
         <v>171</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D172" s="10"/>
       <c r="E172" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F172" s="11" t="s">
         <v>63</v>
@@ -9210,14 +9311,14 @@
         <v>172</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E173" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F173" s="11" t="s">
         <v>63</v>
@@ -9239,16 +9340,16 @@
         <v>173</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D174" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E174" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F174" s="11" t="s">
         <v>63</v>
@@ -9270,14 +9371,14 @@
         <v>174</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D175" s="10"/>
       <c r="E175" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F175" s="11" t="s">
         <v>63</v>
@@ -9299,14 +9400,14 @@
         <v>175</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D176" s="10"/>
       <c r="E176" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F176" s="11" t="s">
         <v>63</v>
@@ -9328,14 +9429,14 @@
         <v>176</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D177" s="10"/>
       <c r="E177" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F177" s="11" t="s">
         <v>63</v>
@@ -9357,14 +9458,14 @@
         <v>177</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D178" s="10"/>
       <c r="E178" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F178" s="11" t="s">
         <v>63</v>
@@ -9386,12 +9487,12 @@
         <v>178</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="10"/>
       <c r="E179" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F179" s="11" t="s">
         <v>63</v>
@@ -9413,12 +9514,12 @@
         <v>179</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C180" s="18"/>
       <c r="D180" s="19"/>
       <c r="E180" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F180" s="20" t="s">
         <v>63</v>
@@ -9440,14 +9541,14 @@
         <v>180</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D181" s="10"/>
       <c r="E181" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F181" s="11" t="s">
         <v>63</v>
@@ -9469,24 +9570,24 @@
         <v>181</v>
       </c>
       <c r="B182" s="69" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C182" s="69" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D182" s="75"/>
       <c r="E182" s="64" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F182" s="64" t="s">
         <v>63</v>
       </c>
       <c r="G182" s="64"/>
       <c r="H182" s="64"/>
-      <c r="I182" s="92"/>
-      <c r="J182" s="92"/>
+      <c r="I182" s="91"/>
+      <c r="J182" s="91"/>
       <c r="K182" s="75"/>
-      <c r="L182" s="96"/>
+      <c r="L182" s="95"/>
       <c r="M182" s="64" t="s">
         <v>64</v>
       </c>
@@ -9498,12 +9599,12 @@
         <v>182</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="10"/>
       <c r="E183" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F183" s="11" t="s">
         <v>63</v>
@@ -9525,14 +9626,14 @@
         <v>183</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D184" s="10"/>
       <c r="E184" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F184" s="11" t="s">
         <v>63</v>
@@ -9554,14 +9655,14 @@
         <v>184</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D185" s="10"/>
       <c r="E185" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F185" s="11" t="s">
         <v>63</v>
@@ -9583,14 +9684,14 @@
         <v>185</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D186" s="10"/>
       <c r="E186" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F186" s="11" t="s">
         <v>63</v>
@@ -9612,14 +9713,14 @@
         <v>186</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C187" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D187" s="10"/>
       <c r="E187" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F187" s="11" t="s">
         <v>63</v>
@@ -9641,14 +9742,14 @@
         <v>187</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D188" s="10"/>
       <c r="E188" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F188" s="11" t="s">
         <v>63</v>
@@ -9670,14 +9771,14 @@
         <v>188</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D189" s="10"/>
       <c r="E189" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F189" s="11" t="s">
         <v>63</v>
@@ -9699,14 +9800,14 @@
         <v>189</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D190" s="10"/>
       <c r="E190" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F190" s="11" t="s">
         <v>63</v>
@@ -9728,14 +9829,14 @@
         <v>190</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D191" s="10"/>
       <c r="E191" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F191" s="11" t="s">
         <v>63</v>
@@ -9757,14 +9858,14 @@
         <v>191</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D192" s="10"/>
       <c r="E192" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F192" s="11" t="s">
         <v>63</v>
@@ -9786,12 +9887,12 @@
         <v>192</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="10"/>
       <c r="E193" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F193" s="11" t="s">
         <v>63</v>
@@ -9813,14 +9914,14 @@
         <v>193</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D194" s="10"/>
       <c r="E194" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F194" s="11" t="s">
         <v>63</v>
@@ -9832,7 +9933,7 @@
       <c r="K194" s="10"/>
       <c r="L194" s="47"/>
       <c r="M194" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N194" s="57"/>
     </row>
@@ -9842,14 +9943,14 @@
         <v>194</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C195" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D195" s="10"/>
       <c r="E195" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F195" s="11" t="s">
         <v>63</v>
@@ -9871,16 +9972,16 @@
         <v>195</v>
       </c>
       <c r="B196" s="28" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C196" s="28" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D196" s="29" t="s">
         <v>67</v>
       </c>
       <c r="E196" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F196" s="33" t="s">
         <v>63</v>
@@ -9890,7 +9991,7 @@
       <c r="I196" s="31"/>
       <c r="J196" s="31"/>
       <c r="K196" s="29" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L196" s="50"/>
       <c r="M196" s="62" t="s">
@@ -9904,16 +10005,16 @@
         <v>196</v>
       </c>
       <c r="B197" s="22" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C197" s="22" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D197" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E197" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F197" s="33" t="s">
         <v>63</v>
@@ -9923,7 +10024,7 @@
       <c r="I197" s="27"/>
       <c r="J197" s="27"/>
       <c r="K197" s="23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L197" s="49"/>
       <c r="M197" s="62" t="s">
@@ -9937,16 +10038,16 @@
         <v>197</v>
       </c>
       <c r="B198" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C198" s="28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D198" s="29" t="s">
         <v>67</v>
       </c>
       <c r="E198" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F198" s="33" t="s">
         <v>63</v>
@@ -9956,7 +10057,7 @@
       <c r="I198" s="31"/>
       <c r="J198" s="31"/>
       <c r="K198" s="29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L198" s="50"/>
       <c r="M198" s="62" t="s">
@@ -9970,16 +10071,16 @@
         <v>198</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C199" s="22" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D199" s="23" t="s">
         <v>79</v>
       </c>
       <c r="E199" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F199" s="33" t="s">
         <v>63</v>
@@ -9989,7 +10090,7 @@
       <c r="I199" s="27"/>
       <c r="J199" s="27"/>
       <c r="K199" s="23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L199" s="49"/>
       <c r="M199" s="62" t="s">
@@ -10003,16 +10104,16 @@
         <v>199</v>
       </c>
       <c r="B200" s="28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C200" s="28" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D200" s="29" t="s">
         <v>79</v>
       </c>
       <c r="E200" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F200" s="33" t="s">
         <v>63</v>
@@ -10022,7 +10123,7 @@
       <c r="I200" s="31"/>
       <c r="J200" s="31"/>
       <c r="K200" s="29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L200" s="50"/>
       <c r="M200" s="62" t="s">
@@ -10036,16 +10137,16 @@
         <v>200</v>
       </c>
       <c r="B201" s="22" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C201" s="22" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D201" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E201" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F201" s="33" t="s">
         <v>63</v>
@@ -10055,10 +10156,10 @@
       <c r="I201" s="27"/>
       <c r="J201" s="27"/>
       <c r="K201" s="23" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L201" s="49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M201" s="62" t="s">
         <v>64</v>
@@ -10071,16 +10172,16 @@
         <v>201</v>
       </c>
       <c r="B202" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C202" s="22" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D202" s="23" t="s">
         <v>67</v>
       </c>
       <c r="E202" s="24" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F202" s="33" t="s">
         <v>63</v>
@@ -10090,7 +10191,7 @@
       <c r="I202" s="27"/>
       <c r="J202" s="27"/>
       <c r="K202" s="23" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L202" s="49"/>
       <c r="M202" s="62" t="s">
@@ -10104,14 +10205,14 @@
         <v>202</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E203" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F203" s="11" t="s">
         <v>68</v>
@@ -10133,14 +10234,14 @@
         <v>203</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C204" s="9"/>
       <c r="D204" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E204" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F204" s="11" t="s">
         <v>68</v>
@@ -10162,14 +10263,14 @@
         <v>204</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E205" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F205" s="11" t="s">
         <v>68</v>
@@ -10191,14 +10292,14 @@
         <v>205</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C206" s="9"/>
       <c r="D206" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E206" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F206" s="11" t="s">
         <v>68</v>
@@ -10220,14 +10321,14 @@
         <v>206</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E207" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F207" s="11" t="s">
         <v>68</v>
@@ -10249,14 +10350,14 @@
         <v>207</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C208" s="9"/>
       <c r="D208" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E208" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F208" s="11" t="s">
         <v>68</v>
@@ -10278,14 +10379,14 @@
         <v>208</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C209" s="9"/>
       <c r="D209" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E209" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F209" s="11" t="s">
         <v>68</v>
@@ -10307,16 +10408,16 @@
         <v>209</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D210" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E210" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F210" s="11" t="s">
         <v>68</v>
@@ -10338,12 +10439,12 @@
         <v>210</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C211" s="9"/>
       <c r="D211" s="10"/>
       <c r="E211" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F211" s="11" t="s">
         <v>68</v>
@@ -10365,12 +10466,12 @@
         <v>211</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C212" s="9"/>
       <c r="D212" s="10"/>
       <c r="E212" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F212" s="11" t="s">
         <v>68</v>
@@ -10392,14 +10493,14 @@
         <v>212</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C213" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D213" s="10"/>
       <c r="E213" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F213" s="11" t="s">
         <v>68</v>
@@ -10421,14 +10522,14 @@
         <v>213</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D214" s="10"/>
       <c r="E214" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F214" s="11" t="s">
         <v>68</v>
@@ -10450,14 +10551,14 @@
         <v>214</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C215" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D215" s="10"/>
       <c r="E215" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F215" s="11" t="s">
         <v>68</v>
@@ -10479,14 +10580,14 @@
         <v>215</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C216" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D216" s="10"/>
       <c r="E216" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F216" s="11" t="s">
         <v>68</v>
@@ -10508,14 +10609,14 @@
         <v>216</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C217" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D217" s="10"/>
       <c r="E217" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F217" s="11" t="s">
         <v>68</v>
@@ -10537,14 +10638,14 @@
         <v>217</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C218" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D218" s="10"/>
       <c r="E218" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F218" s="11" t="s">
         <v>68</v>
@@ -10566,14 +10667,14 @@
         <v>218</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C219" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D219" s="10"/>
       <c r="E219" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F219" s="11" t="s">
         <v>68</v>
@@ -10595,14 +10696,14 @@
         <v>219</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D220" s="10"/>
       <c r="E220" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F220" s="11" t="s">
         <v>68</v>
@@ -10624,14 +10725,14 @@
         <v>220</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C221" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D221" s="10"/>
       <c r="E221" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F221" s="11" t="s">
         <v>68</v>
@@ -10653,14 +10754,14 @@
         <v>221</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D222" s="10"/>
       <c r="E222" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F222" s="11" t="s">
         <v>68</v>
@@ -10682,14 +10783,14 @@
         <v>222</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D223" s="10"/>
       <c r="E223" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F223" s="11" t="s">
         <v>68</v>
@@ -10711,14 +10812,14 @@
         <v>223</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D224" s="10"/>
       <c r="E224" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F224" s="11" t="s">
         <v>68</v>
@@ -10740,14 +10841,14 @@
         <v>224</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C225" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D225" s="10"/>
       <c r="E225" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F225" s="11" t="s">
         <v>68</v>
@@ -10769,14 +10870,14 @@
         <v>225</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C226" s="9" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D226" s="10"/>
       <c r="E226" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F226" s="11" t="s">
         <v>68</v>
@@ -10798,14 +10899,14 @@
         <v>226</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C227" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D227" s="10"/>
       <c r="E227" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F227" s="11" t="s">
         <v>68</v>
@@ -10827,12 +10928,12 @@
         <v>227</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C228" s="9"/>
       <c r="D228" s="10"/>
       <c r="E228" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F228" s="11" t="s">
         <v>68</v>
@@ -10854,14 +10955,14 @@
         <v>228</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C229" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D229" s="10"/>
       <c r="E229" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F229" s="11" t="s">
         <v>68</v>
@@ -10883,14 +10984,14 @@
         <v>229</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C230" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D230" s="10"/>
       <c r="E230" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F230" s="11" t="s">
         <v>68</v>
@@ -10912,14 +11013,14 @@
         <v>230</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C231" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D231" s="10"/>
       <c r="E231" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F231" s="11" t="s">
         <v>68</v>
@@ -10941,14 +11042,14 @@
         <v>231</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C232" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D232" s="10"/>
       <c r="E232" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F232" s="11" t="s">
         <v>68</v>
@@ -10970,14 +11071,14 @@
         <v>232</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C233" s="18" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D233" s="19"/>
       <c r="E233" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F233" s="20" t="s">
         <v>68</v>
@@ -10993,22 +11094,22 @@
       </c>
       <c r="N233" s="58"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="41">
         <f t="shared" si="8"/>
         <v>233</v>
       </c>
       <c r="B234" s="18" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C234" s="18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D234" s="19" t="s">
         <v>67</v>
       </c>
       <c r="E234" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F234" s="20" t="s">
         <v>68</v>
@@ -11020,24 +11121,24 @@
       <c r="K234" s="19"/>
       <c r="L234" s="48"/>
       <c r="M234" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N234" s="59"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="41">
         <f t="shared" si="8"/>
         <v>234</v>
       </c>
       <c r="B235" s="18" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C235" s="18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D235" s="19"/>
       <c r="E235" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F235" s="20" t="s">
         <v>68</v>
@@ -11049,7 +11150,7 @@
       <c r="K235" s="19"/>
       <c r="L235" s="48"/>
       <c r="M235" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N235" s="60"/>
     </row>
@@ -11059,14 +11160,14 @@
         <v>235</v>
       </c>
       <c r="B236" s="18" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C236" s="18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D236" s="19"/>
       <c r="E236" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F236" s="20" t="s">
         <v>68</v>
@@ -11078,38 +11179,38 @@
       <c r="K236" s="19"/>
       <c r="L236" s="48"/>
       <c r="M236" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N236" s="61"/>
     </row>
-    <row r="237" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="41">
         <f t="shared" si="8"/>
         <v>236</v>
       </c>
       <c r="B237" s="18" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C237" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D237" s="101" t="s">
+        <v>116</v>
+      </c>
+      <c r="D237" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="E237" s="102" t="s">
-        <v>336</v>
+      <c r="E237" s="100" t="s">
+        <v>337</v>
       </c>
       <c r="F237" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G237" s="104"/>
+      <c r="G237" s="102"/>
       <c r="H237" s="20"/>
       <c r="I237" s="21"/>
       <c r="J237" s="21"/>
       <c r="K237" s="19"/>
       <c r="L237" s="48"/>
       <c r="M237" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N237" s="60"/>
     </row>
@@ -11119,77 +11220,77 @@
         <v>237</v>
       </c>
       <c r="B238" s="18" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C238" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D238" s="101"/>
-      <c r="E238" s="102" t="s">
-        <v>336</v>
+        <v>116</v>
+      </c>
+      <c r="D238" s="99"/>
+      <c r="E238" s="100" t="s">
+        <v>337</v>
       </c>
       <c r="F238" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G238" s="104"/>
+      <c r="G238" s="102"/>
       <c r="H238" s="20"/>
       <c r="I238" s="21"/>
       <c r="J238" s="21"/>
       <c r="K238" s="19"/>
       <c r="L238" s="48"/>
       <c r="M238" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N238" s="61"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="41">
         <f t="shared" si="8"/>
         <v>238</v>
       </c>
       <c r="B239" s="18" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C239" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="D239" s="101"/>
-      <c r="E239" s="102" t="s">
-        <v>336</v>
+        <v>116</v>
+      </c>
+      <c r="D239" s="99"/>
+      <c r="E239" s="100" t="s">
+        <v>337</v>
       </c>
       <c r="F239" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G239" s="104"/>
+      <c r="G239" s="102"/>
       <c r="H239" s="20"/>
       <c r="I239" s="21"/>
       <c r="J239" s="21"/>
       <c r="K239" s="19"/>
       <c r="L239" s="48"/>
       <c r="M239" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N239" s="60"/>
     </row>
-    <row r="240" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="41">
         <f t="shared" si="8"/>
         <v>239</v>
       </c>
       <c r="B240" s="18" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C240" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D240" s="101"/>
-      <c r="E240" s="103" t="s">
-        <v>336</v>
+        <v>118</v>
+      </c>
+      <c r="D240" s="99"/>
+      <c r="E240" s="101" t="s">
+        <v>337</v>
       </c>
       <c r="F240" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G240" s="104"/>
+      <c r="G240" s="102"/>
       <c r="H240" s="11"/>
       <c r="I240" s="21"/>
       <c r="J240" s="21"/>
@@ -11200,25 +11301,25 @@
       </c>
       <c r="N240" s="61"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="41">
         <f t="shared" si="8"/>
         <v>240</v>
       </c>
       <c r="B241" s="18" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C241" s="18" t="s">
-        <v>485</v>
-      </c>
-      <c r="D241" s="101"/>
-      <c r="E241" s="102" t="s">
-        <v>336</v>
+        <v>486</v>
+      </c>
+      <c r="D241" s="99"/>
+      <c r="E241" s="100" t="s">
+        <v>337</v>
       </c>
       <c r="F241" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G241" s="104"/>
+      <c r="G241" s="102"/>
       <c r="H241" s="20">
         <v>50</v>
       </c>
@@ -11227,89 +11328,89 @@
       <c r="K241" s="19"/>
       <c r="L241" s="48"/>
       <c r="M241" s="20" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N241" s="60"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="41">
         <f t="shared" si="8"/>
         <v>241</v>
       </c>
       <c r="B242" s="18" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C242" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D242" s="101"/>
-      <c r="E242" s="103" t="s">
-        <v>336</v>
+        <v>120</v>
+      </c>
+      <c r="D242" s="99"/>
+      <c r="E242" s="101" t="s">
+        <v>337</v>
       </c>
       <c r="F242" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G242" s="104"/>
+      <c r="G242" s="102"/>
       <c r="H242" s="20"/>
       <c r="I242" s="21"/>
       <c r="J242" s="21"/>
       <c r="K242" s="19"/>
       <c r="L242" s="48"/>
       <c r="M242" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N242" s="61"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="41">
         <f t="shared" si="8"/>
         <v>242</v>
       </c>
       <c r="B243" s="18" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C243" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D243" s="101"/>
-      <c r="E243" s="102" t="s">
-        <v>336</v>
+        <v>120</v>
+      </c>
+      <c r="D243" s="99"/>
+      <c r="E243" s="100" t="s">
+        <v>337</v>
       </c>
       <c r="F243" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G243" s="104"/>
+      <c r="G243" s="102"/>
       <c r="H243" s="20"/>
       <c r="I243" s="21"/>
       <c r="J243" s="21"/>
       <c r="K243" s="19"/>
       <c r="L243" s="48"/>
       <c r="M243" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N243" s="60"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="41">
         <f t="shared" si="8"/>
         <v>243</v>
       </c>
       <c r="B244" s="18" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C244" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D244" s="101" t="s">
+        <v>120</v>
+      </c>
+      <c r="D244" s="99" t="s">
         <v>67</v>
       </c>
-      <c r="E244" s="103" t="s">
-        <v>336</v>
+      <c r="E244" s="101" t="s">
+        <v>337</v>
       </c>
       <c r="F244" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G244" s="104"/>
+      <c r="G244" s="102"/>
       <c r="H244" s="20">
         <v>40</v>
       </c>
@@ -11318,7 +11419,7 @@
       <c r="K244" s="19"/>
       <c r="L244" s="48"/>
       <c r="M244" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N244" s="61"/>
     </row>
@@ -11328,26 +11429,26 @@
         <v>244</v>
       </c>
       <c r="B245" s="67" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C245" s="67" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D245" s="72" t="s">
         <v>67</v>
       </c>
       <c r="E245" s="77" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F245" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="G245" s="85"/>
-      <c r="H245" s="86"/>
-      <c r="I245" s="90"/>
-      <c r="J245" s="90"/>
+      <c r="G245" s="84"/>
+      <c r="H245" s="85"/>
+      <c r="I245" s="89"/>
+      <c r="J245" s="89"/>
       <c r="K245" s="73" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L245" s="72"/>
       <c r="M245" s="63" t="s">
@@ -11355,32 +11456,32 @@
       </c>
       <c r="N245" s="60"/>
     </row>
-    <row r="246" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A246" s="41">
+    <row r="246" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="162">
         <f t="shared" si="8"/>
         <v>245</v>
       </c>
       <c r="B246" s="36" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C246" s="36" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D246" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="E246" s="79" t="s">
-        <v>336</v>
-      </c>
-      <c r="F246" s="32" t="s">
+      <c r="E246" s="77" t="s">
+        <v>337</v>
+      </c>
+      <c r="F246" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="G246" s="83"/>
+      <c r="G246" s="82"/>
       <c r="H246" s="38"/>
       <c r="I246" s="39"/>
       <c r="J246" s="39"/>
       <c r="K246" s="37" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L246" s="51"/>
       <c r="M246" s="63" t="s">
@@ -11388,168 +11489,187 @@
       </c>
       <c r="N246" s="61"/>
     </row>
-    <row r="247" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A247" s="41">
+    <row r="247" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="165">
         <f t="shared" si="8"/>
         <v>246</v>
       </c>
-      <c r="B247" s="36" t="s">
-        <v>495</v>
-      </c>
-      <c r="C247" s="36" t="s">
+      <c r="B247" s="163" t="s">
         <v>496</v>
       </c>
-      <c r="D247" s="51" t="s">
+      <c r="C247" s="154" t="s">
+        <v>497</v>
+      </c>
+      <c r="D247" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="E247" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="F247" s="45" t="s">
+      <c r="E247" s="157" t="s">
+        <v>337</v>
+      </c>
+      <c r="F247" s="136" t="s">
         <v>68</v>
       </c>
-      <c r="G247" s="83"/>
-      <c r="H247" s="38"/>
-      <c r="I247" s="39"/>
-      <c r="J247" s="39"/>
-      <c r="K247" s="37" t="s">
-        <v>497</v>
-      </c>
-      <c r="L247" s="51"/>
-      <c r="M247" s="63" t="s">
-        <v>64</v>
-      </c>
-      <c r="N247" s="60"/>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A248" s="41">
-        <f t="shared" si="8"/>
+      <c r="G247" s="137"/>
+      <c r="H247" s="137"/>
+      <c r="I247" s="155"/>
+      <c r="J247" s="155"/>
+      <c r="K247" s="154" t="s">
+        <v>498</v>
+      </c>
+      <c r="L247" s="154"/>
+      <c r="M247" s="156" t="s">
+        <v>64</v>
+      </c>
+      <c r="N247" s="158"/>
+    </row>
+    <row r="248" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A248" s="165">
+        <f>IF($B248="","",ROW()-1)</f>
         <v>247</v>
       </c>
-      <c r="B248" s="67" t="s">
+      <c r="B248" s="163" t="s">
+        <v>499</v>
+      </c>
+      <c r="C248" s="154" t="s">
+        <v>500</v>
+      </c>
+      <c r="D248" s="154" t="s">
+        <v>71</v>
+      </c>
+      <c r="E248" s="157" t="s">
+        <v>82</v>
+      </c>
+      <c r="F248" s="136" t="s">
+        <v>68</v>
+      </c>
+      <c r="G248" s="137"/>
+      <c r="H248" s="137"/>
+      <c r="I248" s="155"/>
+      <c r="J248" s="155"/>
+      <c r="K248" s="154" t="s">
         <v>498</v>
       </c>
-      <c r="C248" s="67" t="s">
-        <v>499</v>
-      </c>
-      <c r="D248" s="72" t="s">
-        <v>71</v>
-      </c>
-      <c r="E248" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="F248" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="G248" s="85"/>
-      <c r="H248" s="86"/>
-      <c r="I248" s="90"/>
-      <c r="J248" s="90"/>
-      <c r="K248" s="73" t="s">
-        <v>497</v>
-      </c>
-      <c r="L248" s="72"/>
-      <c r="M248" s="63" t="s">
-        <v>64</v>
-      </c>
-      <c r="N248" s="61"/>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A249" s="100">
-        <v>244</v>
-      </c>
-      <c r="B249" s="105" t="s">
-        <v>500</v>
-      </c>
-      <c r="C249" s="105" t="s">
+      <c r="L248" s="154"/>
+      <c r="M248" s="156" t="s">
+        <v>64</v>
+      </c>
+      <c r="N248" s="158"/>
+    </row>
+    <row r="249" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A249" s="162">
+        <f t="shared" ref="A249:A273" si="9">IF($B249="","",ROW()-1)</f>
+        <v>248</v>
+      </c>
+      <c r="B249" s="103" t="s">
         <v>501</v>
       </c>
-      <c r="D249" s="108" t="s">
+      <c r="C249" s="103" t="s">
+        <v>502</v>
+      </c>
+      <c r="D249" s="106" t="s">
         <v>67</v>
       </c>
       <c r="E249" s="44" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F249" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="G249" s="110"/>
-      <c r="H249" s="110">
+      <c r="G249" s="108"/>
+      <c r="H249" s="108">
         <v>6</v>
       </c>
-      <c r="I249" s="112">
+      <c r="I249" s="143">
         <v>46205</v>
       </c>
-      <c r="J249" s="112">
+      <c r="J249" s="143">
         <v>46213</v>
       </c>
-      <c r="K249" s="108"/>
-      <c r="L249" s="108"/>
-      <c r="M249" s="115"/>
-    </row>
-    <row r="250" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A250" s="117">
+      <c r="K249" s="106"/>
+      <c r="L249" s="106"/>
+      <c r="M249" s="112"/>
+    </row>
+    <row r="250" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A250" s="165">
+        <f t="shared" si="9"/>
         <v>249</v>
       </c>
-      <c r="B250" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C250" s="3" t="s">
+      <c r="B250" s="164" t="s">
         <v>503</v>
       </c>
-      <c r="D250" t="s">
+      <c r="C250" s="159" t="s">
+        <v>504</v>
+      </c>
+      <c r="D250" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="F250" s="11" t="s">
+      <c r="E250" s="160"/>
+      <c r="F250" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="I250" s="42"/>
-      <c r="J250" s="42"/>
-    </row>
-    <row r="251" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A251" s="117">
+      <c r="G250" s="160"/>
+      <c r="H250" s="160"/>
+      <c r="I250" s="161"/>
+      <c r="J250" s="161"/>
+      <c r="K250" s="159"/>
+      <c r="L250" s="159"/>
+      <c r="M250" s="160"/>
+      <c r="N250" s="158"/>
+    </row>
+    <row r="251" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A251" s="165">
+        <f t="shared" si="9"/>
         <v>250</v>
       </c>
-      <c r="B251" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="C251" s="3" t="s">
+      <c r="B251" s="164" t="s">
         <v>505</v>
       </c>
-      <c r="D251" t="s">
+      <c r="C251" s="159" t="s">
+        <v>506</v>
+      </c>
+      <c r="D251" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="F251" s="11" t="s">
+      <c r="E251" s="160"/>
+      <c r="F251" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="I251" s="42"/>
-      <c r="J251" s="42"/>
-    </row>
-    <row r="252" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A252" s="117">
+      <c r="G251" s="160"/>
+      <c r="H251" s="160"/>
+      <c r="I251" s="161"/>
+      <c r="J251" s="161"/>
+      <c r="K251" s="159"/>
+      <c r="L251" s="159"/>
+      <c r="M251" s="160"/>
+      <c r="N251" s="158"/>
+    </row>
+    <row r="252" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A252" s="41">
+        <f t="shared" si="9"/>
         <v>251</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="F252" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="F252" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="I252" s="42"/>
-      <c r="J252" s="42"/>
-    </row>
-    <row r="253" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A253" s="116">
+      <c r="I252" s="144"/>
+      <c r="J252" s="144"/>
+    </row>
+    <row r="253" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A253" s="162">
+        <f t="shared" si="9"/>
         <v>252</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D253" t="s">
         <v>67</v>
@@ -11560,532 +11680,613 @@
       <c r="F253" t="s">
         <v>68</v>
       </c>
-      <c r="H253" s="116">
+      <c r="H253" s="113">
         <v>4</v>
       </c>
-      <c r="I253" s="42">
+      <c r="I253" s="144">
         <v>46211</v>
       </c>
-      <c r="J253" s="42">
+      <c r="J253" s="144">
         <v>46212</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A254" s="117">
+    <row r="254" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A254" s="165">
+        <f t="shared" si="9"/>
         <v>253</v>
       </c>
-      <c r="B254" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="D254" t="s">
+      <c r="B254" s="164" t="s">
+        <v>511</v>
+      </c>
+      <c r="C254" s="159"/>
+      <c r="D254" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="F254" s="11" t="s">
+      <c r="E254" s="160"/>
+      <c r="F254" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="I254" s="42"/>
-      <c r="J254" s="42"/>
-    </row>
-    <row r="255" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A255" s="116">
+      <c r="G254" s="160"/>
+      <c r="H254" s="160"/>
+      <c r="I254" s="161"/>
+      <c r="J254" s="161"/>
+      <c r="K254" s="159"/>
+      <c r="L254" s="159"/>
+      <c r="M254" s="160"/>
+      <c r="N254" s="158"/>
+    </row>
+    <row r="255" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A255" s="165">
+        <f t="shared" si="9"/>
         <v>254</v>
       </c>
-      <c r="B255" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="D255" t="s">
+      <c r="B255" s="164" t="s">
+        <v>512</v>
+      </c>
+      <c r="C255" s="159"/>
+      <c r="D255" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="F255" s="11" t="s">
+      <c r="E255" s="160"/>
+      <c r="F255" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="I255" s="42"/>
-      <c r="J255" s="42"/>
-    </row>
-    <row r="256" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A256" s="117">
+      <c r="G255" s="160"/>
+      <c r="H255" s="160"/>
+      <c r="I255" s="161"/>
+      <c r="J255" s="161"/>
+      <c r="K255" s="159"/>
+      <c r="L255" s="159"/>
+      <c r="M255" s="160"/>
+      <c r="N255" s="158"/>
+    </row>
+    <row r="256" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A256" s="165">
+        <f t="shared" si="9"/>
         <v>255</v>
       </c>
-      <c r="B256" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="C256" s="3" t="s">
+      <c r="B256" s="164" t="s">
         <v>513</v>
       </c>
-      <c r="D256" t="s">
+      <c r="C256" s="159" t="s">
+        <v>514</v>
+      </c>
+      <c r="D256" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="F256" s="11" t="s">
+      <c r="E256" s="160"/>
+      <c r="F256" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="I256" s="42"/>
-      <c r="J256" s="42"/>
+      <c r="G256" s="160"/>
+      <c r="H256" s="160"/>
+      <c r="I256" s="161"/>
+      <c r="J256" s="161"/>
+      <c r="K256" s="159"/>
+      <c r="L256" s="159"/>
+      <c r="M256" s="160"/>
+      <c r="N256" s="158"/>
     </row>
     <row r="257" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A257" s="116">
+      <c r="A257" s="165">
+        <f t="shared" si="9"/>
         <v>256</v>
       </c>
-      <c r="B257" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="D257" t="s">
+      <c r="B257" s="164" t="s">
+        <v>515</v>
+      </c>
+      <c r="C257" s="159"/>
+      <c r="D257" s="159" t="s">
         <v>71</v>
       </c>
-      <c r="F257" s="11" t="s">
+      <c r="E257" s="160"/>
+      <c r="F257" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="I257" s="42"/>
-      <c r="J257" s="42"/>
+      <c r="G257" s="160"/>
+      <c r="H257" s="160"/>
+      <c r="I257" s="161"/>
+      <c r="J257" s="161"/>
+      <c r="K257" s="159"/>
+      <c r="L257" s="159"/>
+      <c r="M257" s="160"/>
+      <c r="N257" s="158"/>
     </row>
     <row r="258" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A258" s="141">
+      <c r="A258" s="165">
+        <f t="shared" si="9"/>
         <v>257</v>
       </c>
-      <c r="B258" s="137" t="s">
-        <v>515</v>
-      </c>
-      <c r="C258" s="68"/>
-      <c r="D258" s="74" t="s">
+      <c r="B258" s="138" t="s">
+        <v>516</v>
+      </c>
+      <c r="C258" s="139"/>
+      <c r="D258" s="139" t="s">
         <v>71</v>
       </c>
-      <c r="E258" s="87"/>
-      <c r="F258" s="81" t="s">
+      <c r="E258" s="141"/>
+      <c r="F258" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="G258" s="87"/>
-      <c r="H258" s="87"/>
-      <c r="I258" s="133"/>
-      <c r="J258" s="133"/>
-      <c r="K258" s="74"/>
-      <c r="L258" s="74"/>
-      <c r="M258" s="87"/>
-      <c r="N258" s="74"/>
+      <c r="G258" s="141"/>
+      <c r="H258" s="141"/>
+      <c r="I258" s="145"/>
+      <c r="J258" s="145"/>
+      <c r="K258" s="139"/>
+      <c r="L258" s="139"/>
+      <c r="M258" s="141"/>
+      <c r="N258" s="140"/>
     </row>
     <row r="259" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A259" s="142">
+      <c r="A259" s="41">
+        <f t="shared" si="9"/>
         <v>258</v>
       </c>
-      <c r="B259" s="138" t="s">
+      <c r="B259" s="126" t="s">
         <v>517</v>
       </c>
-      <c r="C259" s="127" t="s">
+      <c r="C259" s="122" t="s">
         <v>518</v>
       </c>
-      <c r="D259" s="128"/>
-      <c r="E259" s="126"/>
-      <c r="F259" s="81" t="s">
+      <c r="D259" s="123"/>
+      <c r="E259" s="119"/>
+      <c r="F259" s="129" t="s">
         <v>73</v>
       </c>
-      <c r="G259" s="126"/>
-      <c r="H259" s="126"/>
-      <c r="I259" s="134"/>
-      <c r="J259" s="134"/>
-      <c r="K259" s="128" t="s">
-        <v>516</v>
-      </c>
-      <c r="L259" s="128"/>
-      <c r="M259" s="126"/>
-      <c r="N259" s="128"/>
+      <c r="G259" s="119"/>
+      <c r="H259" s="119"/>
+      <c r="I259" s="146"/>
+      <c r="J259" s="146"/>
+      <c r="K259" s="123" t="s">
+        <v>519</v>
+      </c>
+      <c r="L259" s="123"/>
+      <c r="M259" s="119"/>
+      <c r="N259" s="123"/>
     </row>
     <row r="260" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A260" s="141">
+      <c r="A260" s="41">
+        <f t="shared" si="9"/>
         <v>259</v>
       </c>
-      <c r="B260" s="137" t="s">
+      <c r="B260" s="125" t="s">
+        <v>520</v>
+      </c>
+      <c r="C260" s="120" t="s">
+        <v>521</v>
+      </c>
+      <c r="D260" s="121"/>
+      <c r="E260" s="124"/>
+      <c r="F260" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="G260" s="124"/>
+      <c r="H260" s="124"/>
+      <c r="I260" s="147"/>
+      <c r="J260" s="147"/>
+      <c r="K260" s="121" t="s">
         <v>519</v>
       </c>
-      <c r="C260" s="68" t="s">
-        <v>520</v>
-      </c>
-      <c r="D260" s="74"/>
-      <c r="E260" s="87"/>
-      <c r="F260" s="81" t="s">
+      <c r="L260" s="121"/>
+      <c r="M260" s="124"/>
+      <c r="N260" s="121"/>
+    </row>
+    <row r="261" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A261" s="41">
+        <f t="shared" si="9"/>
+        <v>260</v>
+      </c>
+      <c r="B261" s="126" t="s">
+        <v>522</v>
+      </c>
+      <c r="C261" s="122" t="s">
+        <v>523</v>
+      </c>
+      <c r="D261" s="123"/>
+      <c r="E261" s="119"/>
+      <c r="F261" s="130" t="s">
+        <v>63</v>
+      </c>
+      <c r="G261" s="119"/>
+      <c r="H261" s="119"/>
+      <c r="I261" s="146"/>
+      <c r="J261" s="146"/>
+      <c r="K261" s="123" t="s">
+        <v>519</v>
+      </c>
+      <c r="L261" s="123"/>
+      <c r="M261" s="119"/>
+      <c r="N261" s="123"/>
+    </row>
+    <row r="262" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A262" s="41">
+        <f t="shared" si="9"/>
+        <v>261</v>
+      </c>
+      <c r="B262" s="125" t="s">
+        <v>524</v>
+      </c>
+      <c r="C262" s="120" t="s">
+        <v>525</v>
+      </c>
+      <c r="D262" s="121"/>
+      <c r="E262" s="124"/>
+      <c r="F262" s="129" t="s">
         <v>73</v>
       </c>
-      <c r="G260" s="87"/>
-      <c r="H260" s="87"/>
-      <c r="I260" s="133"/>
-      <c r="J260" s="133"/>
-      <c r="K260" s="74" t="s">
-        <v>516</v>
-      </c>
-      <c r="L260" s="74"/>
-      <c r="M260" s="87"/>
-      <c r="N260" s="74"/>
-    </row>
-    <row r="261" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A261" s="142">
-        <v>260</v>
-      </c>
-      <c r="B261" s="138" t="s">
-        <v>521</v>
-      </c>
-      <c r="C261" s="127" t="s">
-        <v>522</v>
-      </c>
-      <c r="D261" s="128"/>
-      <c r="E261" s="126"/>
-      <c r="F261" s="135" t="s">
+      <c r="G262" s="124"/>
+      <c r="H262" s="124"/>
+      <c r="I262" s="147"/>
+      <c r="J262" s="147"/>
+      <c r="K262" s="121" t="s">
+        <v>519</v>
+      </c>
+      <c r="L262" s="121"/>
+      <c r="M262" s="124"/>
+      <c r="N262" s="121"/>
+    </row>
+    <row r="263" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A263" s="41">
+        <f t="shared" si="9"/>
+        <v>262</v>
+      </c>
+      <c r="B263" s="127" t="s">
+        <v>526</v>
+      </c>
+      <c r="C263" s="123" t="s">
+        <v>527</v>
+      </c>
+      <c r="D263" s="123"/>
+      <c r="E263" s="119"/>
+      <c r="F263" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="G263" s="119"/>
+      <c r="H263" s="119"/>
+      <c r="I263" s="146"/>
+      <c r="J263" s="146"/>
+      <c r="K263" s="123" t="s">
+        <v>519</v>
+      </c>
+      <c r="L263" s="123"/>
+      <c r="M263" s="119"/>
+      <c r="N263" s="123"/>
+    </row>
+    <row r="264" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A264" s="41">
+        <f t="shared" si="9"/>
+        <v>263</v>
+      </c>
+      <c r="B264" s="128" t="s">
+        <v>528</v>
+      </c>
+      <c r="C264" s="120" t="s">
+        <v>529</v>
+      </c>
+      <c r="D264" s="121"/>
+      <c r="E264" s="124"/>
+      <c r="F264" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="G264" s="124"/>
+      <c r="H264" s="124"/>
+      <c r="I264" s="147"/>
+      <c r="J264" s="147"/>
+      <c r="K264" s="121" t="s">
+        <v>519</v>
+      </c>
+      <c r="L264" s="121"/>
+      <c r="M264" s="124"/>
+      <c r="N264" s="121"/>
+    </row>
+    <row r="265" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A265" s="41">
+        <f t="shared" si="9"/>
+        <v>264</v>
+      </c>
+      <c r="B265" s="127" t="s">
+        <v>530</v>
+      </c>
+      <c r="C265" s="122" t="s">
+        <v>531</v>
+      </c>
+      <c r="D265" s="123"/>
+      <c r="E265" s="119"/>
+      <c r="F265" s="131" t="s">
+        <v>68</v>
+      </c>
+      <c r="G265" s="119"/>
+      <c r="H265" s="119"/>
+      <c r="I265" s="146"/>
+      <c r="J265" s="146"/>
+      <c r="K265" s="123" t="s">
+        <v>519</v>
+      </c>
+      <c r="L265" s="123"/>
+      <c r="M265" s="119"/>
+      <c r="N265" s="123"/>
+    </row>
+    <row r="266" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="41">
+        <f t="shared" si="9"/>
+        <v>265</v>
+      </c>
+      <c r="B266" s="128" t="s">
+        <v>532</v>
+      </c>
+      <c r="C266" s="121" t="s">
+        <v>533</v>
+      </c>
+      <c r="D266" s="121"/>
+      <c r="E266" s="124"/>
+      <c r="F266" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="G266" s="124"/>
+      <c r="H266" s="124"/>
+      <c r="I266" s="147"/>
+      <c r="J266" s="147"/>
+      <c r="K266" s="121" t="s">
+        <v>519</v>
+      </c>
+      <c r="L266" s="121"/>
+      <c r="M266" s="124"/>
+      <c r="N266" s="121"/>
+    </row>
+    <row r="267" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="41">
+        <f t="shared" si="9"/>
+        <v>266</v>
+      </c>
+      <c r="B267" s="127" t="s">
+        <v>534</v>
+      </c>
+      <c r="C267" s="122" t="s">
+        <v>535</v>
+      </c>
+      <c r="D267" s="123"/>
+      <c r="E267" s="119"/>
+      <c r="F267" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="G267" s="119"/>
+      <c r="H267" s="119"/>
+      <c r="I267" s="146"/>
+      <c r="J267" s="146"/>
+      <c r="K267" s="123" t="s">
+        <v>519</v>
+      </c>
+      <c r="L267" s="123"/>
+      <c r="M267" s="119"/>
+      <c r="N267" s="123"/>
+    </row>
+    <row r="268" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="41">
+        <f t="shared" si="9"/>
+        <v>267</v>
+      </c>
+      <c r="B268" s="125" t="s">
+        <v>536</v>
+      </c>
+      <c r="C268" s="120" t="s">
+        <v>537</v>
+      </c>
+      <c r="D268" s="121"/>
+      <c r="E268" s="124"/>
+      <c r="F268" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="G268" s="124"/>
+      <c r="H268" s="124"/>
+      <c r="I268" s="147"/>
+      <c r="J268" s="147"/>
+      <c r="K268" s="121" t="s">
+        <v>519</v>
+      </c>
+      <c r="L268" s="121"/>
+      <c r="M268" s="124"/>
+      <c r="N268" s="121"/>
+    </row>
+    <row r="269" spans="1:14" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="41">
+        <f t="shared" si="9"/>
+        <v>268</v>
+      </c>
+      <c r="B269" s="127" t="s">
+        <v>538</v>
+      </c>
+      <c r="C269" s="122" t="s">
+        <v>539</v>
+      </c>
+      <c r="D269" s="123"/>
+      <c r="E269" s="119"/>
+      <c r="F269" s="131" t="s">
+        <v>68</v>
+      </c>
+      <c r="G269" s="119"/>
+      <c r="H269" s="119"/>
+      <c r="I269" s="146"/>
+      <c r="J269" s="146"/>
+      <c r="K269" s="123" t="s">
+        <v>519</v>
+      </c>
+      <c r="L269" s="123"/>
+      <c r="M269" s="119"/>
+      <c r="N269" s="123"/>
+    </row>
+    <row r="270" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A270" s="41">
+        <f t="shared" si="9"/>
+        <v>269</v>
+      </c>
+      <c r="B270" s="125" t="s">
+        <v>540</v>
+      </c>
+      <c r="C270" s="120" t="s">
+        <v>541</v>
+      </c>
+      <c r="D270" s="121"/>
+      <c r="E270" s="124"/>
+      <c r="F270" s="129" t="s">
+        <v>73</v>
+      </c>
+      <c r="G270" s="124"/>
+      <c r="H270" s="124"/>
+      <c r="I270" s="147"/>
+      <c r="J270" s="147"/>
+      <c r="K270" s="121" t="s">
+        <v>519</v>
+      </c>
+      <c r="L270" s="121"/>
+      <c r="M270" s="124"/>
+      <c r="N270" s="121"/>
+    </row>
+    <row r="271" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A271" s="41">
+        <f t="shared" si="9"/>
+        <v>270</v>
+      </c>
+      <c r="B271" s="126" t="s">
+        <v>542</v>
+      </c>
+      <c r="C271" s="122" t="s">
+        <v>543</v>
+      </c>
+      <c r="D271" s="123"/>
+      <c r="E271" s="119"/>
+      <c r="F271" s="130" t="s">
         <v>63</v>
       </c>
-      <c r="G261" s="126"/>
-      <c r="H261" s="126"/>
-      <c r="I261" s="134"/>
-      <c r="J261" s="134"/>
-      <c r="K261" s="128" t="s">
-        <v>516</v>
-      </c>
-      <c r="L261" s="128"/>
-      <c r="M261" s="126"/>
-      <c r="N261" s="128"/>
-    </row>
-    <row r="262" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A262" s="141">
-        <v>261</v>
-      </c>
-      <c r="B262" s="137" t="s">
-        <v>523</v>
-      </c>
-      <c r="C262" s="68" t="s">
-        <v>524</v>
-      </c>
-      <c r="D262" s="74"/>
-      <c r="E262" s="87"/>
-      <c r="F262" s="81" t="s">
+      <c r="G271" s="119"/>
+      <c r="H271" s="119"/>
+      <c r="I271" s="146"/>
+      <c r="J271" s="146"/>
+      <c r="K271" s="123" t="s">
+        <v>519</v>
+      </c>
+      <c r="L271" s="123"/>
+      <c r="M271" s="119"/>
+      <c r="N271" s="123"/>
+    </row>
+    <row r="272" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A272" s="162">
+        <f t="shared" si="9"/>
+        <v>271</v>
+      </c>
+      <c r="B272" s="148" t="s">
+        <v>544</v>
+      </c>
+      <c r="C272" s="149" t="s">
+        <v>545</v>
+      </c>
+      <c r="D272" s="150"/>
+      <c r="E272" s="151"/>
+      <c r="F272" s="152" t="s">
         <v>73</v>
       </c>
-      <c r="G262" s="87"/>
-      <c r="H262" s="87"/>
-      <c r="I262" s="133"/>
-      <c r="J262" s="133"/>
-      <c r="K262" s="74" t="s">
-        <v>516</v>
-      </c>
-      <c r="L262" s="74"/>
-      <c r="M262" s="87"/>
-      <c r="N262" s="74"/>
-    </row>
-    <row r="263" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A263" s="142">
-        <v>262</v>
-      </c>
-      <c r="B263" s="139" t="s">
-        <v>525</v>
-      </c>
-      <c r="C263" s="129" t="s">
-        <v>526</v>
-      </c>
-      <c r="D263" s="128"/>
-      <c r="E263" s="126"/>
-      <c r="F263" s="81" t="s">
+      <c r="G272" s="151"/>
+      <c r="H272" s="151"/>
+      <c r="I272" s="153"/>
+      <c r="J272" s="153"/>
+      <c r="K272" s="150" t="s">
+        <v>519</v>
+      </c>
+      <c r="L272" s="150"/>
+      <c r="M272" s="151"/>
+      <c r="N272" s="150"/>
+    </row>
+    <row r="273" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="165">
+        <f t="shared" si="9"/>
+        <v>272</v>
+      </c>
+      <c r="B273" s="164" t="s">
+        <v>549</v>
+      </c>
+      <c r="C273" s="159" t="s">
+        <v>550</v>
+      </c>
+      <c r="D273" s="159" t="s">
+        <v>79</v>
+      </c>
+      <c r="E273" s="160" t="s">
+        <v>337</v>
+      </c>
+      <c r="F273" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="G263" s="126"/>
-      <c r="H263" s="126"/>
-      <c r="I263" s="134"/>
-      <c r="J263" s="134"/>
-      <c r="K263" s="128" t="s">
-        <v>516</v>
-      </c>
-      <c r="L263" s="128"/>
-      <c r="M263" s="126"/>
-      <c r="N263" s="128"/>
-    </row>
-    <row r="264" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A264" s="141">
-        <v>263</v>
-      </c>
-      <c r="B264" s="140" t="s">
-        <v>527</v>
-      </c>
-      <c r="C264" s="130" t="s">
-        <v>546</v>
-      </c>
-      <c r="D264" s="74"/>
-      <c r="E264" s="87"/>
-      <c r="F264" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="G264" s="87"/>
-      <c r="H264" s="87"/>
-      <c r="I264" s="133"/>
-      <c r="J264" s="133"/>
-      <c r="K264" s="74" t="s">
-        <v>516</v>
-      </c>
-      <c r="L264" s="74"/>
-      <c r="M264" s="87"/>
-      <c r="N264" s="74"/>
-    </row>
-    <row r="265" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A265" s="142">
-        <v>264</v>
-      </c>
-      <c r="B265" s="139" t="s">
-        <v>528</v>
-      </c>
-      <c r="C265" s="131" t="s">
-        <v>529</v>
-      </c>
-      <c r="D265" s="128"/>
-      <c r="E265" s="126"/>
-      <c r="F265" s="136" t="s">
-        <v>68</v>
-      </c>
-      <c r="G265" s="126"/>
-      <c r="H265" s="126"/>
-      <c r="I265" s="134"/>
-      <c r="J265" s="134"/>
-      <c r="K265" s="128" t="s">
-        <v>516</v>
-      </c>
-      <c r="L265" s="128"/>
-      <c r="M265" s="126"/>
-      <c r="N265" s="128"/>
-    </row>
-    <row r="266" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A266" s="141">
-        <v>265</v>
-      </c>
-      <c r="B266" s="140" t="s">
-        <v>530</v>
-      </c>
-      <c r="C266" s="132" t="s">
-        <v>531</v>
-      </c>
-      <c r="D266" s="74"/>
-      <c r="E266" s="87"/>
-      <c r="F266" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="G266" s="87"/>
-      <c r="H266" s="87"/>
-      <c r="I266" s="133"/>
-      <c r="J266" s="133"/>
-      <c r="K266" s="74" t="s">
-        <v>516</v>
-      </c>
-      <c r="L266" s="74"/>
-      <c r="M266" s="87"/>
-      <c r="N266" s="74"/>
-    </row>
-    <row r="267" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="142">
-        <v>266</v>
-      </c>
-      <c r="B267" s="139" t="s">
-        <v>532</v>
-      </c>
-      <c r="C267" s="127" t="s">
-        <v>533</v>
-      </c>
-      <c r="D267" s="128"/>
-      <c r="E267" s="126"/>
-      <c r="F267" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="G267" s="126"/>
-      <c r="H267" s="126"/>
-      <c r="I267" s="134"/>
-      <c r="J267" s="134"/>
-      <c r="K267" s="128" t="s">
-        <v>516</v>
-      </c>
-      <c r="L267" s="128"/>
-      <c r="M267" s="126"/>
-      <c r="N267" s="128"/>
-    </row>
-    <row r="268" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="141">
-        <v>267</v>
-      </c>
-      <c r="B268" s="137" t="s">
-        <v>534</v>
-      </c>
-      <c r="C268" s="68" t="s">
-        <v>535</v>
-      </c>
-      <c r="D268" s="74"/>
-      <c r="E268" s="87"/>
-      <c r="F268" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="G268" s="87"/>
-      <c r="H268" s="87"/>
-      <c r="I268" s="133"/>
-      <c r="J268" s="133"/>
-      <c r="K268" s="74" t="s">
-        <v>516</v>
-      </c>
-      <c r="L268" s="74"/>
-      <c r="M268" s="87"/>
-      <c r="N268" s="74"/>
-    </row>
-    <row r="269" spans="1:14" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="142">
-        <v>268</v>
-      </c>
-      <c r="B269" s="139" t="s">
-        <v>536</v>
-      </c>
-      <c r="C269" s="127" t="s">
-        <v>537</v>
-      </c>
-      <c r="D269" s="128"/>
-      <c r="E269" s="126"/>
-      <c r="F269" s="136" t="s">
-        <v>68</v>
-      </c>
-      <c r="G269" s="126"/>
-      <c r="H269" s="126"/>
-      <c r="I269" s="134"/>
-      <c r="J269" s="134"/>
-      <c r="K269" s="128" t="s">
-        <v>516</v>
-      </c>
-      <c r="L269" s="128"/>
-      <c r="M269" s="126"/>
-      <c r="N269" s="128"/>
-    </row>
-    <row r="270" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A270" s="141">
-        <v>269</v>
-      </c>
-      <c r="B270" s="137" t="s">
-        <v>538</v>
-      </c>
-      <c r="C270" s="68" t="s">
-        <v>547</v>
-      </c>
-      <c r="D270" s="74"/>
-      <c r="E270" s="87"/>
-      <c r="F270" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="G270" s="87"/>
-      <c r="H270" s="87"/>
-      <c r="I270" s="133"/>
-      <c r="J270" s="133"/>
-      <c r="K270" s="74" t="s">
-        <v>516</v>
-      </c>
-      <c r="L270" s="74"/>
-      <c r="M270" s="87"/>
-      <c r="N270" s="74"/>
-    </row>
-    <row r="271" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A271" s="142">
-        <v>270</v>
-      </c>
-      <c r="B271" s="138" t="s">
-        <v>539</v>
-      </c>
-      <c r="C271" s="127" t="s">
-        <v>540</v>
-      </c>
-      <c r="D271" s="128"/>
-      <c r="E271" s="126"/>
-      <c r="F271" s="135" t="s">
-        <v>63</v>
-      </c>
-      <c r="G271" s="126"/>
-      <c r="H271" s="126"/>
-      <c r="I271" s="134"/>
-      <c r="J271" s="134"/>
-      <c r="K271" s="128" t="s">
-        <v>516</v>
-      </c>
-      <c r="L271" s="128"/>
-      <c r="M271" s="126"/>
-      <c r="N271" s="128"/>
-    </row>
-    <row r="272" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="141">
-        <v>271</v>
-      </c>
-      <c r="B272" s="137" t="s">
-        <v>541</v>
-      </c>
-      <c r="C272" s="68" t="s">
-        <v>542</v>
-      </c>
-      <c r="D272" s="74"/>
-      <c r="E272" s="87"/>
-      <c r="F272" s="81" t="s">
-        <v>73</v>
-      </c>
-      <c r="G272" s="87"/>
-      <c r="H272" s="87"/>
-      <c r="I272" s="133"/>
-      <c r="J272" s="133"/>
-      <c r="K272" s="74" t="s">
-        <v>516</v>
-      </c>
-      <c r="L272" s="74"/>
-      <c r="M272" s="87"/>
-      <c r="N272" s="74"/>
-    </row>
-    <row r="273" spans="9:10" x14ac:dyDescent="0.3">
-      <c r="I273" s="42"/>
-      <c r="J273" s="42"/>
-    </row>
-    <row r="274" spans="9:10" x14ac:dyDescent="0.3">
+      <c r="G273" s="160"/>
+      <c r="H273" s="160"/>
+      <c r="I273" s="161">
+        <v>46226</v>
+      </c>
+      <c r="J273" s="161">
+        <v>46220</v>
+      </c>
+      <c r="K273" s="159"/>
+      <c r="L273" s="159"/>
+      <c r="M273" s="160" t="s">
+        <v>97</v>
+      </c>
+      <c r="N273" s="158"/>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I274" s="42"/>
       <c r="J274" s="42"/>
     </row>
-    <row r="275" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I275" s="42"/>
       <c r="J275" s="42"/>
     </row>
-    <row r="276" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I276" s="42"/>
       <c r="J276" s="42"/>
     </row>
-    <row r="277" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I277" s="42"/>
       <c r="J277" s="42"/>
     </row>
-    <row r="278" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I278" s="42"/>
       <c r="J278" s="42"/>
     </row>
-    <row r="279" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I279" s="42"/>
       <c r="J279" s="42"/>
     </row>
-    <row r="280" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I280" s="42"/>
       <c r="J280" s="42"/>
     </row>
-    <row r="281" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I281" s="42"/>
       <c r="J281" s="42"/>
     </row>
-    <row r="282" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I282" s="42"/>
       <c r="J282" s="42"/>
     </row>
-    <row r="283" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I283" s="42"/>
       <c r="J283" s="42"/>
     </row>
-    <row r="284" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I284" s="42"/>
       <c r="J284" s="42"/>
     </row>
-    <row r="285" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I285" s="42"/>
       <c r="J285" s="42"/>
     </row>
-    <row r="286" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I286" s="42"/>
       <c r="J286" s="42"/>
     </row>
-    <row r="287" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I287" s="42"/>
       <c r="J287" s="42"/>
     </row>
-    <row r="288" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I288" s="42"/>
       <c r="J288" s="42"/>
     </row>
@@ -14926,38 +15127,38 @@
       <c r="J997" s="42"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M181" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <autoFilter ref="A1:M273" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M252">
       <sortCondition descending="1" ref="E1:E181"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="E2:E297">
-    <cfRule type="expression" dxfId="8" priority="15">
+  <conditionalFormatting sqref="E275:E297 E2:E273">
+    <cfRule type="expression" dxfId="8" priority="16">
       <formula>$E2="Done"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="16">
+    <cfRule type="expression" dxfId="7" priority="17">
       <formula>$E2="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="17">
+    <cfRule type="expression" dxfId="6" priority="18">
       <formula>$E2="In review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="18">
+    <cfRule type="expression" dxfId="5" priority="19">
       <formula>$E2="Backlog"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F297">
-    <cfRule type="expression" dxfId="4" priority="19">
+    <cfRule type="expression" dxfId="4" priority="20">
       <formula>$F2="High"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="20">
+    <cfRule type="expression" dxfId="3" priority="21">
       <formula>$F2="Medium"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="21">
+    <cfRule type="expression" dxfId="2" priority="22">
       <formula>$F2="Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:N248 D263:D266 C267:D267 B268:D268 C269:D269 B270:D271 B272 D272 A2:D253 A273:D1048576 G249:M1048576 B254:D262 A254:A272">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="A2:N273">
+    <cfRule type="expression" dxfId="0" priority="15">
       <formula>AND($B2&lt;&gt;"",ISEVEN(ROW()))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14968,7 +15169,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F297" xr:uid="{C1780BFE-B567-4F5D-87FE-F9B5A57B4712}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E243 E245:E297" xr:uid="{6858018E-BA70-46A0-BA18-28D3782838CF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E243 E245:E273 E275:E297" xr:uid="{6858018E-BA70-46A0-BA18-28D3782838CF}">
       <formula1>"Backlog,In progress,In review,Done"</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid date" error="Please enter a valid date between 1/1/2000 and 12/31/2100." promptTitle="Enter a date" prompt="Type a date (e.g. 7/2/2026). Only valid dates are accepted." sqref="I2:J997" xr:uid="{C47FE8E2-BF9C-4D61-B67A-FFEEFDDC2AB9}">
@@ -15006,7 +15207,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -15021,7 +15222,7 @@
     </row>
     <row r="4" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -15031,17 +15232,17 @@
     </row>
     <row r="6" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A7">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15051,6 +15252,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -15305,27 +15526,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
+    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15342,23 +15562,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
-    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30306"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="3998" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3A51BA9-20D2-4560-BDD8-F2D0DC300AD2}"/>
+  <xr:revisionPtr revIDLastSave="4011" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{550153B3-9AA4-4556-9551-94C8348E683E}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="551">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -1680,6 +1680,12 @@
     <t>JM and Carlee reported there were miss cuts because of the distribution issues on one of the systems after customer changed some product positions. </t>
   </si>
   <si>
+    <t>Gonnella EyeQ commisioning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation and gonnella EyeQ commisioning </t>
+  </si>
+  <si>
     <t>Team Member (GitHub username)</t>
   </si>
   <si>
@@ -1687,27 +1693,24 @@
   </si>
   <si>
     <t>ThongHHuynhh</t>
-  </si>
-  <si>
-    <t>Gonnella EyeQ commisioning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Installation and gonnella EyeQ commisioning </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-  </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1846,12 +1849,6 @@
       <sz val="11"/>
       <color rgb="FF7F6000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="19">
@@ -2276,48 +2273,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2329,128 +2326,128 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2459,13 +2456,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2474,13 +2471,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2489,49 +2486,49 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2540,13 +2537,13 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2555,31 +2552,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2605,162 +2602,146 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2888,8 +2869,25 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <namedSheetView name="DG View" id="{FCF2143E-0C7B-44DE-9E27-8F16DD5FB32D}">
+    <nsvFilter filterId="{00000000-0001-0000-0100-000000000000}" ref="A1:M273" tableId="0">
+      <columnFilter colId="3">
+        <filter colId="3">
+          <x:filters>
+            <x:filter val="dilinaabi"/>
+          </x:filters>
+        </filter>
+      </columnFilter>
+      <sortRules>
+        <sortRule colId="4">
+          <sortCondition descending="1" ref="E1:E273"/>
+        </sortRule>
+      </sortRules>
+    </nsvFilter>
+  </namedSheetView>
+</namedSheetViews>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3242,7 +3240,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:C38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -3250,25 +3248,25 @@
     <col min="4" max="4" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="134" t="s">
+    <row r="2" spans="2:3" ht="36" customHeight="1">
+      <c r="B2" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="134"/>
-    </row>
-    <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="135" t="s">
+      <c r="C2" s="153"/>
+    </row>
+    <row r="4" spans="2:3" ht="18" customHeight="1">
+      <c r="B4" s="154" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="135"/>
-    </row>
-    <row r="6" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="133" t="s">
+      <c r="C4" s="154"/>
+    </row>
+    <row r="6" spans="2:3" ht="24" customHeight="1">
+      <c r="B6" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="133"/>
-    </row>
-    <row r="7" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="152"/>
+    </row>
+    <row r="7" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
@@ -3276,7 +3274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -3284,7 +3282,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3292,13 +3290,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="133" t="s">
+    <row r="11" spans="2:3" ht="24" customHeight="1">
+      <c r="B11" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="133"/>
-    </row>
-    <row r="12" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="152"/>
+    </row>
+    <row r="12" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -3306,7 +3304,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
@@ -3314,7 +3312,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3322,7 +3320,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
@@ -3330,7 +3328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
@@ -3338,7 +3336,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
@@ -3346,7 +3344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B18" s="1" t="s">
         <v>22</v>
       </c>
@@ -3354,7 +3352,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
@@ -3362,7 +3360,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
@@ -3370,7 +3368,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B21" s="1" t="s">
         <v>28</v>
       </c>
@@ -3378,7 +3376,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
@@ -3386,7 +3384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B23" s="1" t="s">
         <v>32</v>
       </c>
@@ -3394,13 +3392,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="133" t="s">
+    <row r="25" spans="2:3" ht="24" customHeight="1">
+      <c r="B25" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="133"/>
-    </row>
-    <row r="26" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="152"/>
+    </row>
+    <row r="26" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
@@ -3408,7 +3406,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B27" s="1" t="s">
         <v>37</v>
       </c>
@@ -3416,7 +3414,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B28" s="1" t="s">
         <v>39</v>
       </c>
@@ -3424,7 +3422,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B29" s="1" t="s">
         <v>41</v>
       </c>
@@ -3432,7 +3430,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B30" s="1" t="s">
         <v>43</v>
       </c>
@@ -3440,7 +3438,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B31" s="1" t="s">
         <v>45</v>
       </c>
@@ -3448,13 +3446,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="133" t="s">
+    <row r="33" spans="2:3" ht="24" customHeight="1">
+      <c r="B33" s="152" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="133"/>
-    </row>
-    <row r="34" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="152"/>
+    </row>
+    <row r="34" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B34" s="1" t="s">
         <v>48</v>
       </c>
@@ -3462,7 +3460,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B35" s="1" t="s">
         <v>50</v>
       </c>
@@ -3470,7 +3468,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B36" s="1" t="s">
         <v>52</v>
       </c>
@@ -3478,7 +3476,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B37" s="1" t="s">
         <v>54</v>
       </c>
@@ -3486,7 +3484,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" ht="19.899999999999999" customHeight="1">
       <c r="B38" s="1" t="s">
         <v>56</v>
       </c>
@@ -3514,24 +3512,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N997"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" customWidth="1"/>
-    <col min="2" max="2" width="51.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="70.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="10" width="17.5546875" customWidth="1"/>
-    <col min="11" max="11" width="22.33203125" customWidth="1"/>
-    <col min="12" max="12" width="44.44140625" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="51.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="70.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="10" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="22.28515625" customWidth="1"/>
+    <col min="12" max="12" width="44.42578125" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="114" customFormat="1" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="114" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
       <c r="A1" s="115" t="s">
         <v>10</v>
       </c>
@@ -3575,7 +3573,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A2" s="41">
         <f>IF($B2="","",ROW()-1)</f>
         <v>1</v>
@@ -3604,7 +3602,7 @@
       </c>
       <c r="N2" s="52"/>
     </row>
-    <row r="3" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A3" s="98">
         <v>248</v>
       </c>
@@ -3640,7 +3638,7 @@
       <c r="M3" s="107"/>
       <c r="N3" s="53"/>
     </row>
-    <row r="4" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A4" s="41">
         <f t="shared" ref="A4:A11" si="0">IF($B4="","",ROW()-1)</f>
         <v>3</v>
@@ -3669,7 +3667,7 @@
       </c>
       <c r="N4" s="53"/>
     </row>
-    <row r="5" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A5" s="41">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3700,7 +3698,7 @@
       </c>
       <c r="N5" s="53"/>
     </row>
-    <row r="6" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A6" s="41">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3737,7 +3735,7 @@
       </c>
       <c r="N6" s="53"/>
     </row>
-    <row r="7" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A7" s="41">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3774,7 +3772,7 @@
       </c>
       <c r="N7" s="53"/>
     </row>
-    <row r="8" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A8" s="41">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3809,7 +3807,7 @@
       </c>
       <c r="N8" s="53"/>
     </row>
-    <row r="9" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A9" s="41">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3844,7 +3842,7 @@
       </c>
       <c r="N9" s="53"/>
     </row>
-    <row r="10" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A10" s="41">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3879,7 +3877,7 @@
       </c>
       <c r="N10" s="53"/>
     </row>
-    <row r="11" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A11" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3912,7 +3910,7 @@
       </c>
       <c r="N11" s="53"/>
     </row>
-    <row r="12" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A12" s="41">
         <v>238</v>
       </c>
@@ -3946,7 +3944,7 @@
       </c>
       <c r="N12" s="53"/>
     </row>
-    <row r="13" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A13" s="41">
         <v>241</v>
       </c>
@@ -3984,7 +3982,7 @@
       </c>
       <c r="N13" s="53"/>
     </row>
-    <row r="14" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A14" s="41">
         <v>242</v>
       </c>
@@ -4014,7 +4012,7 @@
       </c>
       <c r="N14" s="53"/>
     </row>
-    <row r="15" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A15" s="41">
         <v>243</v>
       </c>
@@ -4050,7 +4048,7 @@
       </c>
       <c r="N15" s="53"/>
     </row>
-    <row r="16" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A16" s="41">
         <v>247</v>
       </c>
@@ -4088,7 +4086,7 @@
       </c>
       <c r="N16" s="53"/>
     </row>
-    <row r="17" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A17" s="41">
         <f t="shared" ref="A17:A26" si="1">IF($B17="","",ROW()-1)</f>
         <v>16</v>
@@ -4119,7 +4117,7 @@
       </c>
       <c r="N17" s="53"/>
     </row>
-    <row r="18" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A18" s="41">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -4150,7 +4148,7 @@
       </c>
       <c r="N18" s="53"/>
     </row>
-    <row r="19" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A19" s="41">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -4179,7 +4177,7 @@
       </c>
       <c r="N19" s="53"/>
     </row>
-    <row r="20" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A20" s="41">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -4208,7 +4206,7 @@
       </c>
       <c r="N20" s="53"/>
     </row>
-    <row r="21" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A21" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -4245,7 +4243,7 @@
       </c>
       <c r="N21" s="53"/>
     </row>
-    <row r="22" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A22" s="41">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -4282,7 +4280,7 @@
       </c>
       <c r="N22" s="53"/>
     </row>
-    <row r="23" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A23" s="41">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -4315,7 +4313,7 @@
       </c>
       <c r="N23" s="53"/>
     </row>
-    <row r="24" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A24" s="41">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -4350,7 +4348,7 @@
       </c>
       <c r="N24" s="53"/>
     </row>
-    <row r="25" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A25" s="41">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -4383,7 +4381,7 @@
       <c r="M25" s="96"/>
       <c r="N25" s="53"/>
     </row>
-    <row r="26" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A26" s="41">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -4416,7 +4414,7 @@
       <c r="M26" s="96"/>
       <c r="N26" s="53"/>
     </row>
-    <row r="27" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A27" s="41">
         <v>245</v>
       </c>
@@ -4452,7 +4450,7 @@
       </c>
       <c r="N27" s="53"/>
     </row>
-    <row r="28" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A28" s="41">
         <f t="shared" ref="A28:A41" si="2">IF($B28="","",ROW()-1)</f>
         <v>27</v>
@@ -4483,7 +4481,7 @@
       </c>
       <c r="N28" s="53"/>
     </row>
-    <row r="29" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A29" s="41">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -4514,7 +4512,7 @@
       </c>
       <c r="N29" s="53"/>
     </row>
-    <row r="30" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A30" s="41">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -4545,7 +4543,7 @@
       </c>
       <c r="N30" s="53"/>
     </row>
-    <row r="31" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A31" s="41">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -4574,7 +4572,7 @@
       </c>
       <c r="N31" s="53"/>
     </row>
-    <row r="32" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A32" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -4603,7 +4601,7 @@
       </c>
       <c r="N32" s="53"/>
     </row>
-    <row r="33" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A33" s="41">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -4640,7 +4638,7 @@
       </c>
       <c r="N33" s="53"/>
     </row>
-    <row r="34" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A34" s="41">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -4675,7 +4673,7 @@
       </c>
       <c r="N34" s="53"/>
     </row>
-    <row r="35" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A35" s="41">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -4712,7 +4710,7 @@
       </c>
       <c r="N35" s="53"/>
     </row>
-    <row r="36" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A36" s="41">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -4749,7 +4747,7 @@
       </c>
       <c r="N36" s="53"/>
     </row>
-    <row r="37" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A37" s="41">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -4786,7 +4784,7 @@
       </c>
       <c r="N37" s="53"/>
     </row>
-    <row r="38" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A38" s="41">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -4823,7 +4821,7 @@
       </c>
       <c r="N38" s="53"/>
     </row>
-    <row r="39" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A39" s="41">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -4856,7 +4854,7 @@
       </c>
       <c r="N39" s="53"/>
     </row>
-    <row r="40" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A40" s="41">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -4889,7 +4887,7 @@
       </c>
       <c r="N40" s="53"/>
     </row>
-    <row r="41" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A41" s="41">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -4922,7 +4920,7 @@
       </c>
       <c r="N41" s="53"/>
     </row>
-    <row r="42" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A42" s="41">
         <v>239</v>
       </c>
@@ -4958,7 +4956,7 @@
       </c>
       <c r="N42" s="53"/>
     </row>
-    <row r="43" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A43" s="41">
         <v>240</v>
       </c>
@@ -4992,7 +4990,7 @@
       </c>
       <c r="N43" s="53"/>
     </row>
-    <row r="44" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A44" s="41">
         <f>IF($B44="","",ROW()-1)</f>
         <v>43</v>
@@ -5029,7 +5027,7 @@
       </c>
       <c r="N44" s="53"/>
     </row>
-    <row r="45" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A45" s="41">
         <f>IF($B45="","",ROW()-1)</f>
         <v>44</v>
@@ -5066,7 +5064,7 @@
       </c>
       <c r="N45" s="53"/>
     </row>
-    <row r="46" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A46" s="41">
         <v>237</v>
       </c>
@@ -5102,7 +5100,7 @@
       </c>
       <c r="N46" s="53"/>
     </row>
-    <row r="47" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A47" s="41">
         <f t="shared" ref="A47:A83" si="3">IF($B47="","",ROW()-1)</f>
         <v>46</v>
@@ -5131,7 +5129,7 @@
       </c>
       <c r="N47" s="53"/>
     </row>
-    <row r="48" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A48" s="41">
         <f t="shared" si="3"/>
         <v>47</v>
@@ -5162,7 +5160,7 @@
       </c>
       <c r="N48" s="53"/>
     </row>
-    <row r="49" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A49" s="41">
         <f t="shared" si="3"/>
         <v>48</v>
@@ -5193,7 +5191,7 @@
       </c>
       <c r="N49" s="53"/>
     </row>
-    <row r="50" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A50" s="41">
         <f t="shared" si="3"/>
         <v>49</v>
@@ -5224,7 +5222,7 @@
       </c>
       <c r="N50" s="53"/>
     </row>
-    <row r="51" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A51" s="41">
         <f t="shared" si="3"/>
         <v>50</v>
@@ -5257,7 +5255,7 @@
       </c>
       <c r="N51" s="53"/>
     </row>
-    <row r="52" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A52" s="41">
         <f t="shared" si="3"/>
         <v>51</v>
@@ -5290,7 +5288,7 @@
       </c>
       <c r="N52" s="53"/>
     </row>
-    <row r="53" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A53" s="41">
         <f t="shared" si="3"/>
         <v>52</v>
@@ -5327,7 +5325,7 @@
       </c>
       <c r="N53" s="53"/>
     </row>
-    <row r="54" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A54" s="41">
         <f t="shared" si="3"/>
         <v>53</v>
@@ -5356,7 +5354,7 @@
       </c>
       <c r="N54" s="53"/>
     </row>
-    <row r="55" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A55" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
@@ -5385,7 +5383,7 @@
       </c>
       <c r="N55" s="53"/>
     </row>
-    <row r="56" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A56" s="41">
         <f t="shared" si="3"/>
         <v>55</v>
@@ -5416,7 +5414,7 @@
       <c r="M56" s="11"/>
       <c r="N56" s="53"/>
     </row>
-    <row r="57" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A57" s="41">
         <f t="shared" si="3"/>
         <v>56</v>
@@ -5453,7 +5451,7 @@
       </c>
       <c r="N57" s="53"/>
     </row>
-    <row r="58" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A58" s="41">
         <f t="shared" si="3"/>
         <v>57</v>
@@ -5490,7 +5488,7 @@
       </c>
       <c r="N58" s="53"/>
     </row>
-    <row r="59" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A59" s="41">
         <f t="shared" si="3"/>
         <v>58</v>
@@ -5527,7 +5525,7 @@
       </c>
       <c r="N59" s="53"/>
     </row>
-    <row r="60" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A60" s="41">
         <f t="shared" si="3"/>
         <v>59</v>
@@ -5564,7 +5562,7 @@
       </c>
       <c r="N60" s="53"/>
     </row>
-    <row r="61" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A61" s="41">
         <f t="shared" si="3"/>
         <v>60</v>
@@ -5601,7 +5599,7 @@
       </c>
       <c r="N61" s="53"/>
     </row>
-    <row r="62" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A62" s="41">
         <f t="shared" si="3"/>
         <v>61</v>
@@ -5638,7 +5636,7 @@
       </c>
       <c r="N62" s="53"/>
     </row>
-    <row r="63" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A63" s="41">
         <f t="shared" si="3"/>
         <v>62</v>
@@ -5673,7 +5671,7 @@
       </c>
       <c r="N63" s="53"/>
     </row>
-    <row r="64" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A64" s="41">
         <f t="shared" si="3"/>
         <v>63</v>
@@ -5710,7 +5708,7 @@
       </c>
       <c r="N64" s="53"/>
     </row>
-    <row r="65" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A65" s="41">
         <f t="shared" si="3"/>
         <v>64</v>
@@ -5745,7 +5743,7 @@
       </c>
       <c r="N65" s="53"/>
     </row>
-    <row r="66" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A66" s="41">
         <f t="shared" si="3"/>
         <v>65</v>
@@ -5778,7 +5776,7 @@
       </c>
       <c r="N66" s="53"/>
     </row>
-    <row r="67" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A67" s="41">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -5811,7 +5809,7 @@
       </c>
       <c r="N67" s="53"/>
     </row>
-    <row r="68" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A68" s="41">
         <f t="shared" si="3"/>
         <v>67</v>
@@ -5846,7 +5844,7 @@
       </c>
       <c r="N68" s="53"/>
     </row>
-    <row r="69" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A69" s="41">
         <f t="shared" si="3"/>
         <v>68</v>
@@ -5881,7 +5879,7 @@
       </c>
       <c r="N69" s="53"/>
     </row>
-    <row r="70" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A70" s="41">
         <f t="shared" si="3"/>
         <v>69</v>
@@ -5916,7 +5914,7 @@
       </c>
       <c r="N70" s="53"/>
     </row>
-    <row r="71" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A71" s="41">
         <f t="shared" si="3"/>
         <v>70</v>
@@ -5949,7 +5947,7 @@
       </c>
       <c r="N71" s="53"/>
     </row>
-    <row r="72" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A72" s="41">
         <f t="shared" si="3"/>
         <v>71</v>
@@ -5984,7 +5982,7 @@
       </c>
       <c r="N72" s="53"/>
     </row>
-    <row r="73" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A73" s="41">
         <f t="shared" si="3"/>
         <v>72</v>
@@ -6019,7 +6017,7 @@
       </c>
       <c r="N73" s="53"/>
     </row>
-    <row r="74" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A74" s="41">
         <f t="shared" si="3"/>
         <v>73</v>
@@ -6052,7 +6050,7 @@
       </c>
       <c r="N74" s="53"/>
     </row>
-    <row r="75" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A75" s="41">
         <f t="shared" si="3"/>
         <v>74</v>
@@ -6087,7 +6085,7 @@
       </c>
       <c r="N75" s="53"/>
     </row>
-    <row r="76" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A76" s="41">
         <f t="shared" si="3"/>
         <v>75</v>
@@ -6122,7 +6120,7 @@
       </c>
       <c r="N76" s="53"/>
     </row>
-    <row r="77" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A77" s="41">
         <f t="shared" si="3"/>
         <v>76</v>
@@ -6155,7 +6153,7 @@
       </c>
       <c r="N77" s="53"/>
     </row>
-    <row r="78" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A78" s="41">
         <f t="shared" si="3"/>
         <v>77</v>
@@ -6188,7 +6186,7 @@
       </c>
       <c r="N78" s="53"/>
     </row>
-    <row r="79" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A79" s="41">
         <f t="shared" si="3"/>
         <v>78</v>
@@ -6221,7 +6219,7 @@
       </c>
       <c r="N79" s="53"/>
     </row>
-    <row r="80" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A80" s="41">
         <f t="shared" si="3"/>
         <v>79</v>
@@ -6254,7 +6252,7 @@
       </c>
       <c r="N80" s="53"/>
     </row>
-    <row r="81" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A81" s="41">
         <f t="shared" si="3"/>
         <v>80</v>
@@ -6287,7 +6285,7 @@
       </c>
       <c r="N81" s="53"/>
     </row>
-    <row r="82" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A82" s="41">
         <f t="shared" si="3"/>
         <v>81</v>
@@ -6322,7 +6320,7 @@
       </c>
       <c r="N82" s="53"/>
     </row>
-    <row r="83" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A83" s="41">
         <f t="shared" si="3"/>
         <v>82</v>
@@ -6359,7 +6357,7 @@
       </c>
       <c r="N83" s="53"/>
     </row>
-    <row r="84" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A84" s="41">
         <v>246</v>
       </c>
@@ -6395,7 +6393,7 @@
       </c>
       <c r="N84" s="53"/>
     </row>
-    <row r="85" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A85" s="41">
         <f t="shared" ref="A85:A116" si="4">IF($B85="","",ROW()-1)</f>
         <v>84</v>
@@ -6424,7 +6422,7 @@
       </c>
       <c r="N85" s="53"/>
     </row>
-    <row r="86" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A86" s="41">
         <f t="shared" si="4"/>
         <v>85</v>
@@ -6455,7 +6453,7 @@
       </c>
       <c r="N86" s="53"/>
     </row>
-    <row r="87" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A87" s="41">
         <f t="shared" si="4"/>
         <v>86</v>
@@ -6486,7 +6484,7 @@
       </c>
       <c r="N87" s="53"/>
     </row>
-    <row r="88" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A88" s="41">
         <f t="shared" si="4"/>
         <v>87</v>
@@ -6517,7 +6515,7 @@
       </c>
       <c r="N88" s="53"/>
     </row>
-    <row r="89" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A89" s="41">
         <f t="shared" si="4"/>
         <v>88</v>
@@ -6554,7 +6552,7 @@
       </c>
       <c r="N89" s="53"/>
     </row>
-    <row r="90" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A90" s="41">
         <f t="shared" si="4"/>
         <v>89</v>
@@ -6591,7 +6589,7 @@
       </c>
       <c r="N90" s="53"/>
     </row>
-    <row r="91" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A91" s="41">
         <f t="shared" si="4"/>
         <v>90</v>
@@ -6628,7 +6626,7 @@
       </c>
       <c r="N91" s="53"/>
     </row>
-    <row r="92" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A92" s="41">
         <f t="shared" si="4"/>
         <v>91</v>
@@ -6665,7 +6663,7 @@
       </c>
       <c r="N92" s="53"/>
     </row>
-    <row r="93" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A93" s="41">
         <f t="shared" si="4"/>
         <v>92</v>
@@ -6702,7 +6700,7 @@
       </c>
       <c r="N93" s="53"/>
     </row>
-    <row r="94" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A94" s="41">
         <f t="shared" si="4"/>
         <v>93</v>
@@ -6739,7 +6737,7 @@
       </c>
       <c r="N94" s="53"/>
     </row>
-    <row r="95" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A95" s="41">
         <f t="shared" si="4"/>
         <v>94</v>
@@ -6776,7 +6774,7 @@
       </c>
       <c r="N95" s="53"/>
     </row>
-    <row r="96" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A96" s="41">
         <f t="shared" si="4"/>
         <v>95</v>
@@ -6811,7 +6809,7 @@
       </c>
       <c r="N96" s="53"/>
     </row>
-    <row r="97" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A97" s="41">
         <f t="shared" si="4"/>
         <v>96</v>
@@ -6844,7 +6842,7 @@
       </c>
       <c r="N97" s="53"/>
     </row>
-    <row r="98" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A98" s="41">
         <f t="shared" si="4"/>
         <v>97</v>
@@ -6877,7 +6875,7 @@
       </c>
       <c r="N98" s="53"/>
     </row>
-    <row r="99" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A99" s="41">
         <f t="shared" si="4"/>
         <v>98</v>
@@ -6910,7 +6908,7 @@
       </c>
       <c r="N99" s="53"/>
     </row>
-    <row r="100" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A100" s="41">
         <f t="shared" si="4"/>
         <v>99</v>
@@ -6943,7 +6941,7 @@
       </c>
       <c r="N100" s="53"/>
     </row>
-    <row r="101" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A101" s="41">
         <f t="shared" si="4"/>
         <v>100</v>
@@ -6972,7 +6970,7 @@
       </c>
       <c r="N101" s="53"/>
     </row>
-    <row r="102" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A102" s="41">
         <f t="shared" si="4"/>
         <v>101</v>
@@ -7005,7 +7003,7 @@
       </c>
       <c r="N102" s="53"/>
     </row>
-    <row r="103" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A103" s="41">
         <f t="shared" si="4"/>
         <v>102</v>
@@ -7038,7 +7036,7 @@
       </c>
       <c r="N103" s="53"/>
     </row>
-    <row r="104" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A104" s="41">
         <f t="shared" si="4"/>
         <v>103</v>
@@ -7069,7 +7067,7 @@
       </c>
       <c r="N104" s="53"/>
     </row>
-    <row r="105" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A105" s="41">
         <f t="shared" si="4"/>
         <v>104</v>
@@ -7100,7 +7098,7 @@
       </c>
       <c r="N105" s="53"/>
     </row>
-    <row r="106" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A106" s="41">
         <f t="shared" si="4"/>
         <v>105</v>
@@ -7129,7 +7127,7 @@
       </c>
       <c r="N106" s="53"/>
     </row>
-    <row r="107" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A107" s="41">
         <f t="shared" si="4"/>
         <v>106</v>
@@ -7158,7 +7156,7 @@
       </c>
       <c r="N107" s="53"/>
     </row>
-    <row r="108" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A108" s="41">
         <f t="shared" si="4"/>
         <v>107</v>
@@ -7187,7 +7185,7 @@
       </c>
       <c r="N108" s="53"/>
     </row>
-    <row r="109" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A109" s="41">
         <f t="shared" si="4"/>
         <v>108</v>
@@ -7216,7 +7214,7 @@
       </c>
       <c r="N109" s="53"/>
     </row>
-    <row r="110" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A110" s="41">
         <f t="shared" si="4"/>
         <v>109</v>
@@ -7249,7 +7247,7 @@
       </c>
       <c r="N110" s="53"/>
     </row>
-    <row r="111" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A111" s="41">
         <f t="shared" si="4"/>
         <v>110</v>
@@ -7282,7 +7280,7 @@
       </c>
       <c r="N111" s="53"/>
     </row>
-    <row r="112" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A112" s="41">
         <f t="shared" si="4"/>
         <v>111</v>
@@ -7319,7 +7317,7 @@
       </c>
       <c r="N112" s="53"/>
     </row>
-    <row r="113" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A113" s="41">
         <f t="shared" si="4"/>
         <v>112</v>
@@ -7356,7 +7354,7 @@
       </c>
       <c r="N113" s="53"/>
     </row>
-    <row r="114" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A114" s="41">
         <f t="shared" si="4"/>
         <v>113</v>
@@ -7393,7 +7391,7 @@
       </c>
       <c r="N114" s="53"/>
     </row>
-    <row r="115" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A115" s="41">
         <f t="shared" si="4"/>
         <v>114</v>
@@ -7430,7 +7428,7 @@
       </c>
       <c r="N115" s="53"/>
     </row>
-    <row r="116" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A116" s="41">
         <f t="shared" si="4"/>
         <v>115</v>
@@ -7467,7 +7465,7 @@
       </c>
       <c r="N116" s="53"/>
     </row>
-    <row r="117" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A117" s="41">
         <f t="shared" ref="A117:A148" si="5">IF($B117="","",ROW()-1)</f>
         <v>116</v>
@@ -7504,7 +7502,7 @@
       </c>
       <c r="N117" s="53"/>
     </row>
-    <row r="118" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A118" s="41">
         <f t="shared" si="5"/>
         <v>117</v>
@@ -7541,7 +7539,7 @@
       </c>
       <c r="N118" s="53"/>
     </row>
-    <row r="119" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A119" s="41">
         <f t="shared" si="5"/>
         <v>118</v>
@@ -7578,7 +7576,7 @@
       </c>
       <c r="N119" s="53"/>
     </row>
-    <row r="120" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A120" s="41">
         <f t="shared" si="5"/>
         <v>119</v>
@@ -7615,7 +7613,7 @@
       </c>
       <c r="N120" s="53"/>
     </row>
-    <row r="121" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A121" s="41">
         <f t="shared" si="5"/>
         <v>120</v>
@@ -7652,7 +7650,7 @@
       </c>
       <c r="N121" s="53"/>
     </row>
-    <row r="122" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A122" s="41">
         <f t="shared" si="5"/>
         <v>121</v>
@@ -7689,7 +7687,7 @@
       </c>
       <c r="N122" s="53"/>
     </row>
-    <row r="123" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A123" s="41">
         <f t="shared" si="5"/>
         <v>122</v>
@@ -7726,7 +7724,7 @@
       </c>
       <c r="N123" s="53"/>
     </row>
-    <row r="124" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A124" s="41">
         <f t="shared" si="5"/>
         <v>123</v>
@@ -7763,7 +7761,7 @@
       </c>
       <c r="N124" s="53"/>
     </row>
-    <row r="125" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A125" s="41">
         <f t="shared" si="5"/>
         <v>124</v>
@@ -7800,7 +7798,7 @@
       </c>
       <c r="N125" s="53"/>
     </row>
-    <row r="126" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A126" s="41">
         <f t="shared" si="5"/>
         <v>125</v>
@@ -7837,7 +7835,7 @@
       </c>
       <c r="N126" s="53"/>
     </row>
-    <row r="127" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A127" s="41">
         <f t="shared" si="5"/>
         <v>126</v>
@@ -7874,7 +7872,7 @@
       </c>
       <c r="N127" s="53"/>
     </row>
-    <row r="128" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A128" s="41">
         <f t="shared" si="5"/>
         <v>127</v>
@@ -7911,7 +7909,7 @@
       </c>
       <c r="N128" s="53"/>
     </row>
-    <row r="129" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A129" s="41">
         <f t="shared" si="5"/>
         <v>128</v>
@@ -7948,7 +7946,7 @@
       </c>
       <c r="N129" s="53"/>
     </row>
-    <row r="130" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A130" s="41">
         <f t="shared" si="5"/>
         <v>129</v>
@@ -7985,7 +7983,7 @@
       </c>
       <c r="N130" s="53"/>
     </row>
-    <row r="131" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A131" s="41">
         <f t="shared" si="5"/>
         <v>130</v>
@@ -8014,7 +8012,7 @@
       </c>
       <c r="N131" s="53"/>
     </row>
-    <row r="132" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A132" s="41">
         <f t="shared" si="5"/>
         <v>131</v>
@@ -8043,7 +8041,7 @@
       </c>
       <c r="N132" s="53"/>
     </row>
-    <row r="133" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A133" s="41">
         <f t="shared" si="5"/>
         <v>132</v>
@@ -8080,7 +8078,7 @@
       </c>
       <c r="N133" s="53"/>
     </row>
-    <row r="134" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A134" s="41">
         <f t="shared" si="5"/>
         <v>133</v>
@@ -8117,7 +8115,7 @@
       </c>
       <c r="N134" s="53"/>
     </row>
-    <row r="135" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A135" s="41">
         <f t="shared" si="5"/>
         <v>134</v>
@@ -8152,7 +8150,7 @@
       </c>
       <c r="N135" s="53"/>
     </row>
-    <row r="136" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A136" s="41">
         <f t="shared" si="5"/>
         <v>135</v>
@@ -8189,7 +8187,7 @@
       </c>
       <c r="N136" s="53"/>
     </row>
-    <row r="137" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A137" s="41">
         <f t="shared" si="5"/>
         <v>136</v>
@@ -8226,7 +8224,7 @@
       </c>
       <c r="N137" s="53"/>
     </row>
-    <row r="138" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A138" s="41">
         <f t="shared" si="5"/>
         <v>137</v>
@@ -8263,7 +8261,7 @@
       </c>
       <c r="N138" s="53"/>
     </row>
-    <row r="139" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A139" s="41">
         <f t="shared" si="5"/>
         <v>138</v>
@@ -8296,7 +8294,7 @@
       </c>
       <c r="N139" s="53"/>
     </row>
-    <row r="140" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A140" s="41">
         <f t="shared" si="5"/>
         <v>139</v>
@@ -8329,7 +8327,7 @@
       </c>
       <c r="N140" s="53"/>
     </row>
-    <row r="141" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A141" s="41">
         <f t="shared" si="5"/>
         <v>140</v>
@@ -8364,7 +8362,7 @@
       </c>
       <c r="N141" s="53"/>
     </row>
-    <row r="142" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A142" s="41">
         <f t="shared" si="5"/>
         <v>141</v>
@@ -8399,7 +8397,7 @@
       </c>
       <c r="N142" s="53"/>
     </row>
-    <row r="143" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A143" s="4">
         <f t="shared" si="5"/>
         <v>142</v>
@@ -8430,7 +8428,7 @@
       </c>
       <c r="N143" s="53"/>
     </row>
-    <row r="144" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A144" s="41">
         <f t="shared" si="5"/>
         <v>143</v>
@@ -8459,7 +8457,7 @@
       </c>
       <c r="N144" s="53"/>
     </row>
-    <row r="145" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A145" s="41">
         <f t="shared" si="5"/>
         <v>144</v>
@@ -8488,7 +8486,7 @@
       </c>
       <c r="N145" s="53"/>
     </row>
-    <row r="146" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A146" s="41">
         <f t="shared" si="5"/>
         <v>145</v>
@@ -8517,7 +8515,7 @@
       </c>
       <c r="N146" s="53"/>
     </row>
-    <row r="147" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A147" s="41">
         <f t="shared" si="5"/>
         <v>146</v>
@@ -8546,7 +8544,7 @@
       </c>
       <c r="N147" s="53"/>
     </row>
-    <row r="148" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A148" s="41">
         <f t="shared" si="5"/>
         <v>147</v>
@@ -8575,7 +8573,7 @@
       </c>
       <c r="N148" s="53"/>
     </row>
-    <row r="149" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A149" s="41">
         <f t="shared" ref="A149:A180" si="6">IF($B149="","",ROW()-1)</f>
         <v>148</v>
@@ -8604,7 +8602,7 @@
       </c>
       <c r="N149" s="53"/>
     </row>
-    <row r="150" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A150" s="41">
         <f t="shared" si="6"/>
         <v>149</v>
@@ -8633,7 +8631,7 @@
       </c>
       <c r="N150" s="53"/>
     </row>
-    <row r="151" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A151" s="41">
         <f t="shared" si="6"/>
         <v>150</v>
@@ -8662,7 +8660,7 @@
       </c>
       <c r="N151" s="53"/>
     </row>
-    <row r="152" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A152" s="41">
         <f t="shared" si="6"/>
         <v>151</v>
@@ -8691,7 +8689,7 @@
       </c>
       <c r="N152" s="53"/>
     </row>
-    <row r="153" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A153" s="41">
         <f t="shared" si="6"/>
         <v>152</v>
@@ -8720,7 +8718,7 @@
       </c>
       <c r="N153" s="53"/>
     </row>
-    <row r="154" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A154" s="41">
         <f t="shared" si="6"/>
         <v>153</v>
@@ -8749,7 +8747,7 @@
       </c>
       <c r="N154" s="53"/>
     </row>
-    <row r="155" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A155" s="41">
         <f t="shared" si="6"/>
         <v>154</v>
@@ -8778,7 +8776,7 @@
       </c>
       <c r="N155" s="53"/>
     </row>
-    <row r="156" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A156" s="41">
         <f t="shared" si="6"/>
         <v>155</v>
@@ -8807,7 +8805,7 @@
       </c>
       <c r="N156" s="53"/>
     </row>
-    <row r="157" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A157" s="41">
         <f t="shared" si="6"/>
         <v>156</v>
@@ -8834,7 +8832,7 @@
       </c>
       <c r="N157" s="53"/>
     </row>
-    <row r="158" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A158" s="41">
         <f t="shared" si="6"/>
         <v>157</v>
@@ -8863,7 +8861,7 @@
       </c>
       <c r="N158" s="53"/>
     </row>
-    <row r="159" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A159" s="41">
         <f t="shared" si="6"/>
         <v>158</v>
@@ -8896,7 +8894,7 @@
       </c>
       <c r="N159" s="53"/>
     </row>
-    <row r="160" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A160" s="41">
         <f t="shared" si="6"/>
         <v>159</v>
@@ -8929,7 +8927,7 @@
       </c>
       <c r="N160" s="53"/>
     </row>
-    <row r="161" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A161" s="41">
         <f t="shared" si="6"/>
         <v>160</v>
@@ -8962,7 +8960,7 @@
       </c>
       <c r="N161" s="53"/>
     </row>
-    <row r="162" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A162" s="41">
         <f t="shared" si="6"/>
         <v>161</v>
@@ -8995,7 +8993,7 @@
       </c>
       <c r="N162" s="53"/>
     </row>
-    <row r="163" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A163" s="41">
         <f t="shared" si="6"/>
         <v>162</v>
@@ -9028,7 +9026,7 @@
       </c>
       <c r="N163" s="53"/>
     </row>
-    <row r="164" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A164" s="41">
         <f t="shared" si="6"/>
         <v>163</v>
@@ -9061,7 +9059,7 @@
       </c>
       <c r="N164" s="53"/>
     </row>
-    <row r="165" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A165" s="41">
         <f t="shared" si="6"/>
         <v>164</v>
@@ -9094,7 +9092,7 @@
       </c>
       <c r="N165" s="53"/>
     </row>
-    <row r="166" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A166" s="41">
         <f t="shared" si="6"/>
         <v>165</v>
@@ -9129,7 +9127,7 @@
       </c>
       <c r="N166" s="53"/>
     </row>
-    <row r="167" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A167" s="41">
         <f t="shared" si="6"/>
         <v>166</v>
@@ -9158,7 +9156,7 @@
       </c>
       <c r="N167" s="53"/>
     </row>
-    <row r="168" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A168" s="41">
         <f t="shared" si="6"/>
         <v>167</v>
@@ -9187,7 +9185,7 @@
       </c>
       <c r="N168" s="53"/>
     </row>
-    <row r="169" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A169" s="41">
         <f t="shared" si="6"/>
         <v>168</v>
@@ -9216,7 +9214,7 @@
       </c>
       <c r="N169" s="53"/>
     </row>
-    <row r="170" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A170" s="41">
         <f t="shared" si="6"/>
         <v>169</v>
@@ -9247,7 +9245,7 @@
       </c>
       <c r="N170" s="53"/>
     </row>
-    <row r="171" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A171" s="41">
         <f t="shared" si="6"/>
         <v>170</v>
@@ -9276,7 +9274,7 @@
       </c>
       <c r="N171" s="53"/>
     </row>
-    <row r="172" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A172" s="41">
         <f t="shared" si="6"/>
         <v>171</v>
@@ -9305,7 +9303,7 @@
       </c>
       <c r="N172" s="53"/>
     </row>
-    <row r="173" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A173" s="41">
         <f t="shared" si="6"/>
         <v>172</v>
@@ -9334,7 +9332,7 @@
       </c>
       <c r="N173" s="53"/>
     </row>
-    <row r="174" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A174" s="41">
         <f t="shared" si="6"/>
         <v>173</v>
@@ -9365,7 +9363,7 @@
       </c>
       <c r="N174" s="53"/>
     </row>
-    <row r="175" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A175" s="41">
         <f t="shared" si="6"/>
         <v>174</v>
@@ -9394,7 +9392,7 @@
       </c>
       <c r="N175" s="53"/>
     </row>
-    <row r="176" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A176" s="41">
         <f t="shared" si="6"/>
         <v>175</v>
@@ -9423,7 +9421,7 @@
       </c>
       <c r="N176" s="53"/>
     </row>
-    <row r="177" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A177" s="41">
         <f t="shared" si="6"/>
         <v>176</v>
@@ -9452,7 +9450,7 @@
       </c>
       <c r="N177" s="53"/>
     </row>
-    <row r="178" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A178" s="41">
         <f t="shared" si="6"/>
         <v>177</v>
@@ -9481,7 +9479,7 @@
       </c>
       <c r="N178" s="53"/>
     </row>
-    <row r="179" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A179" s="41">
         <f t="shared" si="6"/>
         <v>178</v>
@@ -9508,7 +9506,7 @@
       </c>
       <c r="N179" s="53"/>
     </row>
-    <row r="180" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A180" s="41">
         <f t="shared" si="6"/>
         <v>179</v>
@@ -9535,7 +9533,7 @@
       </c>
       <c r="N180" s="54"/>
     </row>
-    <row r="181" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A181" s="41">
         <f t="shared" ref="A181:A212" si="7">IF($B181="","",ROW()-1)</f>
         <v>180</v>
@@ -9564,7 +9562,7 @@
       </c>
       <c r="N181" s="53"/>
     </row>
-    <row r="182" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A182" s="41">
         <f t="shared" si="7"/>
         <v>181</v>
@@ -9593,7 +9591,7 @@
       </c>
       <c r="N182" s="55"/>
     </row>
-    <row r="183" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A183" s="41">
         <f t="shared" si="7"/>
         <v>182</v>
@@ -9620,7 +9618,7 @@
       </c>
       <c r="N183" s="56"/>
     </row>
-    <row r="184" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A184" s="41">
         <f t="shared" si="7"/>
         <v>183</v>
@@ -9649,7 +9647,7 @@
       </c>
       <c r="N184" s="57"/>
     </row>
-    <row r="185" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A185" s="41">
         <f t="shared" si="7"/>
         <v>184</v>
@@ -9678,7 +9676,7 @@
       </c>
       <c r="N185" s="56"/>
     </row>
-    <row r="186" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A186" s="41">
         <f t="shared" si="7"/>
         <v>185</v>
@@ -9707,7 +9705,7 @@
       </c>
       <c r="N186" s="57"/>
     </row>
-    <row r="187" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A187" s="41">
         <f t="shared" si="7"/>
         <v>186</v>
@@ -9736,7 +9734,7 @@
       </c>
       <c r="N187" s="56"/>
     </row>
-    <row r="188" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A188" s="41">
         <f t="shared" si="7"/>
         <v>187</v>
@@ -9765,7 +9763,7 @@
       </c>
       <c r="N188" s="57"/>
     </row>
-    <row r="189" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A189" s="41">
         <f t="shared" si="7"/>
         <v>188</v>
@@ -9794,7 +9792,7 @@
       </c>
       <c r="N189" s="56"/>
     </row>
-    <row r="190" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A190" s="41">
         <f t="shared" si="7"/>
         <v>189</v>
@@ -9823,7 +9821,7 @@
       </c>
       <c r="N190" s="57"/>
     </row>
-    <row r="191" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A191" s="41">
         <f t="shared" si="7"/>
         <v>190</v>
@@ -9852,7 +9850,7 @@
       </c>
       <c r="N191" s="56"/>
     </row>
-    <row r="192" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A192" s="41">
         <f t="shared" si="7"/>
         <v>191</v>
@@ -9881,7 +9879,7 @@
       </c>
       <c r="N192" s="57"/>
     </row>
-    <row r="193" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A193" s="41">
         <f t="shared" si="7"/>
         <v>192</v>
@@ -9908,7 +9906,7 @@
       </c>
       <c r="N193" s="56"/>
     </row>
-    <row r="194" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A194" s="41">
         <f t="shared" si="7"/>
         <v>193</v>
@@ -9937,7 +9935,7 @@
       </c>
       <c r="N194" s="57"/>
     </row>
-    <row r="195" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A195" s="41">
         <f t="shared" si="7"/>
         <v>194</v>
@@ -9966,7 +9964,7 @@
       </c>
       <c r="N195" s="56"/>
     </row>
-    <row r="196" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A196" s="41">
         <f t="shared" si="7"/>
         <v>195</v>
@@ -9999,7 +9997,7 @@
       </c>
       <c r="N196" s="57"/>
     </row>
-    <row r="197" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A197" s="41">
         <f t="shared" si="7"/>
         <v>196</v>
@@ -10032,7 +10030,7 @@
       </c>
       <c r="N197" s="56"/>
     </row>
-    <row r="198" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A198" s="41">
         <f t="shared" si="7"/>
         <v>197</v>
@@ -10065,7 +10063,7 @@
       </c>
       <c r="N198" s="57"/>
     </row>
-    <row r="199" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A199" s="41">
         <f t="shared" si="7"/>
         <v>198</v>
@@ -10098,7 +10096,7 @@
       </c>
       <c r="N199" s="56"/>
     </row>
-    <row r="200" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A200" s="41">
         <f t="shared" si="7"/>
         <v>199</v>
@@ -10131,7 +10129,7 @@
       </c>
       <c r="N200" s="57"/>
     </row>
-    <row r="201" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A201" s="41">
         <f t="shared" si="7"/>
         <v>200</v>
@@ -10166,7 +10164,7 @@
       </c>
       <c r="N201" s="56"/>
     </row>
-    <row r="202" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A202" s="41">
         <f t="shared" si="7"/>
         <v>201</v>
@@ -10199,7 +10197,7 @@
       </c>
       <c r="N202" s="57"/>
     </row>
-    <row r="203" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A203" s="41">
         <f t="shared" si="7"/>
         <v>202</v>
@@ -10228,7 +10226,7 @@
       </c>
       <c r="N203" s="56"/>
     </row>
-    <row r="204" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A204" s="41">
         <f t="shared" si="7"/>
         <v>203</v>
@@ -10257,7 +10255,7 @@
       </c>
       <c r="N204" s="57"/>
     </row>
-    <row r="205" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A205" s="41">
         <f t="shared" si="7"/>
         <v>204</v>
@@ -10286,7 +10284,7 @@
       </c>
       <c r="N205" s="56"/>
     </row>
-    <row r="206" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A206" s="41">
         <f t="shared" si="7"/>
         <v>205</v>
@@ -10315,7 +10313,7 @@
       </c>
       <c r="N206" s="57"/>
     </row>
-    <row r="207" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A207" s="41">
         <f t="shared" si="7"/>
         <v>206</v>
@@ -10344,7 +10342,7 @@
       </c>
       <c r="N207" s="56"/>
     </row>
-    <row r="208" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A208" s="41">
         <f t="shared" si="7"/>
         <v>207</v>
@@ -10373,7 +10371,7 @@
       </c>
       <c r="N208" s="57"/>
     </row>
-    <row r="209" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A209" s="41">
         <f t="shared" si="7"/>
         <v>208</v>
@@ -10402,7 +10400,7 @@
       </c>
       <c r="N209" s="56"/>
     </row>
-    <row r="210" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A210" s="41">
         <f t="shared" si="7"/>
         <v>209</v>
@@ -10433,7 +10431,7 @@
       </c>
       <c r="N210" s="57"/>
     </row>
-    <row r="211" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A211" s="41">
         <f t="shared" si="7"/>
         <v>210</v>
@@ -10460,7 +10458,7 @@
       </c>
       <c r="N211" s="56"/>
     </row>
-    <row r="212" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A212" s="41">
         <f t="shared" si="7"/>
         <v>211</v>
@@ -10487,7 +10485,7 @@
       </c>
       <c r="N212" s="57"/>
     </row>
-    <row r="213" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A213" s="41">
         <f t="shared" ref="A213:A248" si="8">IF($B213="","",ROW()-1)</f>
         <v>212</v>
@@ -10516,7 +10514,7 @@
       </c>
       <c r="N213" s="56"/>
     </row>
-    <row r="214" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A214" s="41">
         <f t="shared" si="8"/>
         <v>213</v>
@@ -10545,7 +10543,7 @@
       </c>
       <c r="N214" s="57"/>
     </row>
-    <row r="215" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A215" s="41">
         <f t="shared" si="8"/>
         <v>214</v>
@@ -10574,7 +10572,7 @@
       </c>
       <c r="N215" s="56"/>
     </row>
-    <row r="216" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A216" s="41">
         <f t="shared" si="8"/>
         <v>215</v>
@@ -10603,7 +10601,7 @@
       </c>
       <c r="N216" s="57"/>
     </row>
-    <row r="217" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A217" s="41">
         <f t="shared" si="8"/>
         <v>216</v>
@@ -10632,7 +10630,7 @@
       </c>
       <c r="N217" s="56"/>
     </row>
-    <row r="218" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A218" s="41">
         <f t="shared" si="8"/>
         <v>217</v>
@@ -10661,7 +10659,7 @@
       </c>
       <c r="N218" s="57"/>
     </row>
-    <row r="219" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A219" s="41">
         <f t="shared" si="8"/>
         <v>218</v>
@@ -10690,7 +10688,7 @@
       </c>
       <c r="N219" s="56"/>
     </row>
-    <row r="220" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A220" s="41">
         <f t="shared" si="8"/>
         <v>219</v>
@@ -10719,7 +10717,7 @@
       </c>
       <c r="N220" s="57"/>
     </row>
-    <row r="221" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A221" s="41">
         <f t="shared" si="8"/>
         <v>220</v>
@@ -10748,7 +10746,7 @@
       </c>
       <c r="N221" s="56"/>
     </row>
-    <row r="222" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A222" s="41">
         <f t="shared" si="8"/>
         <v>221</v>
@@ -10777,7 +10775,7 @@
       </c>
       <c r="N222" s="57"/>
     </row>
-    <row r="223" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A223" s="41">
         <f t="shared" si="8"/>
         <v>222</v>
@@ -10806,7 +10804,7 @@
       </c>
       <c r="N223" s="56"/>
     </row>
-    <row r="224" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A224" s="41">
         <f t="shared" si="8"/>
         <v>223</v>
@@ -10835,7 +10833,7 @@
       </c>
       <c r="N224" s="57"/>
     </row>
-    <row r="225" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A225" s="41">
         <f t="shared" si="8"/>
         <v>224</v>
@@ -10864,7 +10862,7 @@
       </c>
       <c r="N225" s="56"/>
     </row>
-    <row r="226" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A226" s="41">
         <f t="shared" si="8"/>
         <v>225</v>
@@ -10893,7 +10891,7 @@
       </c>
       <c r="N226" s="57"/>
     </row>
-    <row r="227" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A227" s="41">
         <f t="shared" si="8"/>
         <v>226</v>
@@ -10922,7 +10920,7 @@
       </c>
       <c r="N227" s="56"/>
     </row>
-    <row r="228" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A228" s="41">
         <f t="shared" si="8"/>
         <v>227</v>
@@ -10949,7 +10947,7 @@
       </c>
       <c r="N228" s="57"/>
     </row>
-    <row r="229" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A229" s="41">
         <f t="shared" si="8"/>
         <v>228</v>
@@ -10978,7 +10976,7 @@
       </c>
       <c r="N229" s="56"/>
     </row>
-    <row r="230" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A230" s="41">
         <f t="shared" si="8"/>
         <v>229</v>
@@ -11007,7 +11005,7 @@
       </c>
       <c r="N230" s="57"/>
     </row>
-    <row r="231" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A231" s="41">
         <f t="shared" si="8"/>
         <v>230</v>
@@ -11036,7 +11034,7 @@
       </c>
       <c r="N231" s="56"/>
     </row>
-    <row r="232" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A232" s="41">
         <f t="shared" si="8"/>
         <v>231</v>
@@ -11065,7 +11063,7 @@
       </c>
       <c r="N232" s="57"/>
     </row>
-    <row r="233" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
       <c r="A233" s="41">
         <f t="shared" si="8"/>
         <v>232</v>
@@ -11094,7 +11092,7 @@
       </c>
       <c r="N233" s="58"/>
     </row>
-    <row r="234" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:14" ht="15" thickBot="1">
       <c r="A234" s="41">
         <f t="shared" si="8"/>
         <v>233</v>
@@ -11125,7 +11123,7 @@
       </c>
       <c r="N234" s="59"/>
     </row>
-    <row r="235" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:14" ht="15" thickBot="1">
       <c r="A235" s="41">
         <f t="shared" si="8"/>
         <v>234</v>
@@ -11154,7 +11152,7 @@
       </c>
       <c r="N235" s="60"/>
     </row>
-    <row r="236" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:14" ht="15" thickBot="1">
       <c r="A236" s="41">
         <f t="shared" si="8"/>
         <v>235</v>
@@ -11183,7 +11181,7 @@
       </c>
       <c r="N236" s="61"/>
     </row>
-    <row r="237" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:14" ht="29.45" thickBot="1">
       <c r="A237" s="41">
         <f t="shared" si="8"/>
         <v>236</v>
@@ -11214,7 +11212,7 @@
       </c>
       <c r="N237" s="60"/>
     </row>
-    <row r="238" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:14" ht="15" thickBot="1">
       <c r="A238" s="41">
         <f t="shared" si="8"/>
         <v>237</v>
@@ -11243,7 +11241,7 @@
       </c>
       <c r="N238" s="61"/>
     </row>
-    <row r="239" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:14" ht="15" thickBot="1">
       <c r="A239" s="41">
         <f t="shared" si="8"/>
         <v>238</v>
@@ -11272,7 +11270,7 @@
       </c>
       <c r="N239" s="60"/>
     </row>
-    <row r="240" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:14" ht="29.45" thickBot="1">
       <c r="A240" s="41">
         <f t="shared" si="8"/>
         <v>239</v>
@@ -11301,7 +11299,7 @@
       </c>
       <c r="N240" s="61"/>
     </row>
-    <row r="241" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:14" ht="15" thickBot="1">
       <c r="A241" s="41">
         <f t="shared" si="8"/>
         <v>240</v>
@@ -11332,7 +11330,7 @@
       </c>
       <c r="N241" s="60"/>
     </row>
-    <row r="242" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:14" ht="15" thickBot="1">
       <c r="A242" s="41">
         <f t="shared" si="8"/>
         <v>241</v>
@@ -11361,7 +11359,7 @@
       </c>
       <c r="N242" s="61"/>
     </row>
-    <row r="243" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:14" ht="15" thickBot="1">
       <c r="A243" s="41">
         <f t="shared" si="8"/>
         <v>242</v>
@@ -11390,7 +11388,7 @@
       </c>
       <c r="N243" s="60"/>
     </row>
-    <row r="244" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:14" ht="15" thickBot="1">
       <c r="A244" s="41">
         <f t="shared" si="8"/>
         <v>243</v>
@@ -11423,7 +11421,7 @@
       </c>
       <c r="N244" s="61"/>
     </row>
-    <row r="245" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:14" ht="15" thickBot="1">
       <c r="A245" s="41">
         <f t="shared" si="8"/>
         <v>244</v>
@@ -11456,8 +11454,8 @@
       </c>
       <c r="N245" s="60"/>
     </row>
-    <row r="246" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="162">
+    <row r="246" spans="1:14" ht="29.45" thickBot="1">
+      <c r="A246" s="150">
         <f t="shared" si="8"/>
         <v>245</v>
       </c>
@@ -11489,74 +11487,74 @@
       </c>
       <c r="N246" s="61"/>
     </row>
-    <row r="247" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="165">
+    <row r="247" spans="1:14" ht="29.45" thickBot="1">
+      <c r="A247" s="151">
         <f t="shared" si="8"/>
         <v>246</v>
       </c>
-      <c r="B247" s="163" t="s">
+      <c r="B247" s="53" t="s">
         <v>496</v>
       </c>
-      <c r="C247" s="154" t="s">
+      <c r="C247" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="D247" s="154" t="s">
+      <c r="D247" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E247" s="157" t="s">
+      <c r="E247" s="149" t="s">
         <v>337</v>
       </c>
-      <c r="F247" s="136" t="s">
+      <c r="F247" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="G247" s="137"/>
-      <c r="H247" s="137"/>
-      <c r="I247" s="155"/>
-      <c r="J247" s="155"/>
-      <c r="K247" s="154" t="s">
+      <c r="G247" s="11"/>
+      <c r="H247" s="11"/>
+      <c r="I247" s="13"/>
+      <c r="J247" s="13"/>
+      <c r="K247" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="L247" s="154"/>
-      <c r="M247" s="156" t="s">
-        <v>64</v>
-      </c>
-      <c r="N247" s="158"/>
-    </row>
-    <row r="248" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="165">
+      <c r="L247" s="9"/>
+      <c r="M247" s="148" t="s">
+        <v>64</v>
+      </c>
+      <c r="N247" s="155"/>
+    </row>
+    <row r="248" spans="1:14" ht="29.45" thickBot="1">
+      <c r="A248" s="151">
         <f>IF($B248="","",ROW()-1)</f>
         <v>247</v>
       </c>
-      <c r="B248" s="163" t="s">
+      <c r="B248" s="53" t="s">
         <v>499</v>
       </c>
-      <c r="C248" s="154" t="s">
+      <c r="C248" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="D248" s="154" t="s">
+      <c r="D248" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E248" s="157" t="s">
+      <c r="E248" s="149" t="s">
         <v>82</v>
       </c>
-      <c r="F248" s="136" t="s">
+      <c r="F248" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="G248" s="137"/>
-      <c r="H248" s="137"/>
-      <c r="I248" s="155"/>
-      <c r="J248" s="155"/>
-      <c r="K248" s="154" t="s">
+      <c r="G248" s="11"/>
+      <c r="H248" s="11"/>
+      <c r="I248" s="13"/>
+      <c r="J248" s="13"/>
+      <c r="K248" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="L248" s="154"/>
-      <c r="M248" s="156" t="s">
-        <v>64</v>
-      </c>
-      <c r="N248" s="158"/>
-    </row>
-    <row r="249" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="162">
+      <c r="L248" s="9"/>
+      <c r="M248" s="148" t="s">
+        <v>64</v>
+      </c>
+      <c r="N248" s="155"/>
+    </row>
+    <row r="249" spans="1:14" ht="15" thickBot="1">
+      <c r="A249" s="150">
         <f t="shared" ref="A249:A273" si="9">IF($B249="","",ROW()-1)</f>
         <v>248</v>
       </c>
@@ -11579,71 +11577,71 @@
       <c r="H249" s="108">
         <v>6</v>
       </c>
-      <c r="I249" s="143">
+      <c r="I249" s="138">
         <v>46205</v>
       </c>
-      <c r="J249" s="143">
+      <c r="J249" s="138">
         <v>46213</v>
       </c>
       <c r="K249" s="106"/>
       <c r="L249" s="106"/>
       <c r="M249" s="112"/>
     </row>
-    <row r="250" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A250" s="165">
+    <row r="250" spans="1:14" ht="43.9" thickBot="1">
+      <c r="A250" s="151">
         <f t="shared" si="9"/>
         <v>249</v>
       </c>
-      <c r="B250" s="164" t="s">
+      <c r="B250" s="156" t="s">
         <v>503</v>
       </c>
-      <c r="C250" s="159" t="s">
+      <c r="C250" s="157" t="s">
         <v>504</v>
       </c>
-      <c r="D250" s="159" t="s">
+      <c r="D250" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="E250" s="160"/>
-      <c r="F250" s="137" t="s">
+      <c r="E250" s="158"/>
+      <c r="F250" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G250" s="160"/>
-      <c r="H250" s="160"/>
-      <c r="I250" s="161"/>
-      <c r="J250" s="161"/>
-      <c r="K250" s="159"/>
-      <c r="L250" s="159"/>
-      <c r="M250" s="160"/>
-      <c r="N250" s="158"/>
-    </row>
-    <row r="251" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="165">
+      <c r="G250" s="158"/>
+      <c r="H250" s="158"/>
+      <c r="I250" s="159"/>
+      <c r="J250" s="159"/>
+      <c r="K250" s="157"/>
+      <c r="L250" s="157"/>
+      <c r="M250" s="158"/>
+      <c r="N250" s="155"/>
+    </row>
+    <row r="251" spans="1:14" ht="29.45" thickBot="1">
+      <c r="A251" s="151">
         <f t="shared" si="9"/>
         <v>250</v>
       </c>
-      <c r="B251" s="164" t="s">
+      <c r="B251" s="156" t="s">
         <v>505</v>
       </c>
-      <c r="C251" s="159" t="s">
+      <c r="C251" s="157" t="s">
         <v>506</v>
       </c>
-      <c r="D251" s="159" t="s">
+      <c r="D251" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="E251" s="160"/>
-      <c r="F251" s="137" t="s">
+      <c r="E251" s="158"/>
+      <c r="F251" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G251" s="160"/>
-      <c r="H251" s="160"/>
-      <c r="I251" s="161"/>
-      <c r="J251" s="161"/>
-      <c r="K251" s="159"/>
-      <c r="L251" s="159"/>
-      <c r="M251" s="160"/>
-      <c r="N251" s="158"/>
-    </row>
-    <row r="252" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G251" s="158"/>
+      <c r="H251" s="158"/>
+      <c r="I251" s="159"/>
+      <c r="J251" s="159"/>
+      <c r="K251" s="157"/>
+      <c r="L251" s="157"/>
+      <c r="M251" s="158"/>
+      <c r="N251" s="155"/>
+    </row>
+    <row r="252" spans="1:14" ht="29.45" thickBot="1">
       <c r="A252" s="41">
         <f t="shared" si="9"/>
         <v>251</v>
@@ -11657,11 +11655,11 @@
       <c r="F252" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="I252" s="144"/>
-      <c r="J252" s="144"/>
-    </row>
-    <row r="253" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A253" s="162">
+      <c r="I252" s="42"/>
+      <c r="J252" s="42"/>
+    </row>
+    <row r="253" spans="1:14" ht="29.45" thickBot="1">
+      <c r="A253" s="150">
         <f t="shared" si="9"/>
         <v>252</v>
       </c>
@@ -11683,141 +11681,141 @@
       <c r="H253" s="113">
         <v>4</v>
       </c>
-      <c r="I253" s="144">
+      <c r="I253" s="42">
         <v>46211</v>
       </c>
-      <c r="J253" s="144">
+      <c r="J253" s="42">
         <v>46212</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A254" s="165">
+    <row r="254" spans="1:14" ht="43.9" thickBot="1">
+      <c r="A254" s="151">
         <f t="shared" si="9"/>
         <v>253</v>
       </c>
-      <c r="B254" s="164" t="s">
+      <c r="B254" s="156" t="s">
         <v>511</v>
       </c>
-      <c r="C254" s="159"/>
-      <c r="D254" s="159" t="s">
+      <c r="C254" s="157"/>
+      <c r="D254" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="E254" s="160"/>
-      <c r="F254" s="137" t="s">
+      <c r="E254" s="158"/>
+      <c r="F254" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G254" s="160"/>
-      <c r="H254" s="160"/>
-      <c r="I254" s="161"/>
-      <c r="J254" s="161"/>
-      <c r="K254" s="159"/>
-      <c r="L254" s="159"/>
-      <c r="M254" s="160"/>
-      <c r="N254" s="158"/>
-    </row>
-    <row r="255" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="165">
+      <c r="G254" s="158"/>
+      <c r="H254" s="158"/>
+      <c r="I254" s="159"/>
+      <c r="J254" s="159"/>
+      <c r="K254" s="157"/>
+      <c r="L254" s="157"/>
+      <c r="M254" s="158"/>
+      <c r="N254" s="155"/>
+    </row>
+    <row r="255" spans="1:14" ht="29.45" thickBot="1">
+      <c r="A255" s="151">
         <f t="shared" si="9"/>
         <v>254</v>
       </c>
-      <c r="B255" s="164" t="s">
+      <c r="B255" s="156" t="s">
         <v>512</v>
       </c>
-      <c r="C255" s="159"/>
-      <c r="D255" s="159" t="s">
+      <c r="C255" s="157"/>
+      <c r="D255" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="E255" s="160"/>
-      <c r="F255" s="137" t="s">
+      <c r="E255" s="158"/>
+      <c r="F255" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G255" s="160"/>
-      <c r="H255" s="160"/>
-      <c r="I255" s="161"/>
-      <c r="J255" s="161"/>
-      <c r="K255" s="159"/>
-      <c r="L255" s="159"/>
-      <c r="M255" s="160"/>
-      <c r="N255" s="158"/>
-    </row>
-    <row r="256" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="165">
+      <c r="G255" s="158"/>
+      <c r="H255" s="158"/>
+      <c r="I255" s="159"/>
+      <c r="J255" s="159"/>
+      <c r="K255" s="157"/>
+      <c r="L255" s="157"/>
+      <c r="M255" s="158"/>
+      <c r="N255" s="155"/>
+    </row>
+    <row r="256" spans="1:14" ht="29.45" thickBot="1">
+      <c r="A256" s="151">
         <f t="shared" si="9"/>
         <v>255</v>
       </c>
-      <c r="B256" s="164" t="s">
+      <c r="B256" s="156" t="s">
         <v>513</v>
       </c>
-      <c r="C256" s="159" t="s">
+      <c r="C256" s="157" t="s">
         <v>514</v>
       </c>
-      <c r="D256" s="159" t="s">
+      <c r="D256" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="E256" s="160"/>
-      <c r="F256" s="137" t="s">
+      <c r="E256" s="158"/>
+      <c r="F256" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G256" s="160"/>
-      <c r="H256" s="160"/>
-      <c r="I256" s="161"/>
-      <c r="J256" s="161"/>
-      <c r="K256" s="159"/>
-      <c r="L256" s="159"/>
-      <c r="M256" s="160"/>
-      <c r="N256" s="158"/>
-    </row>
-    <row r="257" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A257" s="165">
+      <c r="G256" s="158"/>
+      <c r="H256" s="158"/>
+      <c r="I256" s="159"/>
+      <c r="J256" s="159"/>
+      <c r="K256" s="157"/>
+      <c r="L256" s="157"/>
+      <c r="M256" s="158"/>
+      <c r="N256" s="155"/>
+    </row>
+    <row r="257" spans="1:14" ht="15" thickBot="1">
+      <c r="A257" s="151">
         <f t="shared" si="9"/>
         <v>256</v>
       </c>
-      <c r="B257" s="164" t="s">
+      <c r="B257" s="156" t="s">
         <v>515</v>
       </c>
-      <c r="C257" s="159"/>
-      <c r="D257" s="159" t="s">
+      <c r="C257" s="157"/>
+      <c r="D257" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="E257" s="160"/>
-      <c r="F257" s="137" t="s">
+      <c r="E257" s="158"/>
+      <c r="F257" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G257" s="160"/>
-      <c r="H257" s="160"/>
-      <c r="I257" s="161"/>
-      <c r="J257" s="161"/>
-      <c r="K257" s="159"/>
-      <c r="L257" s="159"/>
-      <c r="M257" s="160"/>
-      <c r="N257" s="158"/>
-    </row>
-    <row r="258" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A258" s="165">
+      <c r="G257" s="158"/>
+      <c r="H257" s="158"/>
+      <c r="I257" s="159"/>
+      <c r="J257" s="159"/>
+      <c r="K257" s="157"/>
+      <c r="L257" s="157"/>
+      <c r="M257" s="158"/>
+      <c r="N257" s="155"/>
+    </row>
+    <row r="258" spans="1:14" ht="29.45" thickBot="1">
+      <c r="A258" s="151">
         <f t="shared" si="9"/>
         <v>257</v>
       </c>
-      <c r="B258" s="138" t="s">
+      <c r="B258" s="134" t="s">
         <v>516</v>
       </c>
-      <c r="C258" s="139"/>
-      <c r="D258" s="139" t="s">
+      <c r="C258" s="135"/>
+      <c r="D258" s="135" t="s">
         <v>71</v>
       </c>
-      <c r="E258" s="141"/>
-      <c r="F258" s="142" t="s">
+      <c r="E258" s="12"/>
+      <c r="F258" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="G258" s="141"/>
-      <c r="H258" s="141"/>
-      <c r="I258" s="145"/>
-      <c r="J258" s="145"/>
-      <c r="K258" s="139"/>
-      <c r="L258" s="139"/>
-      <c r="M258" s="141"/>
-      <c r="N258" s="140"/>
-    </row>
-    <row r="259" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G258" s="12"/>
+      <c r="H258" s="12"/>
+      <c r="I258" s="139"/>
+      <c r="J258" s="139"/>
+      <c r="K258" s="135"/>
+      <c r="L258" s="135"/>
+      <c r="M258" s="12"/>
+      <c r="N258" s="136"/>
+    </row>
+    <row r="259" spans="1:14" ht="29.45" thickBot="1">
       <c r="A259" s="41">
         <f t="shared" si="9"/>
         <v>258</v>
@@ -11828,15 +11826,17 @@
       <c r="C259" s="122" t="s">
         <v>518</v>
       </c>
-      <c r="D259" s="123"/>
+      <c r="D259" s="123" t="s">
+        <v>71</v>
+      </c>
       <c r="E259" s="119"/>
       <c r="F259" s="129" t="s">
         <v>73</v>
       </c>
       <c r="G259" s="119"/>
       <c r="H259" s="119"/>
-      <c r="I259" s="146"/>
-      <c r="J259" s="146"/>
+      <c r="I259" s="140"/>
+      <c r="J259" s="140"/>
       <c r="K259" s="123" t="s">
         <v>519</v>
       </c>
@@ -11844,7 +11844,7 @@
       <c r="M259" s="119"/>
       <c r="N259" s="123"/>
     </row>
-    <row r="260" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:14" ht="15" thickBot="1">
       <c r="A260" s="41">
         <f t="shared" si="9"/>
         <v>259</v>
@@ -11855,15 +11855,17 @@
       <c r="C260" s="120" t="s">
         <v>521</v>
       </c>
-      <c r="D260" s="121"/>
+      <c r="D260" s="121" t="s">
+        <v>71</v>
+      </c>
       <c r="E260" s="124"/>
       <c r="F260" s="129" t="s">
         <v>73</v>
       </c>
       <c r="G260" s="124"/>
       <c r="H260" s="124"/>
-      <c r="I260" s="147"/>
-      <c r="J260" s="147"/>
+      <c r="I260" s="141"/>
+      <c r="J260" s="141"/>
       <c r="K260" s="121" t="s">
         <v>519</v>
       </c>
@@ -11871,7 +11873,7 @@
       <c r="M260" s="124"/>
       <c r="N260" s="121"/>
     </row>
-    <row r="261" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:14" ht="43.9" thickBot="1">
       <c r="A261" s="41">
         <f t="shared" si="9"/>
         <v>260</v>
@@ -11889,8 +11891,8 @@
       </c>
       <c r="G261" s="119"/>
       <c r="H261" s="119"/>
-      <c r="I261" s="146"/>
-      <c r="J261" s="146"/>
+      <c r="I261" s="140"/>
+      <c r="J261" s="140"/>
       <c r="K261" s="123" t="s">
         <v>519</v>
       </c>
@@ -11898,7 +11900,7 @@
       <c r="M261" s="119"/>
       <c r="N261" s="123"/>
     </row>
-    <row r="262" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:14" ht="29.45" thickBot="1">
       <c r="A262" s="41">
         <f t="shared" si="9"/>
         <v>261</v>
@@ -11909,15 +11911,17 @@
       <c r="C262" s="120" t="s">
         <v>525</v>
       </c>
-      <c r="D262" s="121"/>
+      <c r="D262" s="121" t="s">
+        <v>71</v>
+      </c>
       <c r="E262" s="124"/>
       <c r="F262" s="129" t="s">
         <v>73</v>
       </c>
       <c r="G262" s="124"/>
       <c r="H262" s="124"/>
-      <c r="I262" s="147"/>
-      <c r="J262" s="147"/>
+      <c r="I262" s="141"/>
+      <c r="J262" s="141"/>
       <c r="K262" s="121" t="s">
         <v>519</v>
       </c>
@@ -11925,7 +11929,7 @@
       <c r="M262" s="124"/>
       <c r="N262" s="121"/>
     </row>
-    <row r="263" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:14" ht="15" thickBot="1">
       <c r="A263" s="41">
         <f t="shared" si="9"/>
         <v>262</v>
@@ -11943,8 +11947,8 @@
       </c>
       <c r="G263" s="119"/>
       <c r="H263" s="119"/>
-      <c r="I263" s="146"/>
-      <c r="J263" s="146"/>
+      <c r="I263" s="140"/>
+      <c r="J263" s="140"/>
       <c r="K263" s="123" t="s">
         <v>519</v>
       </c>
@@ -11952,7 +11956,7 @@
       <c r="M263" s="119"/>
       <c r="N263" s="123"/>
     </row>
-    <row r="264" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:14" ht="58.15" thickBot="1">
       <c r="A264" s="41">
         <f t="shared" si="9"/>
         <v>263</v>
@@ -11970,8 +11974,8 @@
       </c>
       <c r="G264" s="124"/>
       <c r="H264" s="124"/>
-      <c r="I264" s="147"/>
-      <c r="J264" s="147"/>
+      <c r="I264" s="141"/>
+      <c r="J264" s="141"/>
       <c r="K264" s="121" t="s">
         <v>519</v>
       </c>
@@ -11979,7 +11983,7 @@
       <c r="M264" s="124"/>
       <c r="N264" s="121"/>
     </row>
-    <row r="265" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:14" ht="43.9" thickBot="1">
       <c r="A265" s="41">
         <f t="shared" si="9"/>
         <v>264</v>
@@ -11990,15 +11994,19 @@
       <c r="C265" s="122" t="s">
         <v>531</v>
       </c>
-      <c r="D265" s="123"/>
-      <c r="E265" s="119"/>
+      <c r="D265" s="123" t="s">
+        <v>71</v>
+      </c>
+      <c r="E265" s="119" t="s">
+        <v>62</v>
+      </c>
       <c r="F265" s="131" t="s">
         <v>68</v>
       </c>
       <c r="G265" s="119"/>
       <c r="H265" s="119"/>
-      <c r="I265" s="146"/>
-      <c r="J265" s="146"/>
+      <c r="I265" s="140"/>
+      <c r="J265" s="140"/>
       <c r="K265" s="123" t="s">
         <v>519</v>
       </c>
@@ -12006,7 +12014,7 @@
       <c r="M265" s="119"/>
       <c r="N265" s="123"/>
     </row>
-    <row r="266" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:14" ht="15" thickBot="1">
       <c r="A266" s="41">
         <f t="shared" si="9"/>
         <v>265</v>
@@ -12017,15 +12025,17 @@
       <c r="C266" s="121" t="s">
         <v>533</v>
       </c>
-      <c r="D266" s="121"/>
+      <c r="D266" s="121" t="s">
+        <v>71</v>
+      </c>
       <c r="E266" s="124"/>
       <c r="F266" s="129" t="s">
         <v>73</v>
       </c>
       <c r="G266" s="124"/>
       <c r="H266" s="124"/>
-      <c r="I266" s="147"/>
-      <c r="J266" s="147"/>
+      <c r="I266" s="141"/>
+      <c r="J266" s="141"/>
       <c r="K266" s="121" t="s">
         <v>519</v>
       </c>
@@ -12033,7 +12043,7 @@
       <c r="M266" s="124"/>
       <c r="N266" s="121"/>
     </row>
-    <row r="267" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:14" ht="29.45" thickBot="1">
       <c r="A267" s="41">
         <f t="shared" si="9"/>
         <v>266</v>
@@ -12051,8 +12061,8 @@
       </c>
       <c r="G267" s="119"/>
       <c r="H267" s="119"/>
-      <c r="I267" s="146"/>
-      <c r="J267" s="146"/>
+      <c r="I267" s="140"/>
+      <c r="J267" s="140"/>
       <c r="K267" s="123" t="s">
         <v>519</v>
       </c>
@@ -12060,7 +12070,7 @@
       <c r="M267" s="119"/>
       <c r="N267" s="123"/>
     </row>
-    <row r="268" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:14" ht="43.9" thickBot="1">
       <c r="A268" s="41">
         <f t="shared" si="9"/>
         <v>267</v>
@@ -12078,8 +12088,8 @@
       </c>
       <c r="G268" s="124"/>
       <c r="H268" s="124"/>
-      <c r="I268" s="147"/>
-      <c r="J268" s="147"/>
+      <c r="I268" s="141"/>
+      <c r="J268" s="141"/>
       <c r="K268" s="121" t="s">
         <v>519</v>
       </c>
@@ -12087,7 +12097,7 @@
       <c r="M268" s="124"/>
       <c r="N268" s="121"/>
     </row>
-    <row r="269" spans="1:14" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:14" ht="72.599999999999994" thickBot="1">
       <c r="A269" s="41">
         <f t="shared" si="9"/>
         <v>268</v>
@@ -12105,8 +12115,8 @@
       </c>
       <c r="G269" s="119"/>
       <c r="H269" s="119"/>
-      <c r="I269" s="146"/>
-      <c r="J269" s="146"/>
+      <c r="I269" s="140"/>
+      <c r="J269" s="140"/>
       <c r="K269" s="123" t="s">
         <v>519</v>
       </c>
@@ -12114,7 +12124,7 @@
       <c r="M269" s="119"/>
       <c r="N269" s="123"/>
     </row>
-    <row r="270" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:14" ht="58.15" thickBot="1">
       <c r="A270" s="41">
         <f t="shared" si="9"/>
         <v>269</v>
@@ -12132,8 +12142,8 @@
       </c>
       <c r="G270" s="124"/>
       <c r="H270" s="124"/>
-      <c r="I270" s="147"/>
-      <c r="J270" s="147"/>
+      <c r="I270" s="141"/>
+      <c r="J270" s="141"/>
       <c r="K270" s="121" t="s">
         <v>519</v>
       </c>
@@ -12141,7 +12151,7 @@
       <c r="M270" s="124"/>
       <c r="N270" s="121"/>
     </row>
-    <row r="271" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:14" ht="29.45" thickBot="1">
       <c r="A271" s="41">
         <f t="shared" si="9"/>
         <v>270</v>
@@ -12159,8 +12169,8 @@
       </c>
       <c r="G271" s="119"/>
       <c r="H271" s="119"/>
-      <c r="I271" s="146"/>
-      <c r="J271" s="146"/>
+      <c r="I271" s="140"/>
+      <c r="J271" s="140"/>
       <c r="K271" s="123" t="s">
         <v>519</v>
       </c>
@@ -12168,2961 +12178,2961 @@
       <c r="M271" s="119"/>
       <c r="N271" s="123"/>
     </row>
-    <row r="272" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="162">
+    <row r="272" spans="1:14" ht="29.45" thickBot="1">
+      <c r="A272" s="150">
         <f t="shared" si="9"/>
         <v>271</v>
       </c>
-      <c r="B272" s="148" t="s">
+      <c r="B272" s="142" t="s">
         <v>544</v>
       </c>
-      <c r="C272" s="149" t="s">
+      <c r="C272" s="143" t="s">
         <v>545</v>
       </c>
-      <c r="D272" s="150"/>
-      <c r="E272" s="151"/>
-      <c r="F272" s="152" t="s">
+      <c r="D272" s="144"/>
+      <c r="E272" s="145"/>
+      <c r="F272" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="G272" s="151"/>
-      <c r="H272" s="151"/>
-      <c r="I272" s="153"/>
-      <c r="J272" s="153"/>
-      <c r="K272" s="150" t="s">
+      <c r="G272" s="145"/>
+      <c r="H272" s="145"/>
+      <c r="I272" s="147"/>
+      <c r="J272" s="147"/>
+      <c r="K272" s="144" t="s">
         <v>519</v>
       </c>
-      <c r="L272" s="150"/>
-      <c r="M272" s="151"/>
-      <c r="N272" s="150"/>
-    </row>
-    <row r="273" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="165">
+      <c r="L272" s="144"/>
+      <c r="M272" s="145"/>
+      <c r="N272" s="144"/>
+    </row>
+    <row r="273" spans="1:14" ht="15" thickBot="1">
+      <c r="A273" s="151">
         <f t="shared" si="9"/>
         <v>272</v>
       </c>
-      <c r="B273" s="164" t="s">
-        <v>549</v>
-      </c>
-      <c r="C273" s="159" t="s">
-        <v>550</v>
-      </c>
-      <c r="D273" s="159" t="s">
+      <c r="B273" s="156" t="s">
+        <v>546</v>
+      </c>
+      <c r="C273" s="157" t="s">
+        <v>547</v>
+      </c>
+      <c r="D273" s="157" t="s">
         <v>79</v>
       </c>
-      <c r="E273" s="160" t="s">
+      <c r="E273" s="158" t="s">
         <v>337</v>
       </c>
-      <c r="F273" s="142" t="s">
+      <c r="F273" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="G273" s="160"/>
-      <c r="H273" s="160"/>
-      <c r="I273" s="161">
+      <c r="G273" s="158"/>
+      <c r="H273" s="158"/>
+      <c r="I273" s="159">
         <v>46226</v>
       </c>
-      <c r="J273" s="161">
+      <c r="J273" s="159">
         <v>46220</v>
       </c>
-      <c r="K273" s="159"/>
-      <c r="L273" s="159"/>
-      <c r="M273" s="160" t="s">
+      <c r="K273" s="157"/>
+      <c r="L273" s="157"/>
+      <c r="M273" s="158" t="s">
         <v>97</v>
       </c>
-      <c r="N273" s="158"/>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N273" s="155"/>
+    </row>
+    <row r="274" spans="1:14">
       <c r="I274" s="42"/>
       <c r="J274" s="42"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14">
       <c r="I275" s="42"/>
       <c r="J275" s="42"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14">
       <c r="I276" s="42"/>
       <c r="J276" s="42"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14">
       <c r="I277" s="42"/>
       <c r="J277" s="42"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14">
       <c r="I278" s="42"/>
       <c r="J278" s="42"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14">
       <c r="I279" s="42"/>
       <c r="J279" s="42"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14">
       <c r="I280" s="42"/>
       <c r="J280" s="42"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14">
       <c r="I281" s="42"/>
       <c r="J281" s="42"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14">
       <c r="I282" s="42"/>
       <c r="J282" s="42"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14">
       <c r="I283" s="42"/>
       <c r="J283" s="42"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14">
       <c r="I284" s="42"/>
       <c r="J284" s="42"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14">
       <c r="I285" s="42"/>
       <c r="J285" s="42"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14">
       <c r="I286" s="42"/>
       <c r="J286" s="42"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14">
       <c r="I287" s="42"/>
       <c r="J287" s="42"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14">
       <c r="I288" s="42"/>
       <c r="J288" s="42"/>
     </row>
-    <row r="289" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="9:10">
       <c r="I289" s="42"/>
       <c r="J289" s="42"/>
     </row>
-    <row r="290" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="9:10">
       <c r="I290" s="42"/>
       <c r="J290" s="42"/>
     </row>
-    <row r="291" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="9:10">
       <c r="I291" s="42"/>
       <c r="J291" s="42"/>
     </row>
-    <row r="292" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="9:10">
       <c r="I292" s="42"/>
       <c r="J292" s="42"/>
     </row>
-    <row r="293" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="9:10">
       <c r="I293" s="42"/>
       <c r="J293" s="42"/>
     </row>
-    <row r="294" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="9:10">
       <c r="I294" s="42"/>
       <c r="J294" s="42"/>
     </row>
-    <row r="295" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="9:10">
       <c r="I295" s="42"/>
       <c r="J295" s="42"/>
     </row>
-    <row r="296" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="9:10">
       <c r="I296" s="42"/>
       <c r="J296" s="42"/>
     </row>
-    <row r="297" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="9:10">
       <c r="I297" s="42"/>
       <c r="J297" s="42"/>
     </row>
-    <row r="298" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="9:10">
       <c r="I298" s="42"/>
       <c r="J298" s="42"/>
     </row>
-    <row r="299" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="9:10">
       <c r="I299" s="42"/>
       <c r="J299" s="42"/>
     </row>
-    <row r="300" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="9:10">
       <c r="I300" s="42"/>
       <c r="J300" s="42"/>
     </row>
-    <row r="301" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="9:10">
       <c r="I301" s="42"/>
       <c r="J301" s="42"/>
     </row>
-    <row r="302" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="9:10">
       <c r="I302" s="42"/>
       <c r="J302" s="42"/>
     </row>
-    <row r="303" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="303" spans="9:10">
       <c r="I303" s="42"/>
       <c r="J303" s="42"/>
     </row>
-    <row r="304" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="9:10">
       <c r="I304" s="42"/>
       <c r="J304" s="42"/>
     </row>
-    <row r="305" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="9:10">
       <c r="I305" s="42"/>
       <c r="J305" s="42"/>
     </row>
-    <row r="306" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="306" spans="9:10">
       <c r="I306" s="42"/>
       <c r="J306" s="42"/>
     </row>
-    <row r="307" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="9:10">
       <c r="I307" s="42"/>
       <c r="J307" s="42"/>
     </row>
-    <row r="308" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="9:10">
       <c r="I308" s="42"/>
       <c r="J308" s="42"/>
     </row>
-    <row r="309" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="9:10">
       <c r="I309" s="42"/>
       <c r="J309" s="42"/>
     </row>
-    <row r="310" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="9:10">
       <c r="I310" s="42"/>
       <c r="J310" s="42"/>
     </row>
-    <row r="311" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="9:10">
       <c r="I311" s="42"/>
       <c r="J311" s="42"/>
     </row>
-    <row r="312" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="9:10">
       <c r="I312" s="42"/>
       <c r="J312" s="42"/>
     </row>
-    <row r="313" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="9:10">
       <c r="I313" s="42"/>
       <c r="J313" s="42"/>
     </row>
-    <row r="314" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="9:10">
       <c r="I314" s="42"/>
       <c r="J314" s="42"/>
     </row>
-    <row r="315" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="9:10">
       <c r="I315" s="42"/>
       <c r="J315" s="42"/>
     </row>
-    <row r="316" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="9:10">
       <c r="I316" s="42"/>
       <c r="J316" s="42"/>
     </row>
-    <row r="317" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="9:10">
       <c r="I317" s="42"/>
       <c r="J317" s="42"/>
     </row>
-    <row r="318" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="9:10">
       <c r="I318" s="42"/>
       <c r="J318" s="42"/>
     </row>
-    <row r="319" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="9:10">
       <c r="I319" s="42"/>
       <c r="J319" s="42"/>
     </row>
-    <row r="320" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="9:10">
       <c r="I320" s="42"/>
       <c r="J320" s="42"/>
     </row>
-    <row r="321" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="9:10">
       <c r="I321" s="42"/>
       <c r="J321" s="42"/>
     </row>
-    <row r="322" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="9:10">
       <c r="I322" s="42"/>
       <c r="J322" s="42"/>
     </row>
-    <row r="323" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="9:10">
       <c r="I323" s="42"/>
       <c r="J323" s="42"/>
     </row>
-    <row r="324" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="9:10">
       <c r="I324" s="42"/>
       <c r="J324" s="42"/>
     </row>
-    <row r="325" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="9:10">
       <c r="I325" s="42"/>
       <c r="J325" s="42"/>
     </row>
-    <row r="326" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="9:10">
       <c r="I326" s="42"/>
       <c r="J326" s="42"/>
     </row>
-    <row r="327" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="9:10">
       <c r="I327" s="42"/>
       <c r="J327" s="42"/>
     </row>
-    <row r="328" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="9:10">
       <c r="I328" s="42"/>
       <c r="J328" s="42"/>
     </row>
-    <row r="329" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="9:10">
       <c r="I329" s="42"/>
       <c r="J329" s="42"/>
     </row>
-    <row r="330" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="9:10">
       <c r="I330" s="42"/>
       <c r="J330" s="42"/>
     </row>
-    <row r="331" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="9:10">
       <c r="I331" s="42"/>
       <c r="J331" s="42"/>
     </row>
-    <row r="332" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="9:10">
       <c r="I332" s="42"/>
       <c r="J332" s="42"/>
     </row>
-    <row r="333" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="9:10">
       <c r="I333" s="42"/>
       <c r="J333" s="42"/>
     </row>
-    <row r="334" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="9:10">
       <c r="I334" s="42"/>
       <c r="J334" s="42"/>
     </row>
-    <row r="335" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="9:10">
       <c r="I335" s="42"/>
       <c r="J335" s="42"/>
     </row>
-    <row r="336" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="9:10">
       <c r="I336" s="42"/>
       <c r="J336" s="42"/>
     </row>
-    <row r="337" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="9:10">
       <c r="I337" s="42"/>
       <c r="J337" s="42"/>
     </row>
-    <row r="338" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="9:10">
       <c r="I338" s="42"/>
       <c r="J338" s="42"/>
     </row>
-    <row r="339" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="339" spans="9:10">
       <c r="I339" s="42"/>
       <c r="J339" s="42"/>
     </row>
-    <row r="340" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="9:10">
       <c r="I340" s="42"/>
       <c r="J340" s="42"/>
     </row>
-    <row r="341" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="9:10">
       <c r="I341" s="42"/>
       <c r="J341" s="42"/>
     </row>
-    <row r="342" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="9:10">
       <c r="I342" s="42"/>
       <c r="J342" s="42"/>
     </row>
-    <row r="343" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="9:10">
       <c r="I343" s="42"/>
       <c r="J343" s="42"/>
     </row>
-    <row r="344" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="9:10">
       <c r="I344" s="42"/>
       <c r="J344" s="42"/>
     </row>
-    <row r="345" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="9:10">
       <c r="I345" s="42"/>
       <c r="J345" s="42"/>
     </row>
-    <row r="346" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="346" spans="9:10">
       <c r="I346" s="42"/>
       <c r="J346" s="42"/>
     </row>
-    <row r="347" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="9:10">
       <c r="I347" s="42"/>
       <c r="J347" s="42"/>
     </row>
-    <row r="348" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="9:10">
       <c r="I348" s="42"/>
       <c r="J348" s="42"/>
     </row>
-    <row r="349" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="349" spans="9:10">
       <c r="I349" s="42"/>
       <c r="J349" s="42"/>
     </row>
-    <row r="350" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="350" spans="9:10">
       <c r="I350" s="42"/>
       <c r="J350" s="42"/>
     </row>
-    <row r="351" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="351" spans="9:10">
       <c r="I351" s="42"/>
       <c r="J351" s="42"/>
     </row>
-    <row r="352" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="352" spans="9:10">
       <c r="I352" s="42"/>
       <c r="J352" s="42"/>
     </row>
-    <row r="353" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="353" spans="9:10">
       <c r="I353" s="42"/>
       <c r="J353" s="42"/>
     </row>
-    <row r="354" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="354" spans="9:10">
       <c r="I354" s="42"/>
       <c r="J354" s="42"/>
     </row>
-    <row r="355" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="355" spans="9:10">
       <c r="I355" s="42"/>
       <c r="J355" s="42"/>
     </row>
-    <row r="356" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="356" spans="9:10">
       <c r="I356" s="42"/>
       <c r="J356" s="42"/>
     </row>
-    <row r="357" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="357" spans="9:10">
       <c r="I357" s="42"/>
       <c r="J357" s="42"/>
     </row>
-    <row r="358" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="9:10">
       <c r="I358" s="42"/>
       <c r="J358" s="42"/>
     </row>
-    <row r="359" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="359" spans="9:10">
       <c r="I359" s="42"/>
       <c r="J359" s="42"/>
     </row>
-    <row r="360" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="9:10">
       <c r="I360" s="42"/>
       <c r="J360" s="42"/>
     </row>
-    <row r="361" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="361" spans="9:10">
       <c r="I361" s="42"/>
       <c r="J361" s="42"/>
     </row>
-    <row r="362" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="362" spans="9:10">
       <c r="I362" s="42"/>
       <c r="J362" s="42"/>
     </row>
-    <row r="363" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="363" spans="9:10">
       <c r="I363" s="42"/>
       <c r="J363" s="42"/>
     </row>
-    <row r="364" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="364" spans="9:10">
       <c r="I364" s="42"/>
       <c r="J364" s="42"/>
     </row>
-    <row r="365" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="365" spans="9:10">
       <c r="I365" s="42"/>
       <c r="J365" s="42"/>
     </row>
-    <row r="366" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="366" spans="9:10">
       <c r="I366" s="42"/>
       <c r="J366" s="42"/>
     </row>
-    <row r="367" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="367" spans="9:10">
       <c r="I367" s="42"/>
       <c r="J367" s="42"/>
     </row>
-    <row r="368" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="368" spans="9:10">
       <c r="I368" s="42"/>
       <c r="J368" s="42"/>
     </row>
-    <row r="369" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="369" spans="9:10">
       <c r="I369" s="42"/>
       <c r="J369" s="42"/>
     </row>
-    <row r="370" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="370" spans="9:10">
       <c r="I370" s="42"/>
       <c r="J370" s="42"/>
     </row>
-    <row r="371" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="371" spans="9:10">
       <c r="I371" s="42"/>
       <c r="J371" s="42"/>
     </row>
-    <row r="372" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="372" spans="9:10">
       <c r="I372" s="42"/>
       <c r="J372" s="42"/>
     </row>
-    <row r="373" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="373" spans="9:10">
       <c r="I373" s="42"/>
       <c r="J373" s="42"/>
     </row>
-    <row r="374" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="374" spans="9:10">
       <c r="I374" s="42"/>
       <c r="J374" s="42"/>
     </row>
-    <row r="375" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="375" spans="9:10">
       <c r="I375" s="42"/>
       <c r="J375" s="42"/>
     </row>
-    <row r="376" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="376" spans="9:10">
       <c r="I376" s="42"/>
       <c r="J376" s="42"/>
     </row>
-    <row r="377" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="377" spans="9:10">
       <c r="I377" s="42"/>
       <c r="J377" s="42"/>
     </row>
-    <row r="378" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="378" spans="9:10">
       <c r="I378" s="42"/>
       <c r="J378" s="42"/>
     </row>
-    <row r="379" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="379" spans="9:10">
       <c r="I379" s="42"/>
       <c r="J379" s="42"/>
     </row>
-    <row r="380" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="380" spans="9:10">
       <c r="I380" s="42"/>
       <c r="J380" s="42"/>
     </row>
-    <row r="381" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="381" spans="9:10">
       <c r="I381" s="42"/>
       <c r="J381" s="42"/>
     </row>
-    <row r="382" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="382" spans="9:10">
       <c r="I382" s="42"/>
       <c r="J382" s="42"/>
     </row>
-    <row r="383" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="383" spans="9:10">
       <c r="I383" s="42"/>
       <c r="J383" s="42"/>
     </row>
-    <row r="384" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="384" spans="9:10">
       <c r="I384" s="42"/>
       <c r="J384" s="42"/>
     </row>
-    <row r="385" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="385" spans="9:10">
       <c r="I385" s="42"/>
       <c r="J385" s="42"/>
     </row>
-    <row r="386" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="9:10">
       <c r="I386" s="42"/>
       <c r="J386" s="42"/>
     </row>
-    <row r="387" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="9:10">
       <c r="I387" s="42"/>
       <c r="J387" s="42"/>
     </row>
-    <row r="388" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="388" spans="9:10">
       <c r="I388" s="42"/>
       <c r="J388" s="42"/>
     </row>
-    <row r="389" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="389" spans="9:10">
       <c r="I389" s="42"/>
       <c r="J389" s="42"/>
     </row>
-    <row r="390" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="390" spans="9:10">
       <c r="I390" s="42"/>
       <c r="J390" s="42"/>
     </row>
-    <row r="391" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="391" spans="9:10">
       <c r="I391" s="42"/>
       <c r="J391" s="42"/>
     </row>
-    <row r="392" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="392" spans="9:10">
       <c r="I392" s="42"/>
       <c r="J392" s="42"/>
     </row>
-    <row r="393" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="393" spans="9:10">
       <c r="I393" s="42"/>
       <c r="J393" s="42"/>
     </row>
-    <row r="394" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="394" spans="9:10">
       <c r="I394" s="42"/>
       <c r="J394" s="42"/>
     </row>
-    <row r="395" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="395" spans="9:10">
       <c r="I395" s="42"/>
       <c r="J395" s="42"/>
     </row>
-    <row r="396" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="9:10">
       <c r="I396" s="42"/>
       <c r="J396" s="42"/>
     </row>
-    <row r="397" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="397" spans="9:10">
       <c r="I397" s="42"/>
       <c r="J397" s="42"/>
     </row>
-    <row r="398" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="9:10">
       <c r="I398" s="42"/>
       <c r="J398" s="42"/>
     </row>
-    <row r="399" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="9:10">
       <c r="I399" s="42"/>
       <c r="J399" s="42"/>
     </row>
-    <row r="400" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="9:10">
       <c r="I400" s="42"/>
       <c r="J400" s="42"/>
     </row>
-    <row r="401" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="9:10">
       <c r="I401" s="42"/>
       <c r="J401" s="42"/>
     </row>
-    <row r="402" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="9:10">
       <c r="I402" s="42"/>
       <c r="J402" s="42"/>
     </row>
-    <row r="403" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="9:10">
       <c r="I403" s="42"/>
       <c r="J403" s="42"/>
     </row>
-    <row r="404" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="404" spans="9:10">
       <c r="I404" s="42"/>
       <c r="J404" s="42"/>
     </row>
-    <row r="405" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="405" spans="9:10">
       <c r="I405" s="42"/>
       <c r="J405" s="42"/>
     </row>
-    <row r="406" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="406" spans="9:10">
       <c r="I406" s="42"/>
       <c r="J406" s="42"/>
     </row>
-    <row r="407" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="407" spans="9:10">
       <c r="I407" s="42"/>
       <c r="J407" s="42"/>
     </row>
-    <row r="408" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="408" spans="9:10">
       <c r="I408" s="42"/>
       <c r="J408" s="42"/>
     </row>
-    <row r="409" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="409" spans="9:10">
       <c r="I409" s="42"/>
       <c r="J409" s="42"/>
     </row>
-    <row r="410" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="9:10">
       <c r="I410" s="42"/>
       <c r="J410" s="42"/>
     </row>
-    <row r="411" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="411" spans="9:10">
       <c r="I411" s="42"/>
       <c r="J411" s="42"/>
     </row>
-    <row r="412" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="9:10">
       <c r="I412" s="42"/>
       <c r="J412" s="42"/>
     </row>
-    <row r="413" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="9:10">
       <c r="I413" s="42"/>
       <c r="J413" s="42"/>
     </row>
-    <row r="414" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="9:10">
       <c r="I414" s="42"/>
       <c r="J414" s="42"/>
     </row>
-    <row r="415" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="9:10">
       <c r="I415" s="42"/>
       <c r="J415" s="42"/>
     </row>
-    <row r="416" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="9:10">
       <c r="I416" s="42"/>
       <c r="J416" s="42"/>
     </row>
-    <row r="417" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="417" spans="9:10">
       <c r="I417" s="42"/>
       <c r="J417" s="42"/>
     </row>
-    <row r="418" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="418" spans="9:10">
       <c r="I418" s="42"/>
       <c r="J418" s="42"/>
     </row>
-    <row r="419" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="419" spans="9:10">
       <c r="I419" s="42"/>
       <c r="J419" s="42"/>
     </row>
-    <row r="420" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="420" spans="9:10">
       <c r="I420" s="42"/>
       <c r="J420" s="42"/>
     </row>
-    <row r="421" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="421" spans="9:10">
       <c r="I421" s="42"/>
       <c r="J421" s="42"/>
     </row>
-    <row r="422" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="422" spans="9:10">
       <c r="I422" s="42"/>
       <c r="J422" s="42"/>
     </row>
-    <row r="423" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="423" spans="9:10">
       <c r="I423" s="42"/>
       <c r="J423" s="42"/>
     </row>
-    <row r="424" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="424" spans="9:10">
       <c r="I424" s="42"/>
       <c r="J424" s="42"/>
     </row>
-    <row r="425" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="425" spans="9:10">
       <c r="I425" s="42"/>
       <c r="J425" s="42"/>
     </row>
-    <row r="426" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="426" spans="9:10">
       <c r="I426" s="42"/>
       <c r="J426" s="42"/>
     </row>
-    <row r="427" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="427" spans="9:10">
       <c r="I427" s="42"/>
       <c r="J427" s="42"/>
     </row>
-    <row r="428" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="428" spans="9:10">
       <c r="I428" s="42"/>
       <c r="J428" s="42"/>
     </row>
-    <row r="429" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="429" spans="9:10">
       <c r="I429" s="42"/>
       <c r="J429" s="42"/>
     </row>
-    <row r="430" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="430" spans="9:10">
       <c r="I430" s="42"/>
       <c r="J430" s="42"/>
     </row>
-    <row r="431" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="431" spans="9:10">
       <c r="I431" s="42"/>
       <c r="J431" s="42"/>
     </row>
-    <row r="432" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="432" spans="9:10">
       <c r="I432" s="42"/>
       <c r="J432" s="42"/>
     </row>
-    <row r="433" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="433" spans="9:10">
       <c r="I433" s="42"/>
       <c r="J433" s="42"/>
     </row>
-    <row r="434" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="434" spans="9:10">
       <c r="I434" s="42"/>
       <c r="J434" s="42"/>
     </row>
-    <row r="435" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="435" spans="9:10">
       <c r="I435" s="42"/>
       <c r="J435" s="42"/>
     </row>
-    <row r="436" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="436" spans="9:10">
       <c r="I436" s="42"/>
       <c r="J436" s="42"/>
     </row>
-    <row r="437" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="437" spans="9:10">
       <c r="I437" s="42"/>
       <c r="J437" s="42"/>
     </row>
-    <row r="438" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="438" spans="9:10">
       <c r="I438" s="42"/>
       <c r="J438" s="42"/>
     </row>
-    <row r="439" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="9:10">
       <c r="I439" s="42"/>
       <c r="J439" s="42"/>
     </row>
-    <row r="440" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="440" spans="9:10">
       <c r="I440" s="42"/>
       <c r="J440" s="42"/>
     </row>
-    <row r="441" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="9:10">
       <c r="I441" s="42"/>
       <c r="J441" s="42"/>
     </row>
-    <row r="442" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="9:10">
       <c r="I442" s="42"/>
       <c r="J442" s="42"/>
     </row>
-    <row r="443" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="9:10">
       <c r="I443" s="42"/>
       <c r="J443" s="42"/>
     </row>
-    <row r="444" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="9:10">
       <c r="I444" s="42"/>
       <c r="J444" s="42"/>
     </row>
-    <row r="445" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="9:10">
       <c r="I445" s="42"/>
       <c r="J445" s="42"/>
     </row>
-    <row r="446" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="9:10">
       <c r="I446" s="42"/>
       <c r="J446" s="42"/>
     </row>
-    <row r="447" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="9:10">
       <c r="I447" s="42"/>
       <c r="J447" s="42"/>
     </row>
-    <row r="448" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="9:10">
       <c r="I448" s="42"/>
       <c r="J448" s="42"/>
     </row>
-    <row r="449" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="9:10">
       <c r="I449" s="42"/>
       <c r="J449" s="42"/>
     </row>
-    <row r="450" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="9:10">
       <c r="I450" s="42"/>
       <c r="J450" s="42"/>
     </row>
-    <row r="451" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="9:10">
       <c r="I451" s="42"/>
       <c r="J451" s="42"/>
     </row>
-    <row r="452" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="9:10">
       <c r="I452" s="42"/>
       <c r="J452" s="42"/>
     </row>
-    <row r="453" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="9:10">
       <c r="I453" s="42"/>
       <c r="J453" s="42"/>
     </row>
-    <row r="454" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="9:10">
       <c r="I454" s="42"/>
       <c r="J454" s="42"/>
     </row>
-    <row r="455" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="9:10">
       <c r="I455" s="42"/>
       <c r="J455" s="42"/>
     </row>
-    <row r="456" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="9:10">
       <c r="I456" s="42"/>
       <c r="J456" s="42"/>
     </row>
-    <row r="457" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="9:10">
       <c r="I457" s="42"/>
       <c r="J457" s="42"/>
     </row>
-    <row r="458" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="9:10">
       <c r="I458" s="42"/>
       <c r="J458" s="42"/>
     </row>
-    <row r="459" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="9:10">
       <c r="I459" s="42"/>
       <c r="J459" s="42"/>
     </row>
-    <row r="460" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="9:10">
       <c r="I460" s="42"/>
       <c r="J460" s="42"/>
     </row>
-    <row r="461" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="9:10">
       <c r="I461" s="42"/>
       <c r="J461" s="42"/>
     </row>
-    <row r="462" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="9:10">
       <c r="I462" s="42"/>
       <c r="J462" s="42"/>
     </row>
-    <row r="463" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="9:10">
       <c r="I463" s="42"/>
       <c r="J463" s="42"/>
     </row>
-    <row r="464" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="9:10">
       <c r="I464" s="42"/>
       <c r="J464" s="42"/>
     </row>
-    <row r="465" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="465" spans="9:10">
       <c r="I465" s="42"/>
       <c r="J465" s="42"/>
     </row>
-    <row r="466" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="466" spans="9:10">
       <c r="I466" s="42"/>
       <c r="J466" s="42"/>
     </row>
-    <row r="467" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="467" spans="9:10">
       <c r="I467" s="42"/>
       <c r="J467" s="42"/>
     </row>
-    <row r="468" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="9:10">
       <c r="I468" s="42"/>
       <c r="J468" s="42"/>
     </row>
-    <row r="469" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="9:10">
       <c r="I469" s="42"/>
       <c r="J469" s="42"/>
     </row>
-    <row r="470" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="9:10">
       <c r="I470" s="42"/>
       <c r="J470" s="42"/>
     </row>
-    <row r="471" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="9:10">
       <c r="I471" s="42"/>
       <c r="J471" s="42"/>
     </row>
-    <row r="472" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="472" spans="9:10">
       <c r="I472" s="42"/>
       <c r="J472" s="42"/>
     </row>
-    <row r="473" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="473" spans="9:10">
       <c r="I473" s="42"/>
       <c r="J473" s="42"/>
     </row>
-    <row r="474" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="474" spans="9:10">
       <c r="I474" s="42"/>
       <c r="J474" s="42"/>
     </row>
-    <row r="475" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="475" spans="9:10">
       <c r="I475" s="42"/>
       <c r="J475" s="42"/>
     </row>
-    <row r="476" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="476" spans="9:10">
       <c r="I476" s="42"/>
       <c r="J476" s="42"/>
     </row>
-    <row r="477" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="477" spans="9:10">
       <c r="I477" s="42"/>
       <c r="J477" s="42"/>
     </row>
-    <row r="478" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="478" spans="9:10">
       <c r="I478" s="42"/>
       <c r="J478" s="42"/>
     </row>
-    <row r="479" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="479" spans="9:10">
       <c r="I479" s="42"/>
       <c r="J479" s="42"/>
     </row>
-    <row r="480" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="480" spans="9:10">
       <c r="I480" s="42"/>
       <c r="J480" s="42"/>
     </row>
-    <row r="481" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="9:10">
       <c r="I481" s="42"/>
       <c r="J481" s="42"/>
     </row>
-    <row r="482" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="482" spans="9:10">
       <c r="I482" s="42"/>
       <c r="J482" s="42"/>
     </row>
-    <row r="483" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="483" spans="9:10">
       <c r="I483" s="42"/>
       <c r="J483" s="42"/>
     </row>
-    <row r="484" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="484" spans="9:10">
       <c r="I484" s="42"/>
       <c r="J484" s="42"/>
     </row>
-    <row r="485" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="485" spans="9:10">
       <c r="I485" s="42"/>
       <c r="J485" s="42"/>
     </row>
-    <row r="486" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="486" spans="9:10">
       <c r="I486" s="42"/>
       <c r="J486" s="42"/>
     </row>
-    <row r="487" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="487" spans="9:10">
       <c r="I487" s="42"/>
       <c r="J487" s="42"/>
     </row>
-    <row r="488" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="488" spans="9:10">
       <c r="I488" s="42"/>
       <c r="J488" s="42"/>
     </row>
-    <row r="489" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="489" spans="9:10">
       <c r="I489" s="42"/>
       <c r="J489" s="42"/>
     </row>
-    <row r="490" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="490" spans="9:10">
       <c r="I490" s="42"/>
       <c r="J490" s="42"/>
     </row>
-    <row r="491" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="491" spans="9:10">
       <c r="I491" s="42"/>
       <c r="J491" s="42"/>
     </row>
-    <row r="492" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="492" spans="9:10">
       <c r="I492" s="42"/>
       <c r="J492" s="42"/>
     </row>
-    <row r="493" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="493" spans="9:10">
       <c r="I493" s="42"/>
       <c r="J493" s="42"/>
     </row>
-    <row r="494" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="494" spans="9:10">
       <c r="I494" s="42"/>
       <c r="J494" s="42"/>
     </row>
-    <row r="495" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="495" spans="9:10">
       <c r="I495" s="42"/>
       <c r="J495" s="42"/>
     </row>
-    <row r="496" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="496" spans="9:10">
       <c r="I496" s="42"/>
       <c r="J496" s="42"/>
     </row>
-    <row r="497" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="497" spans="9:10">
       <c r="I497" s="42"/>
       <c r="J497" s="42"/>
     </row>
-    <row r="498" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="498" spans="9:10">
       <c r="I498" s="42"/>
       <c r="J498" s="42"/>
     </row>
-    <row r="499" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="499" spans="9:10">
       <c r="I499" s="42"/>
       <c r="J499" s="42"/>
     </row>
-    <row r="500" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="500" spans="9:10">
       <c r="I500" s="42"/>
       <c r="J500" s="42"/>
     </row>
-    <row r="501" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="501" spans="9:10">
       <c r="I501" s="42"/>
       <c r="J501" s="42"/>
     </row>
-    <row r="502" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="502" spans="9:10">
       <c r="I502" s="42"/>
       <c r="J502" s="42"/>
     </row>
-    <row r="503" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="503" spans="9:10">
       <c r="I503" s="42"/>
       <c r="J503" s="42"/>
     </row>
-    <row r="504" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="504" spans="9:10">
       <c r="I504" s="42"/>
       <c r="J504" s="42"/>
     </row>
-    <row r="505" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="505" spans="9:10">
       <c r="I505" s="42"/>
       <c r="J505" s="42"/>
     </row>
-    <row r="506" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="506" spans="9:10">
       <c r="I506" s="42"/>
       <c r="J506" s="42"/>
     </row>
-    <row r="507" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="507" spans="9:10">
       <c r="I507" s="42"/>
       <c r="J507" s="42"/>
     </row>
-    <row r="508" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="508" spans="9:10">
       <c r="I508" s="42"/>
       <c r="J508" s="42"/>
     </row>
-    <row r="509" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="509" spans="9:10">
       <c r="I509" s="42"/>
       <c r="J509" s="42"/>
     </row>
-    <row r="510" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="510" spans="9:10">
       <c r="I510" s="42"/>
       <c r="J510" s="42"/>
     </row>
-    <row r="511" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="511" spans="9:10">
       <c r="I511" s="42"/>
       <c r="J511" s="42"/>
     </row>
-    <row r="512" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="512" spans="9:10">
       <c r="I512" s="42"/>
       <c r="J512" s="42"/>
     </row>
-    <row r="513" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="513" spans="9:10">
       <c r="I513" s="42"/>
       <c r="J513" s="42"/>
     </row>
-    <row r="514" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="514" spans="9:10">
       <c r="I514" s="42"/>
       <c r="J514" s="42"/>
     </row>
-    <row r="515" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="515" spans="9:10">
       <c r="I515" s="42"/>
       <c r="J515" s="42"/>
     </row>
-    <row r="516" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="516" spans="9:10">
       <c r="I516" s="42"/>
       <c r="J516" s="42"/>
     </row>
-    <row r="517" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="517" spans="9:10">
       <c r="I517" s="42"/>
       <c r="J517" s="42"/>
     </row>
-    <row r="518" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="518" spans="9:10">
       <c r="I518" s="42"/>
       <c r="J518" s="42"/>
     </row>
-    <row r="519" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="519" spans="9:10">
       <c r="I519" s="42"/>
       <c r="J519" s="42"/>
     </row>
-    <row r="520" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="520" spans="9:10">
       <c r="I520" s="42"/>
       <c r="J520" s="42"/>
     </row>
-    <row r="521" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="521" spans="9:10">
       <c r="I521" s="42"/>
       <c r="J521" s="42"/>
     </row>
-    <row r="522" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="522" spans="9:10">
       <c r="I522" s="42"/>
       <c r="J522" s="42"/>
     </row>
-    <row r="523" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="523" spans="9:10">
       <c r="I523" s="42"/>
       <c r="J523" s="42"/>
     </row>
-    <row r="524" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="524" spans="9:10">
       <c r="I524" s="42"/>
       <c r="J524" s="42"/>
     </row>
-    <row r="525" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="525" spans="9:10">
       <c r="I525" s="42"/>
       <c r="J525" s="42"/>
     </row>
-    <row r="526" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="526" spans="9:10">
       <c r="I526" s="42"/>
       <c r="J526" s="42"/>
     </row>
-    <row r="527" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="527" spans="9:10">
       <c r="I527" s="42"/>
       <c r="J527" s="42"/>
     </row>
-    <row r="528" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="528" spans="9:10">
       <c r="I528" s="42"/>
       <c r="J528" s="42"/>
     </row>
-    <row r="529" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="529" spans="9:10">
       <c r="I529" s="42"/>
       <c r="J529" s="42"/>
     </row>
-    <row r="530" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="530" spans="9:10">
       <c r="I530" s="42"/>
       <c r="J530" s="42"/>
     </row>
-    <row r="531" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="531" spans="9:10">
       <c r="I531" s="42"/>
       <c r="J531" s="42"/>
     </row>
-    <row r="532" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="532" spans="9:10">
       <c r="I532" s="42"/>
       <c r="J532" s="42"/>
     </row>
-    <row r="533" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="533" spans="9:10">
       <c r="I533" s="42"/>
       <c r="J533" s="42"/>
     </row>
-    <row r="534" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="534" spans="9:10">
       <c r="I534" s="42"/>
       <c r="J534" s="42"/>
     </row>
-    <row r="535" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="535" spans="9:10">
       <c r="I535" s="42"/>
       <c r="J535" s="42"/>
     </row>
-    <row r="536" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="536" spans="9:10">
       <c r="I536" s="42"/>
       <c r="J536" s="42"/>
     </row>
-    <row r="537" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="537" spans="9:10">
       <c r="I537" s="42"/>
       <c r="J537" s="42"/>
     </row>
-    <row r="538" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="538" spans="9:10">
       <c r="I538" s="42"/>
       <c r="J538" s="42"/>
     </row>
-    <row r="539" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="539" spans="9:10">
       <c r="I539" s="42"/>
       <c r="J539" s="42"/>
     </row>
-    <row r="540" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="540" spans="9:10">
       <c r="I540" s="42"/>
       <c r="J540" s="42"/>
     </row>
-    <row r="541" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="541" spans="9:10">
       <c r="I541" s="42"/>
       <c r="J541" s="42"/>
     </row>
-    <row r="542" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="542" spans="9:10">
       <c r="I542" s="42"/>
       <c r="J542" s="42"/>
     </row>
-    <row r="543" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="543" spans="9:10">
       <c r="I543" s="42"/>
       <c r="J543" s="42"/>
     </row>
-    <row r="544" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="544" spans="9:10">
       <c r="I544" s="42"/>
       <c r="J544" s="42"/>
     </row>
-    <row r="545" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="545" spans="9:10">
       <c r="I545" s="42"/>
       <c r="J545" s="42"/>
     </row>
-    <row r="546" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="546" spans="9:10">
       <c r="I546" s="42"/>
       <c r="J546" s="42"/>
     </row>
-    <row r="547" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="547" spans="9:10">
       <c r="I547" s="42"/>
       <c r="J547" s="42"/>
     </row>
-    <row r="548" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="548" spans="9:10">
       <c r="I548" s="42"/>
       <c r="J548" s="42"/>
     </row>
-    <row r="549" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="549" spans="9:10">
       <c r="I549" s="42"/>
       <c r="J549" s="42"/>
     </row>
-    <row r="550" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="550" spans="9:10">
       <c r="I550" s="42"/>
       <c r="J550" s="42"/>
     </row>
-    <row r="551" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="551" spans="9:10">
       <c r="I551" s="42"/>
       <c r="J551" s="42"/>
     </row>
-    <row r="552" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="552" spans="9:10">
       <c r="I552" s="42"/>
       <c r="J552" s="42"/>
     </row>
-    <row r="553" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="553" spans="9:10">
       <c r="I553" s="42"/>
       <c r="J553" s="42"/>
     </row>
-    <row r="554" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="554" spans="9:10">
       <c r="I554" s="42"/>
       <c r="J554" s="42"/>
     </row>
-    <row r="555" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="555" spans="9:10">
       <c r="I555" s="42"/>
       <c r="J555" s="42"/>
     </row>
-    <row r="556" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="556" spans="9:10">
       <c r="I556" s="42"/>
       <c r="J556" s="42"/>
     </row>
-    <row r="557" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="557" spans="9:10">
       <c r="I557" s="42"/>
       <c r="J557" s="42"/>
     </row>
-    <row r="558" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="558" spans="9:10">
       <c r="I558" s="42"/>
       <c r="J558" s="42"/>
     </row>
-    <row r="559" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="559" spans="9:10">
       <c r="I559" s="42"/>
       <c r="J559" s="42"/>
     </row>
-    <row r="560" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="560" spans="9:10">
       <c r="I560" s="42"/>
       <c r="J560" s="42"/>
     </row>
-    <row r="561" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="561" spans="9:10">
       <c r="I561" s="42"/>
       <c r="J561" s="42"/>
     </row>
-    <row r="562" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="562" spans="9:10">
       <c r="I562" s="42"/>
       <c r="J562" s="42"/>
     </row>
-    <row r="563" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="563" spans="9:10">
       <c r="I563" s="42"/>
       <c r="J563" s="42"/>
     </row>
-    <row r="564" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="564" spans="9:10">
       <c r="I564" s="42"/>
       <c r="J564" s="42"/>
     </row>
-    <row r="565" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="565" spans="9:10">
       <c r="I565" s="42"/>
       <c r="J565" s="42"/>
     </row>
-    <row r="566" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="566" spans="9:10">
       <c r="I566" s="42"/>
       <c r="J566" s="42"/>
     </row>
-    <row r="567" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="567" spans="9:10">
       <c r="I567" s="42"/>
       <c r="J567" s="42"/>
     </row>
-    <row r="568" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="568" spans="9:10">
       <c r="I568" s="42"/>
       <c r="J568" s="42"/>
     </row>
-    <row r="569" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="569" spans="9:10">
       <c r="I569" s="42"/>
       <c r="J569" s="42"/>
     </row>
-    <row r="570" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="570" spans="9:10">
       <c r="I570" s="42"/>
       <c r="J570" s="42"/>
     </row>
-    <row r="571" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="571" spans="9:10">
       <c r="I571" s="42"/>
       <c r="J571" s="42"/>
     </row>
-    <row r="572" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="572" spans="9:10">
       <c r="I572" s="42"/>
       <c r="J572" s="42"/>
     </row>
-    <row r="573" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="573" spans="9:10">
       <c r="I573" s="42"/>
       <c r="J573" s="42"/>
     </row>
-    <row r="574" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="574" spans="9:10">
       <c r="I574" s="42"/>
       <c r="J574" s="42"/>
     </row>
-    <row r="575" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="575" spans="9:10">
       <c r="I575" s="42"/>
       <c r="J575" s="42"/>
     </row>
-    <row r="576" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="576" spans="9:10">
       <c r="I576" s="42"/>
       <c r="J576" s="42"/>
     </row>
-    <row r="577" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="577" spans="9:10">
       <c r="I577" s="42"/>
       <c r="J577" s="42"/>
     </row>
-    <row r="578" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="578" spans="9:10">
       <c r="I578" s="42"/>
       <c r="J578" s="42"/>
     </row>
-    <row r="579" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="579" spans="9:10">
       <c r="I579" s="42"/>
       <c r="J579" s="42"/>
     </row>
-    <row r="580" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="580" spans="9:10">
       <c r="I580" s="42"/>
       <c r="J580" s="42"/>
     </row>
-    <row r="581" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="581" spans="9:10">
       <c r="I581" s="42"/>
       <c r="J581" s="42"/>
     </row>
-    <row r="582" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="582" spans="9:10">
       <c r="I582" s="42"/>
       <c r="J582" s="42"/>
     </row>
-    <row r="583" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="583" spans="9:10">
       <c r="I583" s="42"/>
       <c r="J583" s="42"/>
     </row>
-    <row r="584" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="584" spans="9:10">
       <c r="I584" s="42"/>
       <c r="J584" s="42"/>
     </row>
-    <row r="585" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="585" spans="9:10">
       <c r="I585" s="42"/>
       <c r="J585" s="42"/>
     </row>
-    <row r="586" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="586" spans="9:10">
       <c r="I586" s="42"/>
       <c r="J586" s="42"/>
     </row>
-    <row r="587" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="587" spans="9:10">
       <c r="I587" s="42"/>
       <c r="J587" s="42"/>
     </row>
-    <row r="588" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="588" spans="9:10">
       <c r="I588" s="42"/>
       <c r="J588" s="42"/>
     </row>
-    <row r="589" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="589" spans="9:10">
       <c r="I589" s="42"/>
       <c r="J589" s="42"/>
     </row>
-    <row r="590" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="590" spans="9:10">
       <c r="I590" s="42"/>
       <c r="J590" s="42"/>
     </row>
-    <row r="591" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="591" spans="9:10">
       <c r="I591" s="42"/>
       <c r="J591" s="42"/>
     </row>
-    <row r="592" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="592" spans="9:10">
       <c r="I592" s="42"/>
       <c r="J592" s="42"/>
     </row>
-    <row r="593" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="593" spans="9:10">
       <c r="I593" s="42"/>
       <c r="J593" s="42"/>
     </row>
-    <row r="594" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="594" spans="9:10">
       <c r="I594" s="42"/>
       <c r="J594" s="42"/>
     </row>
-    <row r="595" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="595" spans="9:10">
       <c r="I595" s="42"/>
       <c r="J595" s="42"/>
     </row>
-    <row r="596" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="596" spans="9:10">
       <c r="I596" s="42"/>
       <c r="J596" s="42"/>
     </row>
-    <row r="597" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="597" spans="9:10">
       <c r="I597" s="42"/>
       <c r="J597" s="42"/>
     </row>
-    <row r="598" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="598" spans="9:10">
       <c r="I598" s="42"/>
       <c r="J598" s="42"/>
     </row>
-    <row r="599" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="599" spans="9:10">
       <c r="I599" s="42"/>
       <c r="J599" s="42"/>
     </row>
-    <row r="600" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="600" spans="9:10">
       <c r="I600" s="42"/>
       <c r="J600" s="42"/>
     </row>
-    <row r="601" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="601" spans="9:10">
       <c r="I601" s="42"/>
       <c r="J601" s="42"/>
     </row>
-    <row r="602" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="602" spans="9:10">
       <c r="I602" s="42"/>
       <c r="J602" s="42"/>
     </row>
-    <row r="603" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="603" spans="9:10">
       <c r="I603" s="42"/>
       <c r="J603" s="42"/>
     </row>
-    <row r="604" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="604" spans="9:10">
       <c r="I604" s="42"/>
       <c r="J604" s="42"/>
     </row>
-    <row r="605" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="605" spans="9:10">
       <c r="I605" s="42"/>
       <c r="J605" s="42"/>
     </row>
-    <row r="606" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="606" spans="9:10">
       <c r="I606" s="42"/>
       <c r="J606" s="42"/>
     </row>
-    <row r="607" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="607" spans="9:10">
       <c r="I607" s="42"/>
       <c r="J607" s="42"/>
     </row>
-    <row r="608" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="608" spans="9:10">
       <c r="I608" s="42"/>
       <c r="J608" s="42"/>
     </row>
-    <row r="609" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="609" spans="9:10">
       <c r="I609" s="42"/>
       <c r="J609" s="42"/>
     </row>
-    <row r="610" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="610" spans="9:10">
       <c r="I610" s="42"/>
       <c r="J610" s="42"/>
     </row>
-    <row r="611" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="611" spans="9:10">
       <c r="I611" s="42"/>
       <c r="J611" s="42"/>
     </row>
-    <row r="612" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="612" spans="9:10">
       <c r="I612" s="42"/>
       <c r="J612" s="42"/>
     </row>
-    <row r="613" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="613" spans="9:10">
       <c r="I613" s="42"/>
       <c r="J613" s="42"/>
     </row>
-    <row r="614" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="614" spans="9:10">
       <c r="I614" s="42"/>
       <c r="J614" s="42"/>
     </row>
-    <row r="615" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="615" spans="9:10">
       <c r="I615" s="42"/>
       <c r="J615" s="42"/>
     </row>
-    <row r="616" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="616" spans="9:10">
       <c r="I616" s="42"/>
       <c r="J616" s="42"/>
     </row>
-    <row r="617" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="617" spans="9:10">
       <c r="I617" s="42"/>
       <c r="J617" s="42"/>
     </row>
-    <row r="618" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="618" spans="9:10">
       <c r="I618" s="42"/>
       <c r="J618" s="42"/>
     </row>
-    <row r="619" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="619" spans="9:10">
       <c r="I619" s="42"/>
       <c r="J619" s="42"/>
     </row>
-    <row r="620" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="620" spans="9:10">
       <c r="I620" s="42"/>
       <c r="J620" s="42"/>
     </row>
-    <row r="621" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="621" spans="9:10">
       <c r="I621" s="42"/>
       <c r="J621" s="42"/>
     </row>
-    <row r="622" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="622" spans="9:10">
       <c r="I622" s="42"/>
       <c r="J622" s="42"/>
     </row>
-    <row r="623" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="623" spans="9:10">
       <c r="I623" s="42"/>
       <c r="J623" s="42"/>
     </row>
-    <row r="624" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="624" spans="9:10">
       <c r="I624" s="42"/>
       <c r="J624" s="42"/>
     </row>
-    <row r="625" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="625" spans="9:10">
       <c r="I625" s="42"/>
       <c r="J625" s="42"/>
     </row>
-    <row r="626" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="626" spans="9:10">
       <c r="I626" s="42"/>
       <c r="J626" s="42"/>
     </row>
-    <row r="627" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="627" spans="9:10">
       <c r="I627" s="42"/>
       <c r="J627" s="42"/>
     </row>
-    <row r="628" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="628" spans="9:10">
       <c r="I628" s="42"/>
       <c r="J628" s="42"/>
     </row>
-    <row r="629" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="629" spans="9:10">
       <c r="I629" s="42"/>
       <c r="J629" s="42"/>
     </row>
-    <row r="630" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="630" spans="9:10">
       <c r="I630" s="42"/>
       <c r="J630" s="42"/>
     </row>
-    <row r="631" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="631" spans="9:10">
       <c r="I631" s="42"/>
       <c r="J631" s="42"/>
     </row>
-    <row r="632" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="632" spans="9:10">
       <c r="I632" s="42"/>
       <c r="J632" s="42"/>
     </row>
-    <row r="633" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="633" spans="9:10">
       <c r="I633" s="42"/>
       <c r="J633" s="42"/>
     </row>
-    <row r="634" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="634" spans="9:10">
       <c r="I634" s="42"/>
       <c r="J634" s="42"/>
     </row>
-    <row r="635" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="635" spans="9:10">
       <c r="I635" s="42"/>
       <c r="J635" s="42"/>
     </row>
-    <row r="636" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="636" spans="9:10">
       <c r="I636" s="42"/>
       <c r="J636" s="42"/>
     </row>
-    <row r="637" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="637" spans="9:10">
       <c r="I637" s="42"/>
       <c r="J637" s="42"/>
     </row>
-    <row r="638" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="638" spans="9:10">
       <c r="I638" s="42"/>
       <c r="J638" s="42"/>
     </row>
-    <row r="639" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="639" spans="9:10">
       <c r="I639" s="42"/>
       <c r="J639" s="42"/>
     </row>
-    <row r="640" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="640" spans="9:10">
       <c r="I640" s="42"/>
       <c r="J640" s="42"/>
     </row>
-    <row r="641" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="641" spans="9:10">
       <c r="I641" s="42"/>
       <c r="J641" s="42"/>
     </row>
-    <row r="642" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="642" spans="9:10">
       <c r="I642" s="42"/>
       <c r="J642" s="42"/>
     </row>
-    <row r="643" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="643" spans="9:10">
       <c r="I643" s="42"/>
       <c r="J643" s="42"/>
     </row>
-    <row r="644" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="644" spans="9:10">
       <c r="I644" s="42"/>
       <c r="J644" s="42"/>
     </row>
-    <row r="645" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="645" spans="9:10">
       <c r="I645" s="42"/>
       <c r="J645" s="42"/>
     </row>
-    <row r="646" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="646" spans="9:10">
       <c r="I646" s="42"/>
       <c r="J646" s="42"/>
     </row>
-    <row r="647" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="647" spans="9:10">
       <c r="I647" s="42"/>
       <c r="J647" s="42"/>
     </row>
-    <row r="648" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="648" spans="9:10">
       <c r="I648" s="42"/>
       <c r="J648" s="42"/>
     </row>
-    <row r="649" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="649" spans="9:10">
       <c r="I649" s="42"/>
       <c r="J649" s="42"/>
     </row>
-    <row r="650" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="650" spans="9:10">
       <c r="I650" s="42"/>
       <c r="J650" s="42"/>
     </row>
-    <row r="651" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="651" spans="9:10">
       <c r="I651" s="42"/>
       <c r="J651" s="42"/>
     </row>
-    <row r="652" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="652" spans="9:10">
       <c r="I652" s="42"/>
       <c r="J652" s="42"/>
     </row>
-    <row r="653" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="653" spans="9:10">
       <c r="I653" s="42"/>
       <c r="J653" s="42"/>
     </row>
-    <row r="654" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="654" spans="9:10">
       <c r="I654" s="42"/>
       <c r="J654" s="42"/>
     </row>
-    <row r="655" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="655" spans="9:10">
       <c r="I655" s="42"/>
       <c r="J655" s="42"/>
     </row>
-    <row r="656" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="656" spans="9:10">
       <c r="I656" s="42"/>
       <c r="J656" s="42"/>
     </row>
-    <row r="657" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="657" spans="9:10">
       <c r="I657" s="42"/>
       <c r="J657" s="42"/>
     </row>
-    <row r="658" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="658" spans="9:10">
       <c r="I658" s="42"/>
       <c r="J658" s="42"/>
     </row>
-    <row r="659" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="659" spans="9:10">
       <c r="I659" s="42"/>
       <c r="J659" s="42"/>
     </row>
-    <row r="660" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="660" spans="9:10">
       <c r="I660" s="42"/>
       <c r="J660" s="42"/>
     </row>
-    <row r="661" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="661" spans="9:10">
       <c r="I661" s="42"/>
       <c r="J661" s="42"/>
     </row>
-    <row r="662" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="662" spans="9:10">
       <c r="I662" s="42"/>
       <c r="J662" s="42"/>
     </row>
-    <row r="663" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="663" spans="9:10">
       <c r="I663" s="42"/>
       <c r="J663" s="42"/>
     </row>
-    <row r="664" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="664" spans="9:10">
       <c r="I664" s="42"/>
       <c r="J664" s="42"/>
     </row>
-    <row r="665" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="665" spans="9:10">
       <c r="I665" s="42"/>
       <c r="J665" s="42"/>
     </row>
-    <row r="666" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="666" spans="9:10">
       <c r="I666" s="42"/>
       <c r="J666" s="42"/>
     </row>
-    <row r="667" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="667" spans="9:10">
       <c r="I667" s="42"/>
       <c r="J667" s="42"/>
     </row>
-    <row r="668" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="668" spans="9:10">
       <c r="I668" s="42"/>
       <c r="J668" s="42"/>
     </row>
-    <row r="669" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="669" spans="9:10">
       <c r="I669" s="42"/>
       <c r="J669" s="42"/>
     </row>
-    <row r="670" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="670" spans="9:10">
       <c r="I670" s="42"/>
       <c r="J670" s="42"/>
     </row>
-    <row r="671" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="671" spans="9:10">
       <c r="I671" s="42"/>
       <c r="J671" s="42"/>
     </row>
-    <row r="672" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="672" spans="9:10">
       <c r="I672" s="42"/>
       <c r="J672" s="42"/>
     </row>
-    <row r="673" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="673" spans="9:10">
       <c r="I673" s="42"/>
       <c r="J673" s="42"/>
     </row>
-    <row r="674" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="674" spans="9:10">
       <c r="I674" s="42"/>
       <c r="J674" s="42"/>
     </row>
-    <row r="675" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="675" spans="9:10">
       <c r="I675" s="42"/>
       <c r="J675" s="42"/>
     </row>
-    <row r="676" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="676" spans="9:10">
       <c r="I676" s="42"/>
       <c r="J676" s="42"/>
     </row>
-    <row r="677" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="677" spans="9:10">
       <c r="I677" s="42"/>
       <c r="J677" s="42"/>
     </row>
-    <row r="678" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="678" spans="9:10">
       <c r="I678" s="42"/>
       <c r="J678" s="42"/>
     </row>
-    <row r="679" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="679" spans="9:10">
       <c r="I679" s="42"/>
       <c r="J679" s="42"/>
     </row>
-    <row r="680" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="680" spans="9:10">
       <c r="I680" s="42"/>
       <c r="J680" s="42"/>
     </row>
-    <row r="681" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="681" spans="9:10">
       <c r="I681" s="42"/>
       <c r="J681" s="42"/>
     </row>
-    <row r="682" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="682" spans="9:10">
       <c r="I682" s="42"/>
       <c r="J682" s="42"/>
     </row>
-    <row r="683" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="683" spans="9:10">
       <c r="I683" s="42"/>
       <c r="J683" s="42"/>
     </row>
-    <row r="684" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="684" spans="9:10">
       <c r="I684" s="42"/>
       <c r="J684" s="42"/>
     </row>
-    <row r="685" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="685" spans="9:10">
       <c r="I685" s="42"/>
       <c r="J685" s="42"/>
     </row>
-    <row r="686" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="686" spans="9:10">
       <c r="I686" s="42"/>
       <c r="J686" s="42"/>
     </row>
-    <row r="687" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="687" spans="9:10">
       <c r="I687" s="42"/>
       <c r="J687" s="42"/>
     </row>
-    <row r="688" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="688" spans="9:10">
       <c r="I688" s="42"/>
       <c r="J688" s="42"/>
     </row>
-    <row r="689" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="689" spans="9:10">
       <c r="I689" s="42"/>
       <c r="J689" s="42"/>
     </row>
-    <row r="690" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="690" spans="9:10">
       <c r="I690" s="42"/>
       <c r="J690" s="42"/>
     </row>
-    <row r="691" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="691" spans="9:10">
       <c r="I691" s="42"/>
       <c r="J691" s="42"/>
     </row>
-    <row r="692" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="692" spans="9:10">
       <c r="I692" s="42"/>
       <c r="J692" s="42"/>
     </row>
-    <row r="693" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="693" spans="9:10">
       <c r="I693" s="42"/>
       <c r="J693" s="42"/>
     </row>
-    <row r="694" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="694" spans="9:10">
       <c r="I694" s="42"/>
       <c r="J694" s="42"/>
     </row>
-    <row r="695" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="695" spans="9:10">
       <c r="I695" s="42"/>
       <c r="J695" s="42"/>
     </row>
-    <row r="696" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="696" spans="9:10">
       <c r="I696" s="42"/>
       <c r="J696" s="42"/>
     </row>
-    <row r="697" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="697" spans="9:10">
       <c r="I697" s="42"/>
       <c r="J697" s="42"/>
     </row>
-    <row r="698" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="698" spans="9:10">
       <c r="I698" s="42"/>
       <c r="J698" s="42"/>
     </row>
-    <row r="699" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="699" spans="9:10">
       <c r="I699" s="42"/>
       <c r="J699" s="42"/>
     </row>
-    <row r="700" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="700" spans="9:10">
       <c r="I700" s="42"/>
       <c r="J700" s="42"/>
     </row>
-    <row r="701" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="701" spans="9:10">
       <c r="I701" s="42"/>
       <c r="J701" s="42"/>
     </row>
-    <row r="702" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="702" spans="9:10">
       <c r="I702" s="42"/>
       <c r="J702" s="42"/>
     </row>
-    <row r="703" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="703" spans="9:10">
       <c r="I703" s="42"/>
       <c r="J703" s="42"/>
     </row>
-    <row r="704" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="704" spans="9:10">
       <c r="I704" s="42"/>
       <c r="J704" s="42"/>
     </row>
-    <row r="705" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="705" spans="9:10">
       <c r="I705" s="42"/>
       <c r="J705" s="42"/>
     </row>
-    <row r="706" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="706" spans="9:10">
       <c r="I706" s="42"/>
       <c r="J706" s="42"/>
     </row>
-    <row r="707" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="707" spans="9:10">
       <c r="I707" s="42"/>
       <c r="J707" s="42"/>
     </row>
-    <row r="708" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="708" spans="9:10">
       <c r="I708" s="42"/>
       <c r="J708" s="42"/>
     </row>
-    <row r="709" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="709" spans="9:10">
       <c r="I709" s="42"/>
       <c r="J709" s="42"/>
     </row>
-    <row r="710" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="710" spans="9:10">
       <c r="I710" s="42"/>
       <c r="J710" s="42"/>
     </row>
-    <row r="711" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="711" spans="9:10">
       <c r="I711" s="42"/>
       <c r="J711" s="42"/>
     </row>
-    <row r="712" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="712" spans="9:10">
       <c r="I712" s="42"/>
       <c r="J712" s="42"/>
     </row>
-    <row r="713" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="713" spans="9:10">
       <c r="I713" s="42"/>
       <c r="J713" s="42"/>
     </row>
-    <row r="714" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="714" spans="9:10">
       <c r="I714" s="42"/>
       <c r="J714" s="42"/>
     </row>
-    <row r="715" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="715" spans="9:10">
       <c r="I715" s="42"/>
       <c r="J715" s="42"/>
     </row>
-    <row r="716" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="716" spans="9:10">
       <c r="I716" s="42"/>
       <c r="J716" s="42"/>
     </row>
-    <row r="717" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="717" spans="9:10">
       <c r="I717" s="42"/>
       <c r="J717" s="42"/>
     </row>
-    <row r="718" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="718" spans="9:10">
       <c r="I718" s="42"/>
       <c r="J718" s="42"/>
     </row>
-    <row r="719" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="719" spans="9:10">
       <c r="I719" s="42"/>
       <c r="J719" s="42"/>
     </row>
-    <row r="720" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="720" spans="9:10">
       <c r="I720" s="42"/>
       <c r="J720" s="42"/>
     </row>
-    <row r="721" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="721" spans="9:10">
       <c r="I721" s="42"/>
       <c r="J721" s="42"/>
     </row>
-    <row r="722" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="722" spans="9:10">
       <c r="I722" s="42"/>
       <c r="J722" s="42"/>
     </row>
-    <row r="723" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="723" spans="9:10">
       <c r="I723" s="42"/>
       <c r="J723" s="42"/>
     </row>
-    <row r="724" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="724" spans="9:10">
       <c r="I724" s="42"/>
       <c r="J724" s="42"/>
     </row>
-    <row r="725" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="725" spans="9:10">
       <c r="I725" s="42"/>
       <c r="J725" s="42"/>
     </row>
-    <row r="726" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="726" spans="9:10">
       <c r="I726" s="42"/>
       <c r="J726" s="42"/>
     </row>
-    <row r="727" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="727" spans="9:10">
       <c r="I727" s="42"/>
       <c r="J727" s="42"/>
     </row>
-    <row r="728" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="728" spans="9:10">
       <c r="I728" s="42"/>
       <c r="J728" s="42"/>
     </row>
-    <row r="729" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="729" spans="9:10">
       <c r="I729" s="42"/>
       <c r="J729" s="42"/>
     </row>
-    <row r="730" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="730" spans="9:10">
       <c r="I730" s="42"/>
       <c r="J730" s="42"/>
     </row>
-    <row r="731" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="731" spans="9:10">
       <c r="I731" s="42"/>
       <c r="J731" s="42"/>
     </row>
-    <row r="732" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="732" spans="9:10">
       <c r="I732" s="42"/>
       <c r="J732" s="42"/>
     </row>
-    <row r="733" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="733" spans="9:10">
       <c r="I733" s="42"/>
       <c r="J733" s="42"/>
     </row>
-    <row r="734" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="734" spans="9:10">
       <c r="I734" s="42"/>
       <c r="J734" s="42"/>
     </row>
-    <row r="735" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="735" spans="9:10">
       <c r="I735" s="42"/>
       <c r="J735" s="42"/>
     </row>
-    <row r="736" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="736" spans="9:10">
       <c r="I736" s="42"/>
       <c r="J736" s="42"/>
     </row>
-    <row r="737" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="737" spans="9:10">
       <c r="I737" s="42"/>
       <c r="J737" s="42"/>
     </row>
-    <row r="738" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="738" spans="9:10">
       <c r="I738" s="42"/>
       <c r="J738" s="42"/>
     </row>
-    <row r="739" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="739" spans="9:10">
       <c r="I739" s="42"/>
       <c r="J739" s="42"/>
     </row>
-    <row r="740" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="740" spans="9:10">
       <c r="I740" s="42"/>
       <c r="J740" s="42"/>
     </row>
-    <row r="741" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="741" spans="9:10">
       <c r="I741" s="42"/>
       <c r="J741" s="42"/>
     </row>
-    <row r="742" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="742" spans="9:10">
       <c r="I742" s="42"/>
       <c r="J742" s="42"/>
     </row>
-    <row r="743" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="743" spans="9:10">
       <c r="I743" s="42"/>
       <c r="J743" s="42"/>
     </row>
-    <row r="744" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="744" spans="9:10">
       <c r="I744" s="42"/>
       <c r="J744" s="42"/>
     </row>
-    <row r="745" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="745" spans="9:10">
       <c r="I745" s="42"/>
       <c r="J745" s="42"/>
     </row>
-    <row r="746" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="746" spans="9:10">
       <c r="I746" s="42"/>
       <c r="J746" s="42"/>
     </row>
-    <row r="747" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="747" spans="9:10">
       <c r="I747" s="42"/>
       <c r="J747" s="42"/>
     </row>
-    <row r="748" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="748" spans="9:10">
       <c r="I748" s="42"/>
       <c r="J748" s="42"/>
     </row>
-    <row r="749" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="749" spans="9:10">
       <c r="I749" s="42"/>
       <c r="J749" s="42"/>
     </row>
-    <row r="750" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="750" spans="9:10">
       <c r="I750" s="42"/>
       <c r="J750" s="42"/>
     </row>
-    <row r="751" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="751" spans="9:10">
       <c r="I751" s="42"/>
       <c r="J751" s="42"/>
     </row>
-    <row r="752" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="752" spans="9:10">
       <c r="I752" s="42"/>
       <c r="J752" s="42"/>
     </row>
-    <row r="753" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="753" spans="9:10">
       <c r="I753" s="42"/>
       <c r="J753" s="42"/>
     </row>
-    <row r="754" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="754" spans="9:10">
       <c r="I754" s="42"/>
       <c r="J754" s="42"/>
     </row>
-    <row r="755" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="755" spans="9:10">
       <c r="I755" s="42"/>
       <c r="J755" s="42"/>
     </row>
-    <row r="756" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="756" spans="9:10">
       <c r="I756" s="42"/>
       <c r="J756" s="42"/>
     </row>
-    <row r="757" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="757" spans="9:10">
       <c r="I757" s="42"/>
       <c r="J757" s="42"/>
     </row>
-    <row r="758" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="758" spans="9:10">
       <c r="I758" s="42"/>
       <c r="J758" s="42"/>
     </row>
-    <row r="759" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="759" spans="9:10">
       <c r="I759" s="42"/>
       <c r="J759" s="42"/>
     </row>
-    <row r="760" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="760" spans="9:10">
       <c r="I760" s="42"/>
       <c r="J760" s="42"/>
     </row>
-    <row r="761" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="761" spans="9:10">
       <c r="I761" s="42"/>
       <c r="J761" s="42"/>
     </row>
-    <row r="762" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="762" spans="9:10">
       <c r="I762" s="42"/>
       <c r="J762" s="42"/>
     </row>
-    <row r="763" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="763" spans="9:10">
       <c r="I763" s="42"/>
       <c r="J763" s="42"/>
     </row>
-    <row r="764" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="764" spans="9:10">
       <c r="I764" s="42"/>
       <c r="J764" s="42"/>
     </row>
-    <row r="765" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="765" spans="9:10">
       <c r="I765" s="42"/>
       <c r="J765" s="42"/>
     </row>
-    <row r="766" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="766" spans="9:10">
       <c r="I766" s="42"/>
       <c r="J766" s="42"/>
     </row>
-    <row r="767" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="767" spans="9:10">
       <c r="I767" s="42"/>
       <c r="J767" s="42"/>
     </row>
-    <row r="768" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="768" spans="9:10">
       <c r="I768" s="42"/>
       <c r="J768" s="42"/>
     </row>
-    <row r="769" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="769" spans="9:10">
       <c r="I769" s="42"/>
       <c r="J769" s="42"/>
     </row>
-    <row r="770" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="770" spans="9:10">
       <c r="I770" s="42"/>
       <c r="J770" s="42"/>
     </row>
-    <row r="771" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="771" spans="9:10">
       <c r="I771" s="42"/>
       <c r="J771" s="42"/>
     </row>
-    <row r="772" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="772" spans="9:10">
       <c r="I772" s="42"/>
       <c r="J772" s="42"/>
     </row>
-    <row r="773" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="773" spans="9:10">
       <c r="I773" s="42"/>
       <c r="J773" s="42"/>
     </row>
-    <row r="774" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="774" spans="9:10">
       <c r="I774" s="42"/>
       <c r="J774" s="42"/>
     </row>
-    <row r="775" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="775" spans="9:10">
       <c r="I775" s="42"/>
       <c r="J775" s="42"/>
     </row>
-    <row r="776" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="776" spans="9:10">
       <c r="I776" s="42"/>
       <c r="J776" s="42"/>
     </row>
-    <row r="777" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="777" spans="9:10">
       <c r="I777" s="42"/>
       <c r="J777" s="42"/>
     </row>
-    <row r="778" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="778" spans="9:10">
       <c r="I778" s="42"/>
       <c r="J778" s="42"/>
     </row>
-    <row r="779" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="779" spans="9:10">
       <c r="I779" s="42"/>
       <c r="J779" s="42"/>
     </row>
-    <row r="780" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="780" spans="9:10">
       <c r="I780" s="42"/>
       <c r="J780" s="42"/>
     </row>
-    <row r="781" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="781" spans="9:10">
       <c r="I781" s="42"/>
       <c r="J781" s="42"/>
     </row>
-    <row r="782" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="782" spans="9:10">
       <c r="I782" s="42"/>
       <c r="J782" s="42"/>
     </row>
-    <row r="783" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="783" spans="9:10">
       <c r="I783" s="42"/>
       <c r="J783" s="42"/>
     </row>
-    <row r="784" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="784" spans="9:10">
       <c r="I784" s="42"/>
       <c r="J784" s="42"/>
     </row>
-    <row r="785" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="785" spans="9:10">
       <c r="I785" s="42"/>
       <c r="J785" s="42"/>
     </row>
-    <row r="786" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="786" spans="9:10">
       <c r="I786" s="42"/>
       <c r="J786" s="42"/>
     </row>
-    <row r="787" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="787" spans="9:10">
       <c r="I787" s="42"/>
       <c r="J787" s="42"/>
     </row>
-    <row r="788" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="788" spans="9:10">
       <c r="I788" s="42"/>
       <c r="J788" s="42"/>
     </row>
-    <row r="789" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="789" spans="9:10">
       <c r="I789" s="42"/>
       <c r="J789" s="42"/>
     </row>
-    <row r="790" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="790" spans="9:10">
       <c r="I790" s="42"/>
       <c r="J790" s="42"/>
     </row>
-    <row r="791" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="791" spans="9:10">
       <c r="I791" s="42"/>
       <c r="J791" s="42"/>
     </row>
-    <row r="792" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="792" spans="9:10">
       <c r="I792" s="42"/>
       <c r="J792" s="42"/>
     </row>
-    <row r="793" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="793" spans="9:10">
       <c r="I793" s="42"/>
       <c r="J793" s="42"/>
     </row>
-    <row r="794" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="794" spans="9:10">
       <c r="I794" s="42"/>
       <c r="J794" s="42"/>
     </row>
-    <row r="795" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="795" spans="9:10">
       <c r="I795" s="42"/>
       <c r="J795" s="42"/>
     </row>
-    <row r="796" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="796" spans="9:10">
       <c r="I796" s="42"/>
       <c r="J796" s="42"/>
     </row>
-    <row r="797" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="797" spans="9:10">
       <c r="I797" s="42"/>
       <c r="J797" s="42"/>
     </row>
-    <row r="798" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="798" spans="9:10">
       <c r="I798" s="42"/>
       <c r="J798" s="42"/>
     </row>
-    <row r="799" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="799" spans="9:10">
       <c r="I799" s="42"/>
       <c r="J799" s="42"/>
     </row>
-    <row r="800" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="800" spans="9:10">
       <c r="I800" s="42"/>
       <c r="J800" s="42"/>
     </row>
-    <row r="801" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="801" spans="9:10">
       <c r="I801" s="42"/>
       <c r="J801" s="42"/>
     </row>
-    <row r="802" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="802" spans="9:10">
       <c r="I802" s="42"/>
       <c r="J802" s="42"/>
     </row>
-    <row r="803" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="803" spans="9:10">
       <c r="I803" s="42"/>
       <c r="J803" s="42"/>
     </row>
-    <row r="804" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="804" spans="9:10">
       <c r="I804" s="42"/>
       <c r="J804" s="42"/>
     </row>
-    <row r="805" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="805" spans="9:10">
       <c r="I805" s="42"/>
       <c r="J805" s="42"/>
     </row>
-    <row r="806" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="806" spans="9:10">
       <c r="I806" s="42"/>
       <c r="J806" s="42"/>
     </row>
-    <row r="807" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="807" spans="9:10">
       <c r="I807" s="42"/>
       <c r="J807" s="42"/>
     </row>
-    <row r="808" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="808" spans="9:10">
       <c r="I808" s="42"/>
       <c r="J808" s="42"/>
     </row>
-    <row r="809" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="809" spans="9:10">
       <c r="I809" s="42"/>
       <c r="J809" s="42"/>
     </row>
-    <row r="810" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="810" spans="9:10">
       <c r="I810" s="42"/>
       <c r="J810" s="42"/>
     </row>
-    <row r="811" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="811" spans="9:10">
       <c r="I811" s="42"/>
       <c r="J811" s="42"/>
     </row>
-    <row r="812" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="812" spans="9:10">
       <c r="I812" s="42"/>
       <c r="J812" s="42"/>
     </row>
-    <row r="813" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="813" spans="9:10">
       <c r="I813" s="42"/>
       <c r="J813" s="42"/>
     </row>
-    <row r="814" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="814" spans="9:10">
       <c r="I814" s="42"/>
       <c r="J814" s="42"/>
     </row>
-    <row r="815" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="815" spans="9:10">
       <c r="I815" s="42"/>
       <c r="J815" s="42"/>
     </row>
-    <row r="816" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="816" spans="9:10">
       <c r="I816" s="42"/>
       <c r="J816" s="42"/>
     </row>
-    <row r="817" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="817" spans="9:10">
       <c r="I817" s="42"/>
       <c r="J817" s="42"/>
     </row>
-    <row r="818" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="818" spans="9:10">
       <c r="I818" s="42"/>
       <c r="J818" s="42"/>
     </row>
-    <row r="819" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="819" spans="9:10">
       <c r="I819" s="42"/>
       <c r="J819" s="42"/>
     </row>
-    <row r="820" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="820" spans="9:10">
       <c r="I820" s="42"/>
       <c r="J820" s="42"/>
     </row>
-    <row r="821" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="821" spans="9:10">
       <c r="I821" s="42"/>
       <c r="J821" s="42"/>
     </row>
-    <row r="822" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="822" spans="9:10">
       <c r="I822" s="42"/>
       <c r="J822" s="42"/>
     </row>
-    <row r="823" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="823" spans="9:10">
       <c r="I823" s="42"/>
       <c r="J823" s="42"/>
     </row>
-    <row r="824" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="824" spans="9:10">
       <c r="I824" s="42"/>
       <c r="J824" s="42"/>
     </row>
-    <row r="825" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="825" spans="9:10">
       <c r="I825" s="42"/>
       <c r="J825" s="42"/>
     </row>
-    <row r="826" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="826" spans="9:10">
       <c r="I826" s="42"/>
       <c r="J826" s="42"/>
     </row>
-    <row r="827" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="827" spans="9:10">
       <c r="I827" s="42"/>
       <c r="J827" s="42"/>
     </row>
-    <row r="828" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="828" spans="9:10">
       <c r="I828" s="42"/>
       <c r="J828" s="42"/>
     </row>
-    <row r="829" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="829" spans="9:10">
       <c r="I829" s="42"/>
       <c r="J829" s="42"/>
     </row>
-    <row r="830" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="830" spans="9:10">
       <c r="I830" s="42"/>
       <c r="J830" s="42"/>
     </row>
-    <row r="831" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="831" spans="9:10">
       <c r="I831" s="42"/>
       <c r="J831" s="42"/>
     </row>
-    <row r="832" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="832" spans="9:10">
       <c r="I832" s="42"/>
       <c r="J832" s="42"/>
     </row>
-    <row r="833" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="833" spans="9:10">
       <c r="I833" s="42"/>
       <c r="J833" s="42"/>
     </row>
-    <row r="834" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="834" spans="9:10">
       <c r="I834" s="42"/>
       <c r="J834" s="42"/>
     </row>
-    <row r="835" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="835" spans="9:10">
       <c r="I835" s="42"/>
       <c r="J835" s="42"/>
     </row>
-    <row r="836" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="836" spans="9:10">
       <c r="I836" s="42"/>
       <c r="J836" s="42"/>
     </row>
-    <row r="837" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="837" spans="9:10">
       <c r="I837" s="42"/>
       <c r="J837" s="42"/>
     </row>
-    <row r="838" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="838" spans="9:10">
       <c r="I838" s="42"/>
       <c r="J838" s="42"/>
     </row>
-    <row r="839" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="839" spans="9:10">
       <c r="I839" s="42"/>
       <c r="J839" s="42"/>
     </row>
-    <row r="840" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="840" spans="9:10">
       <c r="I840" s="42"/>
       <c r="J840" s="42"/>
     </row>
-    <row r="841" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="841" spans="9:10">
       <c r="I841" s="42"/>
       <c r="J841" s="42"/>
     </row>
-    <row r="842" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="842" spans="9:10">
       <c r="I842" s="42"/>
       <c r="J842" s="42"/>
     </row>
-    <row r="843" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="843" spans="9:10">
       <c r="I843" s="42"/>
       <c r="J843" s="42"/>
     </row>
-    <row r="844" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="844" spans="9:10">
       <c r="I844" s="42"/>
       <c r="J844" s="42"/>
     </row>
-    <row r="845" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="845" spans="9:10">
       <c r="I845" s="42"/>
       <c r="J845" s="42"/>
     </row>
-    <row r="846" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="846" spans="9:10">
       <c r="I846" s="42"/>
       <c r="J846" s="42"/>
     </row>
-    <row r="847" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="847" spans="9:10">
       <c r="I847" s="42"/>
       <c r="J847" s="42"/>
     </row>
-    <row r="848" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="848" spans="9:10">
       <c r="I848" s="42"/>
       <c r="J848" s="42"/>
     </row>
-    <row r="849" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="849" spans="9:10">
       <c r="I849" s="42"/>
       <c r="J849" s="42"/>
     </row>
-    <row r="850" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="850" spans="9:10">
       <c r="I850" s="42"/>
       <c r="J850" s="42"/>
     </row>
-    <row r="851" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="851" spans="9:10">
       <c r="I851" s="42"/>
       <c r="J851" s="42"/>
     </row>
-    <row r="852" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="852" spans="9:10">
       <c r="I852" s="42"/>
       <c r="J852" s="42"/>
     </row>
-    <row r="853" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="853" spans="9:10">
       <c r="I853" s="42"/>
       <c r="J853" s="42"/>
     </row>
-    <row r="854" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="854" spans="9:10">
       <c r="I854" s="42"/>
       <c r="J854" s="42"/>
     </row>
-    <row r="855" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="855" spans="9:10">
       <c r="I855" s="42"/>
       <c r="J855" s="42"/>
     </row>
-    <row r="856" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="856" spans="9:10">
       <c r="I856" s="42"/>
       <c r="J856" s="42"/>
     </row>
-    <row r="857" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="857" spans="9:10">
       <c r="I857" s="42"/>
       <c r="J857" s="42"/>
     </row>
-    <row r="858" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="858" spans="9:10">
       <c r="I858" s="42"/>
       <c r="J858" s="42"/>
     </row>
-    <row r="859" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="859" spans="9:10">
       <c r="I859" s="42"/>
       <c r="J859" s="42"/>
     </row>
-    <row r="860" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="860" spans="9:10">
       <c r="I860" s="42"/>
       <c r="J860" s="42"/>
     </row>
-    <row r="861" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="861" spans="9:10">
       <c r="I861" s="42"/>
       <c r="J861" s="42"/>
     </row>
-    <row r="862" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="862" spans="9:10">
       <c r="I862" s="42"/>
       <c r="J862" s="42"/>
     </row>
-    <row r="863" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="863" spans="9:10">
       <c r="I863" s="42"/>
       <c r="J863" s="42"/>
     </row>
-    <row r="864" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="864" spans="9:10">
       <c r="I864" s="42"/>
       <c r="J864" s="42"/>
     </row>
-    <row r="865" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="865" spans="9:10">
       <c r="I865" s="42"/>
       <c r="J865" s="42"/>
     </row>
-    <row r="866" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="866" spans="9:10">
       <c r="I866" s="42"/>
       <c r="J866" s="42"/>
     </row>
-    <row r="867" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="867" spans="9:10">
       <c r="I867" s="42"/>
       <c r="J867" s="42"/>
     </row>
-    <row r="868" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="868" spans="9:10">
       <c r="I868" s="42"/>
       <c r="J868" s="42"/>
     </row>
-    <row r="869" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="869" spans="9:10">
       <c r="I869" s="42"/>
       <c r="J869" s="42"/>
     </row>
-    <row r="870" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="870" spans="9:10">
       <c r="I870" s="42"/>
       <c r="J870" s="42"/>
     </row>
-    <row r="871" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="871" spans="9:10">
       <c r="I871" s="42"/>
       <c r="J871" s="42"/>
     </row>
-    <row r="872" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="872" spans="9:10">
       <c r="I872" s="42"/>
       <c r="J872" s="42"/>
     </row>
-    <row r="873" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="873" spans="9:10">
       <c r="I873" s="42"/>
       <c r="J873" s="42"/>
     </row>
-    <row r="874" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="874" spans="9:10">
       <c r="I874" s="42"/>
       <c r="J874" s="42"/>
     </row>
-    <row r="875" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="875" spans="9:10">
       <c r="I875" s="42"/>
       <c r="J875" s="42"/>
     </row>
-    <row r="876" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="876" spans="9:10">
       <c r="I876" s="42"/>
       <c r="J876" s="42"/>
     </row>
-    <row r="877" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="877" spans="9:10">
       <c r="I877" s="42"/>
       <c r="J877" s="42"/>
     </row>
-    <row r="878" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="878" spans="9:10">
       <c r="I878" s="42"/>
       <c r="J878" s="42"/>
     </row>
-    <row r="879" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="879" spans="9:10">
       <c r="I879" s="42"/>
       <c r="J879" s="42"/>
     </row>
-    <row r="880" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="880" spans="9:10">
       <c r="I880" s="42"/>
       <c r="J880" s="42"/>
     </row>
-    <row r="881" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="881" spans="9:10">
       <c r="I881" s="42"/>
       <c r="J881" s="42"/>
     </row>
-    <row r="882" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="882" spans="9:10">
       <c r="I882" s="42"/>
       <c r="J882" s="42"/>
     </row>
-    <row r="883" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="883" spans="9:10">
       <c r="I883" s="42"/>
       <c r="J883" s="42"/>
     </row>
-    <row r="884" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="884" spans="9:10">
       <c r="I884" s="42"/>
       <c r="J884" s="42"/>
     </row>
-    <row r="885" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="885" spans="9:10">
       <c r="I885" s="42"/>
       <c r="J885" s="42"/>
     </row>
-    <row r="886" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="886" spans="9:10">
       <c r="I886" s="42"/>
       <c r="J886" s="42"/>
     </row>
-    <row r="887" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="887" spans="9:10">
       <c r="I887" s="42"/>
       <c r="J887" s="42"/>
     </row>
-    <row r="888" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="888" spans="9:10">
       <c r="I888" s="42"/>
       <c r="J888" s="42"/>
     </row>
-    <row r="889" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="889" spans="9:10">
       <c r="I889" s="42"/>
       <c r="J889" s="42"/>
     </row>
-    <row r="890" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="890" spans="9:10">
       <c r="I890" s="42"/>
       <c r="J890" s="42"/>
     </row>
-    <row r="891" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="891" spans="9:10">
       <c r="I891" s="42"/>
       <c r="J891" s="42"/>
     </row>
-    <row r="892" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="892" spans="9:10">
       <c r="I892" s="42"/>
       <c r="J892" s="42"/>
     </row>
-    <row r="893" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="893" spans="9:10">
       <c r="I893" s="42"/>
       <c r="J893" s="42"/>
     </row>
-    <row r="894" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="894" spans="9:10">
       <c r="I894" s="42"/>
       <c r="J894" s="42"/>
     </row>
-    <row r="895" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="895" spans="9:10">
       <c r="I895" s="42"/>
       <c r="J895" s="42"/>
     </row>
-    <row r="896" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="896" spans="9:10">
       <c r="I896" s="42"/>
       <c r="J896" s="42"/>
     </row>
-    <row r="897" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="897" spans="9:10">
       <c r="I897" s="42"/>
       <c r="J897" s="42"/>
     </row>
-    <row r="898" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="898" spans="9:10">
       <c r="I898" s="42"/>
       <c r="J898" s="42"/>
     </row>
-    <row r="899" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="899" spans="9:10">
       <c r="I899" s="42"/>
       <c r="J899" s="42"/>
     </row>
-    <row r="900" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="900" spans="9:10">
       <c r="I900" s="42"/>
       <c r="J900" s="42"/>
     </row>
-    <row r="901" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="901" spans="9:10">
       <c r="I901" s="42"/>
       <c r="J901" s="42"/>
     </row>
-    <row r="902" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="902" spans="9:10">
       <c r="I902" s="42"/>
       <c r="J902" s="42"/>
     </row>
-    <row r="903" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="903" spans="9:10">
       <c r="I903" s="42"/>
       <c r="J903" s="42"/>
     </row>
-    <row r="904" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="904" spans="9:10">
       <c r="I904" s="42"/>
       <c r="J904" s="42"/>
     </row>
-    <row r="905" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="905" spans="9:10">
       <c r="I905" s="42"/>
       <c r="J905" s="42"/>
     </row>
-    <row r="906" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="906" spans="9:10">
       <c r="I906" s="42"/>
       <c r="J906" s="42"/>
     </row>
-    <row r="907" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="907" spans="9:10">
       <c r="I907" s="42"/>
       <c r="J907" s="42"/>
     </row>
-    <row r="908" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="908" spans="9:10">
       <c r="I908" s="42"/>
       <c r="J908" s="42"/>
     </row>
-    <row r="909" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="909" spans="9:10">
       <c r="I909" s="42"/>
       <c r="J909" s="42"/>
     </row>
-    <row r="910" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="910" spans="9:10">
       <c r="I910" s="42"/>
       <c r="J910" s="42"/>
     </row>
-    <row r="911" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="911" spans="9:10">
       <c r="I911" s="42"/>
       <c r="J911" s="42"/>
     </row>
-    <row r="912" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="912" spans="9:10">
       <c r="I912" s="42"/>
       <c r="J912" s="42"/>
     </row>
-    <row r="913" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="913" spans="9:10">
       <c r="I913" s="42"/>
       <c r="J913" s="42"/>
     </row>
-    <row r="914" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="914" spans="9:10">
       <c r="I914" s="42"/>
       <c r="J914" s="42"/>
     </row>
-    <row r="915" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="915" spans="9:10">
       <c r="I915" s="42"/>
       <c r="J915" s="42"/>
     </row>
-    <row r="916" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="916" spans="9:10">
       <c r="I916" s="42"/>
       <c r="J916" s="42"/>
     </row>
-    <row r="917" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="917" spans="9:10">
       <c r="I917" s="42"/>
       <c r="J917" s="42"/>
     </row>
-    <row r="918" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="918" spans="9:10">
       <c r="I918" s="42"/>
       <c r="J918" s="42"/>
     </row>
-    <row r="919" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="919" spans="9:10">
       <c r="I919" s="42"/>
       <c r="J919" s="42"/>
     </row>
-    <row r="920" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="920" spans="9:10">
       <c r="I920" s="42"/>
       <c r="J920" s="42"/>
     </row>
-    <row r="921" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="921" spans="9:10">
       <c r="I921" s="42"/>
       <c r="J921" s="42"/>
     </row>
-    <row r="922" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="922" spans="9:10">
       <c r="I922" s="42"/>
       <c r="J922" s="42"/>
     </row>
-    <row r="923" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="923" spans="9:10">
       <c r="I923" s="42"/>
       <c r="J923" s="42"/>
     </row>
-    <row r="924" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="924" spans="9:10">
       <c r="I924" s="42"/>
       <c r="J924" s="42"/>
     </row>
-    <row r="925" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="925" spans="9:10">
       <c r="I925" s="42"/>
       <c r="J925" s="42"/>
     </row>
-    <row r="926" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="926" spans="9:10">
       <c r="I926" s="42"/>
       <c r="J926" s="42"/>
     </row>
-    <row r="927" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="927" spans="9:10">
       <c r="I927" s="42"/>
       <c r="J927" s="42"/>
     </row>
-    <row r="928" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="928" spans="9:10">
       <c r="I928" s="42"/>
       <c r="J928" s="42"/>
     </row>
-    <row r="929" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="929" spans="9:10">
       <c r="I929" s="42"/>
       <c r="J929" s="42"/>
     </row>
-    <row r="930" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="930" spans="9:10">
       <c r="I930" s="42"/>
       <c r="J930" s="42"/>
     </row>
-    <row r="931" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="931" spans="9:10">
       <c r="I931" s="42"/>
       <c r="J931" s="42"/>
     </row>
-    <row r="932" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="932" spans="9:10">
       <c r="I932" s="42"/>
       <c r="J932" s="42"/>
     </row>
-    <row r="933" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="933" spans="9:10">
       <c r="I933" s="42"/>
       <c r="J933" s="42"/>
     </row>
-    <row r="934" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="934" spans="9:10">
       <c r="I934" s="42"/>
       <c r="J934" s="42"/>
     </row>
-    <row r="935" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="935" spans="9:10">
       <c r="I935" s="42"/>
       <c r="J935" s="42"/>
     </row>
-    <row r="936" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="936" spans="9:10">
       <c r="I936" s="42"/>
       <c r="J936" s="42"/>
     </row>
-    <row r="937" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="937" spans="9:10">
       <c r="I937" s="42"/>
       <c r="J937" s="42"/>
     </row>
-    <row r="938" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="938" spans="9:10">
       <c r="I938" s="42"/>
       <c r="J938" s="42"/>
     </row>
-    <row r="939" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="939" spans="9:10">
       <c r="I939" s="42"/>
       <c r="J939" s="42"/>
     </row>
-    <row r="940" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="940" spans="9:10">
       <c r="I940" s="42"/>
       <c r="J940" s="42"/>
     </row>
-    <row r="941" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="941" spans="9:10">
       <c r="I941" s="42"/>
       <c r="J941" s="42"/>
     </row>
-    <row r="942" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="942" spans="9:10">
       <c r="I942" s="42"/>
       <c r="J942" s="42"/>
     </row>
-    <row r="943" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="943" spans="9:10">
       <c r="I943" s="42"/>
       <c r="J943" s="42"/>
     </row>
-    <row r="944" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="944" spans="9:10">
       <c r="I944" s="42"/>
       <c r="J944" s="42"/>
     </row>
-    <row r="945" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="945" spans="9:10">
       <c r="I945" s="42"/>
       <c r="J945" s="42"/>
     </row>
-    <row r="946" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="946" spans="9:10">
       <c r="I946" s="42"/>
       <c r="J946" s="42"/>
     </row>
-    <row r="947" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="947" spans="9:10">
       <c r="I947" s="42"/>
       <c r="J947" s="42"/>
     </row>
-    <row r="948" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="948" spans="9:10">
       <c r="I948" s="42"/>
       <c r="J948" s="42"/>
     </row>
-    <row r="949" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="949" spans="9:10">
       <c r="I949" s="42"/>
       <c r="J949" s="42"/>
     </row>
-    <row r="950" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="950" spans="9:10">
       <c r="I950" s="42"/>
       <c r="J950" s="42"/>
     </row>
-    <row r="951" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="951" spans="9:10">
       <c r="I951" s="42"/>
       <c r="J951" s="42"/>
     </row>
-    <row r="952" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="952" spans="9:10">
       <c r="I952" s="42"/>
       <c r="J952" s="42"/>
     </row>
-    <row r="953" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="953" spans="9:10">
       <c r="I953" s="42"/>
       <c r="J953" s="42"/>
     </row>
-    <row r="954" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="954" spans="9:10">
       <c r="I954" s="42"/>
       <c r="J954" s="42"/>
     </row>
-    <row r="955" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="955" spans="9:10">
       <c r="I955" s="42"/>
       <c r="J955" s="42"/>
     </row>
-    <row r="956" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="956" spans="9:10">
       <c r="I956" s="42"/>
       <c r="J956" s="42"/>
     </row>
-    <row r="957" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="957" spans="9:10">
       <c r="I957" s="42"/>
       <c r="J957" s="42"/>
     </row>
-    <row r="958" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="958" spans="9:10">
       <c r="I958" s="42"/>
       <c r="J958" s="42"/>
     </row>
-    <row r="959" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="959" spans="9:10">
       <c r="I959" s="42"/>
       <c r="J959" s="42"/>
     </row>
-    <row r="960" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="960" spans="9:10">
       <c r="I960" s="42"/>
       <c r="J960" s="42"/>
     </row>
-    <row r="961" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="961" spans="9:10">
       <c r="I961" s="42"/>
       <c r="J961" s="42"/>
     </row>
-    <row r="962" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="962" spans="9:10">
       <c r="I962" s="42"/>
       <c r="J962" s="42"/>
     </row>
-    <row r="963" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="963" spans="9:10">
       <c r="I963" s="42"/>
       <c r="J963" s="42"/>
     </row>
-    <row r="964" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="964" spans="9:10">
       <c r="I964" s="42"/>
       <c r="J964" s="42"/>
     </row>
-    <row r="965" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="965" spans="9:10">
       <c r="I965" s="42"/>
       <c r="J965" s="42"/>
     </row>
-    <row r="966" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="966" spans="9:10">
       <c r="I966" s="42"/>
       <c r="J966" s="42"/>
     </row>
-    <row r="967" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="967" spans="9:10">
       <c r="I967" s="42"/>
       <c r="J967" s="42"/>
     </row>
-    <row r="968" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="968" spans="9:10">
       <c r="I968" s="42"/>
       <c r="J968" s="42"/>
     </row>
-    <row r="969" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="969" spans="9:10">
       <c r="I969" s="42"/>
       <c r="J969" s="42"/>
     </row>
-    <row r="970" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="970" spans="9:10">
       <c r="I970" s="42"/>
       <c r="J970" s="42"/>
     </row>
-    <row r="971" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="971" spans="9:10">
       <c r="I971" s="42"/>
       <c r="J971" s="42"/>
     </row>
-    <row r="972" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="972" spans="9:10">
       <c r="I972" s="42"/>
       <c r="J972" s="42"/>
     </row>
-    <row r="973" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="973" spans="9:10">
       <c r="I973" s="42"/>
       <c r="J973" s="42"/>
     </row>
-    <row r="974" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="974" spans="9:10">
       <c r="I974" s="42"/>
       <c r="J974" s="42"/>
     </row>
-    <row r="975" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="975" spans="9:10">
       <c r="I975" s="42"/>
       <c r="J975" s="42"/>
     </row>
-    <row r="976" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="976" spans="9:10">
       <c r="I976" s="42"/>
       <c r="J976" s="42"/>
     </row>
-    <row r="977" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="977" spans="9:10">
       <c r="I977" s="42"/>
       <c r="J977" s="42"/>
     </row>
-    <row r="978" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="978" spans="9:10">
       <c r="I978" s="42"/>
       <c r="J978" s="42"/>
     </row>
-    <row r="979" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="979" spans="9:10">
       <c r="I979" s="42"/>
       <c r="J979" s="42"/>
     </row>
-    <row r="980" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="980" spans="9:10">
       <c r="I980" s="42"/>
       <c r="J980" s="42"/>
     </row>
-    <row r="981" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="981" spans="9:10">
       <c r="I981" s="42"/>
       <c r="J981" s="42"/>
     </row>
-    <row r="982" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="982" spans="9:10">
       <c r="I982" s="42"/>
       <c r="J982" s="42"/>
     </row>
-    <row r="983" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="983" spans="9:10">
       <c r="I983" s="42"/>
       <c r="J983" s="42"/>
     </row>
-    <row r="984" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="984" spans="9:10">
       <c r="I984" s="42"/>
       <c r="J984" s="42"/>
     </row>
-    <row r="985" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="985" spans="9:10">
       <c r="I985" s="42"/>
       <c r="J985" s="42"/>
     </row>
-    <row r="986" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="986" spans="9:10">
       <c r="I986" s="42"/>
       <c r="J986" s="42"/>
     </row>
-    <row r="987" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="987" spans="9:10">
       <c r="I987" s="42"/>
       <c r="J987" s="42"/>
     </row>
-    <row r="988" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="988" spans="9:10">
       <c r="I988" s="42"/>
       <c r="J988" s="42"/>
     </row>
-    <row r="989" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="989" spans="9:10">
       <c r="I989" s="42"/>
       <c r="J989" s="42"/>
     </row>
-    <row r="990" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="990" spans="9:10">
       <c r="I990" s="42"/>
       <c r="J990" s="42"/>
     </row>
-    <row r="991" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="991" spans="9:10">
       <c r="I991" s="42"/>
       <c r="J991" s="42"/>
     </row>
-    <row r="992" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="992" spans="9:10">
       <c r="I992" s="42"/>
       <c r="J992" s="42"/>
     </row>
-    <row r="993" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="993" spans="9:10">
       <c r="I993" s="42"/>
       <c r="J993" s="42"/>
     </row>
-    <row r="994" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="994" spans="9:10">
       <c r="I994" s="42"/>
       <c r="J994" s="42"/>
     </row>
-    <row r="995" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="995" spans="9:10">
       <c r="I995" s="42"/>
       <c r="J995" s="42"/>
     </row>
-    <row r="996" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="996" spans="9:10">
       <c r="I996" s="42"/>
       <c r="J996" s="42"/>
     </row>
-    <row r="997" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="997" spans="9:10">
       <c r="I997" s="42"/>
       <c r="J997" s="42"/>
     </row>
@@ -15158,7 +15168,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:N273">
-    <cfRule type="expression" dxfId="0" priority="15">
+    <cfRule type="expression" dxfId="1" priority="15">
       <formula>AND($B2&lt;&gt;"",ISEVEN(ROW()))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15200,49 +15210,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="48.109375" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="24" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="22.15" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" ht="22.15" customHeight="1">
       <c r="A3" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="22.15" customHeight="1">
       <c r="A4" s="16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="22.15" customHeight="1">
       <c r="A5" s="16" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" ht="22.15" customHeight="1">
       <c r="A6" s="16" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="22.15" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A7">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15252,26 +15262,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -15526,40 +15516,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
-    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
-    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}"/>
 </file>
--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="4011" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{550153B3-9AA4-4556-9551-94C8348E683E}"/>
+  <xr:revisionPtr revIDLastSave="4112" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F0A1E8A-32AA-48B6-981B-290F74F9873C}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Instructions" sheetId="3" r:id="rId1"/>
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'KII Tasks'!$A$1:$M$273</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="559">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -1693,13 +1693,37 @@
   </si>
   <si>
     <t>ThongHHuynhh</t>
+  </si>
+  <si>
+    <t>Gonnella EyeQ flip position 180 Deg, and recalibration</t>
+  </si>
+  <si>
+    <t>Reposisioning the full EyeQ flipping it up 180 Deg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPC KII demo room </t>
+  </si>
+  <si>
+    <t>Enable OPC-Client in Katana side and connect with OPC-Server in the PLC</t>
+  </si>
+  <si>
+    <t>Timeline Source true change</t>
+  </si>
+  <si>
+    <t>Change the source true from the excel file to github project</t>
+  </si>
+  <si>
+    <t>Update the Software Share point Landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update the information in the software share point </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1957,7 +1981,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -2269,11 +2293,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF2F75B6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -2720,6 +2768,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2729,42 +2792,50 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF4F7FB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF4F7FB"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <font>
         <b/>
@@ -2856,6 +2927,82 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4F7FB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4F7FB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4F7FB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFD966"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF3F3F3F"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFE699"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2888,6 +3035,10 @@
     </nsvFilter>
   </namedSheetView>
 </namedSheetViews>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3212,7 +3363,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -3240,7 +3391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:C38"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -3248,25 +3399,25 @@
     <col min="4" max="4" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="36" customHeight="1">
-      <c r="B2" s="153" t="s">
+    <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="158" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="153"/>
-    </row>
-    <row r="4" spans="2:3" ht="18" customHeight="1">
-      <c r="B4" s="154" t="s">
+      <c r="C2" s="158"/>
+    </row>
+    <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="159" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="154"/>
-    </row>
-    <row r="6" spans="2:3" ht="24" customHeight="1">
-      <c r="B6" s="152" t="s">
+      <c r="C4" s="159"/>
+    </row>
+    <row r="6" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="157" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="152"/>
-    </row>
-    <row r="7" spans="2:3" ht="19.899999999999999" customHeight="1">
+      <c r="C6" s="157"/>
+    </row>
+    <row r="7" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
@@ -3274,7 +3425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="8" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -3282,7 +3433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="9" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
@@ -3290,13 +3441,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="24" customHeight="1">
-      <c r="B11" s="152" t="s">
+    <row r="11" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="157" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="152"/>
-    </row>
-    <row r="12" spans="2:3" ht="19.899999999999999" customHeight="1">
+      <c r="C11" s="157"/>
+    </row>
+    <row r="12" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -3304,7 +3455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="13" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
@@ -3312,7 +3463,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="14" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
@@ -3320,7 +3471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="15" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
@@ -3328,7 +3479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="16" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
@@ -3336,7 +3487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="17" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
@@ -3344,7 +3495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="18" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>22</v>
       </c>
@@ -3352,7 +3503,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="19" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
@@ -3360,7 +3511,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="20" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
@@ -3368,7 +3519,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="21" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>28</v>
       </c>
@@ -3376,7 +3527,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="22" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
@@ -3384,7 +3535,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="23" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>32</v>
       </c>
@@ -3392,13 +3543,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="24" customHeight="1">
-      <c r="B25" s="152" t="s">
+    <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="157" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="152"/>
-    </row>
-    <row r="26" spans="2:3" ht="19.899999999999999" customHeight="1">
+      <c r="C25" s="157"/>
+    </row>
+    <row r="26" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
@@ -3406,7 +3557,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="27" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>37</v>
       </c>
@@ -3414,7 +3565,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="28" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>39</v>
       </c>
@@ -3422,7 +3573,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="29" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>41</v>
       </c>
@@ -3430,7 +3581,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="30" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>43</v>
       </c>
@@ -3438,7 +3589,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="31" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>45</v>
       </c>
@@ -3446,13 +3597,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="24" customHeight="1">
-      <c r="B33" s="152" t="s">
+    <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="157" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="152"/>
-    </row>
-    <row r="34" spans="2:3" ht="19.899999999999999" customHeight="1">
+      <c r="C33" s="157"/>
+    </row>
+    <row r="34" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>48</v>
       </c>
@@ -3460,7 +3611,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="35" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>50</v>
       </c>
@@ -3468,7 +3619,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="36" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>52</v>
       </c>
@@ -3476,7 +3627,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="37" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>54</v>
       </c>
@@ -3484,7 +3635,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="19.899999999999999" customHeight="1">
+    <row r="38" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>56</v>
       </c>
@@ -3512,24 +3663,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N997"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="1"/>
-    <col min="2" max="2" width="51.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="70.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.7109375" customWidth="1"/>
-    <col min="9" max="10" width="17.5703125" customWidth="1"/>
-    <col min="11" max="11" width="22.28515625" customWidth="1"/>
-    <col min="12" max="12" width="44.42578125" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="51.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="70.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" customWidth="1"/>
+    <col min="9" max="10" width="17.5546875" customWidth="1"/>
+    <col min="11" max="11" width="22.33203125" customWidth="1"/>
+    <col min="12" max="12" width="44.44140625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="114" customFormat="1" ht="28.15" customHeight="1" thickBot="1">
+    <row r="1" spans="1:14" s="114" customFormat="1" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="115" t="s">
         <v>10</v>
       </c>
@@ -3573,7 +3724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="41">
         <f>IF($B2="","",ROW()-1)</f>
         <v>1</v>
@@ -3602,7 +3753,7 @@
       </c>
       <c r="N2" s="52"/>
     </row>
-    <row r="3" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="3" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="98">
         <v>248</v>
       </c>
@@ -3638,7 +3789,7 @@
       <c r="M3" s="107"/>
       <c r="N3" s="53"/>
     </row>
-    <row r="4" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="41">
         <f t="shared" ref="A4:A11" si="0">IF($B4="","",ROW()-1)</f>
         <v>3</v>
@@ -3667,7 +3818,7 @@
       </c>
       <c r="N4" s="53"/>
     </row>
-    <row r="5" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="5" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="41">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3698,7 +3849,7 @@
       </c>
       <c r="N5" s="53"/>
     </row>
-    <row r="6" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="6" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="41">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3735,7 +3886,7 @@
       </c>
       <c r="N6" s="53"/>
     </row>
-    <row r="7" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="7" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="41">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3772,7 +3923,7 @@
       </c>
       <c r="N7" s="53"/>
     </row>
-    <row r="8" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="8" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="41">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3807,7 +3958,7 @@
       </c>
       <c r="N8" s="53"/>
     </row>
-    <row r="9" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="9" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="41">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3842,7 +3993,7 @@
       </c>
       <c r="N9" s="53"/>
     </row>
-    <row r="10" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="10" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="41">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3877,7 +4028,7 @@
       </c>
       <c r="N10" s="53"/>
     </row>
-    <row r="11" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="11" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3910,7 +4061,7 @@
       </c>
       <c r="N11" s="53"/>
     </row>
-    <row r="12" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="12" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="41">
         <v>238</v>
       </c>
@@ -3944,7 +4095,7 @@
       </c>
       <c r="N12" s="53"/>
     </row>
-    <row r="13" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="13" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="41">
         <v>241</v>
       </c>
@@ -3982,7 +4133,7 @@
       </c>
       <c r="N13" s="53"/>
     </row>
-    <row r="14" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="41">
         <v>242</v>
       </c>
@@ -4012,7 +4163,7 @@
       </c>
       <c r="N14" s="53"/>
     </row>
-    <row r="15" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="15" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="41">
         <v>243</v>
       </c>
@@ -4048,7 +4199,7 @@
       </c>
       <c r="N15" s="53"/>
     </row>
-    <row r="16" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="16" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="41">
         <v>247</v>
       </c>
@@ -4086,7 +4237,7 @@
       </c>
       <c r="N16" s="53"/>
     </row>
-    <row r="17" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="17" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="41">
         <f t="shared" ref="A17:A26" si="1">IF($B17="","",ROW()-1)</f>
         <v>16</v>
@@ -4117,7 +4268,7 @@
       </c>
       <c r="N17" s="53"/>
     </row>
-    <row r="18" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="18" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="41">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -4148,7 +4299,7 @@
       </c>
       <c r="N18" s="53"/>
     </row>
-    <row r="19" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="19" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="41">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -4177,7 +4328,7 @@
       </c>
       <c r="N19" s="53"/>
     </row>
-    <row r="20" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="41">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -4206,7 +4357,7 @@
       </c>
       <c r="N20" s="53"/>
     </row>
-    <row r="21" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="41">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -4243,7 +4394,7 @@
       </c>
       <c r="N21" s="53"/>
     </row>
-    <row r="22" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="41">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -4280,7 +4431,7 @@
       </c>
       <c r="N22" s="53"/>
     </row>
-    <row r="23" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="41">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -4313,7 +4464,7 @@
       </c>
       <c r="N23" s="53"/>
     </row>
-    <row r="24" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="41">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -4348,7 +4499,7 @@
       </c>
       <c r="N24" s="53"/>
     </row>
-    <row r="25" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="41">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -4381,7 +4532,7 @@
       <c r="M25" s="96"/>
       <c r="N25" s="53"/>
     </row>
-    <row r="26" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="41">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -4414,7 +4565,7 @@
       <c r="M26" s="96"/>
       <c r="N26" s="53"/>
     </row>
-    <row r="27" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="41">
         <v>245</v>
       </c>
@@ -4450,7 +4601,7 @@
       </c>
       <c r="N27" s="53"/>
     </row>
-    <row r="28" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="41">
         <f t="shared" ref="A28:A41" si="2">IF($B28="","",ROW()-1)</f>
         <v>27</v>
@@ -4481,7 +4632,7 @@
       </c>
       <c r="N28" s="53"/>
     </row>
-    <row r="29" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="29" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="41">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -4512,7 +4663,7 @@
       </c>
       <c r="N29" s="53"/>
     </row>
-    <row r="30" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="30" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="41">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -4543,7 +4694,7 @@
       </c>
       <c r="N30" s="53"/>
     </row>
-    <row r="31" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="31" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="41">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -4572,7 +4723,7 @@
       </c>
       <c r="N31" s="53"/>
     </row>
-    <row r="32" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="32" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -4601,7 +4752,7 @@
       </c>
       <c r="N32" s="53"/>
     </row>
-    <row r="33" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="33" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="41">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -4638,7 +4789,7 @@
       </c>
       <c r="N33" s="53"/>
     </row>
-    <row r="34" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="34" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="41">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -4673,7 +4824,7 @@
       </c>
       <c r="N34" s="53"/>
     </row>
-    <row r="35" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="35" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="41">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -4710,7 +4861,7 @@
       </c>
       <c r="N35" s="53"/>
     </row>
-    <row r="36" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="36" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="41">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -4747,7 +4898,7 @@
       </c>
       <c r="N36" s="53"/>
     </row>
-    <row r="37" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="37" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="41">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -4784,7 +4935,7 @@
       </c>
       <c r="N37" s="53"/>
     </row>
-    <row r="38" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="38" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="41">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -4821,7 +4972,7 @@
       </c>
       <c r="N38" s="53"/>
     </row>
-    <row r="39" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="39" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="41">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -4854,7 +5005,7 @@
       </c>
       <c r="N39" s="53"/>
     </row>
-    <row r="40" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="40" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="41">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -4887,7 +5038,7 @@
       </c>
       <c r="N40" s="53"/>
     </row>
-    <row r="41" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="41" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="41">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -4920,7 +5071,7 @@
       </c>
       <c r="N41" s="53"/>
     </row>
-    <row r="42" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="42" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="41">
         <v>239</v>
       </c>
@@ -4956,7 +5107,7 @@
       </c>
       <c r="N42" s="53"/>
     </row>
-    <row r="43" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="43" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="41">
         <v>240</v>
       </c>
@@ -4990,7 +5141,7 @@
       </c>
       <c r="N43" s="53"/>
     </row>
-    <row r="44" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="44" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="41">
         <f>IF($B44="","",ROW()-1)</f>
         <v>43</v>
@@ -5027,7 +5178,7 @@
       </c>
       <c r="N44" s="53"/>
     </row>
-    <row r="45" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="45" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="41">
         <f>IF($B45="","",ROW()-1)</f>
         <v>44</v>
@@ -5064,7 +5215,7 @@
       </c>
       <c r="N45" s="53"/>
     </row>
-    <row r="46" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="46" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="41">
         <v>237</v>
       </c>
@@ -5100,7 +5251,7 @@
       </c>
       <c r="N46" s="53"/>
     </row>
-    <row r="47" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="47" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="41">
         <f t="shared" ref="A47:A83" si="3">IF($B47="","",ROW()-1)</f>
         <v>46</v>
@@ -5129,7 +5280,7 @@
       </c>
       <c r="N47" s="53"/>
     </row>
-    <row r="48" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="48" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="41">
         <f t="shared" si="3"/>
         <v>47</v>
@@ -5160,7 +5311,7 @@
       </c>
       <c r="N48" s="53"/>
     </row>
-    <row r="49" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="49" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="41">
         <f t="shared" si="3"/>
         <v>48</v>
@@ -5191,7 +5342,7 @@
       </c>
       <c r="N49" s="53"/>
     </row>
-    <row r="50" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="50" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="41">
         <f t="shared" si="3"/>
         <v>49</v>
@@ -5222,7 +5373,7 @@
       </c>
       <c r="N50" s="53"/>
     </row>
-    <row r="51" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="51" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="41">
         <f t="shared" si="3"/>
         <v>50</v>
@@ -5255,7 +5406,7 @@
       </c>
       <c r="N51" s="53"/>
     </row>
-    <row r="52" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="52" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="41">
         <f t="shared" si="3"/>
         <v>51</v>
@@ -5288,7 +5439,7 @@
       </c>
       <c r="N52" s="53"/>
     </row>
-    <row r="53" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="53" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="41">
         <f t="shared" si="3"/>
         <v>52</v>
@@ -5325,7 +5476,7 @@
       </c>
       <c r="N53" s="53"/>
     </row>
-    <row r="54" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="54" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="41">
         <f t="shared" si="3"/>
         <v>53</v>
@@ -5354,7 +5505,7 @@
       </c>
       <c r="N54" s="53"/>
     </row>
-    <row r="55" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="55" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
@@ -5383,7 +5534,7 @@
       </c>
       <c r="N55" s="53"/>
     </row>
-    <row r="56" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="56" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="41">
         <f t="shared" si="3"/>
         <v>55</v>
@@ -5414,7 +5565,7 @@
       <c r="M56" s="11"/>
       <c r="N56" s="53"/>
     </row>
-    <row r="57" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="57" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="41">
         <f t="shared" si="3"/>
         <v>56</v>
@@ -5451,7 +5602,7 @@
       </c>
       <c r="N57" s="53"/>
     </row>
-    <row r="58" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="58" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="41">
         <f t="shared" si="3"/>
         <v>57</v>
@@ -5488,7 +5639,7 @@
       </c>
       <c r="N58" s="53"/>
     </row>
-    <row r="59" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="59" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="41">
         <f t="shared" si="3"/>
         <v>58</v>
@@ -5525,7 +5676,7 @@
       </c>
       <c r="N59" s="53"/>
     </row>
-    <row r="60" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="60" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="41">
         <f t="shared" si="3"/>
         <v>59</v>
@@ -5562,7 +5713,7 @@
       </c>
       <c r="N60" s="53"/>
     </row>
-    <row r="61" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="61" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="41">
         <f t="shared" si="3"/>
         <v>60</v>
@@ -5599,7 +5750,7 @@
       </c>
       <c r="N61" s="53"/>
     </row>
-    <row r="62" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="62" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="41">
         <f t="shared" si="3"/>
         <v>61</v>
@@ -5636,7 +5787,7 @@
       </c>
       <c r="N62" s="53"/>
     </row>
-    <row r="63" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="63" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="41">
         <f t="shared" si="3"/>
         <v>62</v>
@@ -5671,7 +5822,7 @@
       </c>
       <c r="N63" s="53"/>
     </row>
-    <row r="64" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="64" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="41">
         <f t="shared" si="3"/>
         <v>63</v>
@@ -5708,7 +5859,7 @@
       </c>
       <c r="N64" s="53"/>
     </row>
-    <row r="65" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="65" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="41">
         <f t="shared" si="3"/>
         <v>64</v>
@@ -5743,7 +5894,7 @@
       </c>
       <c r="N65" s="53"/>
     </row>
-    <row r="66" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="66" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="41">
         <f t="shared" si="3"/>
         <v>65</v>
@@ -5776,7 +5927,7 @@
       </c>
       <c r="N66" s="53"/>
     </row>
-    <row r="67" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="67" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="41">
         <f t="shared" si="3"/>
         <v>66</v>
@@ -5809,7 +5960,7 @@
       </c>
       <c r="N67" s="53"/>
     </row>
-    <row r="68" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="68" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="41">
         <f t="shared" si="3"/>
         <v>67</v>
@@ -5844,7 +5995,7 @@
       </c>
       <c r="N68" s="53"/>
     </row>
-    <row r="69" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="69" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="41">
         <f t="shared" si="3"/>
         <v>68</v>
@@ -5879,7 +6030,7 @@
       </c>
       <c r="N69" s="53"/>
     </row>
-    <row r="70" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="70" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="41">
         <f t="shared" si="3"/>
         <v>69</v>
@@ -5914,7 +6065,7 @@
       </c>
       <c r="N70" s="53"/>
     </row>
-    <row r="71" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="71" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="41">
         <f t="shared" si="3"/>
         <v>70</v>
@@ -5947,7 +6098,7 @@
       </c>
       <c r="N71" s="53"/>
     </row>
-    <row r="72" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="72" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="41">
         <f t="shared" si="3"/>
         <v>71</v>
@@ -5982,7 +6133,7 @@
       </c>
       <c r="N72" s="53"/>
     </row>
-    <row r="73" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="73" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="41">
         <f t="shared" si="3"/>
         <v>72</v>
@@ -6017,7 +6168,7 @@
       </c>
       <c r="N73" s="53"/>
     </row>
-    <row r="74" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="74" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="41">
         <f t="shared" si="3"/>
         <v>73</v>
@@ -6050,7 +6201,7 @@
       </c>
       <c r="N74" s="53"/>
     </row>
-    <row r="75" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="75" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="41">
         <f t="shared" si="3"/>
         <v>74</v>
@@ -6085,7 +6236,7 @@
       </c>
       <c r="N75" s="53"/>
     </row>
-    <row r="76" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="76" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="41">
         <f t="shared" si="3"/>
         <v>75</v>
@@ -6120,7 +6271,7 @@
       </c>
       <c r="N76" s="53"/>
     </row>
-    <row r="77" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="77" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="41">
         <f t="shared" si="3"/>
         <v>76</v>
@@ -6153,7 +6304,7 @@
       </c>
       <c r="N77" s="53"/>
     </row>
-    <row r="78" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="78" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="41">
         <f t="shared" si="3"/>
         <v>77</v>
@@ -6186,7 +6337,7 @@
       </c>
       <c r="N78" s="53"/>
     </row>
-    <row r="79" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="79" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="41">
         <f t="shared" si="3"/>
         <v>78</v>
@@ -6219,7 +6370,7 @@
       </c>
       <c r="N79" s="53"/>
     </row>
-    <row r="80" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="80" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="41">
         <f t="shared" si="3"/>
         <v>79</v>
@@ -6252,7 +6403,7 @@
       </c>
       <c r="N80" s="53"/>
     </row>
-    <row r="81" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="81" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="41">
         <f t="shared" si="3"/>
         <v>80</v>
@@ -6285,7 +6436,7 @@
       </c>
       <c r="N81" s="53"/>
     </row>
-    <row r="82" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="82" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="41">
         <f t="shared" si="3"/>
         <v>81</v>
@@ -6320,7 +6471,7 @@
       </c>
       <c r="N82" s="53"/>
     </row>
-    <row r="83" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="83" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="41">
         <f t="shared" si="3"/>
         <v>82</v>
@@ -6357,7 +6508,7 @@
       </c>
       <c r="N83" s="53"/>
     </row>
-    <row r="84" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="84" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="41">
         <v>246</v>
       </c>
@@ -6393,7 +6544,7 @@
       </c>
       <c r="N84" s="53"/>
     </row>
-    <row r="85" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="85" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="41">
         <f t="shared" ref="A85:A116" si="4">IF($B85="","",ROW()-1)</f>
         <v>84</v>
@@ -6422,7 +6573,7 @@
       </c>
       <c r="N85" s="53"/>
     </row>
-    <row r="86" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="86" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="41">
         <f t="shared" si="4"/>
         <v>85</v>
@@ -6453,7 +6604,7 @@
       </c>
       <c r="N86" s="53"/>
     </row>
-    <row r="87" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="87" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="41">
         <f t="shared" si="4"/>
         <v>86</v>
@@ -6484,7 +6635,7 @@
       </c>
       <c r="N87" s="53"/>
     </row>
-    <row r="88" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="88" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="41">
         <f t="shared" si="4"/>
         <v>87</v>
@@ -6515,7 +6666,7 @@
       </c>
       <c r="N88" s="53"/>
     </row>
-    <row r="89" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="89" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="41">
         <f t="shared" si="4"/>
         <v>88</v>
@@ -6552,7 +6703,7 @@
       </c>
       <c r="N89" s="53"/>
     </row>
-    <row r="90" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="90" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="41">
         <f t="shared" si="4"/>
         <v>89</v>
@@ -6589,7 +6740,7 @@
       </c>
       <c r="N90" s="53"/>
     </row>
-    <row r="91" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="91" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="41">
         <f t="shared" si="4"/>
         <v>90</v>
@@ -6626,7 +6777,7 @@
       </c>
       <c r="N91" s="53"/>
     </row>
-    <row r="92" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="92" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="41">
         <f t="shared" si="4"/>
         <v>91</v>
@@ -6663,7 +6814,7 @@
       </c>
       <c r="N92" s="53"/>
     </row>
-    <row r="93" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="93" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="41">
         <f t="shared" si="4"/>
         <v>92</v>
@@ -6700,7 +6851,7 @@
       </c>
       <c r="N93" s="53"/>
     </row>
-    <row r="94" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="94" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="41">
         <f t="shared" si="4"/>
         <v>93</v>
@@ -6737,7 +6888,7 @@
       </c>
       <c r="N94" s="53"/>
     </row>
-    <row r="95" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="95" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="41">
         <f t="shared" si="4"/>
         <v>94</v>
@@ -6774,7 +6925,7 @@
       </c>
       <c r="N95" s="53"/>
     </row>
-    <row r="96" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="96" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="41">
         <f t="shared" si="4"/>
         <v>95</v>
@@ -6809,7 +6960,7 @@
       </c>
       <c r="N96" s="53"/>
     </row>
-    <row r="97" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="97" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="41">
         <f t="shared" si="4"/>
         <v>96</v>
@@ -6842,7 +6993,7 @@
       </c>
       <c r="N97" s="53"/>
     </row>
-    <row r="98" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="98" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="41">
         <f t="shared" si="4"/>
         <v>97</v>
@@ -6875,7 +7026,7 @@
       </c>
       <c r="N98" s="53"/>
     </row>
-    <row r="99" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="99" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="41">
         <f t="shared" si="4"/>
         <v>98</v>
@@ -6908,7 +7059,7 @@
       </c>
       <c r="N99" s="53"/>
     </row>
-    <row r="100" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="100" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="41">
         <f t="shared" si="4"/>
         <v>99</v>
@@ -6941,7 +7092,7 @@
       </c>
       <c r="N100" s="53"/>
     </row>
-    <row r="101" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="101" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="41">
         <f t="shared" si="4"/>
         <v>100</v>
@@ -6970,7 +7121,7 @@
       </c>
       <c r="N101" s="53"/>
     </row>
-    <row r="102" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="102" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="41">
         <f t="shared" si="4"/>
         <v>101</v>
@@ -7003,7 +7154,7 @@
       </c>
       <c r="N102" s="53"/>
     </row>
-    <row r="103" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="103" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="41">
         <f t="shared" si="4"/>
         <v>102</v>
@@ -7036,7 +7187,7 @@
       </c>
       <c r="N103" s="53"/>
     </row>
-    <row r="104" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="104" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="41">
         <f t="shared" si="4"/>
         <v>103</v>
@@ -7067,7 +7218,7 @@
       </c>
       <c r="N104" s="53"/>
     </row>
-    <row r="105" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="105" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="41">
         <f t="shared" si="4"/>
         <v>104</v>
@@ -7098,7 +7249,7 @@
       </c>
       <c r="N105" s="53"/>
     </row>
-    <row r="106" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="106" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="41">
         <f t="shared" si="4"/>
         <v>105</v>
@@ -7127,7 +7278,7 @@
       </c>
       <c r="N106" s="53"/>
     </row>
-    <row r="107" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="107" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="41">
         <f t="shared" si="4"/>
         <v>106</v>
@@ -7156,7 +7307,7 @@
       </c>
       <c r="N107" s="53"/>
     </row>
-    <row r="108" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="108" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="41">
         <f t="shared" si="4"/>
         <v>107</v>
@@ -7185,7 +7336,7 @@
       </c>
       <c r="N108" s="53"/>
     </row>
-    <row r="109" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="109" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="41">
         <f t="shared" si="4"/>
         <v>108</v>
@@ -7214,7 +7365,7 @@
       </c>
       <c r="N109" s="53"/>
     </row>
-    <row r="110" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="110" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="41">
         <f t="shared" si="4"/>
         <v>109</v>
@@ -7247,7 +7398,7 @@
       </c>
       <c r="N110" s="53"/>
     </row>
-    <row r="111" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="111" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="41">
         <f t="shared" si="4"/>
         <v>110</v>
@@ -7280,7 +7431,7 @@
       </c>
       <c r="N111" s="53"/>
     </row>
-    <row r="112" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="112" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="41">
         <f t="shared" si="4"/>
         <v>111</v>
@@ -7317,7 +7468,7 @@
       </c>
       <c r="N112" s="53"/>
     </row>
-    <row r="113" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="113" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="41">
         <f t="shared" si="4"/>
         <v>112</v>
@@ -7354,7 +7505,7 @@
       </c>
       <c r="N113" s="53"/>
     </row>
-    <row r="114" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="114" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="41">
         <f t="shared" si="4"/>
         <v>113</v>
@@ -7391,7 +7542,7 @@
       </c>
       <c r="N114" s="53"/>
     </row>
-    <row r="115" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="115" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="41">
         <f t="shared" si="4"/>
         <v>114</v>
@@ -7428,7 +7579,7 @@
       </c>
       <c r="N115" s="53"/>
     </row>
-    <row r="116" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="116" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="41">
         <f t="shared" si="4"/>
         <v>115</v>
@@ -7465,7 +7616,7 @@
       </c>
       <c r="N116" s="53"/>
     </row>
-    <row r="117" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="117" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="41">
         <f t="shared" ref="A117:A148" si="5">IF($B117="","",ROW()-1)</f>
         <v>116</v>
@@ -7502,7 +7653,7 @@
       </c>
       <c r="N117" s="53"/>
     </row>
-    <row r="118" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="118" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="41">
         <f t="shared" si="5"/>
         <v>117</v>
@@ -7539,7 +7690,7 @@
       </c>
       <c r="N118" s="53"/>
     </row>
-    <row r="119" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="119" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="41">
         <f t="shared" si="5"/>
         <v>118</v>
@@ -7576,7 +7727,7 @@
       </c>
       <c r="N119" s="53"/>
     </row>
-    <row r="120" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="120" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="41">
         <f t="shared" si="5"/>
         <v>119</v>
@@ -7613,7 +7764,7 @@
       </c>
       <c r="N120" s="53"/>
     </row>
-    <row r="121" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="121" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="41">
         <f t="shared" si="5"/>
         <v>120</v>
@@ -7650,7 +7801,7 @@
       </c>
       <c r="N121" s="53"/>
     </row>
-    <row r="122" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="122" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="41">
         <f t="shared" si="5"/>
         <v>121</v>
@@ -7687,7 +7838,7 @@
       </c>
       <c r="N122" s="53"/>
     </row>
-    <row r="123" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="123" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="41">
         <f t="shared" si="5"/>
         <v>122</v>
@@ -7724,7 +7875,7 @@
       </c>
       <c r="N123" s="53"/>
     </row>
-    <row r="124" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="124" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="41">
         <f t="shared" si="5"/>
         <v>123</v>
@@ -7761,7 +7912,7 @@
       </c>
       <c r="N124" s="53"/>
     </row>
-    <row r="125" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="125" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="41">
         <f t="shared" si="5"/>
         <v>124</v>
@@ -7798,7 +7949,7 @@
       </c>
       <c r="N125" s="53"/>
     </row>
-    <row r="126" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="126" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="41">
         <f t="shared" si="5"/>
         <v>125</v>
@@ -7835,7 +7986,7 @@
       </c>
       <c r="N126" s="53"/>
     </row>
-    <row r="127" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="127" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="41">
         <f t="shared" si="5"/>
         <v>126</v>
@@ -7872,7 +8023,7 @@
       </c>
       <c r="N127" s="53"/>
     </row>
-    <row r="128" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="128" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="41">
         <f t="shared" si="5"/>
         <v>127</v>
@@ -7909,7 +8060,7 @@
       </c>
       <c r="N128" s="53"/>
     </row>
-    <row r="129" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="129" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="41">
         <f t="shared" si="5"/>
         <v>128</v>
@@ -7946,7 +8097,7 @@
       </c>
       <c r="N129" s="53"/>
     </row>
-    <row r="130" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="130" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="41">
         <f t="shared" si="5"/>
         <v>129</v>
@@ -7983,7 +8134,7 @@
       </c>
       <c r="N130" s="53"/>
     </row>
-    <row r="131" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="131" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="41">
         <f t="shared" si="5"/>
         <v>130</v>
@@ -8012,7 +8163,7 @@
       </c>
       <c r="N131" s="53"/>
     </row>
-    <row r="132" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="132" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="41">
         <f t="shared" si="5"/>
         <v>131</v>
@@ -8041,7 +8192,7 @@
       </c>
       <c r="N132" s="53"/>
     </row>
-    <row r="133" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="133" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="41">
         <f t="shared" si="5"/>
         <v>132</v>
@@ -8078,7 +8229,7 @@
       </c>
       <c r="N133" s="53"/>
     </row>
-    <row r="134" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="134" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="41">
         <f t="shared" si="5"/>
         <v>133</v>
@@ -8115,7 +8266,7 @@
       </c>
       <c r="N134" s="53"/>
     </row>
-    <row r="135" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="135" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="41">
         <f t="shared" si="5"/>
         <v>134</v>
@@ -8150,7 +8301,7 @@
       </c>
       <c r="N135" s="53"/>
     </row>
-    <row r="136" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="136" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="41">
         <f t="shared" si="5"/>
         <v>135</v>
@@ -8187,7 +8338,7 @@
       </c>
       <c r="N136" s="53"/>
     </row>
-    <row r="137" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="137" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="41">
         <f t="shared" si="5"/>
         <v>136</v>
@@ -8224,7 +8375,7 @@
       </c>
       <c r="N137" s="53"/>
     </row>
-    <row r="138" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="138" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="41">
         <f t="shared" si="5"/>
         <v>137</v>
@@ -8261,7 +8412,7 @@
       </c>
       <c r="N138" s="53"/>
     </row>
-    <row r="139" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="139" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="41">
         <f t="shared" si="5"/>
         <v>138</v>
@@ -8294,7 +8445,7 @@
       </c>
       <c r="N139" s="53"/>
     </row>
-    <row r="140" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="140" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="41">
         <f t="shared" si="5"/>
         <v>139</v>
@@ -8327,7 +8478,7 @@
       </c>
       <c r="N140" s="53"/>
     </row>
-    <row r="141" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="141" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="41">
         <f t="shared" si="5"/>
         <v>140</v>
@@ -8362,7 +8513,7 @@
       </c>
       <c r="N141" s="53"/>
     </row>
-    <row r="142" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="142" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="41">
         <f t="shared" si="5"/>
         <v>141</v>
@@ -8397,7 +8548,7 @@
       </c>
       <c r="N142" s="53"/>
     </row>
-    <row r="143" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="143" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4">
         <f t="shared" si="5"/>
         <v>142</v>
@@ -8428,7 +8579,7 @@
       </c>
       <c r="N143" s="53"/>
     </row>
-    <row r="144" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="144" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="41">
         <f t="shared" si="5"/>
         <v>143</v>
@@ -8457,7 +8608,7 @@
       </c>
       <c r="N144" s="53"/>
     </row>
-    <row r="145" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="145" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="41">
         <f t="shared" si="5"/>
         <v>144</v>
@@ -8486,7 +8637,7 @@
       </c>
       <c r="N145" s="53"/>
     </row>
-    <row r="146" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="146" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="41">
         <f t="shared" si="5"/>
         <v>145</v>
@@ -8515,7 +8666,7 @@
       </c>
       <c r="N146" s="53"/>
     </row>
-    <row r="147" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="147" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="41">
         <f t="shared" si="5"/>
         <v>146</v>
@@ -8544,7 +8695,7 @@
       </c>
       <c r="N147" s="53"/>
     </row>
-    <row r="148" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="148" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="41">
         <f t="shared" si="5"/>
         <v>147</v>
@@ -8573,7 +8724,7 @@
       </c>
       <c r="N148" s="53"/>
     </row>
-    <row r="149" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="149" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="41">
         <f t="shared" ref="A149:A180" si="6">IF($B149="","",ROW()-1)</f>
         <v>148</v>
@@ -8602,7 +8753,7 @@
       </c>
       <c r="N149" s="53"/>
     </row>
-    <row r="150" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="150" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="41">
         <f t="shared" si="6"/>
         <v>149</v>
@@ -8631,7 +8782,7 @@
       </c>
       <c r="N150" s="53"/>
     </row>
-    <row r="151" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="151" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="41">
         <f t="shared" si="6"/>
         <v>150</v>
@@ -8660,7 +8811,7 @@
       </c>
       <c r="N151" s="53"/>
     </row>
-    <row r="152" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="152" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="41">
         <f t="shared" si="6"/>
         <v>151</v>
@@ -8689,7 +8840,7 @@
       </c>
       <c r="N152" s="53"/>
     </row>
-    <row r="153" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="153" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="41">
         <f t="shared" si="6"/>
         <v>152</v>
@@ -8718,7 +8869,7 @@
       </c>
       <c r="N153" s="53"/>
     </row>
-    <row r="154" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="154" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="41">
         <f t="shared" si="6"/>
         <v>153</v>
@@ -8747,7 +8898,7 @@
       </c>
       <c r="N154" s="53"/>
     </row>
-    <row r="155" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="155" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="41">
         <f t="shared" si="6"/>
         <v>154</v>
@@ -8776,7 +8927,7 @@
       </c>
       <c r="N155" s="53"/>
     </row>
-    <row r="156" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="156" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="41">
         <f t="shared" si="6"/>
         <v>155</v>
@@ -8805,7 +8956,7 @@
       </c>
       <c r="N156" s="53"/>
     </row>
-    <row r="157" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="157" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="41">
         <f t="shared" si="6"/>
         <v>156</v>
@@ -8832,7 +8983,7 @@
       </c>
       <c r="N157" s="53"/>
     </row>
-    <row r="158" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="158" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="41">
         <f t="shared" si="6"/>
         <v>157</v>
@@ -8861,7 +9012,7 @@
       </c>
       <c r="N158" s="53"/>
     </row>
-    <row r="159" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="159" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="41">
         <f t="shared" si="6"/>
         <v>158</v>
@@ -8894,7 +9045,7 @@
       </c>
       <c r="N159" s="53"/>
     </row>
-    <row r="160" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="160" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="41">
         <f t="shared" si="6"/>
         <v>159</v>
@@ -8927,7 +9078,7 @@
       </c>
       <c r="N160" s="53"/>
     </row>
-    <row r="161" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="161" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="41">
         <f t="shared" si="6"/>
         <v>160</v>
@@ -8960,7 +9111,7 @@
       </c>
       <c r="N161" s="53"/>
     </row>
-    <row r="162" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="162" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="41">
         <f t="shared" si="6"/>
         <v>161</v>
@@ -8993,7 +9144,7 @@
       </c>
       <c r="N162" s="53"/>
     </row>
-    <row r="163" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="163" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="41">
         <f t="shared" si="6"/>
         <v>162</v>
@@ -9026,7 +9177,7 @@
       </c>
       <c r="N163" s="53"/>
     </row>
-    <row r="164" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="164" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="41">
         <f t="shared" si="6"/>
         <v>163</v>
@@ -9059,7 +9210,7 @@
       </c>
       <c r="N164" s="53"/>
     </row>
-    <row r="165" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="165" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="41">
         <f t="shared" si="6"/>
         <v>164</v>
@@ -9092,7 +9243,7 @@
       </c>
       <c r="N165" s="53"/>
     </row>
-    <row r="166" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="166" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="41">
         <f t="shared" si="6"/>
         <v>165</v>
@@ -9127,7 +9278,7 @@
       </c>
       <c r="N166" s="53"/>
     </row>
-    <row r="167" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="167" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="41">
         <f t="shared" si="6"/>
         <v>166</v>
@@ -9156,7 +9307,7 @@
       </c>
       <c r="N167" s="53"/>
     </row>
-    <row r="168" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="168" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="41">
         <f t="shared" si="6"/>
         <v>167</v>
@@ -9185,7 +9336,7 @@
       </c>
       <c r="N168" s="53"/>
     </row>
-    <row r="169" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="169" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="41">
         <f t="shared" si="6"/>
         <v>168</v>
@@ -9214,7 +9365,7 @@
       </c>
       <c r="N169" s="53"/>
     </row>
-    <row r="170" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="170" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="41">
         <f t="shared" si="6"/>
         <v>169</v>
@@ -9245,7 +9396,7 @@
       </c>
       <c r="N170" s="53"/>
     </row>
-    <row r="171" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="171" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="41">
         <f t="shared" si="6"/>
         <v>170</v>
@@ -9274,7 +9425,7 @@
       </c>
       <c r="N171" s="53"/>
     </row>
-    <row r="172" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="172" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="41">
         <f t="shared" si="6"/>
         <v>171</v>
@@ -9303,7 +9454,7 @@
       </c>
       <c r="N172" s="53"/>
     </row>
-    <row r="173" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="173" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="41">
         <f t="shared" si="6"/>
         <v>172</v>
@@ -9332,7 +9483,7 @@
       </c>
       <c r="N173" s="53"/>
     </row>
-    <row r="174" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="174" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="41">
         <f t="shared" si="6"/>
         <v>173</v>
@@ -9363,7 +9514,7 @@
       </c>
       <c r="N174" s="53"/>
     </row>
-    <row r="175" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="175" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="41">
         <f t="shared" si="6"/>
         <v>174</v>
@@ -9392,7 +9543,7 @@
       </c>
       <c r="N175" s="53"/>
     </row>
-    <row r="176" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="176" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="41">
         <f t="shared" si="6"/>
         <v>175</v>
@@ -9421,7 +9572,7 @@
       </c>
       <c r="N176" s="53"/>
     </row>
-    <row r="177" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="177" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="41">
         <f t="shared" si="6"/>
         <v>176</v>
@@ -9450,7 +9601,7 @@
       </c>
       <c r="N177" s="53"/>
     </row>
-    <row r="178" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="178" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="41">
         <f t="shared" si="6"/>
         <v>177</v>
@@ -9479,7 +9630,7 @@
       </c>
       <c r="N178" s="53"/>
     </row>
-    <row r="179" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="179" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="41">
         <f t="shared" si="6"/>
         <v>178</v>
@@ -9506,7 +9657,7 @@
       </c>
       <c r="N179" s="53"/>
     </row>
-    <row r="180" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="180" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="41">
         <f t="shared" si="6"/>
         <v>179</v>
@@ -9533,7 +9684,7 @@
       </c>
       <c r="N180" s="54"/>
     </row>
-    <row r="181" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="181" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="41">
         <f t="shared" ref="A181:A212" si="7">IF($B181="","",ROW()-1)</f>
         <v>180</v>
@@ -9562,7 +9713,7 @@
       </c>
       <c r="N181" s="53"/>
     </row>
-    <row r="182" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="182" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="41">
         <f t="shared" si="7"/>
         <v>181</v>
@@ -9591,7 +9742,7 @@
       </c>
       <c r="N182" s="55"/>
     </row>
-    <row r="183" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="183" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="41">
         <f t="shared" si="7"/>
         <v>182</v>
@@ -9618,7 +9769,7 @@
       </c>
       <c r="N183" s="56"/>
     </row>
-    <row r="184" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="184" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="41">
         <f t="shared" si="7"/>
         <v>183</v>
@@ -9647,7 +9798,7 @@
       </c>
       <c r="N184" s="57"/>
     </row>
-    <row r="185" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="185" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="41">
         <f t="shared" si="7"/>
         <v>184</v>
@@ -9676,7 +9827,7 @@
       </c>
       <c r="N185" s="56"/>
     </row>
-    <row r="186" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="186" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="41">
         <f t="shared" si="7"/>
         <v>185</v>
@@ -9705,7 +9856,7 @@
       </c>
       <c r="N186" s="57"/>
     </row>
-    <row r="187" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="187" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="41">
         <f t="shared" si="7"/>
         <v>186</v>
@@ -9734,7 +9885,7 @@
       </c>
       <c r="N187" s="56"/>
     </row>
-    <row r="188" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="188" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="41">
         <f t="shared" si="7"/>
         <v>187</v>
@@ -9763,7 +9914,7 @@
       </c>
       <c r="N188" s="57"/>
     </row>
-    <row r="189" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="189" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="41">
         <f t="shared" si="7"/>
         <v>188</v>
@@ -9792,7 +9943,7 @@
       </c>
       <c r="N189" s="56"/>
     </row>
-    <row r="190" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="190" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="41">
         <f t="shared" si="7"/>
         <v>189</v>
@@ -9821,7 +9972,7 @@
       </c>
       <c r="N190" s="57"/>
     </row>
-    <row r="191" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="191" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="41">
         <f t="shared" si="7"/>
         <v>190</v>
@@ -9850,7 +10001,7 @@
       </c>
       <c r="N191" s="56"/>
     </row>
-    <row r="192" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="192" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="41">
         <f t="shared" si="7"/>
         <v>191</v>
@@ -9879,7 +10030,7 @@
       </c>
       <c r="N192" s="57"/>
     </row>
-    <row r="193" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="193" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="41">
         <f t="shared" si="7"/>
         <v>192</v>
@@ -9906,7 +10057,7 @@
       </c>
       <c r="N193" s="56"/>
     </row>
-    <row r="194" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="194" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="41">
         <f t="shared" si="7"/>
         <v>193</v>
@@ -9935,7 +10086,7 @@
       </c>
       <c r="N194" s="57"/>
     </row>
-    <row r="195" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="195" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="41">
         <f t="shared" si="7"/>
         <v>194</v>
@@ -9964,7 +10115,7 @@
       </c>
       <c r="N195" s="56"/>
     </row>
-    <row r="196" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="196" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="41">
         <f t="shared" si="7"/>
         <v>195</v>
@@ -9997,7 +10148,7 @@
       </c>
       <c r="N196" s="57"/>
     </row>
-    <row r="197" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="197" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="41">
         <f t="shared" si="7"/>
         <v>196</v>
@@ -10030,7 +10181,7 @@
       </c>
       <c r="N197" s="56"/>
     </row>
-    <row r="198" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="198" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="41">
         <f t="shared" si="7"/>
         <v>197</v>
@@ -10063,7 +10214,7 @@
       </c>
       <c r="N198" s="57"/>
     </row>
-    <row r="199" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="199" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="41">
         <f t="shared" si="7"/>
         <v>198</v>
@@ -10096,7 +10247,7 @@
       </c>
       <c r="N199" s="56"/>
     </row>
-    <row r="200" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="200" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="41">
         <f t="shared" si="7"/>
         <v>199</v>
@@ -10129,7 +10280,7 @@
       </c>
       <c r="N200" s="57"/>
     </row>
-    <row r="201" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="201" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="41">
         <f t="shared" si="7"/>
         <v>200</v>
@@ -10164,7 +10315,7 @@
       </c>
       <c r="N201" s="56"/>
     </row>
-    <row r="202" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="202" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="41">
         <f t="shared" si="7"/>
         <v>201</v>
@@ -10197,7 +10348,7 @@
       </c>
       <c r="N202" s="57"/>
     </row>
-    <row r="203" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="203" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="41">
         <f t="shared" si="7"/>
         <v>202</v>
@@ -10226,7 +10377,7 @@
       </c>
       <c r="N203" s="56"/>
     </row>
-    <row r="204" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="204" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="41">
         <f t="shared" si="7"/>
         <v>203</v>
@@ -10255,7 +10406,7 @@
       </c>
       <c r="N204" s="57"/>
     </row>
-    <row r="205" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="205" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="41">
         <f t="shared" si="7"/>
         <v>204</v>
@@ -10284,7 +10435,7 @@
       </c>
       <c r="N205" s="56"/>
     </row>
-    <row r="206" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="206" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="41">
         <f t="shared" si="7"/>
         <v>205</v>
@@ -10313,7 +10464,7 @@
       </c>
       <c r="N206" s="57"/>
     </row>
-    <row r="207" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="207" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="41">
         <f t="shared" si="7"/>
         <v>206</v>
@@ -10342,7 +10493,7 @@
       </c>
       <c r="N207" s="56"/>
     </row>
-    <row r="208" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="208" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="41">
         <f t="shared" si="7"/>
         <v>207</v>
@@ -10371,7 +10522,7 @@
       </c>
       <c r="N208" s="57"/>
     </row>
-    <row r="209" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="209" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="41">
         <f t="shared" si="7"/>
         <v>208</v>
@@ -10400,7 +10551,7 @@
       </c>
       <c r="N209" s="56"/>
     </row>
-    <row r="210" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="210" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="41">
         <f t="shared" si="7"/>
         <v>209</v>
@@ -10431,7 +10582,7 @@
       </c>
       <c r="N210" s="57"/>
     </row>
-    <row r="211" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="211" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="41">
         <f t="shared" si="7"/>
         <v>210</v>
@@ -10458,7 +10609,7 @@
       </c>
       <c r="N211" s="56"/>
     </row>
-    <row r="212" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="212" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="41">
         <f t="shared" si="7"/>
         <v>211</v>
@@ -10485,9 +10636,9 @@
       </c>
       <c r="N212" s="57"/>
     </row>
-    <row r="213" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="213" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="41">
-        <f t="shared" ref="A213:A248" si="8">IF($B213="","",ROW()-1)</f>
+        <f t="shared" ref="A213:A247" si="8">IF($B213="","",ROW()-1)</f>
         <v>212</v>
       </c>
       <c r="B213" s="9" t="s">
@@ -10514,7 +10665,7 @@
       </c>
       <c r="N213" s="56"/>
     </row>
-    <row r="214" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="214" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="41">
         <f t="shared" si="8"/>
         <v>213</v>
@@ -10543,7 +10694,7 @@
       </c>
       <c r="N214" s="57"/>
     </row>
-    <row r="215" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="215" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="41">
         <f t="shared" si="8"/>
         <v>214</v>
@@ -10572,7 +10723,7 @@
       </c>
       <c r="N215" s="56"/>
     </row>
-    <row r="216" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="216" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="41">
         <f t="shared" si="8"/>
         <v>215</v>
@@ -10601,7 +10752,7 @@
       </c>
       <c r="N216" s="57"/>
     </row>
-    <row r="217" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="217" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="41">
         <f t="shared" si="8"/>
         <v>216</v>
@@ -10630,7 +10781,7 @@
       </c>
       <c r="N217" s="56"/>
     </row>
-    <row r="218" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="218" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="41">
         <f t="shared" si="8"/>
         <v>217</v>
@@ -10659,7 +10810,7 @@
       </c>
       <c r="N218" s="57"/>
     </row>
-    <row r="219" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="219" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="41">
         <f t="shared" si="8"/>
         <v>218</v>
@@ -10688,7 +10839,7 @@
       </c>
       <c r="N219" s="56"/>
     </row>
-    <row r="220" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="220" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="41">
         <f t="shared" si="8"/>
         <v>219</v>
@@ -10717,7 +10868,7 @@
       </c>
       <c r="N220" s="57"/>
     </row>
-    <row r="221" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="221" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="41">
         <f t="shared" si="8"/>
         <v>220</v>
@@ -10746,7 +10897,7 @@
       </c>
       <c r="N221" s="56"/>
     </row>
-    <row r="222" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="222" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="41">
         <f t="shared" si="8"/>
         <v>221</v>
@@ -10775,7 +10926,7 @@
       </c>
       <c r="N222" s="57"/>
     </row>
-    <row r="223" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="223" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="41">
         <f t="shared" si="8"/>
         <v>222</v>
@@ -10804,7 +10955,7 @@
       </c>
       <c r="N223" s="56"/>
     </row>
-    <row r="224" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="224" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="41">
         <f t="shared" si="8"/>
         <v>223</v>
@@ -10833,7 +10984,7 @@
       </c>
       <c r="N224" s="57"/>
     </row>
-    <row r="225" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="225" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="41">
         <f t="shared" si="8"/>
         <v>224</v>
@@ -10862,7 +11013,7 @@
       </c>
       <c r="N225" s="56"/>
     </row>
-    <row r="226" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="226" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="41">
         <f t="shared" si="8"/>
         <v>225</v>
@@ -10891,7 +11042,7 @@
       </c>
       <c r="N226" s="57"/>
     </row>
-    <row r="227" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="227" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="41">
         <f t="shared" si="8"/>
         <v>226</v>
@@ -10920,7 +11071,7 @@
       </c>
       <c r="N227" s="56"/>
     </row>
-    <row r="228" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="228" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="41">
         <f t="shared" si="8"/>
         <v>227</v>
@@ -10947,7 +11098,7 @@
       </c>
       <c r="N228" s="57"/>
     </row>
-    <row r="229" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="229" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="41">
         <f t="shared" si="8"/>
         <v>228</v>
@@ -10976,7 +11127,7 @@
       </c>
       <c r="N229" s="56"/>
     </row>
-    <row r="230" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="230" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="41">
         <f t="shared" si="8"/>
         <v>229</v>
@@ -11005,7 +11156,7 @@
       </c>
       <c r="N230" s="57"/>
     </row>
-    <row r="231" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="231" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="41">
         <f t="shared" si="8"/>
         <v>230</v>
@@ -11034,7 +11185,7 @@
       </c>
       <c r="N231" s="56"/>
     </row>
-    <row r="232" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="232" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="41">
         <f t="shared" si="8"/>
         <v>231</v>
@@ -11063,7 +11214,7 @@
       </c>
       <c r="N232" s="57"/>
     </row>
-    <row r="233" spans="1:14" ht="31.9" customHeight="1" thickBot="1">
+    <row r="233" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="41">
         <f t="shared" si="8"/>
         <v>232</v>
@@ -11092,7 +11243,7 @@
       </c>
       <c r="N233" s="58"/>
     </row>
-    <row r="234" spans="1:14" ht="15" thickBot="1">
+    <row r="234" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="41">
         <f t="shared" si="8"/>
         <v>233</v>
@@ -11123,7 +11274,7 @@
       </c>
       <c r="N234" s="59"/>
     </row>
-    <row r="235" spans="1:14" ht="15" thickBot="1">
+    <row r="235" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="41">
         <f t="shared" si="8"/>
         <v>234</v>
@@ -11152,7 +11303,7 @@
       </c>
       <c r="N235" s="60"/>
     </row>
-    <row r="236" spans="1:14" ht="15" thickBot="1">
+    <row r="236" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="41">
         <f t="shared" si="8"/>
         <v>235</v>
@@ -11181,7 +11332,7 @@
       </c>
       <c r="N236" s="61"/>
     </row>
-    <row r="237" spans="1:14" ht="29.45" thickBot="1">
+    <row r="237" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="41">
         <f t="shared" si="8"/>
         <v>236</v>
@@ -11212,7 +11363,7 @@
       </c>
       <c r="N237" s="60"/>
     </row>
-    <row r="238" spans="1:14" ht="15" thickBot="1">
+    <row r="238" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="41">
         <f t="shared" si="8"/>
         <v>237</v>
@@ -11241,7 +11392,7 @@
       </c>
       <c r="N238" s="61"/>
     </row>
-    <row r="239" spans="1:14" ht="15" thickBot="1">
+    <row r="239" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="41">
         <f t="shared" si="8"/>
         <v>238</v>
@@ -11270,7 +11421,7 @@
       </c>
       <c r="N239" s="60"/>
     </row>
-    <row r="240" spans="1:14" ht="29.45" thickBot="1">
+    <row r="240" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="41">
         <f t="shared" si="8"/>
         <v>239</v>
@@ -11299,7 +11450,7 @@
       </c>
       <c r="N240" s="61"/>
     </row>
-    <row r="241" spans="1:14" ht="15" thickBot="1">
+    <row r="241" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="41">
         <f t="shared" si="8"/>
         <v>240</v>
@@ -11330,7 +11481,7 @@
       </c>
       <c r="N241" s="60"/>
     </row>
-    <row r="242" spans="1:14" ht="15" thickBot="1">
+    <row r="242" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="41">
         <f t="shared" si="8"/>
         <v>241</v>
@@ -11359,7 +11510,7 @@
       </c>
       <c r="N242" s="61"/>
     </row>
-    <row r="243" spans="1:14" ht="15" thickBot="1">
+    <row r="243" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="41">
         <f t="shared" si="8"/>
         <v>242</v>
@@ -11388,7 +11539,7 @@
       </c>
       <c r="N243" s="60"/>
     </row>
-    <row r="244" spans="1:14" ht="15" thickBot="1">
+    <row r="244" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="41">
         <f t="shared" si="8"/>
         <v>243</v>
@@ -11421,7 +11572,7 @@
       </c>
       <c r="N244" s="61"/>
     </row>
-    <row r="245" spans="1:14" ht="15" thickBot="1">
+    <row r="245" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="41">
         <f t="shared" si="8"/>
         <v>244</v>
@@ -11454,7 +11605,7 @@
       </c>
       <c r="N245" s="60"/>
     </row>
-    <row r="246" spans="1:14" ht="29.45" thickBot="1">
+    <row r="246" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="150">
         <f t="shared" si="8"/>
         <v>245</v>
@@ -11487,7 +11638,7 @@
       </c>
       <c r="N246" s="61"/>
     </row>
-    <row r="247" spans="1:14" ht="29.45" thickBot="1">
+    <row r="247" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="151">
         <f t="shared" si="8"/>
         <v>246</v>
@@ -11518,9 +11669,9 @@
       <c r="M247" s="148" t="s">
         <v>64</v>
       </c>
-      <c r="N247" s="155"/>
-    </row>
-    <row r="248" spans="1:14" ht="29.45" thickBot="1">
+      <c r="N247" s="152"/>
+    </row>
+    <row r="248" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" s="151">
         <f>IF($B248="","",ROW()-1)</f>
         <v>247</v>
@@ -11551,9 +11702,9 @@
       <c r="M248" s="148" t="s">
         <v>64</v>
       </c>
-      <c r="N248" s="155"/>
-    </row>
-    <row r="249" spans="1:14" ht="15" thickBot="1">
+      <c r="N248" s="152"/>
+    </row>
+    <row r="249" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" s="150">
         <f t="shared" ref="A249:A273" si="9">IF($B249="","",ROW()-1)</f>
         <v>248</v>
@@ -11587,61 +11738,61 @@
       <c r="L249" s="106"/>
       <c r="M249" s="112"/>
     </row>
-    <row r="250" spans="1:14" ht="43.9" thickBot="1">
+    <row r="250" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" s="151">
         <f t="shared" si="9"/>
         <v>249</v>
       </c>
-      <c r="B250" s="156" t="s">
+      <c r="B250" s="153" t="s">
         <v>503</v>
       </c>
-      <c r="C250" s="157" t="s">
+      <c r="C250" s="154" t="s">
         <v>504</v>
       </c>
-      <c r="D250" s="157" t="s">
+      <c r="D250" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="E250" s="158"/>
+      <c r="E250" s="155"/>
       <c r="F250" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G250" s="158"/>
-      <c r="H250" s="158"/>
-      <c r="I250" s="159"/>
-      <c r="J250" s="159"/>
-      <c r="K250" s="157"/>
-      <c r="L250" s="157"/>
-      <c r="M250" s="158"/>
-      <c r="N250" s="155"/>
-    </row>
-    <row r="251" spans="1:14" ht="29.45" thickBot="1">
+      <c r="G250" s="155"/>
+      <c r="H250" s="155"/>
+      <c r="I250" s="156"/>
+      <c r="J250" s="156"/>
+      <c r="K250" s="154"/>
+      <c r="L250" s="154"/>
+      <c r="M250" s="155"/>
+      <c r="N250" s="152"/>
+    </row>
+    <row r="251" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="151">
         <f t="shared" si="9"/>
         <v>250</v>
       </c>
-      <c r="B251" s="156" t="s">
+      <c r="B251" s="153" t="s">
         <v>505</v>
       </c>
-      <c r="C251" s="157" t="s">
+      <c r="C251" s="154" t="s">
         <v>506</v>
       </c>
-      <c r="D251" s="157" t="s">
+      <c r="D251" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="E251" s="158"/>
+      <c r="E251" s="155"/>
       <c r="F251" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G251" s="158"/>
-      <c r="H251" s="158"/>
-      <c r="I251" s="159"/>
-      <c r="J251" s="159"/>
-      <c r="K251" s="157"/>
-      <c r="L251" s="157"/>
-      <c r="M251" s="158"/>
-      <c r="N251" s="155"/>
-    </row>
-    <row r="252" spans="1:14" ht="29.45" thickBot="1">
+      <c r="G251" s="155"/>
+      <c r="H251" s="155"/>
+      <c r="I251" s="156"/>
+      <c r="J251" s="156"/>
+      <c r="K251" s="154"/>
+      <c r="L251" s="154"/>
+      <c r="M251" s="155"/>
+      <c r="N251" s="152"/>
+    </row>
+    <row r="252" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" s="41">
         <f t="shared" si="9"/>
         <v>251</v>
@@ -11658,7 +11809,7 @@
       <c r="I252" s="42"/>
       <c r="J252" s="42"/>
     </row>
-    <row r="253" spans="1:14" ht="29.45" thickBot="1">
+    <row r="253" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="150">
         <f t="shared" si="9"/>
         <v>252</v>
@@ -11688,109 +11839,109 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="43.9" thickBot="1">
+    <row r="254" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="151">
         <f t="shared" si="9"/>
         <v>253</v>
       </c>
-      <c r="B254" s="156" t="s">
+      <c r="B254" s="153" t="s">
         <v>511</v>
       </c>
-      <c r="C254" s="157"/>
-      <c r="D254" s="157" t="s">
+      <c r="C254" s="154"/>
+      <c r="D254" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="E254" s="158"/>
+      <c r="E254" s="155"/>
       <c r="F254" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G254" s="158"/>
-      <c r="H254" s="158"/>
-      <c r="I254" s="159"/>
-      <c r="J254" s="159"/>
-      <c r="K254" s="157"/>
-      <c r="L254" s="157"/>
-      <c r="M254" s="158"/>
-      <c r="N254" s="155"/>
-    </row>
-    <row r="255" spans="1:14" ht="29.45" thickBot="1">
+      <c r="G254" s="155"/>
+      <c r="H254" s="155"/>
+      <c r="I254" s="156"/>
+      <c r="J254" s="156"/>
+      <c r="K254" s="154"/>
+      <c r="L254" s="154"/>
+      <c r="M254" s="155"/>
+      <c r="N254" s="152"/>
+    </row>
+    <row r="255" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="151">
         <f t="shared" si="9"/>
         <v>254</v>
       </c>
-      <c r="B255" s="156" t="s">
+      <c r="B255" s="153" t="s">
         <v>512</v>
       </c>
-      <c r="C255" s="157"/>
-      <c r="D255" s="157" t="s">
+      <c r="C255" s="154"/>
+      <c r="D255" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="E255" s="158"/>
+      <c r="E255" s="155"/>
       <c r="F255" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G255" s="158"/>
-      <c r="H255" s="158"/>
-      <c r="I255" s="159"/>
-      <c r="J255" s="159"/>
-      <c r="K255" s="157"/>
-      <c r="L255" s="157"/>
-      <c r="M255" s="158"/>
-      <c r="N255" s="155"/>
-    </row>
-    <row r="256" spans="1:14" ht="29.45" thickBot="1">
+      <c r="G255" s="155"/>
+      <c r="H255" s="155"/>
+      <c r="I255" s="156"/>
+      <c r="J255" s="156"/>
+      <c r="K255" s="154"/>
+      <c r="L255" s="154"/>
+      <c r="M255" s="155"/>
+      <c r="N255" s="152"/>
+    </row>
+    <row r="256" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="151">
         <f t="shared" si="9"/>
         <v>255</v>
       </c>
-      <c r="B256" s="156" t="s">
+      <c r="B256" s="153" t="s">
         <v>513</v>
       </c>
-      <c r="C256" s="157" t="s">
+      <c r="C256" s="154" t="s">
         <v>514</v>
       </c>
-      <c r="D256" s="157" t="s">
+      <c r="D256" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="E256" s="158"/>
+      <c r="E256" s="155"/>
       <c r="F256" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G256" s="158"/>
-      <c r="H256" s="158"/>
-      <c r="I256" s="159"/>
-      <c r="J256" s="159"/>
-      <c r="K256" s="157"/>
-      <c r="L256" s="157"/>
-      <c r="M256" s="158"/>
-      <c r="N256" s="155"/>
-    </row>
-    <row r="257" spans="1:14" ht="15" thickBot="1">
+      <c r="G256" s="155"/>
+      <c r="H256" s="155"/>
+      <c r="I256" s="156"/>
+      <c r="J256" s="156"/>
+      <c r="K256" s="154"/>
+      <c r="L256" s="154"/>
+      <c r="M256" s="155"/>
+      <c r="N256" s="152"/>
+    </row>
+    <row r="257" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="151">
         <f t="shared" si="9"/>
         <v>256</v>
       </c>
-      <c r="B257" s="156" t="s">
+      <c r="B257" s="153" t="s">
         <v>515</v>
       </c>
-      <c r="C257" s="157"/>
-      <c r="D257" s="157" t="s">
+      <c r="C257" s="154"/>
+      <c r="D257" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="E257" s="158"/>
+      <c r="E257" s="155"/>
       <c r="F257" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G257" s="158"/>
-      <c r="H257" s="158"/>
-      <c r="I257" s="159"/>
-      <c r="J257" s="159"/>
-      <c r="K257" s="157"/>
-      <c r="L257" s="157"/>
-      <c r="M257" s="158"/>
-      <c r="N257" s="155"/>
-    </row>
-    <row r="258" spans="1:14" ht="29.45" thickBot="1">
+      <c r="G257" s="155"/>
+      <c r="H257" s="155"/>
+      <c r="I257" s="156"/>
+      <c r="J257" s="156"/>
+      <c r="K257" s="154"/>
+      <c r="L257" s="154"/>
+      <c r="M257" s="155"/>
+      <c r="N257" s="152"/>
+    </row>
+    <row r="258" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="151">
         <f t="shared" si="9"/>
         <v>257</v>
@@ -11815,7 +11966,7 @@
       <c r="M258" s="12"/>
       <c r="N258" s="136"/>
     </row>
-    <row r="259" spans="1:14" ht="29.45" thickBot="1">
+    <row r="259" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="41">
         <f t="shared" si="9"/>
         <v>258</v>
@@ -11844,7 +11995,7 @@
       <c r="M259" s="119"/>
       <c r="N259" s="123"/>
     </row>
-    <row r="260" spans="1:14" ht="15" thickBot="1">
+    <row r="260" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="41">
         <f t="shared" si="9"/>
         <v>259</v>
@@ -11873,7 +12024,7 @@
       <c r="M260" s="124"/>
       <c r="N260" s="121"/>
     </row>
-    <row r="261" spans="1:14" ht="43.9" thickBot="1">
+    <row r="261" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="41">
         <f t="shared" si="9"/>
         <v>260</v>
@@ -11900,7 +12051,7 @@
       <c r="M261" s="119"/>
       <c r="N261" s="123"/>
     </row>
-    <row r="262" spans="1:14" ht="29.45" thickBot="1">
+    <row r="262" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="41">
         <f t="shared" si="9"/>
         <v>261</v>
@@ -11929,7 +12080,7 @@
       <c r="M262" s="124"/>
       <c r="N262" s="121"/>
     </row>
-    <row r="263" spans="1:14" ht="15" thickBot="1">
+    <row r="263" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="41">
         <f t="shared" si="9"/>
         <v>262</v>
@@ -11956,7 +12107,7 @@
       <c r="M263" s="119"/>
       <c r="N263" s="123"/>
     </row>
-    <row r="264" spans="1:14" ht="58.15" thickBot="1">
+    <row r="264" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="41">
         <f t="shared" si="9"/>
         <v>263</v>
@@ -11983,7 +12134,7 @@
       <c r="M264" s="124"/>
       <c r="N264" s="121"/>
     </row>
-    <row r="265" spans="1:14" ht="43.9" thickBot="1">
+    <row r="265" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="41">
         <f t="shared" si="9"/>
         <v>264</v>
@@ -12014,7 +12165,7 @@
       <c r="M265" s="119"/>
       <c r="N265" s="123"/>
     </row>
-    <row r="266" spans="1:14" ht="15" thickBot="1">
+    <row r="266" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="41">
         <f t="shared" si="9"/>
         <v>265</v>
@@ -12043,7 +12194,7 @@
       <c r="M266" s="124"/>
       <c r="N266" s="121"/>
     </row>
-    <row r="267" spans="1:14" ht="29.45" thickBot="1">
+    <row r="267" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="41">
         <f t="shared" si="9"/>
         <v>266</v>
@@ -12070,7 +12221,7 @@
       <c r="M267" s="119"/>
       <c r="N267" s="123"/>
     </row>
-    <row r="268" spans="1:14" ht="43.9" thickBot="1">
+    <row r="268" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="41">
         <f t="shared" si="9"/>
         <v>267</v>
@@ -12097,7 +12248,7 @@
       <c r="M268" s="124"/>
       <c r="N268" s="121"/>
     </row>
-    <row r="269" spans="1:14" ht="72.599999999999994" thickBot="1">
+    <row r="269" spans="1:14" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="41">
         <f t="shared" si="9"/>
         <v>268</v>
@@ -12124,7 +12275,7 @@
       <c r="M269" s="119"/>
       <c r="N269" s="123"/>
     </row>
-    <row r="270" spans="1:14" ht="58.15" thickBot="1">
+    <row r="270" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="41">
         <f t="shared" si="9"/>
         <v>269</v>
@@ -12151,7 +12302,7 @@
       <c r="M270" s="124"/>
       <c r="N270" s="121"/>
     </row>
-    <row r="271" spans="1:14" ht="29.45" thickBot="1">
+    <row r="271" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="41">
         <f t="shared" si="9"/>
         <v>270</v>
@@ -12178,7 +12329,7 @@
       <c r="M271" s="119"/>
       <c r="N271" s="123"/>
     </row>
-    <row r="272" spans="1:14" ht="29.45" thickBot="1">
+    <row r="272" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" s="150">
         <f t="shared" si="9"/>
         <v>271</v>
@@ -12205,2934 +12356,3060 @@
       <c r="M272" s="145"/>
       <c r="N272" s="144"/>
     </row>
-    <row r="273" spans="1:14" ht="15" thickBot="1">
-      <c r="A273" s="151">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A273" s="169">
         <f t="shared" si="9"/>
         <v>272</v>
       </c>
-      <c r="B273" s="156" t="s">
+      <c r="B273" s="160" t="s">
         <v>546</v>
       </c>
-      <c r="C273" s="157" t="s">
+      <c r="C273" s="161" t="s">
         <v>547</v>
       </c>
-      <c r="D273" s="157" t="s">
+      <c r="D273" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="E273" s="158" t="s">
+      <c r="E273" s="162" t="s">
+        <v>82</v>
+      </c>
+      <c r="F273" s="163" t="s">
+        <v>73</v>
+      </c>
+      <c r="G273" s="162"/>
+      <c r="H273" s="162"/>
+      <c r="I273" s="164">
+        <v>46226</v>
+      </c>
+      <c r="J273" s="164">
+        <v>46220</v>
+      </c>
+      <c r="K273" s="161"/>
+      <c r="L273" s="161"/>
+      <c r="M273" s="162" t="s">
+        <v>97</v>
+      </c>
+      <c r="N273" s="165"/>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A274" s="170">
+        <f>IF($B274="","",ROW()-1)</f>
+        <v>273</v>
+      </c>
+      <c r="B274" s="168" t="s">
+        <v>551</v>
+      </c>
+      <c r="C274" s="166" t="s">
+        <v>552</v>
+      </c>
+      <c r="D274" s="166" t="s">
+        <v>79</v>
+      </c>
+      <c r="E274" s="167" t="s">
+        <v>72</v>
+      </c>
+      <c r="F274" s="167" t="s">
+        <v>73</v>
+      </c>
+      <c r="G274" s="167"/>
+      <c r="H274" s="167">
+        <v>4</v>
+      </c>
+      <c r="I274" s="172">
+        <v>46219</v>
+      </c>
+      <c r="J274" s="172">
+        <v>46219</v>
+      </c>
+      <c r="K274" s="166"/>
+      <c r="L274" s="166"/>
+      <c r="M274" s="167" t="s">
+        <v>97</v>
+      </c>
+      <c r="N274" s="166"/>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A275" s="170">
+        <f>IF($B275="","",ROW()-1)</f>
+        <v>274</v>
+      </c>
+      <c r="B275" s="168" t="s">
+        <v>553</v>
+      </c>
+      <c r="C275" s="166" t="s">
+        <v>554</v>
+      </c>
+      <c r="D275" s="166" t="s">
+        <v>67</v>
+      </c>
+      <c r="E275" s="167" t="s">
         <v>337</v>
       </c>
-      <c r="F273" s="137" t="s">
+      <c r="F275" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="G273" s="158"/>
-      <c r="H273" s="158"/>
-      <c r="I273" s="159">
-        <v>46226</v>
-      </c>
-      <c r="J273" s="159">
-        <v>46220</v>
-      </c>
-      <c r="K273" s="157"/>
-      <c r="L273" s="157"/>
-      <c r="M273" s="158" t="s">
-        <v>97</v>
-      </c>
-      <c r="N273" s="155"/>
-    </row>
-    <row r="274" spans="1:14">
-      <c r="I274" s="42"/>
-      <c r="J274" s="42"/>
-    </row>
-    <row r="275" spans="1:14">
-      <c r="I275" s="42"/>
-      <c r="J275" s="42"/>
-    </row>
-    <row r="276" spans="1:14">
-      <c r="I276" s="42"/>
-      <c r="J276" s="42"/>
-    </row>
-    <row r="277" spans="1:14">
-      <c r="I277" s="42"/>
-      <c r="J277" s="42"/>
-    </row>
-    <row r="278" spans="1:14">
+      <c r="G275" s="167"/>
+      <c r="H275" s="167"/>
+      <c r="I275" s="172">
+        <v>46219</v>
+      </c>
+      <c r="J275" s="172">
+        <v>46221</v>
+      </c>
+      <c r="K275" s="166"/>
+      <c r="L275" s="166"/>
+      <c r="M275" s="167" t="s">
+        <v>64</v>
+      </c>
+      <c r="N275" s="166"/>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A276" s="170">
+        <f>IF($B276="","",ROW()-1)</f>
+        <v>275</v>
+      </c>
+      <c r="B276" s="168" t="s">
+        <v>555</v>
+      </c>
+      <c r="C276" s="166" t="s">
+        <v>556</v>
+      </c>
+      <c r="D276" s="166" t="s">
+        <v>79</v>
+      </c>
+      <c r="E276" s="167" t="s">
+        <v>82</v>
+      </c>
+      <c r="F276" s="167" t="s">
+        <v>73</v>
+      </c>
+      <c r="G276" s="167"/>
+      <c r="H276" s="167">
+        <v>1</v>
+      </c>
+      <c r="I276" s="172">
+        <v>46218</v>
+      </c>
+      <c r="J276" s="172">
+        <v>46218</v>
+      </c>
+      <c r="K276" s="166"/>
+      <c r="L276" s="166"/>
+      <c r="M276" s="167"/>
+      <c r="N276" s="166"/>
+    </row>
+    <row r="277" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A277" s="171">
+        <f>IF($B277="","",ROW()-1)</f>
+        <v>276</v>
+      </c>
+      <c r="B277" s="168" t="s">
+        <v>557</v>
+      </c>
+      <c r="C277" s="166" t="s">
+        <v>558</v>
+      </c>
+      <c r="D277" s="166" t="s">
+        <v>79</v>
+      </c>
+      <c r="E277" s="167" t="s">
+        <v>337</v>
+      </c>
+      <c r="F277" s="167" t="s">
+        <v>63</v>
+      </c>
+      <c r="G277" s="167"/>
+      <c r="H277" s="167">
+        <v>3</v>
+      </c>
+      <c r="I277" s="172">
+        <v>46218</v>
+      </c>
+      <c r="J277" s="172">
+        <v>46221</v>
+      </c>
+      <c r="K277" s="166"/>
+      <c r="L277" s="166"/>
+      <c r="M277" s="167"/>
+      <c r="N277" s="166"/>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I278" s="42"/>
       <c r="J278" s="42"/>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I279" s="42"/>
       <c r="J279" s="42"/>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I280" s="42"/>
       <c r="J280" s="42"/>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I281" s="42"/>
       <c r="J281" s="42"/>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I282" s="42"/>
       <c r="J282" s="42"/>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I283" s="42"/>
       <c r="J283" s="42"/>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I284" s="42"/>
       <c r="J284" s="42"/>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I285" s="42"/>
       <c r="J285" s="42"/>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I286" s="42"/>
       <c r="J286" s="42"/>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I287" s="42"/>
       <c r="J287" s="42"/>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="I288" s="42"/>
       <c r="J288" s="42"/>
     </row>
-    <row r="289" spans="9:10">
+    <row r="289" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I289" s="42"/>
       <c r="J289" s="42"/>
     </row>
-    <row r="290" spans="9:10">
+    <row r="290" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I290" s="42"/>
       <c r="J290" s="42"/>
     </row>
-    <row r="291" spans="9:10">
+    <row r="291" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I291" s="42"/>
       <c r="J291" s="42"/>
     </row>
-    <row r="292" spans="9:10">
+    <row r="292" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I292" s="42"/>
       <c r="J292" s="42"/>
     </row>
-    <row r="293" spans="9:10">
+    <row r="293" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I293" s="42"/>
       <c r="J293" s="42"/>
     </row>
-    <row r="294" spans="9:10">
+    <row r="294" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I294" s="42"/>
       <c r="J294" s="42"/>
     </row>
-    <row r="295" spans="9:10">
+    <row r="295" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I295" s="42"/>
       <c r="J295" s="42"/>
     </row>
-    <row r="296" spans="9:10">
+    <row r="296" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I296" s="42"/>
       <c r="J296" s="42"/>
     </row>
-    <row r="297" spans="9:10">
+    <row r="297" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I297" s="42"/>
       <c r="J297" s="42"/>
     </row>
-    <row r="298" spans="9:10">
+    <row r="298" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I298" s="42"/>
       <c r="J298" s="42"/>
     </row>
-    <row r="299" spans="9:10">
+    <row r="299" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I299" s="42"/>
       <c r="J299" s="42"/>
     </row>
-    <row r="300" spans="9:10">
+    <row r="300" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I300" s="42"/>
       <c r="J300" s="42"/>
     </row>
-    <row r="301" spans="9:10">
+    <row r="301" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I301" s="42"/>
       <c r="J301" s="42"/>
     </row>
-    <row r="302" spans="9:10">
+    <row r="302" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I302" s="42"/>
       <c r="J302" s="42"/>
     </row>
-    <row r="303" spans="9:10">
+    <row r="303" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I303" s="42"/>
       <c r="J303" s="42"/>
     </row>
-    <row r="304" spans="9:10">
+    <row r="304" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I304" s="42"/>
       <c r="J304" s="42"/>
     </row>
-    <row r="305" spans="9:10">
+    <row r="305" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I305" s="42"/>
       <c r="J305" s="42"/>
     </row>
-    <row r="306" spans="9:10">
+    <row r="306" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I306" s="42"/>
       <c r="J306" s="42"/>
     </row>
-    <row r="307" spans="9:10">
+    <row r="307" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I307" s="42"/>
       <c r="J307" s="42"/>
     </row>
-    <row r="308" spans="9:10">
+    <row r="308" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I308" s="42"/>
       <c r="J308" s="42"/>
     </row>
-    <row r="309" spans="9:10">
+    <row r="309" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I309" s="42"/>
       <c r="J309" s="42"/>
     </row>
-    <row r="310" spans="9:10">
+    <row r="310" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I310" s="42"/>
       <c r="J310" s="42"/>
     </row>
-    <row r="311" spans="9:10">
+    <row r="311" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I311" s="42"/>
       <c r="J311" s="42"/>
     </row>
-    <row r="312" spans="9:10">
+    <row r="312" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I312" s="42"/>
       <c r="J312" s="42"/>
     </row>
-    <row r="313" spans="9:10">
+    <row r="313" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I313" s="42"/>
       <c r="J313" s="42"/>
     </row>
-    <row r="314" spans="9:10">
+    <row r="314" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I314" s="42"/>
       <c r="J314" s="42"/>
     </row>
-    <row r="315" spans="9:10">
+    <row r="315" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I315" s="42"/>
       <c r="J315" s="42"/>
     </row>
-    <row r="316" spans="9:10">
+    <row r="316" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I316" s="42"/>
       <c r="J316" s="42"/>
     </row>
-    <row r="317" spans="9:10">
+    <row r="317" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I317" s="42"/>
       <c r="J317" s="42"/>
     </row>
-    <row r="318" spans="9:10">
+    <row r="318" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I318" s="42"/>
       <c r="J318" s="42"/>
     </row>
-    <row r="319" spans="9:10">
+    <row r="319" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I319" s="42"/>
       <c r="J319" s="42"/>
     </row>
-    <row r="320" spans="9:10">
+    <row r="320" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I320" s="42"/>
       <c r="J320" s="42"/>
     </row>
-    <row r="321" spans="9:10">
+    <row r="321" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I321" s="42"/>
       <c r="J321" s="42"/>
     </row>
-    <row r="322" spans="9:10">
+    <row r="322" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I322" s="42"/>
       <c r="J322" s="42"/>
     </row>
-    <row r="323" spans="9:10">
+    <row r="323" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I323" s="42"/>
       <c r="J323" s="42"/>
     </row>
-    <row r="324" spans="9:10">
+    <row r="324" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I324" s="42"/>
       <c r="J324" s="42"/>
     </row>
-    <row r="325" spans="9:10">
+    <row r="325" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I325" s="42"/>
       <c r="J325" s="42"/>
     </row>
-    <row r="326" spans="9:10">
+    <row r="326" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I326" s="42"/>
       <c r="J326" s="42"/>
     </row>
-    <row r="327" spans="9:10">
+    <row r="327" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I327" s="42"/>
       <c r="J327" s="42"/>
     </row>
-    <row r="328" spans="9:10">
+    <row r="328" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I328" s="42"/>
       <c r="J328" s="42"/>
     </row>
-    <row r="329" spans="9:10">
+    <row r="329" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I329" s="42"/>
       <c r="J329" s="42"/>
     </row>
-    <row r="330" spans="9:10">
+    <row r="330" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I330" s="42"/>
       <c r="J330" s="42"/>
     </row>
-    <row r="331" spans="9:10">
+    <row r="331" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I331" s="42"/>
       <c r="J331" s="42"/>
     </row>
-    <row r="332" spans="9:10">
+    <row r="332" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I332" s="42"/>
       <c r="J332" s="42"/>
     </row>
-    <row r="333" spans="9:10">
+    <row r="333" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I333" s="42"/>
       <c r="J333" s="42"/>
     </row>
-    <row r="334" spans="9:10">
+    <row r="334" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I334" s="42"/>
       <c r="J334" s="42"/>
     </row>
-    <row r="335" spans="9:10">
+    <row r="335" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I335" s="42"/>
       <c r="J335" s="42"/>
     </row>
-    <row r="336" spans="9:10">
+    <row r="336" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I336" s="42"/>
       <c r="J336" s="42"/>
     </row>
-    <row r="337" spans="9:10">
+    <row r="337" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I337" s="42"/>
       <c r="J337" s="42"/>
     </row>
-    <row r="338" spans="9:10">
+    <row r="338" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I338" s="42"/>
       <c r="J338" s="42"/>
     </row>
-    <row r="339" spans="9:10">
+    <row r="339" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I339" s="42"/>
       <c r="J339" s="42"/>
     </row>
-    <row r="340" spans="9:10">
+    <row r="340" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I340" s="42"/>
       <c r="J340" s="42"/>
     </row>
-    <row r="341" spans="9:10">
+    <row r="341" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I341" s="42"/>
       <c r="J341" s="42"/>
     </row>
-    <row r="342" spans="9:10">
+    <row r="342" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I342" s="42"/>
       <c r="J342" s="42"/>
     </row>
-    <row r="343" spans="9:10">
+    <row r="343" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I343" s="42"/>
       <c r="J343" s="42"/>
     </row>
-    <row r="344" spans="9:10">
+    <row r="344" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I344" s="42"/>
       <c r="J344" s="42"/>
     </row>
-    <row r="345" spans="9:10">
+    <row r="345" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I345" s="42"/>
       <c r="J345" s="42"/>
     </row>
-    <row r="346" spans="9:10">
+    <row r="346" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I346" s="42"/>
       <c r="J346" s="42"/>
     </row>
-    <row r="347" spans="9:10">
+    <row r="347" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I347" s="42"/>
       <c r="J347" s="42"/>
     </row>
-    <row r="348" spans="9:10">
+    <row r="348" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I348" s="42"/>
       <c r="J348" s="42"/>
     </row>
-    <row r="349" spans="9:10">
+    <row r="349" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I349" s="42"/>
       <c r="J349" s="42"/>
     </row>
-    <row r="350" spans="9:10">
+    <row r="350" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I350" s="42"/>
       <c r="J350" s="42"/>
     </row>
-    <row r="351" spans="9:10">
+    <row r="351" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I351" s="42"/>
       <c r="J351" s="42"/>
     </row>
-    <row r="352" spans="9:10">
+    <row r="352" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I352" s="42"/>
       <c r="J352" s="42"/>
     </row>
-    <row r="353" spans="9:10">
+    <row r="353" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I353" s="42"/>
       <c r="J353" s="42"/>
     </row>
-    <row r="354" spans="9:10">
+    <row r="354" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I354" s="42"/>
       <c r="J354" s="42"/>
     </row>
-    <row r="355" spans="9:10">
+    <row r="355" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I355" s="42"/>
       <c r="J355" s="42"/>
     </row>
-    <row r="356" spans="9:10">
+    <row r="356" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I356" s="42"/>
       <c r="J356" s="42"/>
     </row>
-    <row r="357" spans="9:10">
+    <row r="357" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I357" s="42"/>
       <c r="J357" s="42"/>
     </row>
-    <row r="358" spans="9:10">
+    <row r="358" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I358" s="42"/>
       <c r="J358" s="42"/>
     </row>
-    <row r="359" spans="9:10">
+    <row r="359" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I359" s="42"/>
       <c r="J359" s="42"/>
     </row>
-    <row r="360" spans="9:10">
+    <row r="360" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I360" s="42"/>
       <c r="J360" s="42"/>
     </row>
-    <row r="361" spans="9:10">
+    <row r="361" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I361" s="42"/>
       <c r="J361" s="42"/>
     </row>
-    <row r="362" spans="9:10">
+    <row r="362" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I362" s="42"/>
       <c r="J362" s="42"/>
     </row>
-    <row r="363" spans="9:10">
+    <row r="363" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I363" s="42"/>
       <c r="J363" s="42"/>
     </row>
-    <row r="364" spans="9:10">
+    <row r="364" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I364" s="42"/>
       <c r="J364" s="42"/>
     </row>
-    <row r="365" spans="9:10">
+    <row r="365" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I365" s="42"/>
       <c r="J365" s="42"/>
     </row>
-    <row r="366" spans="9:10">
+    <row r="366" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I366" s="42"/>
       <c r="J366" s="42"/>
     </row>
-    <row r="367" spans="9:10">
+    <row r="367" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I367" s="42"/>
       <c r="J367" s="42"/>
     </row>
-    <row r="368" spans="9:10">
+    <row r="368" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I368" s="42"/>
       <c r="J368" s="42"/>
     </row>
-    <row r="369" spans="9:10">
+    <row r="369" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I369" s="42"/>
       <c r="J369" s="42"/>
     </row>
-    <row r="370" spans="9:10">
+    <row r="370" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I370" s="42"/>
       <c r="J370" s="42"/>
     </row>
-    <row r="371" spans="9:10">
+    <row r="371" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I371" s="42"/>
       <c r="J371" s="42"/>
     </row>
-    <row r="372" spans="9:10">
+    <row r="372" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I372" s="42"/>
       <c r="J372" s="42"/>
     </row>
-    <row r="373" spans="9:10">
+    <row r="373" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I373" s="42"/>
       <c r="J373" s="42"/>
     </row>
-    <row r="374" spans="9:10">
+    <row r="374" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I374" s="42"/>
       <c r="J374" s="42"/>
     </row>
-    <row r="375" spans="9:10">
+    <row r="375" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I375" s="42"/>
       <c r="J375" s="42"/>
     </row>
-    <row r="376" spans="9:10">
+    <row r="376" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I376" s="42"/>
       <c r="J376" s="42"/>
     </row>
-    <row r="377" spans="9:10">
+    <row r="377" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I377" s="42"/>
       <c r="J377" s="42"/>
     </row>
-    <row r="378" spans="9:10">
+    <row r="378" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I378" s="42"/>
       <c r="J378" s="42"/>
     </row>
-    <row r="379" spans="9:10">
+    <row r="379" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I379" s="42"/>
       <c r="J379" s="42"/>
     </row>
-    <row r="380" spans="9:10">
+    <row r="380" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I380" s="42"/>
       <c r="J380" s="42"/>
     </row>
-    <row r="381" spans="9:10">
+    <row r="381" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I381" s="42"/>
       <c r="J381" s="42"/>
     </row>
-    <row r="382" spans="9:10">
+    <row r="382" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I382" s="42"/>
       <c r="J382" s="42"/>
     </row>
-    <row r="383" spans="9:10">
+    <row r="383" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I383" s="42"/>
       <c r="J383" s="42"/>
     </row>
-    <row r="384" spans="9:10">
+    <row r="384" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I384" s="42"/>
       <c r="J384" s="42"/>
     </row>
-    <row r="385" spans="9:10">
+    <row r="385" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I385" s="42"/>
       <c r="J385" s="42"/>
     </row>
-    <row r="386" spans="9:10">
+    <row r="386" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I386" s="42"/>
       <c r="J386" s="42"/>
     </row>
-    <row r="387" spans="9:10">
+    <row r="387" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I387" s="42"/>
       <c r="J387" s="42"/>
     </row>
-    <row r="388" spans="9:10">
+    <row r="388" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I388" s="42"/>
       <c r="J388" s="42"/>
     </row>
-    <row r="389" spans="9:10">
+    <row r="389" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I389" s="42"/>
       <c r="J389" s="42"/>
     </row>
-    <row r="390" spans="9:10">
+    <row r="390" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I390" s="42"/>
       <c r="J390" s="42"/>
     </row>
-    <row r="391" spans="9:10">
+    <row r="391" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I391" s="42"/>
       <c r="J391" s="42"/>
     </row>
-    <row r="392" spans="9:10">
+    <row r="392" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I392" s="42"/>
       <c r="J392" s="42"/>
     </row>
-    <row r="393" spans="9:10">
+    <row r="393" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I393" s="42"/>
       <c r="J393" s="42"/>
     </row>
-    <row r="394" spans="9:10">
+    <row r="394" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I394" s="42"/>
       <c r="J394" s="42"/>
     </row>
-    <row r="395" spans="9:10">
+    <row r="395" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I395" s="42"/>
       <c r="J395" s="42"/>
     </row>
-    <row r="396" spans="9:10">
+    <row r="396" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I396" s="42"/>
       <c r="J396" s="42"/>
     </row>
-    <row r="397" spans="9:10">
+    <row r="397" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I397" s="42"/>
       <c r="J397" s="42"/>
     </row>
-    <row r="398" spans="9:10">
+    <row r="398" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I398" s="42"/>
       <c r="J398" s="42"/>
     </row>
-    <row r="399" spans="9:10">
+    <row r="399" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I399" s="42"/>
       <c r="J399" s="42"/>
     </row>
-    <row r="400" spans="9:10">
+    <row r="400" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I400" s="42"/>
       <c r="J400" s="42"/>
     </row>
-    <row r="401" spans="9:10">
+    <row r="401" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I401" s="42"/>
       <c r="J401" s="42"/>
     </row>
-    <row r="402" spans="9:10">
+    <row r="402" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I402" s="42"/>
       <c r="J402" s="42"/>
     </row>
-    <row r="403" spans="9:10">
+    <row r="403" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I403" s="42"/>
       <c r="J403" s="42"/>
     </row>
-    <row r="404" spans="9:10">
+    <row r="404" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I404" s="42"/>
       <c r="J404" s="42"/>
     </row>
-    <row r="405" spans="9:10">
+    <row r="405" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I405" s="42"/>
       <c r="J405" s="42"/>
     </row>
-    <row r="406" spans="9:10">
+    <row r="406" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I406" s="42"/>
       <c r="J406" s="42"/>
     </row>
-    <row r="407" spans="9:10">
+    <row r="407" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I407" s="42"/>
       <c r="J407" s="42"/>
     </row>
-    <row r="408" spans="9:10">
+    <row r="408" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I408" s="42"/>
       <c r="J408" s="42"/>
     </row>
-    <row r="409" spans="9:10">
+    <row r="409" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I409" s="42"/>
       <c r="J409" s="42"/>
     </row>
-    <row r="410" spans="9:10">
+    <row r="410" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I410" s="42"/>
       <c r="J410" s="42"/>
     </row>
-    <row r="411" spans="9:10">
+    <row r="411" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I411" s="42"/>
       <c r="J411" s="42"/>
     </row>
-    <row r="412" spans="9:10">
+    <row r="412" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I412" s="42"/>
       <c r="J412" s="42"/>
     </row>
-    <row r="413" spans="9:10">
+    <row r="413" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I413" s="42"/>
       <c r="J413" s="42"/>
     </row>
-    <row r="414" spans="9:10">
+    <row r="414" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I414" s="42"/>
       <c r="J414" s="42"/>
     </row>
-    <row r="415" spans="9:10">
+    <row r="415" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I415" s="42"/>
       <c r="J415" s="42"/>
     </row>
-    <row r="416" spans="9:10">
+    <row r="416" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I416" s="42"/>
       <c r="J416" s="42"/>
     </row>
-    <row r="417" spans="9:10">
+    <row r="417" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I417" s="42"/>
       <c r="J417" s="42"/>
     </row>
-    <row r="418" spans="9:10">
+    <row r="418" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I418" s="42"/>
       <c r="J418" s="42"/>
     </row>
-    <row r="419" spans="9:10">
+    <row r="419" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I419" s="42"/>
       <c r="J419" s="42"/>
     </row>
-    <row r="420" spans="9:10">
+    <row r="420" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I420" s="42"/>
       <c r="J420" s="42"/>
     </row>
-    <row r="421" spans="9:10">
+    <row r="421" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I421" s="42"/>
       <c r="J421" s="42"/>
     </row>
-    <row r="422" spans="9:10">
+    <row r="422" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I422" s="42"/>
       <c r="J422" s="42"/>
     </row>
-    <row r="423" spans="9:10">
+    <row r="423" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I423" s="42"/>
       <c r="J423" s="42"/>
     </row>
-    <row r="424" spans="9:10">
+    <row r="424" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I424" s="42"/>
       <c r="J424" s="42"/>
     </row>
-    <row r="425" spans="9:10">
+    <row r="425" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I425" s="42"/>
       <c r="J425" s="42"/>
     </row>
-    <row r="426" spans="9:10">
+    <row r="426" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I426" s="42"/>
       <c r="J426" s="42"/>
     </row>
-    <row r="427" spans="9:10">
+    <row r="427" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I427" s="42"/>
       <c r="J427" s="42"/>
     </row>
-    <row r="428" spans="9:10">
+    <row r="428" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I428" s="42"/>
       <c r="J428" s="42"/>
     </row>
-    <row r="429" spans="9:10">
+    <row r="429" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I429" s="42"/>
       <c r="J429" s="42"/>
     </row>
-    <row r="430" spans="9:10">
+    <row r="430" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I430" s="42"/>
       <c r="J430" s="42"/>
     </row>
-    <row r="431" spans="9:10">
+    <row r="431" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I431" s="42"/>
       <c r="J431" s="42"/>
     </row>
-    <row r="432" spans="9:10">
+    <row r="432" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I432" s="42"/>
       <c r="J432" s="42"/>
     </row>
-    <row r="433" spans="9:10">
+    <row r="433" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I433" s="42"/>
       <c r="J433" s="42"/>
     </row>
-    <row r="434" spans="9:10">
+    <row r="434" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I434" s="42"/>
       <c r="J434" s="42"/>
     </row>
-    <row r="435" spans="9:10">
+    <row r="435" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I435" s="42"/>
       <c r="J435" s="42"/>
     </row>
-    <row r="436" spans="9:10">
+    <row r="436" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I436" s="42"/>
       <c r="J436" s="42"/>
     </row>
-    <row r="437" spans="9:10">
+    <row r="437" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I437" s="42"/>
       <c r="J437" s="42"/>
     </row>
-    <row r="438" spans="9:10">
+    <row r="438" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I438" s="42"/>
       <c r="J438" s="42"/>
     </row>
-    <row r="439" spans="9:10">
+    <row r="439" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I439" s="42"/>
       <c r="J439" s="42"/>
     </row>
-    <row r="440" spans="9:10">
+    <row r="440" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I440" s="42"/>
       <c r="J440" s="42"/>
     </row>
-    <row r="441" spans="9:10">
+    <row r="441" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I441" s="42"/>
       <c r="J441" s="42"/>
     </row>
-    <row r="442" spans="9:10">
+    <row r="442" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I442" s="42"/>
       <c r="J442" s="42"/>
     </row>
-    <row r="443" spans="9:10">
+    <row r="443" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I443" s="42"/>
       <c r="J443" s="42"/>
     </row>
-    <row r="444" spans="9:10">
+    <row r="444" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I444" s="42"/>
       <c r="J444" s="42"/>
     </row>
-    <row r="445" spans="9:10">
+    <row r="445" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I445" s="42"/>
       <c r="J445" s="42"/>
     </row>
-    <row r="446" spans="9:10">
+    <row r="446" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I446" s="42"/>
       <c r="J446" s="42"/>
     </row>
-    <row r="447" spans="9:10">
+    <row r="447" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I447" s="42"/>
       <c r="J447" s="42"/>
     </row>
-    <row r="448" spans="9:10">
+    <row r="448" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I448" s="42"/>
       <c r="J448" s="42"/>
     </row>
-    <row r="449" spans="9:10">
+    <row r="449" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I449" s="42"/>
       <c r="J449" s="42"/>
     </row>
-    <row r="450" spans="9:10">
+    <row r="450" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I450" s="42"/>
       <c r="J450" s="42"/>
     </row>
-    <row r="451" spans="9:10">
+    <row r="451" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I451" s="42"/>
       <c r="J451" s="42"/>
     </row>
-    <row r="452" spans="9:10">
+    <row r="452" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I452" s="42"/>
       <c r="J452" s="42"/>
     </row>
-    <row r="453" spans="9:10">
+    <row r="453" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I453" s="42"/>
       <c r="J453" s="42"/>
     </row>
-    <row r="454" spans="9:10">
+    <row r="454" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I454" s="42"/>
       <c r="J454" s="42"/>
     </row>
-    <row r="455" spans="9:10">
+    <row r="455" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I455" s="42"/>
       <c r="J455" s="42"/>
     </row>
-    <row r="456" spans="9:10">
+    <row r="456" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I456" s="42"/>
       <c r="J456" s="42"/>
     </row>
-    <row r="457" spans="9:10">
+    <row r="457" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I457" s="42"/>
       <c r="J457" s="42"/>
     </row>
-    <row r="458" spans="9:10">
+    <row r="458" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I458" s="42"/>
       <c r="J458" s="42"/>
     </row>
-    <row r="459" spans="9:10">
+    <row r="459" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I459" s="42"/>
       <c r="J459" s="42"/>
     </row>
-    <row r="460" spans="9:10">
+    <row r="460" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I460" s="42"/>
       <c r="J460" s="42"/>
     </row>
-    <row r="461" spans="9:10">
+    <row r="461" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I461" s="42"/>
       <c r="J461" s="42"/>
     </row>
-    <row r="462" spans="9:10">
+    <row r="462" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I462" s="42"/>
       <c r="J462" s="42"/>
     </row>
-    <row r="463" spans="9:10">
+    <row r="463" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I463" s="42"/>
       <c r="J463" s="42"/>
     </row>
-    <row r="464" spans="9:10">
+    <row r="464" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I464" s="42"/>
       <c r="J464" s="42"/>
     </row>
-    <row r="465" spans="9:10">
+    <row r="465" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I465" s="42"/>
       <c r="J465" s="42"/>
     </row>
-    <row r="466" spans="9:10">
+    <row r="466" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I466" s="42"/>
       <c r="J466" s="42"/>
     </row>
-    <row r="467" spans="9:10">
+    <row r="467" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I467" s="42"/>
       <c r="J467" s="42"/>
     </row>
-    <row r="468" spans="9:10">
+    <row r="468" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I468" s="42"/>
       <c r="J468" s="42"/>
     </row>
-    <row r="469" spans="9:10">
+    <row r="469" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I469" s="42"/>
       <c r="J469" s="42"/>
     </row>
-    <row r="470" spans="9:10">
+    <row r="470" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I470" s="42"/>
       <c r="J470" s="42"/>
     </row>
-    <row r="471" spans="9:10">
+    <row r="471" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I471" s="42"/>
       <c r="J471" s="42"/>
     </row>
-    <row r="472" spans="9:10">
+    <row r="472" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I472" s="42"/>
       <c r="J472" s="42"/>
     </row>
-    <row r="473" spans="9:10">
+    <row r="473" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I473" s="42"/>
       <c r="J473" s="42"/>
     </row>
-    <row r="474" spans="9:10">
+    <row r="474" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I474" s="42"/>
       <c r="J474" s="42"/>
     </row>
-    <row r="475" spans="9:10">
+    <row r="475" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I475" s="42"/>
       <c r="J475" s="42"/>
     </row>
-    <row r="476" spans="9:10">
+    <row r="476" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I476" s="42"/>
       <c r="J476" s="42"/>
     </row>
-    <row r="477" spans="9:10">
+    <row r="477" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I477" s="42"/>
       <c r="J477" s="42"/>
     </row>
-    <row r="478" spans="9:10">
+    <row r="478" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I478" s="42"/>
       <c r="J478" s="42"/>
     </row>
-    <row r="479" spans="9:10">
+    <row r="479" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I479" s="42"/>
       <c r="J479" s="42"/>
     </row>
-    <row r="480" spans="9:10">
+    <row r="480" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I480" s="42"/>
       <c r="J480" s="42"/>
     </row>
-    <row r="481" spans="9:10">
+    <row r="481" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I481" s="42"/>
       <c r="J481" s="42"/>
     </row>
-    <row r="482" spans="9:10">
+    <row r="482" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I482" s="42"/>
       <c r="J482" s="42"/>
     </row>
-    <row r="483" spans="9:10">
+    <row r="483" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I483" s="42"/>
       <c r="J483" s="42"/>
     </row>
-    <row r="484" spans="9:10">
+    <row r="484" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I484" s="42"/>
       <c r="J484" s="42"/>
     </row>
-    <row r="485" spans="9:10">
+    <row r="485" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I485" s="42"/>
       <c r="J485" s="42"/>
     </row>
-    <row r="486" spans="9:10">
+    <row r="486" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I486" s="42"/>
       <c r="J486" s="42"/>
     </row>
-    <row r="487" spans="9:10">
+    <row r="487" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I487" s="42"/>
       <c r="J487" s="42"/>
     </row>
-    <row r="488" spans="9:10">
+    <row r="488" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I488" s="42"/>
       <c r="J488" s="42"/>
     </row>
-    <row r="489" spans="9:10">
+    <row r="489" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I489" s="42"/>
       <c r="J489" s="42"/>
     </row>
-    <row r="490" spans="9:10">
+    <row r="490" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I490" s="42"/>
       <c r="J490" s="42"/>
     </row>
-    <row r="491" spans="9:10">
+    <row r="491" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I491" s="42"/>
       <c r="J491" s="42"/>
     </row>
-    <row r="492" spans="9:10">
+    <row r="492" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I492" s="42"/>
       <c r="J492" s="42"/>
     </row>
-    <row r="493" spans="9:10">
+    <row r="493" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I493" s="42"/>
       <c r="J493" s="42"/>
     </row>
-    <row r="494" spans="9:10">
+    <row r="494" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I494" s="42"/>
       <c r="J494" s="42"/>
     </row>
-    <row r="495" spans="9:10">
+    <row r="495" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I495" s="42"/>
       <c r="J495" s="42"/>
     </row>
-    <row r="496" spans="9:10">
+    <row r="496" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I496" s="42"/>
       <c r="J496" s="42"/>
     </row>
-    <row r="497" spans="9:10">
+    <row r="497" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I497" s="42"/>
       <c r="J497" s="42"/>
     </row>
-    <row r="498" spans="9:10">
+    <row r="498" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I498" s="42"/>
       <c r="J498" s="42"/>
     </row>
-    <row r="499" spans="9:10">
+    <row r="499" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I499" s="42"/>
       <c r="J499" s="42"/>
     </row>
-    <row r="500" spans="9:10">
+    <row r="500" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I500" s="42"/>
       <c r="J500" s="42"/>
     </row>
-    <row r="501" spans="9:10">
+    <row r="501" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I501" s="42"/>
       <c r="J501" s="42"/>
     </row>
-    <row r="502" spans="9:10">
+    <row r="502" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I502" s="42"/>
       <c r="J502" s="42"/>
     </row>
-    <row r="503" spans="9:10">
+    <row r="503" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I503" s="42"/>
       <c r="J503" s="42"/>
     </row>
-    <row r="504" spans="9:10">
+    <row r="504" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I504" s="42"/>
       <c r="J504" s="42"/>
     </row>
-    <row r="505" spans="9:10">
+    <row r="505" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I505" s="42"/>
       <c r="J505" s="42"/>
     </row>
-    <row r="506" spans="9:10">
+    <row r="506" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I506" s="42"/>
       <c r="J506" s="42"/>
     </row>
-    <row r="507" spans="9:10">
+    <row r="507" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I507" s="42"/>
       <c r="J507" s="42"/>
     </row>
-    <row r="508" spans="9:10">
+    <row r="508" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I508" s="42"/>
       <c r="J508" s="42"/>
     </row>
-    <row r="509" spans="9:10">
+    <row r="509" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I509" s="42"/>
       <c r="J509" s="42"/>
     </row>
-    <row r="510" spans="9:10">
+    <row r="510" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I510" s="42"/>
       <c r="J510" s="42"/>
     </row>
-    <row r="511" spans="9:10">
+    <row r="511" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I511" s="42"/>
       <c r="J511" s="42"/>
     </row>
-    <row r="512" spans="9:10">
+    <row r="512" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I512" s="42"/>
       <c r="J512" s="42"/>
     </row>
-    <row r="513" spans="9:10">
+    <row r="513" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I513" s="42"/>
       <c r="J513" s="42"/>
     </row>
-    <row r="514" spans="9:10">
+    <row r="514" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I514" s="42"/>
       <c r="J514" s="42"/>
     </row>
-    <row r="515" spans="9:10">
+    <row r="515" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I515" s="42"/>
       <c r="J515" s="42"/>
     </row>
-    <row r="516" spans="9:10">
+    <row r="516" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I516" s="42"/>
       <c r="J516" s="42"/>
     </row>
-    <row r="517" spans="9:10">
+    <row r="517" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I517" s="42"/>
       <c r="J517" s="42"/>
     </row>
-    <row r="518" spans="9:10">
+    <row r="518" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I518" s="42"/>
       <c r="J518" s="42"/>
     </row>
-    <row r="519" spans="9:10">
+    <row r="519" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I519" s="42"/>
       <c r="J519" s="42"/>
     </row>
-    <row r="520" spans="9:10">
+    <row r="520" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I520" s="42"/>
       <c r="J520" s="42"/>
     </row>
-    <row r="521" spans="9:10">
+    <row r="521" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I521" s="42"/>
       <c r="J521" s="42"/>
     </row>
-    <row r="522" spans="9:10">
+    <row r="522" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I522" s="42"/>
       <c r="J522" s="42"/>
     </row>
-    <row r="523" spans="9:10">
+    <row r="523" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I523" s="42"/>
       <c r="J523" s="42"/>
     </row>
-    <row r="524" spans="9:10">
+    <row r="524" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I524" s="42"/>
       <c r="J524" s="42"/>
     </row>
-    <row r="525" spans="9:10">
+    <row r="525" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I525" s="42"/>
       <c r="J525" s="42"/>
     </row>
-    <row r="526" spans="9:10">
+    <row r="526" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I526" s="42"/>
       <c r="J526" s="42"/>
     </row>
-    <row r="527" spans="9:10">
+    <row r="527" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I527" s="42"/>
       <c r="J527" s="42"/>
     </row>
-    <row r="528" spans="9:10">
+    <row r="528" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I528" s="42"/>
       <c r="J528" s="42"/>
     </row>
-    <row r="529" spans="9:10">
+    <row r="529" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I529" s="42"/>
       <c r="J529" s="42"/>
     </row>
-    <row r="530" spans="9:10">
+    <row r="530" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I530" s="42"/>
       <c r="J530" s="42"/>
     </row>
-    <row r="531" spans="9:10">
+    <row r="531" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I531" s="42"/>
       <c r="J531" s="42"/>
     </row>
-    <row r="532" spans="9:10">
+    <row r="532" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I532" s="42"/>
       <c r="J532" s="42"/>
     </row>
-    <row r="533" spans="9:10">
+    <row r="533" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I533" s="42"/>
       <c r="J533" s="42"/>
     </row>
-    <row r="534" spans="9:10">
+    <row r="534" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I534" s="42"/>
       <c r="J534" s="42"/>
     </row>
-    <row r="535" spans="9:10">
+    <row r="535" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I535" s="42"/>
       <c r="J535" s="42"/>
     </row>
-    <row r="536" spans="9:10">
+    <row r="536" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I536" s="42"/>
       <c r="J536" s="42"/>
     </row>
-    <row r="537" spans="9:10">
+    <row r="537" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I537" s="42"/>
       <c r="J537" s="42"/>
     </row>
-    <row r="538" spans="9:10">
+    <row r="538" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I538" s="42"/>
       <c r="J538" s="42"/>
     </row>
-    <row r="539" spans="9:10">
+    <row r="539" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I539" s="42"/>
       <c r="J539" s="42"/>
     </row>
-    <row r="540" spans="9:10">
+    <row r="540" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I540" s="42"/>
       <c r="J540" s="42"/>
     </row>
-    <row r="541" spans="9:10">
+    <row r="541" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I541" s="42"/>
       <c r="J541" s="42"/>
     </row>
-    <row r="542" spans="9:10">
+    <row r="542" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I542" s="42"/>
       <c r="J542" s="42"/>
     </row>
-    <row r="543" spans="9:10">
+    <row r="543" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I543" s="42"/>
       <c r="J543" s="42"/>
     </row>
-    <row r="544" spans="9:10">
+    <row r="544" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I544" s="42"/>
       <c r="J544" s="42"/>
     </row>
-    <row r="545" spans="9:10">
+    <row r="545" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I545" s="42"/>
       <c r="J545" s="42"/>
     </row>
-    <row r="546" spans="9:10">
+    <row r="546" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I546" s="42"/>
       <c r="J546" s="42"/>
     </row>
-    <row r="547" spans="9:10">
+    <row r="547" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I547" s="42"/>
       <c r="J547" s="42"/>
     </row>
-    <row r="548" spans="9:10">
+    <row r="548" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I548" s="42"/>
       <c r="J548" s="42"/>
     </row>
-    <row r="549" spans="9:10">
+    <row r="549" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I549" s="42"/>
       <c r="J549" s="42"/>
     </row>
-    <row r="550" spans="9:10">
+    <row r="550" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I550" s="42"/>
       <c r="J550" s="42"/>
     </row>
-    <row r="551" spans="9:10">
+    <row r="551" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I551" s="42"/>
       <c r="J551" s="42"/>
     </row>
-    <row r="552" spans="9:10">
+    <row r="552" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I552" s="42"/>
       <c r="J552" s="42"/>
     </row>
-    <row r="553" spans="9:10">
+    <row r="553" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I553" s="42"/>
       <c r="J553" s="42"/>
     </row>
-    <row r="554" spans="9:10">
+    <row r="554" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I554" s="42"/>
       <c r="J554" s="42"/>
     </row>
-    <row r="555" spans="9:10">
+    <row r="555" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I555" s="42"/>
       <c r="J555" s="42"/>
     </row>
-    <row r="556" spans="9:10">
+    <row r="556" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I556" s="42"/>
       <c r="J556" s="42"/>
     </row>
-    <row r="557" spans="9:10">
+    <row r="557" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I557" s="42"/>
       <c r="J557" s="42"/>
     </row>
-    <row r="558" spans="9:10">
+    <row r="558" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I558" s="42"/>
       <c r="J558" s="42"/>
     </row>
-    <row r="559" spans="9:10">
+    <row r="559" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I559" s="42"/>
       <c r="J559" s="42"/>
     </row>
-    <row r="560" spans="9:10">
+    <row r="560" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I560" s="42"/>
       <c r="J560" s="42"/>
     </row>
-    <row r="561" spans="9:10">
+    <row r="561" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I561" s="42"/>
       <c r="J561" s="42"/>
     </row>
-    <row r="562" spans="9:10">
+    <row r="562" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I562" s="42"/>
       <c r="J562" s="42"/>
     </row>
-    <row r="563" spans="9:10">
+    <row r="563" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I563" s="42"/>
       <c r="J563" s="42"/>
     </row>
-    <row r="564" spans="9:10">
+    <row r="564" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I564" s="42"/>
       <c r="J564" s="42"/>
     </row>
-    <row r="565" spans="9:10">
+    <row r="565" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I565" s="42"/>
       <c r="J565" s="42"/>
     </row>
-    <row r="566" spans="9:10">
+    <row r="566" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I566" s="42"/>
       <c r="J566" s="42"/>
     </row>
-    <row r="567" spans="9:10">
+    <row r="567" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I567" s="42"/>
       <c r="J567" s="42"/>
     </row>
-    <row r="568" spans="9:10">
+    <row r="568" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I568" s="42"/>
       <c r="J568" s="42"/>
     </row>
-    <row r="569" spans="9:10">
+    <row r="569" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I569" s="42"/>
       <c r="J569" s="42"/>
     </row>
-    <row r="570" spans="9:10">
+    <row r="570" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I570" s="42"/>
       <c r="J570" s="42"/>
     </row>
-    <row r="571" spans="9:10">
+    <row r="571" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I571" s="42"/>
       <c r="J571" s="42"/>
     </row>
-    <row r="572" spans="9:10">
+    <row r="572" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I572" s="42"/>
       <c r="J572" s="42"/>
     </row>
-    <row r="573" spans="9:10">
+    <row r="573" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I573" s="42"/>
       <c r="J573" s="42"/>
     </row>
-    <row r="574" spans="9:10">
+    <row r="574" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I574" s="42"/>
       <c r="J574" s="42"/>
     </row>
-    <row r="575" spans="9:10">
+    <row r="575" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I575" s="42"/>
       <c r="J575" s="42"/>
     </row>
-    <row r="576" spans="9:10">
+    <row r="576" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I576" s="42"/>
       <c r="J576" s="42"/>
     </row>
-    <row r="577" spans="9:10">
+    <row r="577" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I577" s="42"/>
       <c r="J577" s="42"/>
     </row>
-    <row r="578" spans="9:10">
+    <row r="578" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I578" s="42"/>
       <c r="J578" s="42"/>
     </row>
-    <row r="579" spans="9:10">
+    <row r="579" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I579" s="42"/>
       <c r="J579" s="42"/>
     </row>
-    <row r="580" spans="9:10">
+    <row r="580" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I580" s="42"/>
       <c r="J580" s="42"/>
     </row>
-    <row r="581" spans="9:10">
+    <row r="581" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I581" s="42"/>
       <c r="J581" s="42"/>
     </row>
-    <row r="582" spans="9:10">
+    <row r="582" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I582" s="42"/>
       <c r="J582" s="42"/>
     </row>
-    <row r="583" spans="9:10">
+    <row r="583" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I583" s="42"/>
       <c r="J583" s="42"/>
     </row>
-    <row r="584" spans="9:10">
+    <row r="584" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I584" s="42"/>
       <c r="J584" s="42"/>
     </row>
-    <row r="585" spans="9:10">
+    <row r="585" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I585" s="42"/>
       <c r="J585" s="42"/>
     </row>
-    <row r="586" spans="9:10">
+    <row r="586" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I586" s="42"/>
       <c r="J586" s="42"/>
     </row>
-    <row r="587" spans="9:10">
+    <row r="587" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I587" s="42"/>
       <c r="J587" s="42"/>
     </row>
-    <row r="588" spans="9:10">
+    <row r="588" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I588" s="42"/>
       <c r="J588" s="42"/>
     </row>
-    <row r="589" spans="9:10">
+    <row r="589" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I589" s="42"/>
       <c r="J589" s="42"/>
     </row>
-    <row r="590" spans="9:10">
+    <row r="590" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I590" s="42"/>
       <c r="J590" s="42"/>
     </row>
-    <row r="591" spans="9:10">
+    <row r="591" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I591" s="42"/>
       <c r="J591" s="42"/>
     </row>
-    <row r="592" spans="9:10">
+    <row r="592" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I592" s="42"/>
       <c r="J592" s="42"/>
     </row>
-    <row r="593" spans="9:10">
+    <row r="593" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I593" s="42"/>
       <c r="J593" s="42"/>
     </row>
-    <row r="594" spans="9:10">
+    <row r="594" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I594" s="42"/>
       <c r="J594" s="42"/>
     </row>
-    <row r="595" spans="9:10">
+    <row r="595" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I595" s="42"/>
       <c r="J595" s="42"/>
     </row>
-    <row r="596" spans="9:10">
+    <row r="596" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I596" s="42"/>
       <c r="J596" s="42"/>
     </row>
-    <row r="597" spans="9:10">
+    <row r="597" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I597" s="42"/>
       <c r="J597" s="42"/>
     </row>
-    <row r="598" spans="9:10">
+    <row r="598" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I598" s="42"/>
       <c r="J598" s="42"/>
     </row>
-    <row r="599" spans="9:10">
+    <row r="599" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I599" s="42"/>
       <c r="J599" s="42"/>
     </row>
-    <row r="600" spans="9:10">
+    <row r="600" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I600" s="42"/>
       <c r="J600" s="42"/>
     </row>
-    <row r="601" spans="9:10">
+    <row r="601" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I601" s="42"/>
       <c r="J601" s="42"/>
     </row>
-    <row r="602" spans="9:10">
+    <row r="602" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I602" s="42"/>
       <c r="J602" s="42"/>
     </row>
-    <row r="603" spans="9:10">
+    <row r="603" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I603" s="42"/>
       <c r="J603" s="42"/>
     </row>
-    <row r="604" spans="9:10">
+    <row r="604" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I604" s="42"/>
       <c r="J604" s="42"/>
     </row>
-    <row r="605" spans="9:10">
+    <row r="605" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I605" s="42"/>
       <c r="J605" s="42"/>
     </row>
-    <row r="606" spans="9:10">
+    <row r="606" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I606" s="42"/>
       <c r="J606" s="42"/>
     </row>
-    <row r="607" spans="9:10">
+    <row r="607" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I607" s="42"/>
       <c r="J607" s="42"/>
     </row>
-    <row r="608" spans="9:10">
+    <row r="608" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I608" s="42"/>
       <c r="J608" s="42"/>
     </row>
-    <row r="609" spans="9:10">
+    <row r="609" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I609" s="42"/>
       <c r="J609" s="42"/>
     </row>
-    <row r="610" spans="9:10">
+    <row r="610" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I610" s="42"/>
       <c r="J610" s="42"/>
     </row>
-    <row r="611" spans="9:10">
+    <row r="611" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I611" s="42"/>
       <c r="J611" s="42"/>
     </row>
-    <row r="612" spans="9:10">
+    <row r="612" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I612" s="42"/>
       <c r="J612" s="42"/>
     </row>
-    <row r="613" spans="9:10">
+    <row r="613" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I613" s="42"/>
       <c r="J613" s="42"/>
     </row>
-    <row r="614" spans="9:10">
+    <row r="614" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I614" s="42"/>
       <c r="J614" s="42"/>
     </row>
-    <row r="615" spans="9:10">
+    <row r="615" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I615" s="42"/>
       <c r="J615" s="42"/>
     </row>
-    <row r="616" spans="9:10">
+    <row r="616" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I616" s="42"/>
       <c r="J616" s="42"/>
     </row>
-    <row r="617" spans="9:10">
+    <row r="617" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I617" s="42"/>
       <c r="J617" s="42"/>
     </row>
-    <row r="618" spans="9:10">
+    <row r="618" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I618" s="42"/>
       <c r="J618" s="42"/>
     </row>
-    <row r="619" spans="9:10">
+    <row r="619" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I619" s="42"/>
       <c r="J619" s="42"/>
     </row>
-    <row r="620" spans="9:10">
+    <row r="620" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I620" s="42"/>
       <c r="J620" s="42"/>
     </row>
-    <row r="621" spans="9:10">
+    <row r="621" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I621" s="42"/>
       <c r="J621" s="42"/>
     </row>
-    <row r="622" spans="9:10">
+    <row r="622" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I622" s="42"/>
       <c r="J622" s="42"/>
     </row>
-    <row r="623" spans="9:10">
+    <row r="623" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I623" s="42"/>
       <c r="J623" s="42"/>
     </row>
-    <row r="624" spans="9:10">
+    <row r="624" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I624" s="42"/>
       <c r="J624" s="42"/>
     </row>
-    <row r="625" spans="9:10">
+    <row r="625" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I625" s="42"/>
       <c r="J625" s="42"/>
     </row>
-    <row r="626" spans="9:10">
+    <row r="626" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I626" s="42"/>
       <c r="J626" s="42"/>
     </row>
-    <row r="627" spans="9:10">
+    <row r="627" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I627" s="42"/>
       <c r="J627" s="42"/>
     </row>
-    <row r="628" spans="9:10">
+    <row r="628" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I628" s="42"/>
       <c r="J628" s="42"/>
     </row>
-    <row r="629" spans="9:10">
+    <row r="629" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I629" s="42"/>
       <c r="J629" s="42"/>
     </row>
-    <row r="630" spans="9:10">
+    <row r="630" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I630" s="42"/>
       <c r="J630" s="42"/>
     </row>
-    <row r="631" spans="9:10">
+    <row r="631" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I631" s="42"/>
       <c r="J631" s="42"/>
     </row>
-    <row r="632" spans="9:10">
+    <row r="632" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I632" s="42"/>
       <c r="J632" s="42"/>
     </row>
-    <row r="633" spans="9:10">
+    <row r="633" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I633" s="42"/>
       <c r="J633" s="42"/>
     </row>
-    <row r="634" spans="9:10">
+    <row r="634" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I634" s="42"/>
       <c r="J634" s="42"/>
     </row>
-    <row r="635" spans="9:10">
+    <row r="635" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I635" s="42"/>
       <c r="J635" s="42"/>
     </row>
-    <row r="636" spans="9:10">
+    <row r="636" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I636" s="42"/>
       <c r="J636" s="42"/>
     </row>
-    <row r="637" spans="9:10">
+    <row r="637" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I637" s="42"/>
       <c r="J637" s="42"/>
     </row>
-    <row r="638" spans="9:10">
+    <row r="638" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I638" s="42"/>
       <c r="J638" s="42"/>
     </row>
-    <row r="639" spans="9:10">
+    <row r="639" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I639" s="42"/>
       <c r="J639" s="42"/>
     </row>
-    <row r="640" spans="9:10">
+    <row r="640" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I640" s="42"/>
       <c r="J640" s="42"/>
     </row>
-    <row r="641" spans="9:10">
+    <row r="641" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I641" s="42"/>
       <c r="J641" s="42"/>
     </row>
-    <row r="642" spans="9:10">
+    <row r="642" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I642" s="42"/>
       <c r="J642" s="42"/>
     </row>
-    <row r="643" spans="9:10">
+    <row r="643" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I643" s="42"/>
       <c r="J643" s="42"/>
     </row>
-    <row r="644" spans="9:10">
+    <row r="644" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I644" s="42"/>
       <c r="J644" s="42"/>
     </row>
-    <row r="645" spans="9:10">
+    <row r="645" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I645" s="42"/>
       <c r="J645" s="42"/>
     </row>
-    <row r="646" spans="9:10">
+    <row r="646" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I646" s="42"/>
       <c r="J646" s="42"/>
     </row>
-    <row r="647" spans="9:10">
+    <row r="647" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I647" s="42"/>
       <c r="J647" s="42"/>
     </row>
-    <row r="648" spans="9:10">
+    <row r="648" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I648" s="42"/>
       <c r="J648" s="42"/>
     </row>
-    <row r="649" spans="9:10">
+    <row r="649" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I649" s="42"/>
       <c r="J649" s="42"/>
     </row>
-    <row r="650" spans="9:10">
+    <row r="650" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I650" s="42"/>
       <c r="J650" s="42"/>
     </row>
-    <row r="651" spans="9:10">
+    <row r="651" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I651" s="42"/>
       <c r="J651" s="42"/>
     </row>
-    <row r="652" spans="9:10">
+    <row r="652" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I652" s="42"/>
       <c r="J652" s="42"/>
     </row>
-    <row r="653" spans="9:10">
+    <row r="653" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I653" s="42"/>
       <c r="J653" s="42"/>
     </row>
-    <row r="654" spans="9:10">
+    <row r="654" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I654" s="42"/>
       <c r="J654" s="42"/>
     </row>
-    <row r="655" spans="9:10">
+    <row r="655" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I655" s="42"/>
       <c r="J655" s="42"/>
     </row>
-    <row r="656" spans="9:10">
+    <row r="656" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I656" s="42"/>
       <c r="J656" s="42"/>
     </row>
-    <row r="657" spans="9:10">
+    <row r="657" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I657" s="42"/>
       <c r="J657" s="42"/>
     </row>
-    <row r="658" spans="9:10">
+    <row r="658" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I658" s="42"/>
       <c r="J658" s="42"/>
     </row>
-    <row r="659" spans="9:10">
+    <row r="659" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I659" s="42"/>
       <c r="J659" s="42"/>
     </row>
-    <row r="660" spans="9:10">
+    <row r="660" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I660" s="42"/>
       <c r="J660" s="42"/>
     </row>
-    <row r="661" spans="9:10">
+    <row r="661" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I661" s="42"/>
       <c r="J661" s="42"/>
     </row>
-    <row r="662" spans="9:10">
+    <row r="662" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I662" s="42"/>
       <c r="J662" s="42"/>
     </row>
-    <row r="663" spans="9:10">
+    <row r="663" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I663" s="42"/>
       <c r="J663" s="42"/>
     </row>
-    <row r="664" spans="9:10">
+    <row r="664" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I664" s="42"/>
       <c r="J664" s="42"/>
     </row>
-    <row r="665" spans="9:10">
+    <row r="665" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I665" s="42"/>
       <c r="J665" s="42"/>
     </row>
-    <row r="666" spans="9:10">
+    <row r="666" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I666" s="42"/>
       <c r="J666" s="42"/>
     </row>
-    <row r="667" spans="9:10">
+    <row r="667" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I667" s="42"/>
       <c r="J667" s="42"/>
     </row>
-    <row r="668" spans="9:10">
+    <row r="668" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I668" s="42"/>
       <c r="J668" s="42"/>
     </row>
-    <row r="669" spans="9:10">
+    <row r="669" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I669" s="42"/>
       <c r="J669" s="42"/>
     </row>
-    <row r="670" spans="9:10">
+    <row r="670" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I670" s="42"/>
       <c r="J670" s="42"/>
     </row>
-    <row r="671" spans="9:10">
+    <row r="671" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I671" s="42"/>
       <c r="J671" s="42"/>
     </row>
-    <row r="672" spans="9:10">
+    <row r="672" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I672" s="42"/>
       <c r="J672" s="42"/>
     </row>
-    <row r="673" spans="9:10">
+    <row r="673" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I673" s="42"/>
       <c r="J673" s="42"/>
     </row>
-    <row r="674" spans="9:10">
+    <row r="674" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I674" s="42"/>
       <c r="J674" s="42"/>
     </row>
-    <row r="675" spans="9:10">
+    <row r="675" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I675" s="42"/>
       <c r="J675" s="42"/>
     </row>
-    <row r="676" spans="9:10">
+    <row r="676" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I676" s="42"/>
       <c r="J676" s="42"/>
     </row>
-    <row r="677" spans="9:10">
+    <row r="677" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I677" s="42"/>
       <c r="J677" s="42"/>
     </row>
-    <row r="678" spans="9:10">
+    <row r="678" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I678" s="42"/>
       <c r="J678" s="42"/>
     </row>
-    <row r="679" spans="9:10">
+    <row r="679" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I679" s="42"/>
       <c r="J679" s="42"/>
     </row>
-    <row r="680" spans="9:10">
+    <row r="680" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I680" s="42"/>
       <c r="J680" s="42"/>
     </row>
-    <row r="681" spans="9:10">
+    <row r="681" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I681" s="42"/>
       <c r="J681" s="42"/>
     </row>
-    <row r="682" spans="9:10">
+    <row r="682" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I682" s="42"/>
       <c r="J682" s="42"/>
     </row>
-    <row r="683" spans="9:10">
+    <row r="683" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I683" s="42"/>
       <c r="J683" s="42"/>
     </row>
-    <row r="684" spans="9:10">
+    <row r="684" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I684" s="42"/>
       <c r="J684" s="42"/>
     </row>
-    <row r="685" spans="9:10">
+    <row r="685" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I685" s="42"/>
       <c r="J685" s="42"/>
     </row>
-    <row r="686" spans="9:10">
+    <row r="686" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I686" s="42"/>
       <c r="J686" s="42"/>
     </row>
-    <row r="687" spans="9:10">
+    <row r="687" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I687" s="42"/>
       <c r="J687" s="42"/>
     </row>
-    <row r="688" spans="9:10">
+    <row r="688" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I688" s="42"/>
       <c r="J688" s="42"/>
     </row>
-    <row r="689" spans="9:10">
+    <row r="689" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I689" s="42"/>
       <c r="J689" s="42"/>
     </row>
-    <row r="690" spans="9:10">
+    <row r="690" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I690" s="42"/>
       <c r="J690" s="42"/>
     </row>
-    <row r="691" spans="9:10">
+    <row r="691" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I691" s="42"/>
       <c r="J691" s="42"/>
     </row>
-    <row r="692" spans="9:10">
+    <row r="692" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I692" s="42"/>
       <c r="J692" s="42"/>
     </row>
-    <row r="693" spans="9:10">
+    <row r="693" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I693" s="42"/>
       <c r="J693" s="42"/>
     </row>
-    <row r="694" spans="9:10">
+    <row r="694" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I694" s="42"/>
       <c r="J694" s="42"/>
     </row>
-    <row r="695" spans="9:10">
+    <row r="695" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I695" s="42"/>
       <c r="J695" s="42"/>
     </row>
-    <row r="696" spans="9:10">
+    <row r="696" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I696" s="42"/>
       <c r="J696" s="42"/>
     </row>
-    <row r="697" spans="9:10">
+    <row r="697" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I697" s="42"/>
       <c r="J697" s="42"/>
     </row>
-    <row r="698" spans="9:10">
+    <row r="698" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I698" s="42"/>
       <c r="J698" s="42"/>
     </row>
-    <row r="699" spans="9:10">
+    <row r="699" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I699" s="42"/>
       <c r="J699" s="42"/>
     </row>
-    <row r="700" spans="9:10">
+    <row r="700" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I700" s="42"/>
       <c r="J700" s="42"/>
     </row>
-    <row r="701" spans="9:10">
+    <row r="701" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I701" s="42"/>
       <c r="J701" s="42"/>
     </row>
-    <row r="702" spans="9:10">
+    <row r="702" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I702" s="42"/>
       <c r="J702" s="42"/>
     </row>
-    <row r="703" spans="9:10">
+    <row r="703" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I703" s="42"/>
       <c r="J703" s="42"/>
     </row>
-    <row r="704" spans="9:10">
+    <row r="704" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I704" s="42"/>
       <c r="J704" s="42"/>
     </row>
-    <row r="705" spans="9:10">
+    <row r="705" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I705" s="42"/>
       <c r="J705" s="42"/>
     </row>
-    <row r="706" spans="9:10">
+    <row r="706" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I706" s="42"/>
       <c r="J706" s="42"/>
     </row>
-    <row r="707" spans="9:10">
+    <row r="707" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I707" s="42"/>
       <c r="J707" s="42"/>
     </row>
-    <row r="708" spans="9:10">
+    <row r="708" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I708" s="42"/>
       <c r="J708" s="42"/>
     </row>
-    <row r="709" spans="9:10">
+    <row r="709" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I709" s="42"/>
       <c r="J709" s="42"/>
     </row>
-    <row r="710" spans="9:10">
+    <row r="710" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I710" s="42"/>
       <c r="J710" s="42"/>
     </row>
-    <row r="711" spans="9:10">
+    <row r="711" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I711" s="42"/>
       <c r="J711" s="42"/>
     </row>
-    <row r="712" spans="9:10">
+    <row r="712" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I712" s="42"/>
       <c r="J712" s="42"/>
     </row>
-    <row r="713" spans="9:10">
+    <row r="713" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I713" s="42"/>
       <c r="J713" s="42"/>
     </row>
-    <row r="714" spans="9:10">
+    <row r="714" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I714" s="42"/>
       <c r="J714" s="42"/>
     </row>
-    <row r="715" spans="9:10">
+    <row r="715" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I715" s="42"/>
       <c r="J715" s="42"/>
     </row>
-    <row r="716" spans="9:10">
+    <row r="716" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I716" s="42"/>
       <c r="J716" s="42"/>
     </row>
-    <row r="717" spans="9:10">
+    <row r="717" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I717" s="42"/>
       <c r="J717" s="42"/>
     </row>
-    <row r="718" spans="9:10">
+    <row r="718" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I718" s="42"/>
       <c r="J718" s="42"/>
     </row>
-    <row r="719" spans="9:10">
+    <row r="719" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I719" s="42"/>
       <c r="J719" s="42"/>
     </row>
-    <row r="720" spans="9:10">
+    <row r="720" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I720" s="42"/>
       <c r="J720" s="42"/>
     </row>
-    <row r="721" spans="9:10">
+    <row r="721" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I721" s="42"/>
       <c r="J721" s="42"/>
     </row>
-    <row r="722" spans="9:10">
+    <row r="722" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I722" s="42"/>
       <c r="J722" s="42"/>
     </row>
-    <row r="723" spans="9:10">
+    <row r="723" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I723" s="42"/>
       <c r="J723" s="42"/>
     </row>
-    <row r="724" spans="9:10">
+    <row r="724" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I724" s="42"/>
       <c r="J724" s="42"/>
     </row>
-    <row r="725" spans="9:10">
+    <row r="725" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I725" s="42"/>
       <c r="J725" s="42"/>
     </row>
-    <row r="726" spans="9:10">
+    <row r="726" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I726" s="42"/>
       <c r="J726" s="42"/>
     </row>
-    <row r="727" spans="9:10">
+    <row r="727" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I727" s="42"/>
       <c r="J727" s="42"/>
     </row>
-    <row r="728" spans="9:10">
+    <row r="728" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I728" s="42"/>
       <c r="J728" s="42"/>
     </row>
-    <row r="729" spans="9:10">
+    <row r="729" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I729" s="42"/>
       <c r="J729" s="42"/>
     </row>
-    <row r="730" spans="9:10">
+    <row r="730" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I730" s="42"/>
       <c r="J730" s="42"/>
     </row>
-    <row r="731" spans="9:10">
+    <row r="731" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I731" s="42"/>
       <c r="J731" s="42"/>
     </row>
-    <row r="732" spans="9:10">
+    <row r="732" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I732" s="42"/>
       <c r="J732" s="42"/>
     </row>
-    <row r="733" spans="9:10">
+    <row r="733" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I733" s="42"/>
       <c r="J733" s="42"/>
     </row>
-    <row r="734" spans="9:10">
+    <row r="734" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I734" s="42"/>
       <c r="J734" s="42"/>
     </row>
-    <row r="735" spans="9:10">
+    <row r="735" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I735" s="42"/>
       <c r="J735" s="42"/>
     </row>
-    <row r="736" spans="9:10">
+    <row r="736" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I736" s="42"/>
       <c r="J736" s="42"/>
     </row>
-    <row r="737" spans="9:10">
+    <row r="737" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I737" s="42"/>
       <c r="J737" s="42"/>
     </row>
-    <row r="738" spans="9:10">
+    <row r="738" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I738" s="42"/>
       <c r="J738" s="42"/>
     </row>
-    <row r="739" spans="9:10">
+    <row r="739" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I739" s="42"/>
       <c r="J739" s="42"/>
     </row>
-    <row r="740" spans="9:10">
+    <row r="740" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I740" s="42"/>
       <c r="J740" s="42"/>
     </row>
-    <row r="741" spans="9:10">
+    <row r="741" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I741" s="42"/>
       <c r="J741" s="42"/>
     </row>
-    <row r="742" spans="9:10">
+    <row r="742" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I742" s="42"/>
       <c r="J742" s="42"/>
     </row>
-    <row r="743" spans="9:10">
+    <row r="743" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I743" s="42"/>
       <c r="J743" s="42"/>
     </row>
-    <row r="744" spans="9:10">
+    <row r="744" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I744" s="42"/>
       <c r="J744" s="42"/>
     </row>
-    <row r="745" spans="9:10">
+    <row r="745" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I745" s="42"/>
       <c r="J745" s="42"/>
     </row>
-    <row r="746" spans="9:10">
+    <row r="746" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I746" s="42"/>
       <c r="J746" s="42"/>
     </row>
-    <row r="747" spans="9:10">
+    <row r="747" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I747" s="42"/>
       <c r="J747" s="42"/>
     </row>
-    <row r="748" spans="9:10">
+    <row r="748" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I748" s="42"/>
       <c r="J748" s="42"/>
     </row>
-    <row r="749" spans="9:10">
+    <row r="749" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I749" s="42"/>
       <c r="J749" s="42"/>
     </row>
-    <row r="750" spans="9:10">
+    <row r="750" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I750" s="42"/>
       <c r="J750" s="42"/>
     </row>
-    <row r="751" spans="9:10">
+    <row r="751" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I751" s="42"/>
       <c r="J751" s="42"/>
     </row>
-    <row r="752" spans="9:10">
+    <row r="752" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I752" s="42"/>
       <c r="J752" s="42"/>
     </row>
-    <row r="753" spans="9:10">
+    <row r="753" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I753" s="42"/>
       <c r="J753" s="42"/>
     </row>
-    <row r="754" spans="9:10">
+    <row r="754" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I754" s="42"/>
       <c r="J754" s="42"/>
     </row>
-    <row r="755" spans="9:10">
+    <row r="755" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I755" s="42"/>
       <c r="J755" s="42"/>
     </row>
-    <row r="756" spans="9:10">
+    <row r="756" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I756" s="42"/>
       <c r="J756" s="42"/>
     </row>
-    <row r="757" spans="9:10">
+    <row r="757" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I757" s="42"/>
       <c r="J757" s="42"/>
     </row>
-    <row r="758" spans="9:10">
+    <row r="758" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I758" s="42"/>
       <c r="J758" s="42"/>
     </row>
-    <row r="759" spans="9:10">
+    <row r="759" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I759" s="42"/>
       <c r="J759" s="42"/>
     </row>
-    <row r="760" spans="9:10">
+    <row r="760" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I760" s="42"/>
       <c r="J760" s="42"/>
     </row>
-    <row r="761" spans="9:10">
+    <row r="761" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I761" s="42"/>
       <c r="J761" s="42"/>
     </row>
-    <row r="762" spans="9:10">
+    <row r="762" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I762" s="42"/>
       <c r="J762" s="42"/>
     </row>
-    <row r="763" spans="9:10">
+    <row r="763" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I763" s="42"/>
       <c r="J763" s="42"/>
     </row>
-    <row r="764" spans="9:10">
+    <row r="764" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I764" s="42"/>
       <c r="J764" s="42"/>
     </row>
-    <row r="765" spans="9:10">
+    <row r="765" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I765" s="42"/>
       <c r="J765" s="42"/>
     </row>
-    <row r="766" spans="9:10">
+    <row r="766" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I766" s="42"/>
       <c r="J766" s="42"/>
     </row>
-    <row r="767" spans="9:10">
+    <row r="767" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I767" s="42"/>
       <c r="J767" s="42"/>
     </row>
-    <row r="768" spans="9:10">
+    <row r="768" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I768" s="42"/>
       <c r="J768" s="42"/>
     </row>
-    <row r="769" spans="9:10">
+    <row r="769" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I769" s="42"/>
       <c r="J769" s="42"/>
     </row>
-    <row r="770" spans="9:10">
+    <row r="770" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I770" s="42"/>
       <c r="J770" s="42"/>
     </row>
-    <row r="771" spans="9:10">
+    <row r="771" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I771" s="42"/>
       <c r="J771" s="42"/>
     </row>
-    <row r="772" spans="9:10">
+    <row r="772" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I772" s="42"/>
       <c r="J772" s="42"/>
     </row>
-    <row r="773" spans="9:10">
+    <row r="773" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I773" s="42"/>
       <c r="J773" s="42"/>
     </row>
-    <row r="774" spans="9:10">
+    <row r="774" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I774" s="42"/>
       <c r="J774" s="42"/>
     </row>
-    <row r="775" spans="9:10">
+    <row r="775" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I775" s="42"/>
       <c r="J775" s="42"/>
     </row>
-    <row r="776" spans="9:10">
+    <row r="776" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I776" s="42"/>
       <c r="J776" s="42"/>
     </row>
-    <row r="777" spans="9:10">
+    <row r="777" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I777" s="42"/>
       <c r="J777" s="42"/>
     </row>
-    <row r="778" spans="9:10">
+    <row r="778" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I778" s="42"/>
       <c r="J778" s="42"/>
     </row>
-    <row r="779" spans="9:10">
+    <row r="779" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I779" s="42"/>
       <c r="J779" s="42"/>
     </row>
-    <row r="780" spans="9:10">
+    <row r="780" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I780" s="42"/>
       <c r="J780" s="42"/>
     </row>
-    <row r="781" spans="9:10">
+    <row r="781" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I781" s="42"/>
       <c r="J781" s="42"/>
     </row>
-    <row r="782" spans="9:10">
+    <row r="782" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I782" s="42"/>
       <c r="J782" s="42"/>
     </row>
-    <row r="783" spans="9:10">
+    <row r="783" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I783" s="42"/>
       <c r="J783" s="42"/>
     </row>
-    <row r="784" spans="9:10">
+    <row r="784" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I784" s="42"/>
       <c r="J784" s="42"/>
     </row>
-    <row r="785" spans="9:10">
+    <row r="785" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I785" s="42"/>
       <c r="J785" s="42"/>
     </row>
-    <row r="786" spans="9:10">
+    <row r="786" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I786" s="42"/>
       <c r="J786" s="42"/>
     </row>
-    <row r="787" spans="9:10">
+    <row r="787" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I787" s="42"/>
       <c r="J787" s="42"/>
     </row>
-    <row r="788" spans="9:10">
+    <row r="788" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I788" s="42"/>
       <c r="J788" s="42"/>
     </row>
-    <row r="789" spans="9:10">
+    <row r="789" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I789" s="42"/>
       <c r="J789" s="42"/>
     </row>
-    <row r="790" spans="9:10">
+    <row r="790" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I790" s="42"/>
       <c r="J790" s="42"/>
     </row>
-    <row r="791" spans="9:10">
+    <row r="791" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I791" s="42"/>
       <c r="J791" s="42"/>
     </row>
-    <row r="792" spans="9:10">
+    <row r="792" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I792" s="42"/>
       <c r="J792" s="42"/>
     </row>
-    <row r="793" spans="9:10">
+    <row r="793" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I793" s="42"/>
       <c r="J793" s="42"/>
     </row>
-    <row r="794" spans="9:10">
+    <row r="794" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I794" s="42"/>
       <c r="J794" s="42"/>
     </row>
-    <row r="795" spans="9:10">
+    <row r="795" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I795" s="42"/>
       <c r="J795" s="42"/>
     </row>
-    <row r="796" spans="9:10">
+    <row r="796" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I796" s="42"/>
       <c r="J796" s="42"/>
     </row>
-    <row r="797" spans="9:10">
+    <row r="797" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I797" s="42"/>
       <c r="J797" s="42"/>
     </row>
-    <row r="798" spans="9:10">
+    <row r="798" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I798" s="42"/>
       <c r="J798" s="42"/>
     </row>
-    <row r="799" spans="9:10">
+    <row r="799" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I799" s="42"/>
       <c r="J799" s="42"/>
     </row>
-    <row r="800" spans="9:10">
+    <row r="800" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I800" s="42"/>
       <c r="J800" s="42"/>
     </row>
-    <row r="801" spans="9:10">
+    <row r="801" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I801" s="42"/>
       <c r="J801" s="42"/>
     </row>
-    <row r="802" spans="9:10">
+    <row r="802" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I802" s="42"/>
       <c r="J802" s="42"/>
     </row>
-    <row r="803" spans="9:10">
+    <row r="803" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I803" s="42"/>
       <c r="J803" s="42"/>
     </row>
-    <row r="804" spans="9:10">
+    <row r="804" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I804" s="42"/>
       <c r="J804" s="42"/>
     </row>
-    <row r="805" spans="9:10">
+    <row r="805" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I805" s="42"/>
       <c r="J805" s="42"/>
     </row>
-    <row r="806" spans="9:10">
+    <row r="806" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I806" s="42"/>
       <c r="J806" s="42"/>
     </row>
-    <row r="807" spans="9:10">
+    <row r="807" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I807" s="42"/>
       <c r="J807" s="42"/>
     </row>
-    <row r="808" spans="9:10">
+    <row r="808" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I808" s="42"/>
       <c r="J808" s="42"/>
     </row>
-    <row r="809" spans="9:10">
+    <row r="809" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I809" s="42"/>
       <c r="J809" s="42"/>
     </row>
-    <row r="810" spans="9:10">
+    <row r="810" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I810" s="42"/>
       <c r="J810" s="42"/>
     </row>
-    <row r="811" spans="9:10">
+    <row r="811" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I811" s="42"/>
       <c r="J811" s="42"/>
     </row>
-    <row r="812" spans="9:10">
+    <row r="812" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I812" s="42"/>
       <c r="J812" s="42"/>
     </row>
-    <row r="813" spans="9:10">
+    <row r="813" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I813" s="42"/>
       <c r="J813" s="42"/>
     </row>
-    <row r="814" spans="9:10">
+    <row r="814" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I814" s="42"/>
       <c r="J814" s="42"/>
     </row>
-    <row r="815" spans="9:10">
+    <row r="815" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I815" s="42"/>
       <c r="J815" s="42"/>
     </row>
-    <row r="816" spans="9:10">
+    <row r="816" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I816" s="42"/>
       <c r="J816" s="42"/>
     </row>
-    <row r="817" spans="9:10">
+    <row r="817" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I817" s="42"/>
       <c r="J817" s="42"/>
     </row>
-    <row r="818" spans="9:10">
+    <row r="818" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I818" s="42"/>
       <c r="J818" s="42"/>
     </row>
-    <row r="819" spans="9:10">
+    <row r="819" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I819" s="42"/>
       <c r="J819" s="42"/>
     </row>
-    <row r="820" spans="9:10">
+    <row r="820" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I820" s="42"/>
       <c r="J820" s="42"/>
     </row>
-    <row r="821" spans="9:10">
+    <row r="821" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I821" s="42"/>
       <c r="J821" s="42"/>
     </row>
-    <row r="822" spans="9:10">
+    <row r="822" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I822" s="42"/>
       <c r="J822" s="42"/>
     </row>
-    <row r="823" spans="9:10">
+    <row r="823" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I823" s="42"/>
       <c r="J823" s="42"/>
     </row>
-    <row r="824" spans="9:10">
+    <row r="824" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I824" s="42"/>
       <c r="J824" s="42"/>
     </row>
-    <row r="825" spans="9:10">
+    <row r="825" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I825" s="42"/>
       <c r="J825" s="42"/>
     </row>
-    <row r="826" spans="9:10">
+    <row r="826" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I826" s="42"/>
       <c r="J826" s="42"/>
     </row>
-    <row r="827" spans="9:10">
+    <row r="827" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I827" s="42"/>
       <c r="J827" s="42"/>
     </row>
-    <row r="828" spans="9:10">
+    <row r="828" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I828" s="42"/>
       <c r="J828" s="42"/>
     </row>
-    <row r="829" spans="9:10">
+    <row r="829" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I829" s="42"/>
       <c r="J829" s="42"/>
     </row>
-    <row r="830" spans="9:10">
+    <row r="830" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I830" s="42"/>
       <c r="J830" s="42"/>
     </row>
-    <row r="831" spans="9:10">
+    <row r="831" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I831" s="42"/>
       <c r="J831" s="42"/>
     </row>
-    <row r="832" spans="9:10">
+    <row r="832" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I832" s="42"/>
       <c r="J832" s="42"/>
     </row>
-    <row r="833" spans="9:10">
+    <row r="833" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I833" s="42"/>
       <c r="J833" s="42"/>
     </row>
-    <row r="834" spans="9:10">
+    <row r="834" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I834" s="42"/>
       <c r="J834" s="42"/>
     </row>
-    <row r="835" spans="9:10">
+    <row r="835" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I835" s="42"/>
       <c r="J835" s="42"/>
     </row>
-    <row r="836" spans="9:10">
+    <row r="836" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I836" s="42"/>
       <c r="J836" s="42"/>
     </row>
-    <row r="837" spans="9:10">
+    <row r="837" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I837" s="42"/>
       <c r="J837" s="42"/>
     </row>
-    <row r="838" spans="9:10">
+    <row r="838" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I838" s="42"/>
       <c r="J838" s="42"/>
     </row>
-    <row r="839" spans="9:10">
+    <row r="839" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I839" s="42"/>
       <c r="J839" s="42"/>
     </row>
-    <row r="840" spans="9:10">
+    <row r="840" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I840" s="42"/>
       <c r="J840" s="42"/>
     </row>
-    <row r="841" spans="9:10">
+    <row r="841" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I841" s="42"/>
       <c r="J841" s="42"/>
     </row>
-    <row r="842" spans="9:10">
+    <row r="842" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I842" s="42"/>
       <c r="J842" s="42"/>
     </row>
-    <row r="843" spans="9:10">
+    <row r="843" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I843" s="42"/>
       <c r="J843" s="42"/>
     </row>
-    <row r="844" spans="9:10">
+    <row r="844" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I844" s="42"/>
       <c r="J844" s="42"/>
     </row>
-    <row r="845" spans="9:10">
+    <row r="845" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I845" s="42"/>
       <c r="J845" s="42"/>
     </row>
-    <row r="846" spans="9:10">
+    <row r="846" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I846" s="42"/>
       <c r="J846" s="42"/>
     </row>
-    <row r="847" spans="9:10">
+    <row r="847" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I847" s="42"/>
       <c r="J847" s="42"/>
     </row>
-    <row r="848" spans="9:10">
+    <row r="848" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I848" s="42"/>
       <c r="J848" s="42"/>
     </row>
-    <row r="849" spans="9:10">
+    <row r="849" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I849" s="42"/>
       <c r="J849" s="42"/>
     </row>
-    <row r="850" spans="9:10">
+    <row r="850" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I850" s="42"/>
       <c r="J850" s="42"/>
     </row>
-    <row r="851" spans="9:10">
+    <row r="851" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I851" s="42"/>
       <c r="J851" s="42"/>
     </row>
-    <row r="852" spans="9:10">
+    <row r="852" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I852" s="42"/>
       <c r="J852" s="42"/>
     </row>
-    <row r="853" spans="9:10">
+    <row r="853" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I853" s="42"/>
       <c r="J853" s="42"/>
     </row>
-    <row r="854" spans="9:10">
+    <row r="854" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I854" s="42"/>
       <c r="J854" s="42"/>
     </row>
-    <row r="855" spans="9:10">
+    <row r="855" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I855" s="42"/>
       <c r="J855" s="42"/>
     </row>
-    <row r="856" spans="9:10">
+    <row r="856" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I856" s="42"/>
       <c r="J856" s="42"/>
     </row>
-    <row r="857" spans="9:10">
+    <row r="857" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I857" s="42"/>
       <c r="J857" s="42"/>
     </row>
-    <row r="858" spans="9:10">
+    <row r="858" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I858" s="42"/>
       <c r="J858" s="42"/>
     </row>
-    <row r="859" spans="9:10">
+    <row r="859" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I859" s="42"/>
       <c r="J859" s="42"/>
     </row>
-    <row r="860" spans="9:10">
+    <row r="860" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I860" s="42"/>
       <c r="J860" s="42"/>
     </row>
-    <row r="861" spans="9:10">
+    <row r="861" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I861" s="42"/>
       <c r="J861" s="42"/>
     </row>
-    <row r="862" spans="9:10">
+    <row r="862" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I862" s="42"/>
       <c r="J862" s="42"/>
     </row>
-    <row r="863" spans="9:10">
+    <row r="863" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I863" s="42"/>
       <c r="J863" s="42"/>
     </row>
-    <row r="864" spans="9:10">
+    <row r="864" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I864" s="42"/>
       <c r="J864" s="42"/>
     </row>
-    <row r="865" spans="9:10">
+    <row r="865" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I865" s="42"/>
       <c r="J865" s="42"/>
     </row>
-    <row r="866" spans="9:10">
+    <row r="866" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I866" s="42"/>
       <c r="J866" s="42"/>
     </row>
-    <row r="867" spans="9:10">
+    <row r="867" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I867" s="42"/>
       <c r="J867" s="42"/>
     </row>
-    <row r="868" spans="9:10">
+    <row r="868" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I868" s="42"/>
       <c r="J868" s="42"/>
     </row>
-    <row r="869" spans="9:10">
+    <row r="869" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I869" s="42"/>
       <c r="J869" s="42"/>
     </row>
-    <row r="870" spans="9:10">
+    <row r="870" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I870" s="42"/>
       <c r="J870" s="42"/>
     </row>
-    <row r="871" spans="9:10">
+    <row r="871" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I871" s="42"/>
       <c r="J871" s="42"/>
     </row>
-    <row r="872" spans="9:10">
+    <row r="872" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I872" s="42"/>
       <c r="J872" s="42"/>
     </row>
-    <row r="873" spans="9:10">
+    <row r="873" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I873" s="42"/>
       <c r="J873" s="42"/>
     </row>
-    <row r="874" spans="9:10">
+    <row r="874" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I874" s="42"/>
       <c r="J874" s="42"/>
     </row>
-    <row r="875" spans="9:10">
+    <row r="875" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I875" s="42"/>
       <c r="J875" s="42"/>
     </row>
-    <row r="876" spans="9:10">
+    <row r="876" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I876" s="42"/>
       <c r="J876" s="42"/>
     </row>
-    <row r="877" spans="9:10">
+    <row r="877" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I877" s="42"/>
       <c r="J877" s="42"/>
     </row>
-    <row r="878" spans="9:10">
+    <row r="878" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I878" s="42"/>
       <c r="J878" s="42"/>
     </row>
-    <row r="879" spans="9:10">
+    <row r="879" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I879" s="42"/>
       <c r="J879" s="42"/>
     </row>
-    <row r="880" spans="9:10">
+    <row r="880" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I880" s="42"/>
       <c r="J880" s="42"/>
     </row>
-    <row r="881" spans="9:10">
+    <row r="881" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I881" s="42"/>
       <c r="J881" s="42"/>
     </row>
-    <row r="882" spans="9:10">
+    <row r="882" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I882" s="42"/>
       <c r="J882" s="42"/>
     </row>
-    <row r="883" spans="9:10">
+    <row r="883" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I883" s="42"/>
       <c r="J883" s="42"/>
     </row>
-    <row r="884" spans="9:10">
+    <row r="884" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I884" s="42"/>
       <c r="J884" s="42"/>
     </row>
-    <row r="885" spans="9:10">
+    <row r="885" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I885" s="42"/>
       <c r="J885" s="42"/>
     </row>
-    <row r="886" spans="9:10">
+    <row r="886" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I886" s="42"/>
       <c r="J886" s="42"/>
     </row>
-    <row r="887" spans="9:10">
+    <row r="887" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I887" s="42"/>
       <c r="J887" s="42"/>
     </row>
-    <row r="888" spans="9:10">
+    <row r="888" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I888" s="42"/>
       <c r="J888" s="42"/>
     </row>
-    <row r="889" spans="9:10">
+    <row r="889" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I889" s="42"/>
       <c r="J889" s="42"/>
     </row>
-    <row r="890" spans="9:10">
+    <row r="890" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I890" s="42"/>
       <c r="J890" s="42"/>
     </row>
-    <row r="891" spans="9:10">
+    <row r="891" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I891" s="42"/>
       <c r="J891" s="42"/>
     </row>
-    <row r="892" spans="9:10">
+    <row r="892" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I892" s="42"/>
       <c r="J892" s="42"/>
     </row>
-    <row r="893" spans="9:10">
+    <row r="893" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I893" s="42"/>
       <c r="J893" s="42"/>
     </row>
-    <row r="894" spans="9:10">
+    <row r="894" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I894" s="42"/>
       <c r="J894" s="42"/>
     </row>
-    <row r="895" spans="9:10">
+    <row r="895" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I895" s="42"/>
       <c r="J895" s="42"/>
     </row>
-    <row r="896" spans="9:10">
+    <row r="896" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I896" s="42"/>
       <c r="J896" s="42"/>
     </row>
-    <row r="897" spans="9:10">
+    <row r="897" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I897" s="42"/>
       <c r="J897" s="42"/>
     </row>
-    <row r="898" spans="9:10">
+    <row r="898" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I898" s="42"/>
       <c r="J898" s="42"/>
     </row>
-    <row r="899" spans="9:10">
+    <row r="899" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I899" s="42"/>
       <c r="J899" s="42"/>
     </row>
-    <row r="900" spans="9:10">
+    <row r="900" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I900" s="42"/>
       <c r="J900" s="42"/>
     </row>
-    <row r="901" spans="9:10">
+    <row r="901" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I901" s="42"/>
       <c r="J901" s="42"/>
     </row>
-    <row r="902" spans="9:10">
+    <row r="902" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I902" s="42"/>
       <c r="J902" s="42"/>
     </row>
-    <row r="903" spans="9:10">
+    <row r="903" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I903" s="42"/>
       <c r="J903" s="42"/>
     </row>
-    <row r="904" spans="9:10">
+    <row r="904" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I904" s="42"/>
       <c r="J904" s="42"/>
     </row>
-    <row r="905" spans="9:10">
+    <row r="905" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I905" s="42"/>
       <c r="J905" s="42"/>
     </row>
-    <row r="906" spans="9:10">
+    <row r="906" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I906" s="42"/>
       <c r="J906" s="42"/>
     </row>
-    <row r="907" spans="9:10">
+    <row r="907" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I907" s="42"/>
       <c r="J907" s="42"/>
     </row>
-    <row r="908" spans="9:10">
+    <row r="908" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I908" s="42"/>
       <c r="J908" s="42"/>
     </row>
-    <row r="909" spans="9:10">
+    <row r="909" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I909" s="42"/>
       <c r="J909" s="42"/>
     </row>
-    <row r="910" spans="9:10">
+    <row r="910" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I910" s="42"/>
       <c r="J910" s="42"/>
     </row>
-    <row r="911" spans="9:10">
+    <row r="911" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I911" s="42"/>
       <c r="J911" s="42"/>
     </row>
-    <row r="912" spans="9:10">
+    <row r="912" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I912" s="42"/>
       <c r="J912" s="42"/>
     </row>
-    <row r="913" spans="9:10">
+    <row r="913" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I913" s="42"/>
       <c r="J913" s="42"/>
     </row>
-    <row r="914" spans="9:10">
+    <row r="914" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I914" s="42"/>
       <c r="J914" s="42"/>
     </row>
-    <row r="915" spans="9:10">
+    <row r="915" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I915" s="42"/>
       <c r="J915" s="42"/>
     </row>
-    <row r="916" spans="9:10">
+    <row r="916" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I916" s="42"/>
       <c r="J916" s="42"/>
     </row>
-    <row r="917" spans="9:10">
+    <row r="917" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I917" s="42"/>
       <c r="J917" s="42"/>
     </row>
-    <row r="918" spans="9:10">
+    <row r="918" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I918" s="42"/>
       <c r="J918" s="42"/>
     </row>
-    <row r="919" spans="9:10">
+    <row r="919" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I919" s="42"/>
       <c r="J919" s="42"/>
     </row>
-    <row r="920" spans="9:10">
+    <row r="920" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I920" s="42"/>
       <c r="J920" s="42"/>
     </row>
-    <row r="921" spans="9:10">
+    <row r="921" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I921" s="42"/>
       <c r="J921" s="42"/>
     </row>
-    <row r="922" spans="9:10">
+    <row r="922" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I922" s="42"/>
       <c r="J922" s="42"/>
     </row>
-    <row r="923" spans="9:10">
+    <row r="923" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I923" s="42"/>
       <c r="J923" s="42"/>
     </row>
-    <row r="924" spans="9:10">
+    <row r="924" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I924" s="42"/>
       <c r="J924" s="42"/>
     </row>
-    <row r="925" spans="9:10">
+    <row r="925" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I925" s="42"/>
       <c r="J925" s="42"/>
     </row>
-    <row r="926" spans="9:10">
+    <row r="926" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I926" s="42"/>
       <c r="J926" s="42"/>
     </row>
-    <row r="927" spans="9:10">
+    <row r="927" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I927" s="42"/>
       <c r="J927" s="42"/>
     </row>
-    <row r="928" spans="9:10">
+    <row r="928" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I928" s="42"/>
       <c r="J928" s="42"/>
     </row>
-    <row r="929" spans="9:10">
+    <row r="929" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I929" s="42"/>
       <c r="J929" s="42"/>
     </row>
-    <row r="930" spans="9:10">
+    <row r="930" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I930" s="42"/>
       <c r="J930" s="42"/>
     </row>
-    <row r="931" spans="9:10">
+    <row r="931" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I931" s="42"/>
       <c r="J931" s="42"/>
     </row>
-    <row r="932" spans="9:10">
+    <row r="932" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I932" s="42"/>
       <c r="J932" s="42"/>
     </row>
-    <row r="933" spans="9:10">
+    <row r="933" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I933" s="42"/>
       <c r="J933" s="42"/>
     </row>
-    <row r="934" spans="9:10">
+    <row r="934" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I934" s="42"/>
       <c r="J934" s="42"/>
     </row>
-    <row r="935" spans="9:10">
+    <row r="935" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I935" s="42"/>
       <c r="J935" s="42"/>
     </row>
-    <row r="936" spans="9:10">
+    <row r="936" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I936" s="42"/>
       <c r="J936" s="42"/>
     </row>
-    <row r="937" spans="9:10">
+    <row r="937" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I937" s="42"/>
       <c r="J937" s="42"/>
     </row>
-    <row r="938" spans="9:10">
+    <row r="938" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I938" s="42"/>
       <c r="J938" s="42"/>
     </row>
-    <row r="939" spans="9:10">
+    <row r="939" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I939" s="42"/>
       <c r="J939" s="42"/>
     </row>
-    <row r="940" spans="9:10">
+    <row r="940" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I940" s="42"/>
       <c r="J940" s="42"/>
     </row>
-    <row r="941" spans="9:10">
+    <row r="941" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I941" s="42"/>
       <c r="J941" s="42"/>
     </row>
-    <row r="942" spans="9:10">
+    <row r="942" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I942" s="42"/>
       <c r="J942" s="42"/>
     </row>
-    <row r="943" spans="9:10">
+    <row r="943" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I943" s="42"/>
       <c r="J943" s="42"/>
     </row>
-    <row r="944" spans="9:10">
+    <row r="944" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I944" s="42"/>
       <c r="J944" s="42"/>
     </row>
-    <row r="945" spans="9:10">
+    <row r="945" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I945" s="42"/>
       <c r="J945" s="42"/>
     </row>
-    <row r="946" spans="9:10">
+    <row r="946" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I946" s="42"/>
       <c r="J946" s="42"/>
     </row>
-    <row r="947" spans="9:10">
+    <row r="947" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I947" s="42"/>
       <c r="J947" s="42"/>
     </row>
-    <row r="948" spans="9:10">
+    <row r="948" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I948" s="42"/>
       <c r="J948" s="42"/>
     </row>
-    <row r="949" spans="9:10">
+    <row r="949" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I949" s="42"/>
       <c r="J949" s="42"/>
     </row>
-    <row r="950" spans="9:10">
+    <row r="950" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I950" s="42"/>
       <c r="J950" s="42"/>
     </row>
-    <row r="951" spans="9:10">
+    <row r="951" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I951" s="42"/>
       <c r="J951" s="42"/>
     </row>
-    <row r="952" spans="9:10">
+    <row r="952" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I952" s="42"/>
       <c r="J952" s="42"/>
     </row>
-    <row r="953" spans="9:10">
+    <row r="953" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I953" s="42"/>
       <c r="J953" s="42"/>
     </row>
-    <row r="954" spans="9:10">
+    <row r="954" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I954" s="42"/>
       <c r="J954" s="42"/>
     </row>
-    <row r="955" spans="9:10">
+    <row r="955" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I955" s="42"/>
       <c r="J955" s="42"/>
     </row>
-    <row r="956" spans="9:10">
+    <row r="956" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I956" s="42"/>
       <c r="J956" s="42"/>
     </row>
-    <row r="957" spans="9:10">
+    <row r="957" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I957" s="42"/>
       <c r="J957" s="42"/>
     </row>
-    <row r="958" spans="9:10">
+    <row r="958" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I958" s="42"/>
       <c r="J958" s="42"/>
     </row>
-    <row r="959" spans="9:10">
+    <row r="959" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I959" s="42"/>
       <c r="J959" s="42"/>
     </row>
-    <row r="960" spans="9:10">
+    <row r="960" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I960" s="42"/>
       <c r="J960" s="42"/>
     </row>
-    <row r="961" spans="9:10">
+    <row r="961" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I961" s="42"/>
       <c r="J961" s="42"/>
     </row>
-    <row r="962" spans="9:10">
+    <row r="962" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I962" s="42"/>
       <c r="J962" s="42"/>
     </row>
-    <row r="963" spans="9:10">
+    <row r="963" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I963" s="42"/>
       <c r="J963" s="42"/>
     </row>
-    <row r="964" spans="9:10">
+    <row r="964" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I964" s="42"/>
       <c r="J964" s="42"/>
     </row>
-    <row r="965" spans="9:10">
+    <row r="965" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I965" s="42"/>
       <c r="J965" s="42"/>
     </row>
-    <row r="966" spans="9:10">
+    <row r="966" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I966" s="42"/>
       <c r="J966" s="42"/>
     </row>
-    <row r="967" spans="9:10">
+    <row r="967" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I967" s="42"/>
       <c r="J967" s="42"/>
     </row>
-    <row r="968" spans="9:10">
+    <row r="968" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I968" s="42"/>
       <c r="J968" s="42"/>
     </row>
-    <row r="969" spans="9:10">
+    <row r="969" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I969" s="42"/>
       <c r="J969" s="42"/>
     </row>
-    <row r="970" spans="9:10">
+    <row r="970" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I970" s="42"/>
       <c r="J970" s="42"/>
     </row>
-    <row r="971" spans="9:10">
+    <row r="971" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I971" s="42"/>
       <c r="J971" s="42"/>
     </row>
-    <row r="972" spans="9:10">
+    <row r="972" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I972" s="42"/>
       <c r="J972" s="42"/>
     </row>
-    <row r="973" spans="9:10">
+    <row r="973" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I973" s="42"/>
       <c r="J973" s="42"/>
     </row>
-    <row r="974" spans="9:10">
+    <row r="974" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I974" s="42"/>
       <c r="J974" s="42"/>
     </row>
-    <row r="975" spans="9:10">
+    <row r="975" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I975" s="42"/>
       <c r="J975" s="42"/>
     </row>
-    <row r="976" spans="9:10">
+    <row r="976" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I976" s="42"/>
       <c r="J976" s="42"/>
     </row>
-    <row r="977" spans="9:10">
+    <row r="977" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I977" s="42"/>
       <c r="J977" s="42"/>
     </row>
-    <row r="978" spans="9:10">
+    <row r="978" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I978" s="42"/>
       <c r="J978" s="42"/>
     </row>
-    <row r="979" spans="9:10">
+    <row r="979" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I979" s="42"/>
       <c r="J979" s="42"/>
     </row>
-    <row r="980" spans="9:10">
+    <row r="980" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I980" s="42"/>
       <c r="J980" s="42"/>
     </row>
-    <row r="981" spans="9:10">
+    <row r="981" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I981" s="42"/>
       <c r="J981" s="42"/>
     </row>
-    <row r="982" spans="9:10">
+    <row r="982" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I982" s="42"/>
       <c r="J982" s="42"/>
     </row>
-    <row r="983" spans="9:10">
+    <row r="983" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I983" s="42"/>
       <c r="J983" s="42"/>
     </row>
-    <row r="984" spans="9:10">
+    <row r="984" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I984" s="42"/>
       <c r="J984" s="42"/>
     </row>
-    <row r="985" spans="9:10">
+    <row r="985" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I985" s="42"/>
       <c r="J985" s="42"/>
     </row>
-    <row r="986" spans="9:10">
+    <row r="986" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I986" s="42"/>
       <c r="J986" s="42"/>
     </row>
-    <row r="987" spans="9:10">
+    <row r="987" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I987" s="42"/>
       <c r="J987" s="42"/>
     </row>
-    <row r="988" spans="9:10">
+    <row r="988" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I988" s="42"/>
       <c r="J988" s="42"/>
     </row>
-    <row r="989" spans="9:10">
+    <row r="989" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I989" s="42"/>
       <c r="J989" s="42"/>
     </row>
-    <row r="990" spans="9:10">
+    <row r="990" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I990" s="42"/>
       <c r="J990" s="42"/>
     </row>
-    <row r="991" spans="9:10">
+    <row r="991" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I991" s="42"/>
       <c r="J991" s="42"/>
     </row>
-    <row r="992" spans="9:10">
+    <row r="992" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I992" s="42"/>
       <c r="J992" s="42"/>
     </row>
-    <row r="993" spans="9:10">
+    <row r="993" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I993" s="42"/>
       <c r="J993" s="42"/>
     </row>
-    <row r="994" spans="9:10">
+    <row r="994" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I994" s="42"/>
       <c r="J994" s="42"/>
     </row>
-    <row r="995" spans="9:10">
+    <row r="995" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I995" s="42"/>
       <c r="J995" s="42"/>
     </row>
-    <row r="996" spans="9:10">
+    <row r="996" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I996" s="42"/>
       <c r="J996" s="42"/>
     </row>
-    <row r="997" spans="9:10">
+    <row r="997" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I997" s="42"/>
       <c r="J997" s="42"/>
     </row>
@@ -15142,34 +15419,44 @@
       <sortCondition descending="1" ref="E1:E181"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="E275:E297 E2:E273">
-    <cfRule type="expression" dxfId="8" priority="16">
+  <conditionalFormatting sqref="A2:N297">
+    <cfRule type="expression" dxfId="7" priority="9">
+      <formula>AND($B2&lt;&gt;"",ISEVEN(ROW()))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E297">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$E2="Done"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="17">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E297">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>$E2="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="18">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E297">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>$E2="In review"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="19">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E297">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>$E2="Backlog"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F297">
-    <cfRule type="expression" dxfId="4" priority="20">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>$F2="High"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="21">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F297">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>$F2="Medium"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="22">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F297">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>$F2="Low"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:N273">
-    <cfRule type="expression" dxfId="1" priority="15">
-      <formula>AND($B2&lt;&gt;"",ISEVEN(ROW()))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
@@ -15179,7 +15466,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F297" xr:uid="{C1780BFE-B567-4F5D-87FE-F9B5A57B4712}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E243 E245:E273 E275:E297" xr:uid="{6858018E-BA70-46A0-BA18-28D3782838CF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E243 E245:E297" xr:uid="{6858018E-BA70-46A0-BA18-28D3782838CF}">
       <formula1>"Backlog,In progress,In review,Done"</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid date" error="Please enter a valid date between 1/1/2000 and 12/31/2100." promptTitle="Enter a date" prompt="Type a date (e.g. 7/2/2026). Only valid dates are accepted." sqref="I2:J997" xr:uid="{C47FE8E2-BF9C-4D61-B67A-FFEEFDDC2AB9}">
@@ -15210,49 +15497,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="1" max="1" width="48.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="24" customHeight="1">
+    <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="22.15" customHeight="1">
+    <row r="2" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="22.15" customHeight="1">
+    <row r="3" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="22.15" customHeight="1">
+    <row r="4" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="22.15" customHeight="1">
+    <row r="5" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="22.15" customHeight="1">
+    <row r="6" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="22.15" customHeight="1">
+    <row r="7" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>550</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A7">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15262,6 +15549,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -15516,34 +15823,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
+    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
+    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="54122" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FABF22-ACA5-4D48-BD63-4959357EF8E2}"/>
+  <xr:revisionPtr revIDLastSave="56887" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E451D5F5-FE4A-4B21-8444-2A328EF660D0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2225" uniqueCount="804">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -2440,6 +2440,15 @@
   </si>
   <si>
     <t>Documentation</t>
+  </si>
+  <si>
+    <t>Add labeling tool - EyeQ</t>
+  </si>
+  <si>
+    <t>Add steps for detection - EyeQ</t>
+  </si>
+  <si>
+    <t>Auto-trigger calibration -EyeQ</t>
   </si>
 </sst>
 </file>
@@ -15796,14 +15805,59 @@
       </c>
     </row>
     <row r="419" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A419">
+        <v>418</v>
+      </c>
+      <c r="B419" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="D419" t="s">
+        <v>66</v>
+      </c>
+      <c r="E419" t="s">
+        <v>71</v>
+      </c>
+      <c r="F419" t="s">
+        <v>431</v>
+      </c>
       <c r="I419" s="42"/>
       <c r="J419" s="42"/>
     </row>
     <row r="420" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A420">
+        <v>419</v>
+      </c>
+      <c r="B420" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="D420" t="s">
+        <v>66</v>
+      </c>
+      <c r="E420" t="s">
+        <v>71</v>
+      </c>
+      <c r="F420" t="s">
+        <v>431</v>
+      </c>
       <c r="I420" s="42"/>
       <c r="J420" s="42"/>
     </row>
     <row r="421" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A421">
+        <v>420</v>
+      </c>
+      <c r="B421" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="D421" t="s">
+        <v>66</v>
+      </c>
+      <c r="E421" t="s">
+        <v>71</v>
+      </c>
+      <c r="F421" t="s">
+        <v>431</v>
+      </c>
       <c r="I421" s="42"/>
       <c r="J421" s="42"/>
     </row>
@@ -18237,26 +18291,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -18511,10 +18545,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
+    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18531,20 +18596,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
-    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="65138" documentId="11_3E36CF56B8E44E068221A0921DFEBA9330CC02F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFD72DD4-FEAB-440C-85E4-CBD11C194469}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169DDE66-1599-4C9B-93B3-BE14E466E66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="913">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -2680,6 +2680,102 @@
   </si>
   <si>
     <t>Phantom images in Engineering Settings should not be saveable; the save action should be blocked or disabled for phantom images.</t>
+  </si>
+  <si>
+    <t>Remove the standalone Detection page</t>
+  </si>
+  <si>
+    <t>Retire the dedicated /#detection screen; the classical product detector is reached as a Classical Product Detector node in the Workflow editor, fed by camera, upload, network source, crop or stitcher nodes.</t>
+  </si>
+  <si>
+    <t>cleanup,frontend,docs</t>
+  </si>
+  <si>
+    <t>Commit b2cf7ce (08:35). Touched ProductDetection.md, Workflow.md, README.md, index.html, docs/content.html. Net -46 lines.</t>
+  </si>
+  <si>
+    <t>Remove the Colour analysis view</t>
+  </si>
+  <si>
+    <t>Delete the Colour analysis screen, its rail entry, chart icon, export/clear controls and supporting JavaScript, plus 54 lines of now-unused CSS.</t>
+  </si>
+  <si>
+    <t>cleanup,frontend</t>
+  </si>
+  <si>
+    <t>Commit 37ca892 (12:41). index.html -86 lines, app.css -54. The /color-data and /export_color_csv endpoints were not removed.</t>
+  </si>
+  <si>
+    <t>API.md described views that no longer exist</t>
+  </si>
+  <si>
+    <t>Correct the GET / section: the page is documented as live stream, training, workflow, camera settings, settings, logs, system and documentation views, replacing the stale list of five.</t>
+  </si>
+  <si>
+    <t>docs</t>
+  </si>
+  <si>
+    <t>Commit 37ca892 (12:41). Documentation drift caught during the same cleanup.</t>
+  </si>
+  <si>
+    <t>No physical measurement from a stitched 2D image</t>
+  </si>
+  <si>
+    <t>Add a Planar World Metrology postprocess node: a four-point image-to-conveyor-plane homography that maps product contours into plane coordinates and outputs length_mm, width_mm, area_mm2 and a world-coordinate oriented box.</t>
+  </si>
+  <si>
+    <t>feature,workflow,metrology</t>
+  </si>
+  <si>
+    <t>Commit 78d2f08 (17:01). New planar_metrology in postprocess_nodes.py (+81).</t>
+  </si>
+  <si>
+    <t>No way to mark the calibrated reference plane</t>
+  </si>
+  <si>
+    <t>Extend the workflow ROI picker so the metrology node offers Select reference plane: mark the four corners of a known rectangular conveyor area and enter its physical width and height.</t>
+  </si>
+  <si>
+    <t>feature,frontend,workflow</t>
+  </si>
+  <si>
+    <t>Commit 78d2f08 (17:01), workflow.js (+38/-?). Reuses the existing crop ROI selector.</t>
+  </si>
+  <si>
+    <t>RealSense 3D Metrology accepted sources it cannot measure</t>
+  </si>
+  <si>
+    <t>Require an explicit RealSense depth source; reject Basler, RGB-only, uploaded and combined sources. Depth intrinsics come from the active RealSense runtime or can be entered manually.</t>
+  </si>
+  <si>
+    <t>bugfix,workflow,validation</t>
+  </si>
+  <si>
+    <t>Commit 78d2f08 (17:01), inference_nodes.py (+24).</t>
+  </si>
+  <si>
+    <t>Export node could not choose where output lands</t>
+  </si>
+  <si>
+    <t>Give the Export node an Output directory that accepts a typed path or the Image Archive Browse dialog, including drive navigation and New folder.</t>
+  </si>
+  <si>
+    <t>feature,workflow,frontend</t>
+  </si>
+  <si>
+    <t>Commit 78d2f08 (17:01), result_nodes.py and workflow.js.</t>
+  </si>
+  <si>
+    <t>New metrology and export behaviour undocumented</t>
+  </si>
+  <si>
+    <t>Document Planar World Metrology, the RealSense 3D Metrology source rules and the Export output directory in Workflow.md and the in-app documentation view.</t>
+  </si>
+  <si>
+    <t>docs,workflow</t>
+  </si>
+  <si>
+    <t>Commit 78d2f08 (17:01). Workflow.md (+20) and ui/docs/content.html (+3).</t>
   </si>
 </sst>
 </file>
@@ -3940,10 +4036,6 @@
 </namedSheetViews>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4565,7 +4657,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N997"/>
+  <dimension ref="A1:N1005"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -18226,25 +18318,305 @@
       <c r="I992" s="42"/>
       <c r="J992" s="42"/>
     </row>
-    <row r="993" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="993" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I993" s="42"/>
       <c r="J993" s="42"/>
     </row>
-    <row r="994" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I994" s="42"/>
       <c r="J994" s="42"/>
     </row>
-    <row r="995" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="995" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I995" s="42"/>
       <c r="J995" s="42"/>
     </row>
-    <row r="996" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="996" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I996" s="42"/>
       <c r="J996" s="42"/>
     </row>
-    <row r="997" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="997" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I997" s="42"/>
       <c r="J997" s="42"/>
+    </row>
+    <row r="998" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A998">
+        <v>467</v>
+      </c>
+      <c r="B998" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="C998" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="D998" t="s">
+        <v>62</v>
+      </c>
+      <c r="E998" t="s">
+        <v>78</v>
+      </c>
+      <c r="F998" t="s">
+        <v>428</v>
+      </c>
+      <c r="H998">
+        <v>1</v>
+      </c>
+      <c r="J998" s="42">
+        <v>46248</v>
+      </c>
+      <c r="K998" t="s">
+        <v>883</v>
+      </c>
+      <c r="L998" t="s">
+        <v>884</v>
+      </c>
+      <c r="M998" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="999" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A999">
+        <v>468</v>
+      </c>
+      <c r="B999" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="C999" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="D999" t="s">
+        <v>62</v>
+      </c>
+      <c r="E999" t="s">
+        <v>78</v>
+      </c>
+      <c r="F999" t="s">
+        <v>428</v>
+      </c>
+      <c r="H999">
+        <v>0.5</v>
+      </c>
+      <c r="J999" s="42">
+        <v>46248</v>
+      </c>
+      <c r="K999" t="s">
+        <v>887</v>
+      </c>
+      <c r="L999" t="s">
+        <v>888</v>
+      </c>
+      <c r="M999" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1000">
+        <v>469</v>
+      </c>
+      <c r="B1000" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="C1000" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1000" t="s">
+        <v>428</v>
+      </c>
+      <c r="H1000">
+        <v>0.25</v>
+      </c>
+      <c r="J1000" s="42">
+        <v>46248</v>
+      </c>
+      <c r="K1000" t="s">
+        <v>891</v>
+      </c>
+      <c r="L1000" t="s">
+        <v>892</v>
+      </c>
+      <c r="M1000" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1001">
+        <v>470</v>
+      </c>
+      <c r="B1001" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="C1001" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1001" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1001" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1001">
+        <v>3</v>
+      </c>
+      <c r="J1001" s="42">
+        <v>46248</v>
+      </c>
+      <c r="K1001" t="s">
+        <v>895</v>
+      </c>
+      <c r="L1001" t="s">
+        <v>896</v>
+      </c>
+      <c r="M1001" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1002">
+        <v>471</v>
+      </c>
+      <c r="B1002" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="C1002" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="D1002" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1002" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1002" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1002">
+        <v>1.5</v>
+      </c>
+      <c r="J1002" s="42">
+        <v>46248</v>
+      </c>
+      <c r="K1002" t="s">
+        <v>899</v>
+      </c>
+      <c r="L1002" t="s">
+        <v>900</v>
+      </c>
+      <c r="M1002" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1003">
+        <v>472</v>
+      </c>
+      <c r="B1003" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1003" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="D1003" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1003" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1003" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1003">
+        <v>0.75</v>
+      </c>
+      <c r="J1003" s="42">
+        <v>46248</v>
+      </c>
+      <c r="K1003" t="s">
+        <v>903</v>
+      </c>
+      <c r="L1003" t="s">
+        <v>904</v>
+      </c>
+      <c r="M1003" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1004">
+        <v>473</v>
+      </c>
+      <c r="B1004" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="C1004" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="D1004" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1004" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1004" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1004">
+        <v>0.75</v>
+      </c>
+      <c r="J1004" s="42">
+        <v>46248</v>
+      </c>
+      <c r="K1004" t="s">
+        <v>907</v>
+      </c>
+      <c r="L1004" t="s">
+        <v>908</v>
+      </c>
+      <c r="M1004" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1005">
+        <v>474</v>
+      </c>
+      <c r="B1005" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C1005" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="D1005" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1005" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1005" t="s">
+        <v>428</v>
+      </c>
+      <c r="H1005">
+        <v>0.5</v>
+      </c>
+      <c r="J1005" s="42">
+        <v>46248</v>
+      </c>
+      <c r="K1005" t="s">
+        <v>911</v>
+      </c>
+      <c r="L1005" t="s">
+        <v>912</v>
+      </c>
+      <c r="M1005" t="s">
+        <v>182</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M273" xr:uid="{00000000-0001-0000-0100-000000000000}">
@@ -18372,26 +18744,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -18646,26 +18998,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
-    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e20d828-e3fd-41fd-921c-fbe0ff523ae8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18682,4 +19035,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
+    <ds:schemaRef ds:uri="adfc7943-f9ee-4478-a01e-ebfcb6e54f53"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169DDE66-1599-4C9B-93B3-BE14E466E66C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA09DB0-2BE5-4B4D-9AC2-06A4383CC9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2548" uniqueCount="937">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -2776,6 +2776,78 @@
   </si>
   <si>
     <t>Commit 78d2f08 (17:01). Workflow.md (+20) and ui/docs/content.html (+3).</t>
+  </si>
+  <si>
+    <t>Tested the IPC after updating the bios, ran 3 phantom of 30min, no sign of lagging or getting slow</t>
+  </si>
+  <si>
+    <t>worked well with JM's logic</t>
+  </si>
+  <si>
+    <t>Created a new distribution according to JM's logic and multiple phantom runs proved its evenly distributing the products to robots</t>
+  </si>
+  <si>
+    <t>Consolidation needs time and resources and testing on all the different types of robot cells ABI has</t>
+  </si>
+  <si>
+    <t>Validated the Katana side and the robot side cut points are accurate +/- 3mm</t>
+  </si>
+  <si>
+    <t>Scroll should be removed for the user pages, Katana shouldn't have any scroll page, except information ie. manual user</t>
+  </si>
+  <si>
+    <t>Review the UI</t>
+  </si>
+  <si>
+    <t>come up with a plan for this</t>
+  </si>
+  <si>
+    <t>Need to fix the bug, also should be in English and Spanish only</t>
+  </si>
+  <si>
+    <t>On hold, pending review</t>
+  </si>
+  <si>
+    <t>On hold, pending review || 2026-08-14 KH is working on it</t>
+  </si>
+  <si>
+    <t>Just hide it</t>
+  </si>
+  <si>
+    <t>Pending to review</t>
+  </si>
+  <si>
+    <t>Include deep tank cycles recipe dependant, request Controls. Ask current status of this.</t>
+  </si>
+  <si>
+    <t>DG - started fixing layouts/search; content in .md files, system auto-generates layout. Someone needs to generate correct up-to-date documentation.</t>
+  </si>
+  <si>
+    <t>Ask Controls for make this</t>
+  </si>
+  <si>
+    <t>Export is complete, waiting for controls to finalize the settings</t>
+  </si>
+  <si>
+    <t>Split client access vs ABI</t>
+  </si>
+  <si>
+    <t>be more specific</t>
+  </si>
+  <si>
+    <t>This is already in the 40 item</t>
+  </si>
+  <si>
+    <t>Beckoff IPC reaches &gt;4 GHZ speed; tested with phantom mode and production mode, IPC performed well</t>
+  </si>
+  <si>
+    <t>Require Controls || 2026-08-14 KH is working on it</t>
+  </si>
+  <si>
+    <t>no show</t>
+  </si>
+  <si>
+    <t>no BDF</t>
   </si>
 </sst>
 </file>
@@ -12038,7 +12110,7 @@
         <v>78</v>
       </c>
       <c r="F274" s="164" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="G274" s="164"/>
       <c r="H274" s="164">
@@ -12049,7 +12121,9 @@
       <c r="K274" s="163" t="s">
         <v>661</v>
       </c>
-      <c r="L274" s="163"/>
+      <c r="L274" s="163" t="s">
+        <v>913</v>
+      </c>
       <c r="M274" s="164"/>
       <c r="N274" s="163"/>
     </row>
@@ -12096,7 +12170,7 @@
         <v>78</v>
       </c>
       <c r="F276" s="164" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G276" s="164"/>
       <c r="H276" s="164"/>
@@ -12105,7 +12179,9 @@
       <c r="K276" s="163" t="s">
         <v>663</v>
       </c>
-      <c r="L276" s="163"/>
+      <c r="L276" s="163" t="s">
+        <v>914</v>
+      </c>
       <c r="M276" s="164"/>
       <c r="N276" s="163"/>
     </row>
@@ -12124,7 +12200,7 @@
         <v>78</v>
       </c>
       <c r="F277" s="164" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G277" s="164"/>
       <c r="H277" s="164"/>
@@ -12133,7 +12209,9 @@
       <c r="K277" s="163" t="s">
         <v>664</v>
       </c>
-      <c r="L277" s="163"/>
+      <c r="L277" s="163" t="s">
+        <v>915</v>
+      </c>
       <c r="M277" s="164"/>
       <c r="N277" s="163"/>
     </row>
@@ -12151,7 +12229,7 @@
         <v>78</v>
       </c>
       <c r="F278" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I278" s="42"/>
       <c r="J278" s="42"/>
@@ -12173,13 +12251,16 @@
         <v>71</v>
       </c>
       <c r="F279" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I279" s="42"/>
       <c r="J279" s="42"/>
       <c r="K279" t="s">
         <v>666</v>
       </c>
+      <c r="L279" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="280" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B280" s="3" t="s">
@@ -12192,13 +12273,16 @@
         <v>78</v>
       </c>
       <c r="F280" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I280" s="42"/>
       <c r="J280" s="42"/>
       <c r="K280" t="s">
         <v>415</v>
       </c>
+      <c r="L280" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="281" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B281" s="3" t="s">
@@ -12211,7 +12295,7 @@
         <v>78</v>
       </c>
       <c r="F281" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="I281" s="42"/>
       <c r="J281" s="42"/>
@@ -12233,7 +12317,7 @@
         <v>78</v>
       </c>
       <c r="F282" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I282" s="42"/>
       <c r="J282" s="42"/>
@@ -12255,7 +12339,7 @@
         <v>78</v>
       </c>
       <c r="F283" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I283" s="42"/>
       <c r="J283" s="42"/>
@@ -12277,7 +12361,7 @@
         <v>68</v>
       </c>
       <c r="F284" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="I284" s="42"/>
       <c r="J284" s="42"/>
@@ -12311,6 +12395,9 @@
       <c r="K285" t="s">
         <v>670</v>
       </c>
+      <c r="L285" t="s">
+        <v>918</v>
+      </c>
     </row>
     <row r="286" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B286" s="3" t="s">
@@ -12330,6 +12417,9 @@
       <c r="K286" t="s">
         <v>671</v>
       </c>
+      <c r="L286" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="287" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B287" s="3" t="s">
@@ -12377,7 +12467,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="289" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B289" s="3" t="s">
         <v>360</v>
       </c>
@@ -12402,7 +12492,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="290" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B290" s="3" t="s">
         <v>361</v>
       </c>
@@ -12423,8 +12513,11 @@
       <c r="K290" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="291" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L290" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="291" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B291" s="3" t="s">
         <v>362</v>
       </c>
@@ -12438,7 +12531,7 @@
         <v>71</v>
       </c>
       <c r="F291" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I291" s="42"/>
       <c r="J291" s="42"/>
@@ -12446,7 +12539,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="292" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B292" s="3" t="s">
         <v>363</v>
       </c>
@@ -12470,8 +12563,11 @@
       <c r="K292" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="293" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="L292" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="293" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B293" s="3" t="s">
         <v>364</v>
       </c>
@@ -12493,7 +12589,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="294" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B294" s="3" t="s">
         <v>365</v>
       </c>
@@ -12514,8 +12610,11 @@
       <c r="K294" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="295" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="L294" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="295" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B295" s="3" t="s">
         <v>366</v>
       </c>
@@ -12536,8 +12635,11 @@
       <c r="K295" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="296" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L295" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="296" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B296" s="3" t="s">
         <v>367</v>
       </c>
@@ -12562,7 +12664,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="297" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B297" s="3" t="s">
         <v>368</v>
       </c>
@@ -12587,7 +12689,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="298" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B298" s="3" t="s">
         <v>369</v>
       </c>
@@ -12601,7 +12703,7 @@
         <v>68</v>
       </c>
       <c r="F298" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="H298">
         <v>6</v>
@@ -12614,7 +12716,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="299" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B299" s="3" t="s">
         <v>370</v>
       </c>
@@ -12636,7 +12738,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="300" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B300" s="3" t="s">
         <v>371</v>
       </c>
@@ -12661,7 +12763,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="301" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B301" s="3" t="s">
         <v>372</v>
       </c>
@@ -12669,7 +12771,7 @@
         <v>607</v>
       </c>
       <c r="E301" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F301" t="s">
         <v>431</v>
@@ -12680,7 +12782,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="302" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B302" s="3" t="s">
         <v>373</v>
       </c>
@@ -12694,7 +12796,7 @@
         <v>71</v>
       </c>
       <c r="F302" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H302">
         <v>2</v>
@@ -12705,7 +12807,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="303" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B303" s="3" t="s">
         <v>374</v>
       </c>
@@ -12716,7 +12818,7 @@
         <v>71</v>
       </c>
       <c r="F303" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I303" s="42"/>
       <c r="J303" s="42"/>
@@ -12724,7 +12826,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="304" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B304" s="3" t="s">
         <v>375</v>
       </c>
@@ -12746,7 +12848,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="305" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B305" s="3" t="s">
         <v>376</v>
       </c>
@@ -12760,7 +12862,7 @@
         <v>68</v>
       </c>
       <c r="F305" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="I305" s="42"/>
       <c r="J305" s="42"/>
@@ -12768,7 +12870,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="306" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B306" s="3" t="s">
         <v>377</v>
       </c>
@@ -12793,7 +12895,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="307" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B307" s="3" t="s">
         <v>378</v>
       </c>
@@ -12815,7 +12917,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="308" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B308" s="3" t="s">
         <v>379</v>
       </c>
@@ -12826,7 +12928,7 @@
         <v>71</v>
       </c>
       <c r="F308" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I308" s="42"/>
       <c r="J308" s="42"/>
@@ -12834,7 +12936,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="309" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B309" s="3" t="s">
         <v>380</v>
       </c>
@@ -12848,7 +12950,7 @@
         <v>71</v>
       </c>
       <c r="F309" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I309" s="42"/>
       <c r="J309" s="42"/>
@@ -12856,7 +12958,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="310" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B310" s="3" t="s">
         <v>381</v>
       </c>
@@ -12882,8 +12984,11 @@
       <c r="K310" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="311" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="L310" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="311" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B311" s="3" t="s">
         <v>382</v>
       </c>
@@ -12905,7 +13010,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="312" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B312" s="3" t="s">
         <v>383</v>
       </c>
@@ -12930,7 +13035,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="313" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B313" s="3" t="s">
         <v>384</v>
       </c>
@@ -12952,7 +13057,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="314" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B314" s="3" t="s">
         <v>385</v>
       </c>
@@ -12977,7 +13082,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="315" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B315" s="3" t="s">
         <v>386</v>
       </c>
@@ -12999,7 +13104,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="316" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B316" s="3" t="s">
         <v>387</v>
       </c>
@@ -13024,7 +13129,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="317" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B317" s="3" t="s">
         <v>388</v>
       </c>
@@ -13049,7 +13154,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="318" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B318" s="3" t="s">
         <v>389</v>
       </c>
@@ -13070,8 +13175,11 @@
       <c r="K318" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="319" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L318" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="319" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B319" s="3" t="s">
         <v>390</v>
       </c>
@@ -13082,7 +13190,7 @@
         <v>71</v>
       </c>
       <c r="F319" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I319" s="42"/>
       <c r="J319" s="42"/>
@@ -13090,7 +13198,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="320" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B320" s="3" t="s">
         <v>391</v>
       </c>
@@ -13104,15 +13212,18 @@
         <v>71</v>
       </c>
       <c r="F320" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I320" s="42"/>
       <c r="J320" s="42"/>
       <c r="K320" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="321" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L320" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="321" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B321" s="3" t="s">
         <v>392</v>
       </c>
@@ -13139,7 +13250,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="322" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B322" s="3" t="s">
         <v>393</v>
       </c>
@@ -13163,8 +13274,11 @@
       <c r="K322" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="323" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L322" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="323" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B323" s="3" t="s">
         <v>394</v>
       </c>
@@ -13178,7 +13292,7 @@
         <v>71</v>
       </c>
       <c r="F323" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I323" s="42"/>
       <c r="J323" s="42"/>
@@ -13186,7 +13300,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="324" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B324" s="3" t="s">
         <v>395</v>
       </c>
@@ -13205,7 +13319,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="325" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B325" s="3" t="s">
         <v>396</v>
       </c>
@@ -13226,8 +13340,11 @@
       <c r="K325" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="326" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="L325" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="326" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B326" s="3" t="s">
         <v>397</v>
       </c>
@@ -13241,15 +13358,18 @@
         <v>71</v>
       </c>
       <c r="F326" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I326" s="42"/>
       <c r="J326" s="42"/>
       <c r="K326" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="327" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L326" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="327" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B327" s="3" t="s">
         <v>398</v>
       </c>
@@ -13268,7 +13388,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="328" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B328" s="3" t="s">
         <v>399</v>
       </c>
@@ -13290,7 +13410,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="329" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B329" s="3" t="s">
         <v>400</v>
       </c>
@@ -13312,7 +13432,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="330" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B330" s="3" t="s">
         <v>401</v>
       </c>
@@ -13326,15 +13446,18 @@
         <v>78</v>
       </c>
       <c r="F330" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I330" s="42"/>
       <c r="J330" s="42"/>
       <c r="K330" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="331" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L330" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="331" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B331" s="3" t="s">
         <v>402</v>
       </c>
@@ -13355,8 +13478,11 @@
       <c r="K331" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="332" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L331" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="332" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B332" s="3" t="s">
         <v>403</v>
       </c>
@@ -13378,7 +13504,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="333" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B333" s="3" t="s">
         <v>404</v>
       </c>
@@ -13392,7 +13518,7 @@
         <v>71</v>
       </c>
       <c r="F333" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I333" s="42"/>
       <c r="J333" s="42"/>
@@ -13400,7 +13526,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="334" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B334" s="3" t="s">
         <v>405</v>
       </c>
@@ -13414,7 +13540,7 @@
         <v>71</v>
       </c>
       <c r="F334" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I334" s="42"/>
       <c r="J334" s="42"/>
@@ -13422,7 +13548,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="335" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B335" s="3" t="s">
         <v>406</v>
       </c>
@@ -13436,7 +13562,7 @@
         <v>71</v>
       </c>
       <c r="F335" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I335" s="42"/>
       <c r="J335" s="42"/>
@@ -13444,7 +13570,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="336" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B336" s="3" t="s">
         <v>407</v>
       </c>
@@ -13529,7 +13655,7 @@
         <v>78</v>
       </c>
       <c r="F339" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H339">
         <v>10</v>
@@ -13570,13 +13696,16 @@
         <v>71</v>
       </c>
       <c r="F341" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I341" s="42"/>
       <c r="J341" s="42"/>
       <c r="K341" t="s">
         <v>700</v>
       </c>
+      <c r="L341" t="s">
+        <v>932</v>
+      </c>
     </row>
     <row r="342" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B342" s="3" t="s">
@@ -13586,7 +13715,7 @@
         <v>648</v>
       </c>
       <c r="D342" t="s">
-        <v>61</v>
+        <v>655</v>
       </c>
       <c r="E342" t="s">
         <v>78</v>
@@ -13602,6 +13731,9 @@
       <c r="K342" t="s">
         <v>701</v>
       </c>
+      <c r="L342" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="343" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B343" s="3" t="s">
@@ -13614,7 +13746,7 @@
         <v>71</v>
       </c>
       <c r="F343" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="I343" s="42"/>
       <c r="J343" s="42"/>
@@ -13636,7 +13768,7 @@
         <v>71</v>
       </c>
       <c r="F344" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="I344" s="42"/>
       <c r="J344" s="42"/>
@@ -13736,6 +13868,9 @@
       <c r="K348" t="s">
         <v>703</v>
       </c>
+      <c r="L348" t="s">
+        <v>934</v>
+      </c>
     </row>
     <row r="349" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B349" s="3" t="s">
@@ -13755,6 +13890,9 @@
       <c r="K349" t="s">
         <v>704</v>
       </c>
+      <c r="L349" t="s">
+        <v>935</v>
+      </c>
     </row>
     <row r="350" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B350" s="3" t="s">
@@ -16026,7 +16164,7 @@
         <v>870</v>
       </c>
       <c r="E444" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F444" t="s">
         <v>428</v>
@@ -16053,7 +16191,7 @@
         <v>873</v>
       </c>
       <c r="E445" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F445" t="s">
         <v>428</v>
@@ -16137,6 +16275,9 @@
       <c r="J448" s="42"/>
       <c r="K448" t="s">
         <v>871</v>
+      </c>
+      <c r="L448" t="s">
+        <v>936</v>
       </c>
       <c r="M448" t="s">
         <v>69</v>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA09DB0-2BE5-4B4D-9AC2-06A4383CC9A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C85290-57EC-41E4-9212-66FDB17DC545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2548" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="982">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -2848,6 +2848,141 @@
   </si>
   <si>
     <t>no BDF</t>
+  </si>
+  <si>
+    <t>Tablet and touch-friendly workflow UI</t>
+  </si>
+  <si>
+    <t>Improved tablet layouts, touch targets, node dragging, connector interaction, responsive shell behavior, and workflow documentation for coarse-pointer devices.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as ad6fb7b; includes workflow, Train, shell, and documentation updates</t>
+  </si>
+  <si>
+    <t>Pan cavity detection workflow node</t>
+  </si>
+  <si>
+    <t>Added a reusable cavity-detection library and Workflow node that classifies configured pan cavities as occupied or empty and exposes structured results.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as 9c95489; includes detector and workflow-node tests</t>
+  </si>
+  <si>
+    <t>Pan cavity auto-detection and optimization</t>
+  </si>
+  <si>
+    <t>Added automatic cavity-layout detection, workflow API support, UI action, improved detector logic, result handling, tests, and documentation.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as ebe01a1; optimized beyond original fixed R7-6 configuration</t>
+  </si>
+  <si>
+    <t>OpenSpec project integration</t>
+  </si>
+  <si>
+    <t>Added OpenSpec configuration, change-management skills, and command workflows for proposing, applying, updating, syncing, and archiving specifications.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as 8f83217; structured specification-driven development support</t>
+  </si>
+  <si>
+    <t>Experimental synthetic-data feature</t>
+  </si>
+  <si>
+    <t>Integrated the local bakery synthetic-data system with training UI, APIs, engine, dataset handling, configuration, tests, documentation, and an OpenSpec change package.</t>
+  </si>
+  <si>
+    <t>Experimental and rollback-ready; committed as 5ebe7b4</t>
+  </si>
+  <si>
+    <t>Project-aware AI Agent page</t>
+  </si>
+  <si>
+    <t>Created an Agent page with operator and developer profiles, provider routing, guarded project context, image-capable conversation UI, server routes, tests, and documentation.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as 4b97a77; includes prompt-injection boundaries and profile authorization</t>
+  </si>
+  <si>
+    <t>AI Agent usability and configuration</t>
+  </si>
+  <si>
+    <t>Added safe Markdown rendering, Enter-to-send, automatic conversation scrolling, general Settings integration for profile/provider/model, local Ollama support, and developer-mode controls.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as 9816d62; provider configuration centralized in Settings</t>
+  </si>
+  <si>
+    <t>Distinct Agent navigation icon</t>
+  </si>
+  <si>
+    <t>Replaced the duplicated Documentation icon with a dedicated Agent menu icon.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as c8da67d</t>
+  </si>
+  <si>
+    <t>Multi-camera Racer2 workflow support</t>
+  </si>
+  <si>
+    <t>Extended workflow camera-source handling and associated UI behavior for multiple Racer2 cameras, matching the existing multi-camera Ace workflow model.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as abd9f24; includes responsive UI and regression tests</t>
+  </si>
+  <si>
+    <t>Phone tablet and webcam image capture</t>
+  </si>
+  <si>
+    <t>Added file selection, native phone/tablet camera capture, and live webcam capture to the Workflow Upload Image node.</t>
+  </si>
+  <si>
+    <t>Implemented within commit abd9f24 and workflow UI tests</t>
+  </si>
+  <si>
+    <t>Browser camera as a live Workflow source</t>
+  </si>
+  <si>
+    <t>Added Browser camera to the Live Camera node with device preview, single-frame execution, continuous processing, stop behavior, and browser-frame forwarding through the workflow API.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as 0dfacb0; live network camera requires HTTPS on tablets</t>
+  </si>
+  <si>
+    <t>Collapsible Settings groups</t>
+  </si>
+  <si>
+    <t>Converted every generated Settings section into an independently collapsible touch-friendly panel while preserving collapsed state across re-rendering.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as d309b76 with UI regression coverage</t>
+  </si>
+  <si>
+    <t>Descriptions for every setting</t>
+  </si>
+  <si>
+    <t>Added a short explanatory line to every Settings entry, using authored catalog notes where available and readable generated descriptions otherwise.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as d309b76; range, allowed-value, source, lock notes remain separate</t>
+  </si>
+  <si>
+    <t>Installable tablet Progressive Web App</t>
+  </si>
+  <si>
+    <t>Added the web-app manifest, ABI application icons, Apple home-screen metadata, service worker, install controls, standalone landscape behavior, and deterministic icon generation.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as b2ea7dc; live APIs remain network-first</t>
+  </si>
+  <si>
+    <t>iPad status-bar overlap and fullscreen behavior</t>
+  </si>
+  <si>
+    <t>Changed the Apple status-bar presentation, corrected toolbar/sidebar/content safe-area geometry, and added a user-initiated tablet fullscreen control where supported.</t>
+  </si>
+  <si>
+    <t>Implemented and committed as b2ea7dc; iPadOS does not permit PWA to hide system indicators automatically</t>
   </si>
 </sst>
 </file>
@@ -4729,7 +4864,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1005"/>
+  <dimension ref="A1:N1020"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -18756,6 +18891,486 @@
         <v>912</v>
       </c>
       <c r="M1005" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1006">
+        <v>475</v>
+      </c>
+      <c r="B1006" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="C1006" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="D1006" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1006" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1006" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1006">
+        <v>6</v>
+      </c>
+      <c r="J1006" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1006" t="s">
+        <v>939</v>
+      </c>
+      <c r="M1006" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1007">
+        <v>476</v>
+      </c>
+      <c r="B1007" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="C1007" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="D1007" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1007" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1007" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1007">
+        <v>6</v>
+      </c>
+      <c r="J1007" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1007" t="s">
+        <v>942</v>
+      </c>
+      <c r="M1007" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1008">
+        <v>477</v>
+      </c>
+      <c r="B1008" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C1008" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="D1008" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1008" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1008" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1008">
+        <v>6</v>
+      </c>
+      <c r="J1008" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1008" t="s">
+        <v>945</v>
+      </c>
+      <c r="M1008" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1009">
+        <v>478</v>
+      </c>
+      <c r="B1009" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="C1009" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="D1009" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1009" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1009" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1009">
+        <v>3</v>
+      </c>
+      <c r="J1009" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1009" t="s">
+        <v>948</v>
+      </c>
+      <c r="M1009" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1010">
+        <v>479</v>
+      </c>
+      <c r="B1010" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="C1010" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1010" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1010" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1010">
+        <v>8</v>
+      </c>
+      <c r="J1010" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1010" t="s">
+        <v>951</v>
+      </c>
+      <c r="M1010" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1011">
+        <v>480</v>
+      </c>
+      <c r="B1011" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="C1011" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="D1011" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1011" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1011" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1011">
+        <v>10</v>
+      </c>
+      <c r="J1011" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1011" t="s">
+        <v>954</v>
+      </c>
+      <c r="M1011" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1012">
+        <v>481</v>
+      </c>
+      <c r="B1012" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C1012" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="D1012" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1012" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1012" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1012">
+        <v>5</v>
+      </c>
+      <c r="J1012" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1012" t="s">
+        <v>957</v>
+      </c>
+      <c r="M1012" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1013">
+        <v>482</v>
+      </c>
+      <c r="B1013" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="C1013" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="D1013" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1013" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1013" t="s">
+        <v>428</v>
+      </c>
+      <c r="H1013">
+        <v>0.5</v>
+      </c>
+      <c r="J1013" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1013" t="s">
+        <v>960</v>
+      </c>
+      <c r="M1013" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1014">
+        <v>483</v>
+      </c>
+      <c r="B1014" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="C1014" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="D1014" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1014" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1014" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1014">
+        <v>5</v>
+      </c>
+      <c r="J1014" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1014" t="s">
+        <v>963</v>
+      </c>
+      <c r="M1014" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1015">
+        <v>484</v>
+      </c>
+      <c r="B1015" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="C1015" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="D1015" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1015" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1015" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1015">
+        <v>3</v>
+      </c>
+      <c r="J1015" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1015" t="s">
+        <v>966</v>
+      </c>
+      <c r="M1015" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1016">
+        <v>485</v>
+      </c>
+      <c r="B1016" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="C1016" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1016" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1016" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1016">
+        <v>5</v>
+      </c>
+      <c r="J1016" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1016" t="s">
+        <v>969</v>
+      </c>
+      <c r="M1016" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1017">
+        <v>486</v>
+      </c>
+      <c r="B1017" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="C1017" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="D1017" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1017" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1017" t="s">
+        <v>428</v>
+      </c>
+      <c r="H1017">
+        <v>2</v>
+      </c>
+      <c r="J1017" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1017" t="s">
+        <v>972</v>
+      </c>
+      <c r="M1017" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1018">
+        <v>487</v>
+      </c>
+      <c r="B1018" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="C1018" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D1018" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1018" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1018" t="s">
+        <v>428</v>
+      </c>
+      <c r="H1018">
+        <v>2</v>
+      </c>
+      <c r="J1018" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1018" t="s">
+        <v>975</v>
+      </c>
+      <c r="M1018" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1019">
+        <v>488</v>
+      </c>
+      <c r="B1019" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="C1019" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="D1019" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1019" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1019" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1019">
+        <v>6</v>
+      </c>
+      <c r="J1019" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1019" t="s">
+        <v>978</v>
+      </c>
+      <c r="M1019" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1020">
+        <v>489</v>
+      </c>
+      <c r="B1020" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="C1020" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1020" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1020" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1020">
+        <v>3</v>
+      </c>
+      <c r="J1020" s="42">
+        <v>46251</v>
+      </c>
+      <c r="L1020" t="s">
+        <v>981</v>
+      </c>
+      <c r="M1020" t="s">
         <v>182</v>
       </c>
     </row>
@@ -18885,6 +19500,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -19139,15 +19763,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -19160,6 +19775,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19178,14 +19801,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
   <ds:schemaRefs>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C85290-57EC-41E4-9212-66FDB17DC545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B052D40-1573-4692-A87F-0EE66AEB1929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2723" uniqueCount="982">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -12259,7 +12259,9 @@
       <c r="L274" s="163" t="s">
         <v>913</v>
       </c>
-      <c r="M274" s="164"/>
+      <c r="M274" s="164" t="s">
+        <v>69</v>
+      </c>
       <c r="N274" s="163"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.3">
@@ -12317,7 +12319,9 @@
       <c r="L276" s="163" t="s">
         <v>914</v>
       </c>
-      <c r="M276" s="164"/>
+      <c r="M276" s="164" t="s">
+        <v>69</v>
+      </c>
       <c r="N276" s="163"/>
     </row>
     <row r="277" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -12347,7 +12351,9 @@
       <c r="L277" s="163" t="s">
         <v>915</v>
       </c>
-      <c r="M277" s="164"/>
+      <c r="M277" s="164" t="s">
+        <v>69</v>
+      </c>
       <c r="N277" s="163"/>
     </row>
     <row r="278" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -12371,6 +12377,9 @@
       <c r="K278" t="s">
         <v>665</v>
       </c>
+      <c r="M278" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="279" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B279" s="3" t="s">
@@ -12396,6 +12405,9 @@
       <c r="L279" t="s">
         <v>916</v>
       </c>
+      <c r="M279" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="280" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B280" s="3" t="s">
@@ -12418,6 +12430,9 @@
       <c r="L280" t="s">
         <v>917</v>
       </c>
+      <c r="M280" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="281" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B281" s="3" t="s">
@@ -12437,6 +12452,9 @@
       <c r="K281" t="s">
         <v>667</v>
       </c>
+      <c r="M281" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="282" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B282" s="3" t="s">
@@ -12459,6 +12477,9 @@
       <c r="K282" t="s">
         <v>668</v>
       </c>
+      <c r="M282" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="283" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B283" s="3" t="s">
@@ -12481,6 +12502,9 @@
       <c r="K283" t="s">
         <v>668</v>
       </c>
+      <c r="M283" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="284" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B284" s="3" t="s">
@@ -12493,7 +12517,7 @@
         <v>61</v>
       </c>
       <c r="E284" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F284" t="s">
         <v>431</v>
@@ -12503,6 +12527,9 @@
       <c r="K284" t="s">
         <v>669</v>
       </c>
+      <c r="M284" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="285" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B285" s="3" t="s">
@@ -12515,7 +12542,7 @@
         <v>61</v>
       </c>
       <c r="E285" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F285" t="s">
         <v>427</v>
@@ -12532,6 +12559,9 @@
       </c>
       <c r="L285" t="s">
         <v>918</v>
+      </c>
+      <c r="M285" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="286" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -12555,6 +12585,9 @@
       <c r="L286" t="s">
         <v>919</v>
       </c>
+      <c r="M286" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="287" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B287" s="3" t="s">
@@ -12581,6 +12614,9 @@
       </c>
       <c r="K287" t="s">
         <v>672</v>
+      </c>
+      <c r="M287" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="288" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -12601,8 +12637,11 @@
       <c r="K288" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="289" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M288" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="289" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B289" s="3" t="s">
         <v>360</v>
       </c>
@@ -12613,7 +12652,7 @@
         <v>61</v>
       </c>
       <c r="E289" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F289" t="s">
         <v>431</v>
@@ -12626,8 +12665,11 @@
       <c r="K289" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="290" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M289" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="290" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B290" s="3" t="s">
         <v>361</v>
       </c>
@@ -12651,8 +12693,11 @@
       <c r="L290" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="291" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M290" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="291" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B291" s="3" t="s">
         <v>362</v>
       </c>
@@ -12673,8 +12718,11 @@
       <c r="K291" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="292" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M291" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="292" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B292" s="3" t="s">
         <v>363</v>
       </c>
@@ -12701,8 +12749,11 @@
       <c r="L292" t="s">
         <v>921</v>
       </c>
-    </row>
-    <row r="293" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M292" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="293" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B293" s="3" t="s">
         <v>364</v>
       </c>
@@ -12723,8 +12774,11 @@
       <c r="K293" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="294" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M293" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="294" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B294" s="3" t="s">
         <v>365</v>
       </c>
@@ -12748,8 +12802,11 @@
       <c r="L294" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="295" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M294" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="295" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B295" s="3" t="s">
         <v>366</v>
       </c>
@@ -12773,8 +12830,11 @@
       <c r="L295" t="s">
         <v>923</v>
       </c>
-    </row>
-    <row r="296" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M295" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="296" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B296" s="3" t="s">
         <v>367</v>
       </c>
@@ -12798,8 +12858,11 @@
       <c r="K296" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="297" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M296" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="297" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B297" s="3" t="s">
         <v>368</v>
       </c>
@@ -12810,7 +12873,7 @@
         <v>61</v>
       </c>
       <c r="E297" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F297" t="s">
         <v>431</v>
@@ -12823,8 +12886,11 @@
       <c r="K297" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="298" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M297" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="298" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B298" s="3" t="s">
         <v>369</v>
       </c>
@@ -12835,7 +12901,7 @@
         <v>61</v>
       </c>
       <c r="E298" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F298" t="s">
         <v>427</v>
@@ -12850,8 +12916,11 @@
       <c r="K298" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="299" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M298" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="299" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B299" s="3" t="s">
         <v>370</v>
       </c>
@@ -12862,7 +12931,7 @@
         <v>866</v>
       </c>
       <c r="E299" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F299" t="s">
         <v>431</v>
@@ -12872,8 +12941,11 @@
       <c r="K299" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="300" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M299" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="300" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B300" s="3" t="s">
         <v>371</v>
       </c>
@@ -12884,7 +12956,7 @@
         <v>61</v>
       </c>
       <c r="E300" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F300" t="s">
         <v>431</v>
@@ -12897,8 +12969,11 @@
       <c r="K300" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="301" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M300" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="301" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B301" s="3" t="s">
         <v>372</v>
       </c>
@@ -12916,8 +12991,11 @@
       <c r="K301" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="302" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M301" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="302" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B302" s="3" t="s">
         <v>373</v>
       </c>
@@ -12941,8 +13019,11 @@
       <c r="K302" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="303" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M302" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="303" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B303" s="3" t="s">
         <v>374</v>
       </c>
@@ -12960,8 +13041,11 @@
       <c r="K303" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="304" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M303" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="304" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B304" s="3" t="s">
         <v>375</v>
       </c>
@@ -12982,8 +13066,11 @@
       <c r="K304" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="305" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="M304" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="305" spans="2:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B305" s="3" t="s">
         <v>376</v>
       </c>
@@ -12994,7 +13081,7 @@
         <v>61</v>
       </c>
       <c r="E305" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F305" t="s">
         <v>427</v>
@@ -13004,8 +13091,11 @@
       <c r="K305" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="306" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M305" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="306" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B306" s="3" t="s">
         <v>377</v>
       </c>
@@ -13029,8 +13119,11 @@
       <c r="K306" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="307" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M306" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="307" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B307" s="3" t="s">
         <v>378</v>
       </c>
@@ -13051,8 +13144,11 @@
       <c r="K307" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="308" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M307" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="308" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B308" s="3" t="s">
         <v>379</v>
       </c>
@@ -13070,8 +13166,11 @@
       <c r="K308" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="309" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M308" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="309" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B309" s="3" t="s">
         <v>380</v>
       </c>
@@ -13092,8 +13191,11 @@
       <c r="K309" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="310" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M309" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="310" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B310" s="3" t="s">
         <v>381</v>
       </c>
@@ -13104,7 +13206,7 @@
         <v>61</v>
       </c>
       <c r="E310" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F310" t="s">
         <v>431</v>
@@ -13122,8 +13224,11 @@
       <c r="L310" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="311" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M310" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="311" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B311" s="3" t="s">
         <v>382</v>
       </c>
@@ -13144,8 +13249,11 @@
       <c r="K311" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="312" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M311" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="312" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B312" s="3" t="s">
         <v>383</v>
       </c>
@@ -13169,8 +13277,11 @@
       <c r="K312" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="313" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M312" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="313" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B313" s="3" t="s">
         <v>384</v>
       </c>
@@ -13181,7 +13292,7 @@
         <v>61</v>
       </c>
       <c r="E313" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F313" t="s">
         <v>431</v>
@@ -13191,8 +13302,11 @@
       <c r="K313" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="314" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M313" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="314" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B314" s="3" t="s">
         <v>385</v>
       </c>
@@ -13203,7 +13317,7 @@
         <v>61</v>
       </c>
       <c r="E314" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F314" t="s">
         <v>431</v>
@@ -13216,8 +13330,11 @@
       <c r="K314" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="315" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M314" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="315" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B315" s="3" t="s">
         <v>386</v>
       </c>
@@ -13238,8 +13355,11 @@
       <c r="K315" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="316" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M315" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="316" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B316" s="3" t="s">
         <v>387</v>
       </c>
@@ -13263,8 +13383,11 @@
       <c r="K316" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="317" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M316" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="317" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B317" s="3" t="s">
         <v>388</v>
       </c>
@@ -13288,8 +13411,11 @@
       <c r="K317" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="318" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M317" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="318" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B318" s="3" t="s">
         <v>389</v>
       </c>
@@ -13313,8 +13439,11 @@
       <c r="L318" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="319" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M318" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="319" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B319" s="3" t="s">
         <v>390</v>
       </c>
@@ -13332,8 +13461,11 @@
       <c r="K319" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="320" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M319" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="320" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B320" s="3" t="s">
         <v>391</v>
       </c>
@@ -13357,8 +13489,11 @@
       <c r="L320" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="321" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M320" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="321" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B321" s="3" t="s">
         <v>392</v>
       </c>
@@ -13384,8 +13519,11 @@
       <c r="K321" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="322" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M321" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="322" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B322" s="3" t="s">
         <v>393</v>
       </c>
@@ -13396,7 +13534,7 @@
         <v>62</v>
       </c>
       <c r="E322" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F322" t="s">
         <v>431</v>
@@ -13412,8 +13550,11 @@
       <c r="L322" t="s">
         <v>927</v>
       </c>
-    </row>
-    <row r="323" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M322" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="323" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B323" s="3" t="s">
         <v>394</v>
       </c>
@@ -13434,8 +13575,11 @@
       <c r="K323" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="324" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M323" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="324" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B324" s="3" t="s">
         <v>395</v>
       </c>
@@ -13453,8 +13597,11 @@
       <c r="K324" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="325" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M324" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="325" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B325" s="3" t="s">
         <v>396</v>
       </c>
@@ -13478,8 +13625,11 @@
       <c r="L325" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="326" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M325" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="326" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B326" s="3" t="s">
         <v>397</v>
       </c>
@@ -13503,8 +13653,11 @@
       <c r="L326" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="327" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M326" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="327" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B327" s="3" t="s">
         <v>398</v>
       </c>
@@ -13522,8 +13675,11 @@
       <c r="K327" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="328" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M327" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="328" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B328" s="3" t="s">
         <v>399</v>
       </c>
@@ -13534,7 +13690,7 @@
         <v>61</v>
       </c>
       <c r="E328" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F328" t="s">
         <v>431</v>
@@ -13544,8 +13700,11 @@
       <c r="K328" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="329" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M328" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="329" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B329" s="3" t="s">
         <v>400</v>
       </c>
@@ -13566,8 +13725,11 @@
       <c r="K329" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="330" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M329" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="330" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B330" s="3" t="s">
         <v>401</v>
       </c>
@@ -13591,8 +13753,11 @@
       <c r="L330" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="331" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M330" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="331" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B331" s="3" t="s">
         <v>402</v>
       </c>
@@ -13616,8 +13781,11 @@
       <c r="L331" t="s">
         <v>931</v>
       </c>
-    </row>
-    <row r="332" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M331" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="332" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B332" s="3" t="s">
         <v>403</v>
       </c>
@@ -13638,8 +13806,11 @@
       <c r="K332" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="333" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M332" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="333" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B333" s="3" t="s">
         <v>404</v>
       </c>
@@ -13660,8 +13831,11 @@
       <c r="K333" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="334" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M333" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="334" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B334" s="3" t="s">
         <v>405</v>
       </c>
@@ -13682,8 +13856,11 @@
       <c r="K334" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="335" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M334" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="335" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B335" s="3" t="s">
         <v>406</v>
       </c>
@@ -13704,8 +13881,11 @@
       <c r="K335" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="336" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M335" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="336" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B336" s="3" t="s">
         <v>407</v>
       </c>
@@ -13726,6 +13906,9 @@
       <c r="K336" t="s">
         <v>696</v>
       </c>
+      <c r="M336" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="337" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B337" s="3" t="s">
@@ -13738,7 +13921,7 @@
         <v>61</v>
       </c>
       <c r="E337" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F337" t="s">
         <v>431</v>
@@ -13752,6 +13935,9 @@
       </c>
       <c r="K337" t="s">
         <v>697</v>
+      </c>
+      <c r="M337" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="338" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -13775,6 +13961,9 @@
       <c r="K338" t="s">
         <v>698</v>
       </c>
+      <c r="M338" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="339" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B339" s="3" t="s">
@@ -13800,6 +13989,9 @@
       <c r="K339" t="s">
         <v>699</v>
       </c>
+      <c r="M339" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="340" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B340" s="3" t="s">
@@ -13819,6 +14011,9 @@
       <c r="K340" t="s">
         <v>420</v>
       </c>
+      <c r="M340" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="341" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B341" s="3" t="s">
@@ -13841,6 +14036,9 @@
       <c r="L341" t="s">
         <v>932</v>
       </c>
+      <c r="M341" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="342" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B342" s="3" t="s">
@@ -13869,6 +14067,9 @@
       <c r="L342" t="s">
         <v>933</v>
       </c>
+      <c r="M342" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="343" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B343" s="3" t="s">
@@ -14006,6 +14207,9 @@
       <c r="L348" t="s">
         <v>934</v>
       </c>
+      <c r="M348" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="349" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B349" s="3" t="s">
@@ -14028,6 +14232,9 @@
       <c r="L349" t="s">
         <v>935</v>
       </c>
+      <c r="M349" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="350" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B350" s="3" t="s">
@@ -16326,7 +16533,7 @@
         <v>873</v>
       </c>
       <c r="E445" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F445" t="s">
         <v>428</v>
@@ -19500,15 +19707,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -19763,6 +19961,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -19775,14 +19982,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19801,6 +20000,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
   <ds:schemaRefs>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B052D40-1573-4692-A87F-0EE66AEB1929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C006B5-D551-4B1A-A191-E0B596FEA2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2723" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2954" uniqueCount="1082">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -2983,6 +2983,306 @@
   </si>
   <si>
     <t>Implemented and committed as b2ea7dc; iPadOS does not permit PWA to hide system indicators automatically</t>
+  </si>
+  <si>
+    <t>Integrate AI_CORE inside EyeQ settings</t>
+  </si>
+  <si>
+    <t>Add authenticated AI_CORE page under Settings with embedded AI Core UI.</t>
+  </si>
+  <si>
+    <t>Iframe embedding and authenticated access implemented.</t>
+  </si>
+  <si>
+    <t>Make AI_CORE iframe responsive</t>
+  </si>
+  <si>
+    <t>Use explicit embedded URL, automatic port handling, full-screen behavior, Web Browser compatibility, light-mode support, and remove open-in-new-tab control.</t>
+  </si>
+  <si>
+    <t>Desktop and WEB Browser layout adjustments applied.</t>
+  </si>
+  <si>
+    <t>Add AI_CORE submenu to EyeQ</t>
+  </si>
+  <si>
+    <t>Expose AI_CORE workflow sections as EyeQ Settings submenu items and hide them when the feature is disabled.</t>
+  </si>
+  <si>
+    <t>Controlled by the AICoreAccess general setting.</t>
+  </si>
+  <si>
+    <t>Protect AI_CORE pages with authentication</t>
+  </si>
+  <si>
+    <t>Prevent logged-out users from opening AI_CORE URLs directly.</t>
+  </si>
+  <si>
+    <t>Direct URL access now follows EyeQ authentication.</t>
+  </si>
+  <si>
+    <t>Enable EyeQ remote access</t>
+  </si>
+  <si>
+    <t>Make EyeQ and AI_CORE reachable from a tablet on the plant network and diagnose access failures.</t>
+  </si>
+  <si>
+    <t>Binding/access troubleshooting completed; device/network firewall validation may still be required.</t>
+  </si>
+  <si>
+    <t>Define EyeQ to AI_CORE communication</t>
+  </si>
+  <si>
+    <t>Document and implement communication responsibilities, API usage, and result delivery between both applications.</t>
+  </si>
+  <si>
+    <t>Frame-correlated trigger/result architecture selected.</t>
+  </si>
+  <si>
+    <t>Implement EyeQ Output workflow node</t>
+  </si>
+  <si>
+    <t>Create a configurable AI_CORE node that maps detections and measurements into EyeQ scan data with retries and authentication.</t>
+  </si>
+  <si>
+    <t>Existing node posts authenticated scan payloads.</t>
+  </si>
+  <si>
+    <t>Fix EyeQ results not appearing</t>
+  </si>
+  <si>
+    <t>Diagnose and correct the path from AI_CORE output to EyeQ measurements, database records, and dashboards.</t>
+  </si>
+  <si>
+    <t>Ingest and dashboard scan-source handling corrected.</t>
+  </si>
+  <si>
+    <t>Fix Planar World Metrology reference handling</t>
+  </si>
+  <si>
+    <t>Resolve empty planar references and add full-image fallback when a connected reference image exists.</t>
+  </si>
+  <si>
+    <t>Clear validation message and fallback test added.</t>
+  </si>
+  <si>
+    <t>Support rectangle and four-corner planar selection</t>
+  </si>
+  <si>
+    <t>Allow Planar World Metrology to use either a rectangular crop or four manually selected corners.</t>
+  </si>
+  <si>
+    <t>UI mode selector and persistence implemented.</t>
+  </si>
+  <si>
+    <t>Design photoeye-triggered inspection workflow</t>
+  </si>
+  <si>
+    <t>Evaluate options for EyeQ photoeye trigger, AI_CORE frame capture, workflow processing, and result return.</t>
+  </si>
+  <si>
+    <t>Option 1 selected: synchronous short wait plus asynchronous fallback.</t>
+  </si>
+  <si>
+    <t>Implement photoeye inspection trigger API</t>
+  </si>
+  <si>
+    <t>EyeQ sends frameId/triggerId to AI_CORE, AI_CORE runs the active workflow, and returns a completed response or 202 job.</t>
+  </si>
+  <si>
+    <t>Endpoints implemented: /api/inspection/trigger and job status route.</t>
+  </si>
+  <si>
+    <t>Implement scan-result ingest with base64 images</t>
+  </si>
+  <si>
+    <t>Add EyeQ endpoint to receive scan data, original image, processed image, and correlated frame identifiers.</t>
+  </si>
+  <si>
+    <t>Images are stored under EyeQ inference image storage.</t>
+  </si>
+  <si>
+    <t>Restart and validate both applications</t>
+  </si>
+  <si>
+    <t>Rebuild/publish EyeQ, restart EyeQ and AI_CORE, and verify ports and service health after changes.</t>
+  </si>
+  <si>
+    <t>EyeQ port 5000 and AI_CORE port 8000 verified.</t>
+  </si>
+  <si>
+    <t>Compare beta with dev/md-ui</t>
+  </si>
+  <si>
+    <t>Identify merge constraints, conflicts, and overlapping changes before integration.</t>
+  </si>
+  <si>
+    <t>Eight content conflicts identified.</t>
+  </si>
+  <si>
+    <t>Create integration branch</t>
+  </si>
+  <si>
+    <t>Create dev/md-ui-beta-integration from dev/md-ui for safe beta integration.</t>
+  </si>
+  <si>
+    <t>Isolated branch used; beta and dev branches preserved.</t>
+  </si>
+  <si>
+    <t>Integrate beta backend and configuration</t>
+  </si>
+  <si>
+    <t>Merge beta model library, deployment, training, inspection, and runtime changes.</t>
+  </si>
+  <si>
+    <t>Preserved dev camera, Agent, synthetic-data, and multi-camera settings.</t>
+  </si>
+  <si>
+    <t>Integrate beta frontend</t>
+  </si>
+  <si>
+    <t>Merge model library, deployment, training, workflow, Agent, PWA, and iframe UI changes.</t>
+  </si>
+  <si>
+    <t>Resolved conflicts in index.html, training UI, and workflow UI.</t>
+  </si>
+  <si>
+    <t>Preserve multi-camera and camera networking</t>
+  </si>
+  <si>
+    <t>Keep jumbo-frame settings, camera serial configuration, stitching, crop, caching, and calibration behavior from dev.</t>
+  </si>
+  <si>
+    <t>Dev camera/network settings were intentionally retained.</t>
+  </si>
+  <si>
+    <t>Preserve serial-aware calibration</t>
+  </si>
+  <si>
+    <t>Keep serial-aware calibration and integrate beta calibration-related changes.</t>
+  </si>
+  <si>
+    <t>Calibration routes and profiles remain available.</t>
+  </si>
+  <si>
+    <t>Integrate workflow deployment support</t>
+  </si>
+  <si>
+    <t>Add beta's workflow deployment, runtime history, start/stop, and rollback functionality.</t>
+  </si>
+  <si>
+    <t>Deployment API and UI are available.</t>
+  </si>
+  <si>
+    <t>Integrate model library and training features</t>
+  </si>
+  <si>
+    <t>Add model import, benchmark, deployment, batch workspace, autolabel, review, and publish features.</t>
+  </si>
+  <si>
+    <t>Model and training endpoints respond successfully.</t>
+  </si>
+  <si>
+    <t>Reintroduce synthetic-data support</t>
+  </si>
+  <si>
+    <t>Preserve synthetic-data generation, metadata lineage, review, and train-only grouping.</t>
+  </si>
+  <si>
+    <t>Synthetic data remains experimental and available in Training.</t>
+  </si>
+  <si>
+    <t>Fix dataset merge compatibility</t>
+  </si>
+  <si>
+    <t>Preserve beta batch metadata while maintaining dev synthetic metadata and legacy positional API compatibility.</t>
+  </si>
+  <si>
+    <t>Dataset tests pass.</t>
+  </si>
+  <si>
+    <t>Fix detector test instability</t>
+  </si>
+  <si>
+    <t>Make OpenCV k-means deterministic by resetting its process-global RNG seed.</t>
+  </si>
+  <si>
+    <t>Removed order-dependent test failure.</t>
+  </si>
+  <si>
+    <t>Update documentation coverage</t>
+  </si>
+  <si>
+    <t>Add the beta workflow node documentation, including Misshapen Geometry Check.</t>
+  </si>
+  <si>
+    <t>Documentation validation passes.</t>
+  </si>
+  <si>
+    <t>Run automated validation</t>
+  </si>
+  <si>
+    <t>Execute syntax checks and the complete automated test suite.</t>
+  </si>
+  <si>
+    <t>677 tests passed.</t>
+  </si>
+  <si>
+    <t>Restart and smoke-test the application</t>
+  </si>
+  <si>
+    <t>Restart the service and verify key pages and APIs.</t>
+  </si>
+  <si>
+    <t>Workflow, training, models, Agent, synthetic data, deployment, and camera APIs responded.</t>
+  </si>
+  <si>
+    <t>Live-test both Ace cameras</t>
+  </si>
+  <si>
+    <t>Verify both physical Ace cameras after merge.</t>
+  </si>
+  <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>No Pylon devices were discoverable on the host during testing. Requires cameras/network connection.</t>
+  </si>
+  <si>
+    <t>Compare integration branch with beta</t>
+  </si>
+  <si>
+    <t>Confirm whether dev/md-ui-beta-integration can be deleted safely.</t>
+  </si>
+  <si>
+    <t>Beta contains the integration commit and no integration-only changes remain.</t>
+  </si>
+  <si>
+    <t>Embed AI Core inside the EyeQ user interface</t>
+  </si>
+  <si>
+    <t>Created the authenticated /settings/ai_core EyeQ page, embedded the AI Core application in an iframe, generated its URL from EyeQ configuration.</t>
+  </si>
+  <si>
+    <t>Git commit 6a6b7d1a.</t>
+  </si>
+  <si>
+    <t>Add tablet-responsive support for the EyeQ AI Core view</t>
+  </si>
+  <si>
+    <t>Updated EyeQ application-level viewport/scaling behavior and refined the AI Core page so the embedded interface works more reliably on tablet-sized displays.</t>
+  </si>
+  <si>
+    <t>Git commit 04d09734.</t>
+  </si>
+  <si>
+    <t>Control AI Core visibility and access from EyeQ settings</t>
+  </si>
+  <si>
+    <t>Added an AI Core feature setting and notification flow, exposed an enable/disable switch in General Settings, dynamically showed or hid the AI Core menu.</t>
+  </si>
+  <si>
+    <t>Git commit b699b85f.</t>
   </si>
 </sst>
 </file>
@@ -4864,7 +5164,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1020"/>
+  <dimension ref="A1:N1053"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -19578,6 +19878,1062 @@
         <v>981</v>
       </c>
       <c r="M1020" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1021">
+        <v>490</v>
+      </c>
+      <c r="B1021" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="C1021" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1021" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1021">
+        <v>4</v>
+      </c>
+      <c r="J1021" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1021" t="s">
+        <v>984</v>
+      </c>
+      <c r="M1021" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1022">
+        <v>491</v>
+      </c>
+      <c r="B1022" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="C1022" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="D1022" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1022" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1022" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1022">
+        <v>5</v>
+      </c>
+      <c r="J1022" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1022" t="s">
+        <v>987</v>
+      </c>
+      <c r="M1022" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1023">
+        <v>492</v>
+      </c>
+      <c r="B1023" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="C1023" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="D1023" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1023" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1023" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1023">
+        <v>3</v>
+      </c>
+      <c r="J1023" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1023" t="s">
+        <v>990</v>
+      </c>
+      <c r="M1023" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1024">
+        <v>493</v>
+      </c>
+      <c r="B1024" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C1024" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="D1024" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1024" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1024" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1024">
+        <v>3</v>
+      </c>
+      <c r="J1024" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1024" t="s">
+        <v>993</v>
+      </c>
+      <c r="M1024" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1025">
+        <v>494</v>
+      </c>
+      <c r="B1025" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="C1025" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="D1025" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1025" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1025" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1025">
+        <v>3</v>
+      </c>
+      <c r="J1025" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1025" t="s">
+        <v>996</v>
+      </c>
+      <c r="M1025" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1026">
+        <v>495</v>
+      </c>
+      <c r="B1026" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="C1026" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="D1026" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1026" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1026" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1026">
+        <v>4</v>
+      </c>
+      <c r="J1026" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1026" t="s">
+        <v>999</v>
+      </c>
+      <c r="M1026" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1027">
+        <v>496</v>
+      </c>
+      <c r="B1027" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C1027" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1027" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1027" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1027">
+        <v>8</v>
+      </c>
+      <c r="J1027" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1027" t="s">
+        <v>1002</v>
+      </c>
+      <c r="M1027" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1028">
+        <v>497</v>
+      </c>
+      <c r="B1028" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C1028" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D1028" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1028" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1028" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1028">
+        <v>6</v>
+      </c>
+      <c r="J1028" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1028" t="s">
+        <v>1005</v>
+      </c>
+      <c r="M1028" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1029">
+        <v>498</v>
+      </c>
+      <c r="B1029" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C1029" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D1029" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1029" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1029" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1029">
+        <v>6</v>
+      </c>
+      <c r="J1029" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1029" t="s">
+        <v>1008</v>
+      </c>
+      <c r="M1029" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1030">
+        <v>499</v>
+      </c>
+      <c r="B1030" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C1030" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D1030" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1030" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1030" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1030">
+        <v>5</v>
+      </c>
+      <c r="J1030" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1030" t="s">
+        <v>1011</v>
+      </c>
+      <c r="M1030" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1031">
+        <v>500</v>
+      </c>
+      <c r="B1031" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C1031" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D1031" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1031" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1031" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1031">
+        <v>4</v>
+      </c>
+      <c r="J1031" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1031" t="s">
+        <v>1014</v>
+      </c>
+      <c r="M1031" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1032">
+        <v>501</v>
+      </c>
+      <c r="B1032" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C1032" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D1032" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1032" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1032" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1032">
+        <v>12</v>
+      </c>
+      <c r="J1032" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1032" t="s">
+        <v>1017</v>
+      </c>
+      <c r="M1032" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1033">
+        <v>502</v>
+      </c>
+      <c r="B1033" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C1033" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D1033" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1033" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1033" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1033">
+        <v>8</v>
+      </c>
+      <c r="J1033" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1033" t="s">
+        <v>1020</v>
+      </c>
+      <c r="M1033" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1034">
+        <v>503</v>
+      </c>
+      <c r="B1034" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C1034" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D1034" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1034" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1034" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1034">
+        <v>3</v>
+      </c>
+      <c r="J1034" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1034" t="s">
+        <v>1023</v>
+      </c>
+      <c r="M1034" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1035">
+        <v>504</v>
+      </c>
+      <c r="B1035" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C1035" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D1035" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1035" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1035" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1035">
+        <v>1.5</v>
+      </c>
+      <c r="J1035" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1035" t="s">
+        <v>1026</v>
+      </c>
+      <c r="M1035" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1036">
+        <v>505</v>
+      </c>
+      <c r="B1036" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C1036" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D1036" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1036" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1036" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1036">
+        <v>0.5</v>
+      </c>
+      <c r="J1036" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1036" t="s">
+        <v>1029</v>
+      </c>
+      <c r="M1036" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1037">
+        <v>506</v>
+      </c>
+      <c r="B1037" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C1037" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D1037" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1037" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1037" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1037">
+        <v>4</v>
+      </c>
+      <c r="J1037" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1037" t="s">
+        <v>1032</v>
+      </c>
+      <c r="M1037" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1038">
+        <v>507</v>
+      </c>
+      <c r="B1038" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C1038" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D1038" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1038" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1038" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1038">
+        <v>5</v>
+      </c>
+      <c r="J1038" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1038" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M1038" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1039">
+        <v>508</v>
+      </c>
+      <c r="B1039" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C1039" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D1039" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1039" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1039" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1039">
+        <v>2</v>
+      </c>
+      <c r="J1039" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1039" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M1039" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1040">
+        <v>509</v>
+      </c>
+      <c r="B1040" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C1040" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D1040" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1040" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1040" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1040">
+        <v>2</v>
+      </c>
+      <c r="J1040" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1040" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M1040" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1041">
+        <v>510</v>
+      </c>
+      <c r="B1041" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C1041" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D1041" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1041" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1041" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1041">
+        <v>3</v>
+      </c>
+      <c r="J1041" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1041" t="s">
+        <v>1044</v>
+      </c>
+      <c r="M1041" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1042">
+        <v>511</v>
+      </c>
+      <c r="B1042" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C1042" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1042" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1042" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1042">
+        <v>4</v>
+      </c>
+      <c r="J1042" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1042" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M1042" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1043">
+        <v>512</v>
+      </c>
+      <c r="B1043" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C1043" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1043" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1043" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1043">
+        <v>2</v>
+      </c>
+      <c r="J1043" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1043" t="s">
+        <v>1050</v>
+      </c>
+      <c r="M1043" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1044">
+        <v>513</v>
+      </c>
+      <c r="B1044" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C1044" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1044" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1044" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1044">
+        <v>1.5</v>
+      </c>
+      <c r="J1044" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1044" t="s">
+        <v>1053</v>
+      </c>
+      <c r="M1044" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1045">
+        <v>514</v>
+      </c>
+      <c r="B1045" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C1045" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1045" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1045" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1045">
+        <v>1</v>
+      </c>
+      <c r="J1045" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1045" t="s">
+        <v>1056</v>
+      </c>
+      <c r="M1045" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1046">
+        <v>515</v>
+      </c>
+      <c r="B1046" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C1046" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1046" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1046" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1046">
+        <v>1</v>
+      </c>
+      <c r="J1046" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1046" t="s">
+        <v>1059</v>
+      </c>
+      <c r="M1046" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1047">
+        <v>516</v>
+      </c>
+      <c r="B1047" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C1047" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D1047" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1047" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1047" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1047">
+        <v>1.5</v>
+      </c>
+      <c r="J1047" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1047" t="s">
+        <v>1062</v>
+      </c>
+      <c r="M1047" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1048">
+        <v>517</v>
+      </c>
+      <c r="B1048" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C1048" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D1048" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1048" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1048" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1048">
+        <v>1</v>
+      </c>
+      <c r="J1048" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1048" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M1048" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1049">
+        <v>518</v>
+      </c>
+      <c r="B1049" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C1049" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D1049" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1049" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F1049" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1049">
+        <v>2</v>
+      </c>
+      <c r="J1049" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1049" t="s">
+        <v>1069</v>
+      </c>
+      <c r="M1049" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1050">
+        <v>519</v>
+      </c>
+      <c r="B1050" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C1050" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D1050" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1050" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1050" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1050">
+        <v>0.5</v>
+      </c>
+      <c r="J1050" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1050" t="s">
+        <v>1072</v>
+      </c>
+      <c r="M1050" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1051">
+        <v>520</v>
+      </c>
+      <c r="B1051" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C1051" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1051" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1051" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1051" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1051">
+        <v>2</v>
+      </c>
+      <c r="J1051" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1051" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M1051" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1052">
+        <v>521</v>
+      </c>
+      <c r="B1052" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C1052" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D1052" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1052" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1052" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1052">
+        <v>1</v>
+      </c>
+      <c r="J1052" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1052" t="s">
+        <v>1078</v>
+      </c>
+      <c r="M1052" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1053">
+        <v>522</v>
+      </c>
+      <c r="B1053" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C1053" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D1053" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1053" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1053" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1053">
+        <v>2</v>
+      </c>
+      <c r="J1053" s="42">
+        <v>46252</v>
+      </c>
+      <c r="L1053" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M1053" t="s">
         <v>182</v>
       </c>
     </row>
@@ -19707,6 +21063,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -19961,15 +21326,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -19982,6 +21338,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20000,14 +21364,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
   <ds:schemaRefs>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C006B5-D551-4B1A-A191-E0B596FEA2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A1CB4B-2609-4B1E-B10C-A14C0AE29F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2954" uniqueCount="1082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2962" uniqueCount="1086">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -3283,6 +3283,18 @@
   </si>
   <si>
     <t>Git commit b699b85f.</t>
+  </si>
+  <si>
+    <t>Test IPC last BIOS upgrade with Backoff team</t>
+  </si>
+  <si>
+    <t>Test the Beckoff IPC after the last BIOS upgrade with the Backoff team.</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>Beckoff IPC reaches &gt;4 GHz speed; tested with phantom mode and production mode, IPC performs well.</t>
   </si>
 </sst>
 </file>
@@ -5164,7 +5176,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1053"/>
+  <dimension ref="A1:N1054"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -20935,6 +20947,38 @@
       </c>
       <c r="M1053" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1054">
+        <v>523</v>
+      </c>
+      <c r="B1054" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C1054" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D1054" t="s">
+        <v>485</v>
+      </c>
+      <c r="E1054" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1054" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1054">
+        <v>2</v>
+      </c>
+      <c r="K1054" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L1054" t="s">
+        <v>1085</v>
+      </c>
+      <c r="M1054" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -21063,15 +21107,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -21326,6 +21361,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -21338,14 +21382,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21364,6 +21400,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
   <ds:schemaRefs>
